--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davitt/Desktop/Analisis_Asfalto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348F16B5-239C-4A44-8940-6259E9F87CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB0AA89-6904-2048-9625-D73E6BD35753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{FC2B8901-ED9E-184C-BCB1-2CFD191E8EE2}"/>
+    <workbookView xWindow="28800" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{FC2B8901-ED9E-184C-BCB1-2CFD191E8EE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$AI$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$AI$79</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="45">
   <si>
     <t>Mezcla</t>
   </si>
@@ -175,12 +175,18 @@
   <si>
     <t>BBTM11B</t>
   </si>
+  <si>
+    <t>SMA16</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -192,6 +198,18 @@
       <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -224,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -239,6 +257,23 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,16 +608,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6820742-B6BB-224A-B3FC-2A5B149FF72F}">
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AJ79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.33203125" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="35" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="35" width="15.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -689,7 +729,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -720,83 +760,83 @@
       <c r="J2" s="1">
         <v>50</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="7">
         <v>14.1927</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="7">
         <v>8253403.0808814485</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="7">
         <v>5597.4518901650481</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="7">
         <v>2128.1711928904156</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="7">
         <v>3469.2806972746257</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="7">
         <v>2.6147409980476923</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="7">
         <v>17.465246584084589</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="7">
         <v>8116282.1562428633</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="7">
         <v>8878277.5150890499</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T2" s="7">
         <v>9824307.8994215354</v>
       </c>
-      <c r="U2" s="2">
+      <c r="U2" s="7">
         <v>11166257.477405874</v>
       </c>
-      <c r="V2" s="2">
+      <c r="V2" s="7">
         <v>12603732.951070141</v>
       </c>
-      <c r="W2" s="2">
+      <c r="W2" s="7">
         <v>13336407.271943403</v>
       </c>
-      <c r="X2" s="2">
+      <c r="X2" s="7">
         <v>13474679.314941157</v>
       </c>
-      <c r="Y2" s="2">
+      <c r="Y2" s="7">
         <v>13110828.453251969</v>
       </c>
-      <c r="Z2" s="2">
+      <c r="Z2" s="7">
         <v>12451426.432672478</v>
       </c>
-      <c r="AA2" s="2">
+      <c r="AA2" s="7">
         <v>8132758.3531402349</v>
       </c>
-      <c r="AB2" s="2">
+      <c r="AB2" s="7">
         <v>8888989.119545199</v>
       </c>
-      <c r="AC2" s="2">
+      <c r="AC2" s="7">
         <v>9891686.9587113392</v>
       </c>
-      <c r="AD2" s="2">
+      <c r="AD2" s="7">
         <v>11041798.436057637</v>
       </c>
-      <c r="AE2" s="2">
+      <c r="AE2" s="7">
         <v>12155229.559350107</v>
       </c>
-      <c r="AF2" s="2">
+      <c r="AF2" s="7">
         <v>13024662.541145021</v>
       </c>
-      <c r="AG2" s="2">
+      <c r="AG2" s="7">
         <v>13222655.837606285</v>
       </c>
-      <c r="AH2" s="2">
+      <c r="AH2" s="7">
         <v>12942859.974972261</v>
       </c>
-      <c r="AI2" s="2">
+      <c r="AI2" s="7">
         <v>12354682.163536195</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -827,83 +867,83 @@
       <c r="J3" s="1">
         <v>50</v>
       </c>
-      <c r="K3" s="1">
+      <c r="K3" s="7">
         <v>15.768000000000001</v>
       </c>
-      <c r="L3" s="1">
+      <c r="L3" s="7">
         <v>8789429.3118240349</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="7">
         <v>5690.0782768158087</v>
       </c>
-      <c r="N3" s="1">
+      <c r="N3" s="7">
         <v>1899.3769994293334</v>
       </c>
-      <c r="O3" s="1">
+      <c r="O3" s="7">
         <v>3790.7012773864762</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="7">
         <v>2.4702870525150269</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="7">
         <v>15.66561681983154</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="7">
         <v>10468682.089332411</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3" s="7">
         <v>12255277.26305341</v>
       </c>
-      <c r="T3" s="2">
+      <c r="T3" s="7">
         <v>15119471.332628476</v>
       </c>
-      <c r="U3" s="2">
+      <c r="U3" s="7">
         <v>18087434.280043613</v>
       </c>
-      <c r="V3" s="2">
+      <c r="V3" s="7">
         <v>19520508.738511011</v>
       </c>
-      <c r="W3" s="2">
+      <c r="W3" s="7">
         <v>20010668.958849277</v>
       </c>
-      <c r="X3" s="2">
+      <c r="X3" s="7">
         <v>19662812.469710197</v>
       </c>
-      <c r="Y3" s="2">
+      <c r="Y3" s="7">
         <v>18966333.773282584</v>
       </c>
-      <c r="Z3" s="2">
+      <c r="Z3" s="7">
         <v>17523151.416949309</v>
       </c>
-      <c r="AA3" s="2">
+      <c r="AA3" s="7">
         <v>10612251.670412583</v>
       </c>
-      <c r="AB3" s="2">
+      <c r="AB3" s="7">
         <v>12371423.301238989</v>
       </c>
-      <c r="AC3" s="2">
+      <c r="AC3" s="7">
         <v>14610857.817657402</v>
       </c>
-      <c r="AD3" s="2">
+      <c r="AD3" s="7">
         <v>17040412.359598234</v>
       </c>
-      <c r="AE3" s="2">
+      <c r="AE3" s="7">
         <v>19000508.105264552</v>
       </c>
-      <c r="AF3" s="2">
+      <c r="AF3" s="7">
         <v>19591402.198859483</v>
       </c>
-      <c r="AG3" s="2">
+      <c r="AG3" s="7">
         <v>19474510.60352182</v>
       </c>
-      <c r="AH3" s="2">
+      <c r="AH3" s="7">
         <v>18531424.45036472</v>
       </c>
-      <c r="AI3" s="2">
+      <c r="AI3" s="7">
         <v>17194937.548380703</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -934,83 +974,83 @@
       <c r="J4" s="1">
         <v>50</v>
       </c>
-      <c r="K4" s="1">
+      <c r="K4" s="7">
         <v>15.273899999999999</v>
       </c>
-      <c r="L4" s="1">
+      <c r="L4" s="7">
         <v>7913410.9089839282</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="7">
         <v>6690.1798944189095</v>
       </c>
-      <c r="N4" s="1">
+      <c r="N4" s="7">
         <v>2456.2263835372701</v>
       </c>
-      <c r="O4" s="1">
+      <c r="O4" s="7">
         <v>4233.953510881639</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="7">
         <v>2.9232069449492566</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="7">
         <v>24.079400243145951</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="7">
         <v>8578140.1392299365</v>
       </c>
-      <c r="S4" s="2">
+      <c r="S4" s="7">
         <v>9988192.8045357447</v>
       </c>
-      <c r="T4" s="2">
+      <c r="T4" s="7">
         <v>11911929.180443261</v>
       </c>
-      <c r="U4" s="2">
+      <c r="U4" s="7">
         <v>14192253.023745121</v>
       </c>
-      <c r="V4" s="2">
+      <c r="V4" s="7">
         <v>15938918.156161731</v>
       </c>
-      <c r="W4" s="2">
+      <c r="W4" s="7">
         <v>16523471.919830203</v>
       </c>
-      <c r="X4" s="2">
+      <c r="X4" s="7">
         <v>16477651.868992524</v>
       </c>
-      <c r="Y4" s="2">
+      <c r="Y4" s="7">
         <v>15830724.003693346</v>
       </c>
-      <c r="Z4" s="2">
+      <c r="Z4" s="7">
         <v>14762869.141178906</v>
       </c>
-      <c r="AA4" s="2">
+      <c r="AA4" s="7">
         <v>8634395.350003954</v>
       </c>
-      <c r="AB4" s="2">
+      <c r="AB4" s="7">
         <v>9973826.4662985951</v>
       </c>
-      <c r="AC4" s="2">
+      <c r="AC4" s="7">
         <v>11724759.794637742</v>
       </c>
-      <c r="AD4" s="2">
+      <c r="AD4" s="7">
         <v>13634289.97289704</v>
       </c>
-      <c r="AE4" s="2">
+      <c r="AE4" s="7">
         <v>15269396.685102707</v>
       </c>
-      <c r="AF4" s="2">
+      <c r="AF4" s="7">
         <v>16203808.38205892</v>
       </c>
-      <c r="AG4" s="2">
+      <c r="AG4" s="7">
         <v>16169681.618044775</v>
       </c>
-      <c r="AH4" s="2">
+      <c r="AH4" s="7">
         <v>15573198.553035514</v>
       </c>
-      <c r="AI4" s="2">
+      <c r="AI4" s="7">
         <v>14589574.436153652</v>
       </c>
     </row>
-    <row r="5" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
@@ -1041,83 +1081,83 @@
       <c r="J5" s="4">
         <v>50</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="8">
         <v>15.7704</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="8">
         <v>8944177.9844431132</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="8">
         <v>6116.8621965284747</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5" s="8">
         <v>2279.8813875796895</v>
       </c>
-      <c r="O5" s="4">
+      <c r="O5" s="8">
         <v>3836.9808089487856</v>
       </c>
-      <c r="P5" s="4">
+      <c r="P5" s="8">
         <v>2.7536702060301508</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="Q5" s="8">
         <v>18.488148060099267</v>
       </c>
-      <c r="R5" s="5">
+      <c r="R5" s="8">
         <v>9362952.6494312733</v>
       </c>
-      <c r="S5" s="5">
+      <c r="S5" s="8">
         <v>10928055.385490295</v>
       </c>
-      <c r="T5" s="5">
+      <c r="T5" s="8">
         <v>12923269.719718838</v>
       </c>
-      <c r="U5" s="5">
+      <c r="U5" s="8">
         <v>15055989.753165269</v>
       </c>
-      <c r="V5" s="5">
+      <c r="V5" s="8">
         <v>16406809.288429121</v>
       </c>
-      <c r="W5" s="5">
+      <c r="W5" s="8">
         <v>16654540.050857287</v>
       </c>
-      <c r="X5" s="5">
+      <c r="X5" s="8">
         <v>16484364.798766017</v>
       </c>
-      <c r="Y5" s="5">
+      <c r="Y5" s="8">
         <v>15776595.003160853</v>
       </c>
-      <c r="Z5" s="5">
+      <c r="Z5" s="8">
         <v>14734301.297375673</v>
       </c>
-      <c r="AA5" s="5">
+      <c r="AA5" s="8">
         <v>9358374.0784872025</v>
       </c>
-      <c r="AB5" s="5">
+      <c r="AB5" s="8">
         <v>10858723.426277183</v>
       </c>
-      <c r="AC5" s="5">
+      <c r="AC5" s="8">
         <v>12664132.087824523</v>
       </c>
-      <c r="AD5" s="5">
+      <c r="AD5" s="8">
         <v>14458169.145432957</v>
       </c>
-      <c r="AE5" s="5">
+      <c r="AE5" s="8">
         <v>15814972.874882689</v>
       </c>
-      <c r="AF5" s="5">
+      <c r="AF5" s="8">
         <v>16445495.607865181</v>
       </c>
-      <c r="AG5" s="5">
+      <c r="AG5" s="8">
         <v>16203684.077578595</v>
       </c>
-      <c r="AH5" s="5">
+      <c r="AH5" s="8">
         <v>15560280.307485027</v>
       </c>
-      <c r="AI5" s="5">
+      <c r="AI5" s="8">
         <v>14611906.308258634</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -1148,84 +1188,84 @@
       <c r="J6" s="1">
         <v>50</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K6" s="7">
         <v>16.014500000000002</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L6" s="7">
         <v>8111695.1342813419</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="7">
         <v>6243.9978933404227</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N6" s="7">
         <v>2197.0567111308114</v>
       </c>
-      <c r="O6" s="1">
+      <c r="O6" s="7">
         <v>4046.9411822096122</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="7">
         <v>3.0783491596413595</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="7">
         <v>23.529122156420371</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6" s="7">
         <v>9865417.1981567629</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6" s="7">
         <v>12077628.95750919</v>
       </c>
-      <c r="T6" s="2">
+      <c r="T6" s="7">
         <v>15021329.747639183</v>
       </c>
-      <c r="U6" s="2">
+      <c r="U6" s="7">
         <v>17330475.373862516</v>
       </c>
-      <c r="V6" s="2">
+      <c r="V6" s="7">
         <v>18313313.321357608</v>
       </c>
-      <c r="W6" s="2">
+      <c r="W6" s="7">
         <v>18482086.959576812</v>
       </c>
-      <c r="X6" s="2">
+      <c r="X6" s="7">
         <v>17936492.156640351</v>
       </c>
-      <c r="Y6" s="2">
+      <c r="Y6" s="7">
         <v>17286195.783378057</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="Z6" s="7">
         <v>16088334.537685303</v>
       </c>
-      <c r="AA6" s="2">
+      <c r="AA6" s="7">
         <v>9950937.7242692802</v>
       </c>
-      <c r="AB6" s="2">
+      <c r="AB6" s="7">
         <v>11909285.303885572</v>
       </c>
-      <c r="AC6" s="2">
+      <c r="AC6" s="7">
         <v>14234923.058231598</v>
       </c>
-      <c r="AD6" s="2">
+      <c r="AD6" s="7">
         <v>16504770.583717238</v>
       </c>
-      <c r="AE6" s="2">
+      <c r="AE6" s="7">
         <v>17887765.188555308</v>
       </c>
-      <c r="AF6" s="2">
+      <c r="AF6" s="7">
         <v>18122944.187934961</v>
       </c>
-      <c r="AG6" s="2">
+      <c r="AG6" s="7">
         <v>17864149.41777382</v>
       </c>
-      <c r="AH6" s="2">
+      <c r="AH6" s="7">
         <v>16962219.313623913</v>
       </c>
-      <c r="AI6" s="2">
+      <c r="AI6" s="7">
         <v>15804649.634190621</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B7" t="s">
@@ -1255,84 +1295,84 @@
       <c r="J7" s="1">
         <v>50</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7" s="7">
         <v>14.924799999999999</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7" s="7">
         <v>6273760.7870711759</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="7">
         <v>7127.3163245055412</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N7" s="7">
         <v>2709.393711608278</v>
       </c>
-      <c r="O7" s="1">
+      <c r="O7" s="7">
         <v>4417.9226128972659</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7" s="7">
         <v>3.3287539392198369</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="7">
         <v>36.91244481633305</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R7" s="7">
         <v>6460189.0363154514</v>
       </c>
-      <c r="S7" s="2">
+      <c r="S7" s="7">
         <v>7749499.0685391221</v>
       </c>
-      <c r="T7" s="2">
+      <c r="T7" s="7">
         <v>9285195.7630087845</v>
       </c>
-      <c r="U7" s="2">
+      <c r="U7" s="7">
         <v>11014177.363848913</v>
       </c>
-      <c r="V7" s="2">
+      <c r="V7" s="7">
         <v>12651060.172161458</v>
       </c>
-      <c r="W7" s="2">
+      <c r="W7" s="7">
         <v>13656140.392693788</v>
       </c>
-      <c r="X7" s="2">
+      <c r="X7" s="7">
         <v>13793928.437193971</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Y7" s="7">
         <v>13378262.180143071</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="Z7" s="7">
         <v>12670033.961652769</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AA7" s="7">
         <v>6475476.5298331073</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AB7" s="7">
         <v>7619263.7566795377</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AC7" s="7">
         <v>9097828.7255626973</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AD7" s="7">
         <v>10709901.512389617</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AE7" s="7">
         <v>12193693.966577375</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AF7" s="7">
         <v>13197798.739659464</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AG7" s="7">
         <v>13515773.174574597</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AH7" s="7">
         <v>13208115.937428305</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AI7" s="7">
         <v>12442672.642323911</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B8" t="s">
@@ -1362,83 +1402,83 @@
       <c r="J8" s="1">
         <v>50</v>
       </c>
-      <c r="K8" s="1">
+      <c r="K8" s="7">
         <v>13.9833</v>
       </c>
-      <c r="L8" s="1">
+      <c r="L8" s="7">
         <v>7571076.8242832934</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="7">
         <v>6184.5960701349904</v>
       </c>
-      <c r="N8" s="1">
+      <c r="N8" s="7">
         <v>2710.3631637385506</v>
       </c>
-      <c r="O8" s="1">
+      <c r="O8" s="7">
         <v>3474.2329063964398</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8" s="7">
         <v>3.0953688849031691</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="7">
         <v>24.677036043217715</v>
       </c>
-      <c r="R8" s="2">
+      <c r="R8" s="7">
         <v>7384175.4387683533</v>
       </c>
-      <c r="S8" s="2">
+      <c r="S8" s="7">
         <v>7924095.5919207064</v>
       </c>
-      <c r="T8" s="2">
+      <c r="T8" s="7">
         <v>8608824.1952788234</v>
       </c>
-      <c r="U8" s="2">
+      <c r="U8" s="7">
         <v>9605269.6153139547</v>
       </c>
-      <c r="V8" s="2">
+      <c r="V8" s="7">
         <v>10747675.286966439</v>
       </c>
-      <c r="W8" s="2">
+      <c r="W8" s="7">
         <v>11457469.742690034</v>
       </c>
-      <c r="X8" s="2">
+      <c r="X8" s="7">
         <v>11530840.182773625</v>
       </c>
-      <c r="Y8" s="2">
+      <c r="Y8" s="7">
         <v>11211938.295527047</v>
       </c>
-      <c r="Z8" s="2">
+      <c r="Z8" s="7">
         <v>10656890.087780597</v>
       </c>
-      <c r="AA8" s="2">
+      <c r="AA8" s="7">
         <v>7370493.7827976895</v>
       </c>
-      <c r="AB8" s="2">
+      <c r="AB8" s="7">
         <v>7949611.6593564739</v>
       </c>
-      <c r="AC8" s="2">
+      <c r="AC8" s="7">
         <v>8684065.1350576077</v>
       </c>
-      <c r="AD8" s="2">
+      <c r="AD8" s="7">
         <v>9560080.5443469062</v>
       </c>
-      <c r="AE8" s="2">
+      <c r="AE8" s="7">
         <v>10449930.953166261</v>
       </c>
-      <c r="AF8" s="2">
+      <c r="AF8" s="7">
         <v>11125492.292220641</v>
       </c>
-      <c r="AG8" s="2">
+      <c r="AG8" s="7">
         <v>11333374.348491549</v>
       </c>
-      <c r="AH8" s="2">
+      <c r="AH8" s="7">
         <v>11076653.172646755</v>
       </c>
-      <c r="AI8" s="2">
+      <c r="AI8" s="7">
         <v>10441497.973194702</v>
       </c>
     </row>
-    <row r="9" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>31</v>
       </c>
@@ -1469,83 +1509,83 @@
       <c r="J9" s="4">
         <v>50</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="8">
         <v>16.6934</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="8">
         <v>9911499.7145404145</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="8">
         <v>7551.6044203584561</v>
       </c>
-      <c r="N9" s="4">
+      <c r="N9" s="8">
         <v>2641.8583913251564</v>
       </c>
-      <c r="O9" s="4">
+      <c r="O9" s="8">
         <v>4909.7460290332974</v>
       </c>
-      <c r="P9" s="4">
+      <c r="P9" s="8">
         <v>2.8511422328511848</v>
       </c>
-      <c r="Q9" s="4">
+      <c r="Q9" s="8">
         <v>21.135840314234844</v>
       </c>
-      <c r="R9" s="5">
+      <c r="R9" s="8">
         <v>8381420.0087174885</v>
       </c>
-      <c r="S9" s="5">
+      <c r="S9" s="8">
         <v>10259507.907906407</v>
       </c>
-      <c r="T9" s="5">
+      <c r="T9" s="8">
         <v>12366368.942383677</v>
       </c>
-      <c r="U9" s="5">
+      <c r="U9" s="8">
         <v>13921313.206846157</v>
       </c>
-      <c r="V9" s="5">
+      <c r="V9" s="8">
         <v>14630828.776472708</v>
       </c>
-      <c r="W9" s="5">
+      <c r="W9" s="8">
         <v>14670234.946231553</v>
       </c>
-      <c r="X9" s="5">
+      <c r="X9" s="8">
         <v>14250304.057113729</v>
       </c>
-      <c r="Y9" s="5">
+      <c r="Y9" s="8">
         <v>13609802.473399473</v>
       </c>
-      <c r="Z9" s="5">
+      <c r="Z9" s="8">
         <v>12846952.963085955</v>
       </c>
-      <c r="AA9" s="5">
+      <c r="AA9" s="8">
         <v>8366291.9984124228</v>
       </c>
-      <c r="AB9" s="5">
+      <c r="AB9" s="8">
         <v>9991207.4807736166</v>
       </c>
-      <c r="AC9" s="5">
+      <c r="AC9" s="8">
         <v>11813149.128086716</v>
       </c>
-      <c r="AD9" s="5">
+      <c r="AD9" s="8">
         <v>13403630.144645233</v>
       </c>
-      <c r="AE9" s="5">
+      <c r="AE9" s="8">
         <v>14285965.517577283</v>
       </c>
-      <c r="AF9" s="5">
+      <c r="AF9" s="8">
         <v>14438059.606155328</v>
       </c>
-      <c r="AG9" s="5">
+      <c r="AG9" s="8">
         <v>14120136.893310981</v>
       </c>
-      <c r="AH9" s="5">
+      <c r="AH9" s="8">
         <v>13512289.143874677</v>
       </c>
-      <c r="AI9" s="5">
+      <c r="AI9" s="8">
         <v>12719837.964141108</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -1576,84 +1616,84 @@
       <c r="J10" s="1">
         <v>50</v>
       </c>
-      <c r="K10" s="1">
+      <c r="K10" s="7">
         <v>16.994199999999999</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L10" s="7">
         <v>11256583.311405884</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="7">
         <v>6220.9752091130476</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N10" s="7">
         <v>2526.8089521856846</v>
       </c>
-      <c r="O10" s="1">
+      <c r="O10" s="7">
         <v>3694.1662569273658</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10" s="7">
         <v>2.9932713650719927</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="7">
         <v>16.214298554959448</v>
       </c>
-      <c r="R10" s="2">
+      <c r="R10" s="7">
         <v>8417552.7149950992</v>
       </c>
-      <c r="S10" s="2">
+      <c r="S10" s="7">
         <v>9943246.269822685</v>
       </c>
-      <c r="T10" s="2">
+      <c r="T10" s="7">
         <v>11859346.962977584</v>
       </c>
-      <c r="U10" s="2">
+      <c r="U10" s="7">
         <v>13330467.469250569</v>
       </c>
-      <c r="V10" s="2">
+      <c r="V10" s="7">
         <v>13756738.40840229</v>
       </c>
-      <c r="W10" s="2">
+      <c r="W10" s="7">
         <v>13434611.188394597</v>
       </c>
-      <c r="X10" s="2">
+      <c r="X10" s="7">
         <v>12863670.033315104</v>
       </c>
-      <c r="Y10" s="2">
+      <c r="Y10" s="7">
         <v>12211995.669127366</v>
       </c>
-      <c r="Z10" s="2">
+      <c r="Z10" s="7">
         <v>11736444.177228887</v>
       </c>
-      <c r="AA10" s="2">
+      <c r="AA10" s="7">
         <v>8495358.0328350514</v>
       </c>
-      <c r="AB10" s="2">
+      <c r="AB10" s="7">
         <v>9846345.3300728351</v>
       </c>
-      <c r="AC10" s="2">
+      <c r="AC10" s="7">
         <v>11390371.336920666</v>
       </c>
-      <c r="AD10" s="2">
+      <c r="AD10" s="7">
         <v>12737772.497154551</v>
       </c>
-      <c r="AE10" s="2">
+      <c r="AE10" s="7">
         <v>13382336.715664297</v>
       </c>
-      <c r="AF10" s="2">
+      <c r="AF10" s="7">
         <v>13295223.775980717</v>
       </c>
-      <c r="AG10" s="2">
+      <c r="AG10" s="7">
         <v>12794161.392228482</v>
       </c>
-      <c r="AH10" s="2">
+      <c r="AH10" s="7">
         <v>12274231.246909015</v>
       </c>
-      <c r="AI10" s="2">
+      <c r="AI10" s="7">
         <v>11846978.692702495</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A11" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B11" t="s">
@@ -1683,84 +1723,84 @@
       <c r="J11" s="1">
         <v>50</v>
       </c>
-      <c r="K11" s="1">
+      <c r="K11" s="7">
         <v>18.105899999999998</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L11" s="7">
         <v>8946455.3314072825</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="7">
         <v>7732.2667338139372</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N11" s="7">
         <v>2401.7498037468645</v>
       </c>
-      <c r="O11" s="1">
+      <c r="O11" s="7">
         <v>5330.5169300670723</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P11" s="7">
         <v>2.7451325131233597</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="7">
         <v>23.522704328826023</v>
       </c>
-      <c r="R11" s="2">
+      <c r="R11" s="7">
         <v>11524228.794649191</v>
       </c>
-      <c r="S11" s="2">
+      <c r="S11" s="7">
         <v>15021460.929348191</v>
       </c>
-      <c r="T11" s="2">
+      <c r="T11" s="7">
         <v>18417759.35253739</v>
       </c>
-      <c r="U11" s="2">
+      <c r="U11" s="7">
         <v>20704505.210122034</v>
       </c>
-      <c r="V11" s="2">
+      <c r="V11" s="7">
         <v>22007020.388973594</v>
       </c>
-      <c r="W11" s="2">
+      <c r="W11" s="7">
         <v>22308442.812791545</v>
       </c>
-      <c r="X11" s="2">
+      <c r="X11" s="7">
         <v>22050919.210792053</v>
       </c>
-      <c r="Y11" s="2">
+      <c r="Y11" s="7">
         <v>21173858.523779295</v>
       </c>
-      <c r="Z11" s="2">
+      <c r="Z11" s="7">
         <v>19995317.826049808</v>
       </c>
-      <c r="AA11" s="2">
+      <c r="AA11" s="7">
         <v>11348018.075095564</v>
       </c>
-      <c r="AB11" s="2">
+      <c r="AB11" s="7">
         <v>14177446.842879364</v>
       </c>
-      <c r="AC11" s="2">
+      <c r="AC11" s="7">
         <v>17410973.00832554</v>
       </c>
-      <c r="AD11" s="2">
+      <c r="AD11" s="7">
         <v>20053047.075691968</v>
       </c>
-      <c r="AE11" s="2">
+      <c r="AE11" s="7">
         <v>21476568.878798984</v>
       </c>
-      <c r="AF11" s="2">
+      <c r="AF11" s="7">
         <v>22028947.929743472</v>
       </c>
-      <c r="AG11" s="2">
+      <c r="AG11" s="7">
         <v>21726348.306527823</v>
       </c>
-      <c r="AH11" s="2">
+      <c r="AH11" s="7">
         <v>20972870.299427498</v>
       </c>
-      <c r="AI11" s="2">
+      <c r="AI11" s="7">
         <v>19808839.116337959</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B12" t="s">
@@ -1790,83 +1830,83 @@
       <c r="J12" s="1">
         <v>50</v>
       </c>
-      <c r="K12" s="1">
+      <c r="K12" s="7">
         <v>16.671600000000002</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12" s="7">
         <v>8415507.9126979895</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="7">
         <v>7185.2264613329589</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N12" s="7">
         <v>3202.6662596253855</v>
       </c>
-      <c r="O12" s="1">
+      <c r="O12" s="7">
         <v>3982.5602017075757</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="7">
         <v>3.3458298350646594</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="Q12" s="7">
         <v>28.214457831854208</v>
       </c>
-      <c r="R12" s="2">
+      <c r="R12" s="7">
         <v>7362095.3492581462</v>
       </c>
-      <c r="S12" s="2">
+      <c r="S12" s="7">
         <v>8326904.2360911313</v>
       </c>
-      <c r="T12" s="2">
+      <c r="T12" s="7">
         <v>10010307.115174383</v>
       </c>
-      <c r="U12" s="2">
+      <c r="U12" s="7">
         <v>12087713.219503308</v>
       </c>
-      <c r="V12" s="2">
+      <c r="V12" s="7">
         <v>13210951.193914106</v>
       </c>
-      <c r="W12" s="2">
+      <c r="W12" s="7">
         <v>13372201.393686485</v>
       </c>
-      <c r="X12" s="2">
+      <c r="X12" s="7">
         <v>13055250.774885729</v>
       </c>
-      <c r="Y12" s="2">
+      <c r="Y12" s="7">
         <v>12372111.017264126</v>
       </c>
-      <c r="Z12" s="2">
+      <c r="Z12" s="7">
         <v>11382339.536538474</v>
       </c>
-      <c r="AA12" s="2">
+      <c r="AA12" s="7">
         <v>7470135.4495948404</v>
       </c>
-      <c r="AB12" s="2">
+      <c r="AB12" s="7">
         <v>8484357.3717745282</v>
       </c>
-      <c r="AC12" s="2">
+      <c r="AC12" s="7">
         <v>9860898.0188902579</v>
       </c>
-      <c r="AD12" s="2">
+      <c r="AD12" s="7">
         <v>11390052.767545391</v>
       </c>
-      <c r="AE12" s="2">
+      <c r="AE12" s="7">
         <v>12697555.197344268</v>
       </c>
-      <c r="AF12" s="2">
+      <c r="AF12" s="7">
         <v>13132639.505033499</v>
       </c>
-      <c r="AG12" s="2">
+      <c r="AG12" s="7">
         <v>12852730.929223081</v>
       </c>
-      <c r="AH12" s="2">
+      <c r="AH12" s="7">
         <v>12161534.35430485</v>
       </c>
-      <c r="AI12" s="2">
+      <c r="AI12" s="7">
         <v>11144888.490922293</v>
       </c>
     </row>
-    <row r="13" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>31</v>
       </c>
@@ -1897,83 +1937,83 @@
       <c r="J13" s="4">
         <v>50</v>
       </c>
-      <c r="K13" s="4">
+      <c r="K13" s="8">
         <v>19.2285</v>
       </c>
-      <c r="L13" s="4">
+      <c r="L13" s="8">
         <v>13459696.741385918</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13" s="8">
         <v>6654.0145631889818</v>
       </c>
-      <c r="N13" s="4">
+      <c r="N13" s="8">
         <v>2651.2676735578229</v>
       </c>
-      <c r="O13" s="4">
+      <c r="O13" s="8">
         <v>4002.7468896311602</v>
       </c>
-      <c r="P13" s="4">
+      <c r="P13" s="8">
         <v>2.5420997287855074</v>
       </c>
-      <c r="Q13" s="4">
+      <c r="Q13" s="8">
         <v>12.120042824849866</v>
       </c>
-      <c r="R13" s="5">
+      <c r="R13" s="8">
         <v>13737411.018187204</v>
       </c>
-      <c r="S13" s="5">
+      <c r="S13" s="8">
         <v>17567337.585628234</v>
       </c>
-      <c r="T13" s="5">
+      <c r="T13" s="8">
         <v>20712337.1270684</v>
       </c>
-      <c r="U13" s="5">
+      <c r="U13" s="8">
         <v>22503025.707681414</v>
       </c>
-      <c r="V13" s="5">
+      <c r="V13" s="8">
         <v>22989585.765568115</v>
       </c>
-      <c r="W13" s="5">
+      <c r="W13" s="8">
         <v>23000397.713554658</v>
       </c>
-      <c r="X13" s="5">
+      <c r="X13" s="8">
         <v>22470684.503705516</v>
       </c>
-      <c r="Y13" s="5">
+      <c r="Y13" s="8">
         <v>21595202.27037067</v>
       </c>
-      <c r="Z13" s="5">
+      <c r="Z13" s="8">
         <v>20562082.525530171</v>
       </c>
-      <c r="AA13" s="5">
+      <c r="AA13" s="8">
         <v>13136203.429165399</v>
       </c>
-      <c r="AB13" s="5">
+      <c r="AB13" s="8">
         <v>16518779.008895783</v>
       </c>
-      <c r="AC13" s="5">
+      <c r="AC13" s="8">
         <v>19731203.653494921</v>
       </c>
-      <c r="AD13" s="5">
+      <c r="AD13" s="8">
         <v>21791629.258873224</v>
       </c>
-      <c r="AE13" s="5">
+      <c r="AE13" s="8">
         <v>22748993.465553962</v>
       </c>
-      <c r="AF13" s="5">
+      <c r="AF13" s="8">
         <v>22727173.663906794</v>
       </c>
-      <c r="AG13" s="5">
+      <c r="AG13" s="8">
         <v>22275661.325432144</v>
       </c>
-      <c r="AH13" s="5">
+      <c r="AH13" s="8">
         <v>21474058.075625971</v>
       </c>
-      <c r="AI13" s="5">
+      <c r="AI13" s="8">
         <v>20146751.329910308</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -2004,84 +2044,84 @@
       <c r="J14" s="1">
         <v>50</v>
       </c>
-      <c r="K14" s="1">
+      <c r="K14" s="7">
         <v>16.172699999999999</v>
       </c>
-      <c r="L14" s="1">
+      <c r="L14" s="7">
         <v>6462609.4981648158</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="7">
         <v>8507.7956141772902</v>
       </c>
-      <c r="N14" s="1">
+      <c r="N14" s="7">
         <v>3375.7890852202636</v>
       </c>
-      <c r="O14" s="1">
+      <c r="O14" s="7">
         <v>5132.0065289570266</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="7">
         <v>3.6316822420154589</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="7">
         <v>47.388942297550457</v>
       </c>
-      <c r="R14" s="2">
+      <c r="R14" s="7">
         <v>8795190.4367636088</v>
       </c>
-      <c r="S14" s="2">
+      <c r="S14" s="7">
         <v>9838200.9052775539</v>
       </c>
-      <c r="T14" s="2">
+      <c r="T14" s="7">
         <v>11017771.024783209</v>
       </c>
-      <c r="U14" s="2">
+      <c r="U14" s="7">
         <v>11908699.044573504</v>
       </c>
-      <c r="V14" s="2">
+      <c r="V14" s="7">
         <v>12264212.436163494</v>
       </c>
-      <c r="W14" s="2">
+      <c r="W14" s="7">
         <v>12237497.009407902</v>
       </c>
-      <c r="X14" s="2">
+      <c r="X14" s="7">
         <v>12006713.921825461</v>
       </c>
-      <c r="Y14" s="2">
+      <c r="Y14" s="7">
         <v>11524857.169104319</v>
       </c>
-      <c r="Z14" s="2">
+      <c r="Z14" s="7">
         <v>10535907.217635749</v>
       </c>
-      <c r="AA14" s="2">
+      <c r="AA14" s="7">
         <v>8791029.355404431</v>
       </c>
-      <c r="AB14" s="2">
+      <c r="AB14" s="7">
         <v>9781818.28493388</v>
       </c>
-      <c r="AC14" s="2">
+      <c r="AC14" s="7">
         <v>10774885.063266536</v>
       </c>
-      <c r="AD14" s="2">
+      <c r="AD14" s="7">
         <v>11607626.527834803</v>
       </c>
-      <c r="AE14" s="2">
+      <c r="AE14" s="7">
         <v>12070859.411404265</v>
       </c>
-      <c r="AF14" s="2">
+      <c r="AF14" s="7">
         <v>12134097.234326601</v>
       </c>
-      <c r="AG14" s="2">
+      <c r="AG14" s="7">
         <v>11870490.952306617</v>
       </c>
-      <c r="AH14" s="2">
+      <c r="AH14" s="7">
         <v>11223328.741270946</v>
       </c>
-      <c r="AI14" s="2">
+      <c r="AI14" s="7">
         <v>10133937.446832882</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B15" t="s">
@@ -2111,84 +2151,84 @@
       <c r="J15" s="1">
         <v>50</v>
       </c>
-      <c r="K15" s="1">
+      <c r="K15" s="7">
         <v>19.677900000000001</v>
       </c>
-      <c r="L15" s="1">
+      <c r="L15" s="7">
         <v>14866769.439705364</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="7">
         <v>6836.8251558970578</v>
       </c>
-      <c r="N15" s="1">
+      <c r="N15" s="7">
         <v>2804.0443380015849</v>
       </c>
-      <c r="O15" s="1">
+      <c r="O15" s="7">
         <v>4032.7808178954751</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P15" s="7">
         <v>3.5279799848075628</v>
       </c>
-      <c r="Q15" s="1">
+      <c r="Q15" s="7">
         <v>15.825154366205851</v>
       </c>
-      <c r="R15" s="2">
+      <c r="R15" s="7">
         <v>14368966.97085502</v>
       </c>
-      <c r="S15" s="2">
+      <c r="S15" s="7">
         <v>18908248.170906004</v>
       </c>
-      <c r="T15" s="2">
+      <c r="T15" s="7">
         <v>22530608.537433799</v>
       </c>
-      <c r="U15" s="2">
+      <c r="U15" s="7">
         <v>24668045.127362002</v>
       </c>
-      <c r="V15" s="2">
+      <c r="V15" s="7">
         <v>25303827.976420153</v>
       </c>
-      <c r="W15" s="2">
+      <c r="W15" s="7">
         <v>25272604.632300254</v>
       </c>
-      <c r="X15" s="2">
+      <c r="X15" s="7">
         <v>24598899.263474327</v>
       </c>
-      <c r="Y15" s="2">
+      <c r="Y15" s="7">
         <v>23654862.901020207</v>
       </c>
-      <c r="Z15" s="2">
+      <c r="Z15" s="7">
         <v>21891817.426759005</v>
       </c>
-      <c r="AA15" s="2">
+      <c r="AA15" s="7">
         <v>13239551.666400462</v>
       </c>
-      <c r="AB15" s="2">
+      <c r="AB15" s="7">
         <v>17547170.418528404</v>
       </c>
-      <c r="AC15" s="2">
+      <c r="AC15" s="7">
         <v>21407489.433150485</v>
       </c>
-      <c r="AD15" s="2">
+      <c r="AD15" s="7">
         <v>23836829.03717998</v>
       </c>
-      <c r="AE15" s="2">
+      <c r="AE15" s="7">
         <v>24966665.614315256</v>
       </c>
-      <c r="AF15" s="2">
+      <c r="AF15" s="7">
         <v>24946384.688756298</v>
       </c>
-      <c r="AG15" s="2">
+      <c r="AG15" s="7">
         <v>24436989.1951438</v>
       </c>
-      <c r="AH15" s="2">
+      <c r="AH15" s="7">
         <v>23166543.771021131</v>
       </c>
-      <c r="AI15" s="2">
+      <c r="AI15" s="7">
         <v>21521424.223709635</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A16" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B16" t="s">
@@ -2218,81 +2258,82 @@
       <c r="J16" s="1">
         <v>50</v>
       </c>
-      <c r="K16" s="1">
+      <c r="K16" s="7">
         <v>19.732600000000001</v>
       </c>
-      <c r="L16" s="1">
+      <c r="L16" s="7">
         <v>13426636.579512706</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="7">
         <v>6400.692472397639</v>
       </c>
-      <c r="N16" s="1">
+      <c r="N16" s="7">
         <v>2777.3000104016801</v>
       </c>
-      <c r="O16" s="1">
+      <c r="O16" s="7">
         <v>3623.3924619959557</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="7">
         <v>2.6247226721059111</v>
       </c>
-      <c r="Q16" s="1">
+      <c r="Q16" s="7">
         <v>12.237916529035209</v>
       </c>
-      <c r="R16" s="2">
+      <c r="R16" s="7">
         <v>12434964.802015029</v>
       </c>
-      <c r="S16" s="2">
+      <c r="S16" s="7">
         <v>15306907.20428703</v>
       </c>
-      <c r="T16" s="2">
+      <c r="T16" s="7">
         <v>17653205.109771222</v>
       </c>
-      <c r="U16" s="2">
+      <c r="U16" s="7">
         <v>18783327.662235521</v>
       </c>
-      <c r="V16" s="2">
+      <c r="V16" s="7">
         <v>19005314.73292622</v>
       </c>
-      <c r="W16" s="2">
+      <c r="W16" s="7">
         <v>18718973.91477257</v>
       </c>
-      <c r="X16" s="2">
+      <c r="X16" s="7">
         <v>18181671.331191737</v>
       </c>
-      <c r="Y16" s="2">
+      <c r="Y16" s="7">
         <v>17496927.023271821</v>
       </c>
-      <c r="Z16" s="2">
+      <c r="Z16" s="7">
         <v>16640419.41947584</v>
       </c>
-      <c r="AA16" s="2">
+      <c r="AA16" s="7">
         <v>12136558.424164921</v>
       </c>
-      <c r="AB16" s="2">
+      <c r="AB16" s="7">
         <v>14591580.998535041</v>
       </c>
-      <c r="AC16" s="2">
+      <c r="AC16" s="7">
         <v>16867859.939322576</v>
       </c>
-      <c r="AD16" s="2">
+      <c r="AD16" s="7">
         <v>18304324.375111815</v>
       </c>
-      <c r="AE16" s="2">
+      <c r="AE16" s="7">
         <v>18751095.573162075</v>
       </c>
-      <c r="AF16" s="2">
+      <c r="AF16" s="7">
         <v>18584371.716714263</v>
       </c>
-      <c r="AG16" s="2">
+      <c r="AG16" s="7">
         <v>18087332.472971492</v>
       </c>
-      <c r="AH16" s="2">
+      <c r="AH16" s="7">
         <v>17376936.891262908</v>
       </c>
-      <c r="AI16" s="2">
+      <c r="AI16" s="7">
         <v>16452570.457583116</v>
       </c>
+      <c r="AJ16" s="6"/>
     </row>
     <row r="17" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
@@ -2325,79 +2366,79 @@
       <c r="J17" s="4">
         <v>50</v>
       </c>
-      <c r="K17" s="4">
+      <c r="K17" s="8">
         <v>23.551100000000002</v>
       </c>
-      <c r="L17" s="4">
+      <c r="L17" s="8">
         <v>19125589.134683296</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="8">
         <v>7793.7355038013447</v>
       </c>
-      <c r="N17" s="4">
+      <c r="N17" s="8">
         <v>3810.6172970179778</v>
       </c>
-      <c r="O17" s="4">
+      <c r="O17" s="8">
         <v>3983.1182067833665</v>
       </c>
-      <c r="P17" s="4">
+      <c r="P17" s="8">
         <v>2.9255963372380953</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="Q17" s="8">
         <v>11.571114610628989</v>
       </c>
-      <c r="R17" s="5">
+      <c r="R17" s="8">
         <v>18902186.644834843</v>
       </c>
-      <c r="S17" s="5">
+      <c r="S17" s="8">
         <v>22550149.880342484</v>
       </c>
-      <c r="T17" s="5">
+      <c r="T17" s="8">
         <v>24654361.60708141</v>
       </c>
-      <c r="U17" s="5">
+      <c r="U17" s="8">
         <v>25542657.420510616</v>
       </c>
-      <c r="V17" s="5">
+      <c r="V17" s="8">
         <v>25512034.566040333</v>
       </c>
-      <c r="W17" s="5">
+      <c r="W17" s="8">
         <v>25090284.114149973</v>
       </c>
-      <c r="X17" s="5">
+      <c r="X17" s="8">
         <v>23848009.819196973</v>
       </c>
-      <c r="Y17" s="5">
+      <c r="Y17" s="8">
         <v>22166354.4283958</v>
       </c>
-      <c r="Z17" s="5">
+      <c r="Z17" s="8">
         <v>20487976.479211565</v>
       </c>
-      <c r="AA17" s="5">
+      <c r="AA17" s="8">
         <v>17366289.761913434</v>
       </c>
-      <c r="AB17" s="5">
+      <c r="AB17" s="8">
         <v>21398451.594970025</v>
       </c>
-      <c r="AC17" s="5">
+      <c r="AC17" s="8">
         <v>23953301.35633564</v>
       </c>
-      <c r="AD17" s="5">
+      <c r="AD17" s="8">
         <v>25075866.456618879</v>
       </c>
-      <c r="AE17" s="5">
+      <c r="AE17" s="8">
         <v>25314449.932651278</v>
       </c>
-      <c r="AF17" s="5">
+      <c r="AF17" s="8">
         <v>24651973.409512866</v>
       </c>
-      <c r="AG17" s="5">
+      <c r="AG17" s="8">
         <v>23537862.511430167</v>
       </c>
-      <c r="AH17" s="5">
+      <c r="AH17" s="8">
         <v>22040671.925652072</v>
       </c>
-      <c r="AI17" s="5">
+      <c r="AI17" s="8">
         <v>20150158.797653325</v>
       </c>
     </row>
@@ -2432,84 +2473,84 @@
       <c r="J18" s="1">
         <v>50</v>
       </c>
-      <c r="K18" s="1">
+      <c r="K18" s="7">
         <v>27.1968</v>
       </c>
-      <c r="L18" s="1">
+      <c r="L18" s="7">
         <v>20183633.2041215</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="7">
         <v>8153.3668276810804</v>
       </c>
-      <c r="N18" s="1">
+      <c r="N18" s="7">
         <v>3031.8201769108482</v>
       </c>
-      <c r="O18" s="1">
+      <c r="O18" s="7">
         <v>5121.5466507702358</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="7">
         <v>2.3220290642160748</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="Q18" s="7">
         <v>9.1719247980580523</v>
       </c>
-      <c r="R18" s="2">
+      <c r="R18" s="7">
         <v>28026234.04195375</v>
       </c>
-      <c r="S18" s="2">
+      <c r="S18" s="7">
         <v>32143831.404388312</v>
       </c>
-      <c r="T18" s="2">
+      <c r="T18" s="7">
         <v>34248460.823753662</v>
       </c>
-      <c r="U18" s="2">
+      <c r="U18" s="7">
         <v>35124512.806481704</v>
       </c>
-      <c r="V18" s="2">
+      <c r="V18" s="7">
         <v>35238151.880997516</v>
       </c>
-      <c r="W18" s="2">
+      <c r="W18" s="7">
         <v>34668073.98994419</v>
       </c>
-      <c r="X18" s="2">
+      <c r="X18" s="7">
         <v>33843471.284417614</v>
       </c>
-      <c r="Y18" s="2">
+      <c r="Y18" s="7">
         <v>32856847.162292738</v>
       </c>
-      <c r="Z18" s="2">
+      <c r="Z18" s="7">
         <v>30921135.983414505</v>
       </c>
-      <c r="AA18" s="2">
+      <c r="AA18" s="7">
         <v>25807913.041817181</v>
       </c>
-      <c r="AB18" s="2">
+      <c r="AB18" s="7">
         <v>30826498.008319087</v>
       </c>
-      <c r="AC18" s="2">
+      <c r="AC18" s="7">
         <v>33568134.642160043</v>
       </c>
-      <c r="AD18" s="2">
+      <c r="AD18" s="7">
         <v>34736258.315705925</v>
       </c>
-      <c r="AE18" s="2">
+      <c r="AE18" s="7">
         <v>34894800.858655341</v>
       </c>
-      <c r="AF18" s="2">
+      <c r="AF18" s="7">
         <v>34526733.0631437</v>
       </c>
-      <c r="AG18" s="2">
+      <c r="AG18" s="7">
         <v>33738169.228826046</v>
       </c>
-      <c r="AH18" s="2">
+      <c r="AH18" s="7">
         <v>32316372.224989485</v>
       </c>
-      <c r="AI18" s="2">
+      <c r="AI18" s="7">
         <v>30381041.003094517</v>
       </c>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B19" t="s">
@@ -2539,84 +2580,84 @@
       <c r="J19" s="1">
         <v>50</v>
       </c>
-      <c r="K19" s="1">
+      <c r="K19" s="7">
         <v>21.612100000000002</v>
       </c>
-      <c r="L19" s="1">
+      <c r="L19" s="7">
         <v>14445044.039830649</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="7">
         <v>7819.6855564675834</v>
       </c>
-      <c r="N19" s="1">
+      <c r="N19" s="7">
         <v>3635.6827417094873</v>
       </c>
-      <c r="O19" s="1">
+      <c r="O19" s="7">
         <v>4184.002814758097</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P19" s="7">
         <v>2.8780401345844813</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q19" s="7">
         <v>15.201933787082577</v>
       </c>
-      <c r="R19" s="2">
+      <c r="R19" s="7">
         <v>12063512.182029223</v>
       </c>
-      <c r="S19" s="2">
+      <c r="S19" s="7">
         <v>14747362.896105697</v>
       </c>
-      <c r="T19" s="2">
+      <c r="T19" s="7">
         <v>15876711.24979955</v>
       </c>
-      <c r="U19" s="2">
+      <c r="U19" s="7">
         <v>15979328.4507076</v>
       </c>
-      <c r="V19" s="2">
+      <c r="V19" s="7">
         <v>15889230.334371746</v>
       </c>
-      <c r="W19" s="2">
+      <c r="W19" s="7">
         <v>15861071.808531517</v>
       </c>
-      <c r="X19" s="2">
+      <c r="X19" s="7">
         <v>15718323.09321606</v>
       </c>
-      <c r="Y19" s="2">
+      <c r="Y19" s="7">
         <v>15280094.41293785</v>
       </c>
-      <c r="Z19" s="2">
+      <c r="Z19" s="7">
         <v>14694880.655699167</v>
       </c>
-      <c r="AA19" s="2">
+      <c r="AA19" s="7">
         <v>11247780.179828193</v>
       </c>
-      <c r="AB19" s="2">
+      <c r="AB19" s="7">
         <v>13709904.649819842</v>
       </c>
-      <c r="AC19" s="2">
+      <c r="AC19" s="7">
         <v>15338648.267646382</v>
       </c>
-      <c r="AD19" s="2">
+      <c r="AD19" s="7">
         <v>15882968.32517501</v>
       </c>
-      <c r="AE19" s="2">
+      <c r="AE19" s="7">
         <v>15919980.524443353</v>
       </c>
-      <c r="AF19" s="2">
+      <c r="AF19" s="7">
         <v>15803314.652009426</v>
       </c>
-      <c r="AG19" s="2">
+      <c r="AG19" s="7">
         <v>15565163.680842586</v>
       </c>
-      <c r="AH19" s="2">
+      <c r="AH19" s="7">
         <v>15189381.813862257</v>
       </c>
-      <c r="AI19" s="2">
+      <c r="AI19" s="7">
         <v>14652670.000708176</v>
       </c>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="A20" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B20" t="s">
@@ -2646,79 +2687,79 @@
       <c r="J20" s="1">
         <v>50</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K20" s="7">
         <v>25.642800000000001</v>
       </c>
-      <c r="L20" s="1">
+      <c r="L20" s="7">
         <v>17819576.179180816</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="7">
         <v>8627.627361269615</v>
       </c>
-      <c r="N20" s="1">
+      <c r="N20" s="7">
         <v>3522.9458062131903</v>
       </c>
-      <c r="O20" s="1">
+      <c r="O20" s="7">
         <v>5104.6815550564288</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P20" s="7">
         <v>2.5554317472545485</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="Q20" s="7">
         <v>11.982437090646577</v>
       </c>
-      <c r="R20" s="2">
+      <c r="R20" s="7">
         <v>22819030.945934437</v>
       </c>
-      <c r="S20" s="2">
+      <c r="S20" s="7">
         <v>26741615.337891877</v>
       </c>
-      <c r="T20" s="2">
+      <c r="T20" s="7">
         <v>29085038.038137883</v>
       </c>
-      <c r="U20" s="2">
+      <c r="U20" s="7">
         <v>30092413.93621349</v>
       </c>
-      <c r="V20" s="2">
+      <c r="V20" s="7">
         <v>30470633.479616378</v>
       </c>
-      <c r="W20" s="2">
+      <c r="W20" s="7">
         <v>30138624.205490906</v>
       </c>
-      <c r="X20" s="2">
+      <c r="X20" s="7">
         <v>29292772.088935249</v>
       </c>
-      <c r="Y20" s="2">
+      <c r="Y20" s="7">
         <v>28230373.148913082</v>
       </c>
-      <c r="Z20" s="2">
+      <c r="Z20" s="7">
         <v>26345575.304769173</v>
       </c>
-      <c r="AA20" s="2">
+      <c r="AA20" s="7">
         <v>21060370.355055209</v>
       </c>
-      <c r="AB20" s="2">
+      <c r="AB20" s="7">
         <v>25573809.377434909</v>
       </c>
-      <c r="AC20" s="2">
+      <c r="AC20" s="7">
         <v>28318237.096643195</v>
       </c>
-      <c r="AD20" s="2">
+      <c r="AD20" s="7">
         <v>29761717.439004991</v>
       </c>
-      <c r="AE20" s="2">
+      <c r="AE20" s="7">
         <v>30115501.344202843</v>
       </c>
-      <c r="AF20" s="2">
+      <c r="AF20" s="7">
         <v>29870095.702630628</v>
       </c>
-      <c r="AG20" s="2">
+      <c r="AG20" s="7">
         <v>29153305.558766015</v>
       </c>
-      <c r="AH20" s="2">
+      <c r="AH20" s="7">
         <v>27741116.302164193</v>
       </c>
-      <c r="AI20" s="2">
+      <c r="AI20" s="7">
         <v>25953927.425724126</v>
       </c>
     </row>
@@ -2753,79 +2794,79 @@
       <c r="J21" s="4">
         <v>50</v>
       </c>
-      <c r="K21" s="4">
+      <c r="K21" s="8">
         <v>23.185500000000001</v>
       </c>
-      <c r="L21" s="4">
+      <c r="L21" s="8">
         <v>17138330.513733305</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="8">
         <v>5863.4578150916941</v>
       </c>
-      <c r="N21" s="4">
+      <c r="N21" s="8">
         <v>2683.6797137876292</v>
       </c>
-      <c r="O21" s="4">
+      <c r="O21" s="8">
         <v>3179.7781013040658</v>
       </c>
-      <c r="P21" s="4">
+      <c r="P21" s="8">
         <v>2.3597334411486699</v>
       </c>
-      <c r="Q21" s="4">
+      <c r="Q21" s="8">
         <v>7.9549407519239361</v>
       </c>
-      <c r="R21" s="5">
+      <c r="R21" s="8">
         <v>21954020.576787651</v>
       </c>
-      <c r="S21" s="5">
+      <c r="S21" s="8">
         <v>25740782.020151533</v>
       </c>
-      <c r="T21" s="5">
+      <c r="T21" s="8">
         <v>27081482.326011539</v>
       </c>
-      <c r="U21" s="5">
+      <c r="U21" s="8">
         <v>27884011.599201165</v>
       </c>
-      <c r="V21" s="5">
+      <c r="V21" s="8">
         <v>27981163.971325677</v>
       </c>
-      <c r="W21" s="5">
+      <c r="W21" s="8">
         <v>27432581.443124358</v>
       </c>
-      <c r="X21" s="5">
+      <c r="X21" s="8">
         <v>26722574.028892163</v>
       </c>
-      <c r="Y21" s="5">
+      <c r="Y21" s="8">
         <v>25755570.075274117</v>
       </c>
-      <c r="Z21" s="5">
+      <c r="Z21" s="8">
         <v>24307784.982681435</v>
       </c>
-      <c r="AA21" s="5">
+      <c r="AA21" s="8">
         <v>19766572.192563768</v>
       </c>
-      <c r="AB21" s="5">
+      <c r="AB21" s="8">
         <v>24249671.56607784</v>
       </c>
-      <c r="AC21" s="5">
+      <c r="AC21" s="8">
         <v>26769567.43245656</v>
       </c>
-      <c r="AD21" s="5">
+      <c r="AD21" s="8">
         <v>27523973.092711031</v>
       </c>
-      <c r="AE21" s="5">
+      <c r="AE21" s="8">
         <v>27656454.49533825</v>
       </c>
-      <c r="AF21" s="5">
+      <c r="AF21" s="8">
         <v>27337390.568642419</v>
       </c>
-      <c r="AG21" s="5">
+      <c r="AG21" s="8">
         <v>26567637.849179689</v>
       </c>
-      <c r="AH21" s="5">
+      <c r="AH21" s="8">
         <v>25458044.828991983</v>
       </c>
-      <c r="AI21" s="5">
+      <c r="AI21" s="8">
         <v>24063165.530871075</v>
       </c>
     </row>
@@ -2860,84 +2901,84 @@
       <c r="J22" s="1">
         <v>50</v>
       </c>
-      <c r="K22" s="1">
+      <c r="K22" s="7">
         <v>24.927499999999998</v>
       </c>
-      <c r="L22" s="1">
+      <c r="L22" s="7">
         <v>22170841.725542035</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="7">
         <v>8105.8364181028874</v>
       </c>
-      <c r="N22" s="1">
+      <c r="N22" s="7">
         <v>3772.9795098664299</v>
       </c>
-      <c r="O22" s="1">
+      <c r="O22" s="7">
         <v>4332.8569082364538</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P22" s="7">
         <v>2.6376883356510361</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="Q22" s="7">
         <v>9.5616895001190745</v>
       </c>
-      <c r="R22" s="2">
+      <c r="R22" s="7">
         <v>19723328.894795854</v>
       </c>
-      <c r="S22" s="2">
+      <c r="S22" s="7">
         <v>21802230.696893044</v>
       </c>
-      <c r="T22" s="2">
+      <c r="T22" s="7">
         <v>22381838.538321029</v>
       </c>
-      <c r="U22" s="2">
+      <c r="U22" s="7">
         <v>22272780.66408851</v>
       </c>
-      <c r="V22" s="2">
+      <c r="V22" s="7">
         <v>21644847.226970162</v>
       </c>
-      <c r="W22" s="2">
+      <c r="W22" s="7">
         <v>20899529.608433697</v>
       </c>
-      <c r="X22" s="2">
+      <c r="X22" s="7">
         <v>20210219.242029969</v>
       </c>
-      <c r="Y22" s="2">
+      <c r="Y22" s="7">
         <v>19489829.562064055</v>
       </c>
-      <c r="Z22" s="2">
+      <c r="Z22" s="7">
         <v>18703042.038104396</v>
       </c>
-      <c r="AA22" s="2">
+      <c r="AA22" s="7">
         <v>18061798.4107127</v>
       </c>
-      <c r="AB22" s="2">
+      <c r="AB22" s="7">
         <v>20968654.902643342</v>
       </c>
-      <c r="AC22" s="2">
+      <c r="AC22" s="7">
         <v>22034993.857296746</v>
       </c>
-      <c r="AD22" s="2">
+      <c r="AD22" s="7">
         <v>22007174.394334868</v>
       </c>
-      <c r="AE22" s="2">
+      <c r="AE22" s="7">
         <v>21564314.534612119</v>
       </c>
-      <c r="AF22" s="2">
+      <c r="AF22" s="7">
         <v>20902946.51622669</v>
       </c>
-      <c r="AG22" s="2">
+      <c r="AG22" s="7">
         <v>20170078.375158545</v>
       </c>
-      <c r="AH22" s="2">
+      <c r="AH22" s="7">
         <v>19427442.863852795</v>
       </c>
-      <c r="AI22" s="2">
+      <c r="AI22" s="7">
         <v>18545278.578721382</v>
       </c>
     </row>
     <row r="23" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B23" t="s">
@@ -2967,84 +3008,84 @@
       <c r="J23" s="1">
         <v>50</v>
       </c>
-      <c r="K23" s="1">
+      <c r="K23" s="7">
         <v>26.137499999999999</v>
       </c>
-      <c r="L23" s="1">
+      <c r="L23" s="7">
         <v>19490655.066456571</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="7">
         <v>7576.7937977969968</v>
       </c>
-      <c r="N23" s="1">
+      <c r="N23" s="7">
         <v>3062.4107935250122</v>
       </c>
-      <c r="O23" s="1">
+      <c r="O23" s="7">
         <v>4514.3830042719819</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="7">
         <v>2.3027344601451962</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="Q23" s="7">
         <v>8.8185717944715964</v>
       </c>
-      <c r="R23" s="2">
+      <c r="R23" s="7">
         <v>20399276.196271483</v>
       </c>
-      <c r="S23" s="2">
+      <c r="S23" s="7">
         <v>23975022.214020494</v>
       </c>
-      <c r="T23" s="2">
+      <c r="T23" s="7">
         <v>26841544.038064789</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U23" s="7">
         <v>28732699.492918812</v>
       </c>
-      <c r="V23" s="2">
+      <c r="V23" s="7">
         <v>29807425.998950582</v>
       </c>
-      <c r="W23" s="2">
+      <c r="W23" s="7">
         <v>30441067.195630118</v>
       </c>
-      <c r="X23" s="2">
+      <c r="X23" s="7">
         <v>30417827.538020916</v>
       </c>
-      <c r="Y23" s="2">
+      <c r="Y23" s="7">
         <v>29873301.434443958</v>
       </c>
-      <c r="Z23" s="2">
+      <c r="Z23" s="7">
         <v>28836202.17174292</v>
       </c>
-      <c r="AA23" s="2">
+      <c r="AA23" s="7">
         <v>19038003.995269224</v>
       </c>
-      <c r="AB23" s="2">
+      <c r="AB23" s="7">
         <v>23181141.548803631</v>
       </c>
-      <c r="AC23" s="2">
+      <c r="AC23" s="7">
         <v>26139134.316663515</v>
       </c>
-      <c r="AD23" s="2">
+      <c r="AD23" s="7">
         <v>28246844.985510089</v>
       </c>
-      <c r="AE23" s="2">
+      <c r="AE23" s="7">
         <v>29562222.752503891</v>
       </c>
-      <c r="AF23" s="2">
+      <c r="AF23" s="7">
         <v>30109533.464456145</v>
       </c>
-      <c r="AG23" s="2">
+      <c r="AG23" s="7">
         <v>30154512.000239607</v>
       </c>
-      <c r="AH23" s="2">
+      <c r="AH23" s="7">
         <v>29605906.258458119</v>
       </c>
-      <c r="AI23" s="2">
+      <c r="AI23" s="7">
         <v>28328542.512437902</v>
       </c>
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="A24" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B24" t="s">
@@ -3074,79 +3115,79 @@
       <c r="J24" s="1">
         <v>50</v>
       </c>
-      <c r="K24" s="1">
+      <c r="K24" s="7">
         <v>25.952200000000001</v>
       </c>
-      <c r="L24" s="1">
+      <c r="L24" s="7">
         <v>24849323.480220713</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="7">
         <v>6021.5910541267149</v>
       </c>
-      <c r="N24" s="1">
+      <c r="N24" s="7">
         <v>2893.4510873188074</v>
       </c>
-      <c r="O24" s="1">
+      <c r="O24" s="7">
         <v>3128.139966807908</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="7">
         <v>2.1274384482329212</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="Q24" s="7">
         <v>5.0953650048961165</v>
       </c>
-      <c r="R24" s="2">
+      <c r="R24" s="7">
         <v>24825225.32747291</v>
       </c>
-      <c r="S24" s="2">
+      <c r="S24" s="7">
         <v>29241285.363728955</v>
       </c>
-      <c r="T24" s="2">
+      <c r="T24" s="7">
         <v>31893841.835492283</v>
       </c>
-      <c r="U24" s="2">
+      <c r="U24" s="7">
         <v>32984449.969104163</v>
       </c>
-      <c r="V24" s="2">
+      <c r="V24" s="7">
         <v>33493400.846528765</v>
       </c>
-      <c r="W24" s="2">
+      <c r="W24" s="7">
         <v>33278647.744484402</v>
       </c>
-      <c r="X24" s="2">
+      <c r="X24" s="7">
         <v>32698840.337061882</v>
       </c>
-      <c r="Y24" s="2">
+      <c r="Y24" s="7">
         <v>31762978.151851851</v>
       </c>
-      <c r="Z24" s="2">
+      <c r="Z24" s="7">
         <v>29855976.950598363</v>
       </c>
-      <c r="AA24" s="2">
+      <c r="AA24" s="7">
         <v>23073946.217075173</v>
       </c>
-      <c r="AB24" s="2">
+      <c r="AB24" s="7">
         <v>27919070.243167426</v>
       </c>
-      <c r="AC24" s="2">
+      <c r="AC24" s="7">
         <v>31000283.369999729</v>
       </c>
-      <c r="AD24" s="2">
+      <c r="AD24" s="7">
         <v>32674056.446354922</v>
       </c>
-      <c r="AE24" s="2">
+      <c r="AE24" s="7">
         <v>33130895.760772325</v>
       </c>
-      <c r="AF24" s="2">
+      <c r="AF24" s="7">
         <v>33091351.706561081</v>
       </c>
-      <c r="AG24" s="2">
+      <c r="AG24" s="7">
         <v>32503153.070494615</v>
       </c>
-      <c r="AH24" s="2">
+      <c r="AH24" s="7">
         <v>31212810.323632576</v>
       </c>
-      <c r="AI24" s="2">
+      <c r="AI24" s="7">
         <v>29408628.258093428</v>
       </c>
     </row>
@@ -3181,79 +3222,79 @@
       <c r="J25" s="4">
         <v>50</v>
       </c>
-      <c r="K25" s="4">
+      <c r="K25" s="8">
         <v>24.7196</v>
       </c>
-      <c r="L25" s="4">
+      <c r="L25" s="8">
         <v>16961165.030899476</v>
       </c>
-      <c r="M25" s="3">
+      <c r="M25" s="8">
         <v>8353.6458812873116</v>
       </c>
-      <c r="N25" s="4">
+      <c r="N25" s="8">
         <v>3779.596577448187</v>
       </c>
-      <c r="O25" s="4">
+      <c r="O25" s="8">
         <v>4574.049303839126</v>
       </c>
-      <c r="P25" s="4">
+      <c r="P25" s="8">
         <v>3.2661391420203572</v>
       </c>
-      <c r="Q25" s="4">
+      <c r="Q25" s="8">
         <v>15.5678577509637</v>
       </c>
-      <c r="R25" s="5">
+      <c r="R25" s="8">
         <v>16227241.024887826</v>
       </c>
-      <c r="S25" s="5">
+      <c r="S25" s="8">
         <v>19696972.480273023</v>
       </c>
-      <c r="T25" s="5">
+      <c r="T25" s="8">
         <v>21775607.914163094</v>
       </c>
-      <c r="U25" s="5">
+      <c r="U25" s="8">
         <v>23020387.679041855</v>
       </c>
-      <c r="V25" s="5">
+      <c r="V25" s="8">
         <v>23818255.588281136</v>
       </c>
-      <c r="W25" s="5">
+      <c r="W25" s="8">
         <v>24310067.354904823</v>
       </c>
-      <c r="X25" s="5">
+      <c r="X25" s="8">
         <v>24379003.112845901</v>
       </c>
-      <c r="Y25" s="5">
+      <c r="Y25" s="8">
         <v>23917978.869199421</v>
       </c>
-      <c r="Z25" s="5">
+      <c r="Z25" s="8">
         <v>22768409.92634562</v>
       </c>
-      <c r="AA25" s="5">
+      <c r="AA25" s="8">
         <v>14314805.132985387</v>
       </c>
-      <c r="AB25" s="5">
+      <c r="AB25" s="8">
         <v>18596397.267652016</v>
       </c>
-      <c r="AC25" s="5">
+      <c r="AC25" s="8">
         <v>21229399.050326332</v>
       </c>
-      <c r="AD25" s="5">
+      <c r="AD25" s="8">
         <v>22751175.489303712</v>
       </c>
-      <c r="AE25" s="5">
+      <c r="AE25" s="8">
         <v>23647656.65625437</v>
       </c>
-      <c r="AF25" s="5">
+      <c r="AF25" s="8">
         <v>24095367.362280581</v>
       </c>
-      <c r="AG25" s="5">
+      <c r="AG25" s="8">
         <v>24112429.294837259</v>
       </c>
-      <c r="AH25" s="5">
+      <c r="AH25" s="8">
         <v>23546196.946480423</v>
       </c>
-      <c r="AI25" s="5">
+      <c r="AI25" s="8">
         <v>22231435.672014918</v>
       </c>
     </row>
@@ -3270,7 +3311,7 @@
       <c r="D26" s="1">
         <v>34</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="2">
         <v>62.6</v>
       </c>
       <c r="F26" s="1">
@@ -3288,79 +3329,79 @@
       <c r="J26" s="1">
         <v>50</v>
       </c>
-      <c r="K26" s="1">
+      <c r="K26" s="7">
         <v>22.279699999999998</v>
       </c>
-      <c r="L26" s="1">
+      <c r="L26" s="7">
         <v>10522831.506272467</v>
       </c>
-      <c r="M26" s="1">
+      <c r="M26" s="7">
         <v>9501.8792857954577</v>
       </c>
-      <c r="N26" s="1">
+      <c r="N26" s="7">
         <v>3300.419956011739</v>
       </c>
-      <c r="O26" s="1">
+      <c r="O26" s="7">
         <v>6201.4593297837182</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P26" s="7">
         <v>4.0663833672884335</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="Q26" s="7">
         <v>36.346925812752147</v>
       </c>
-      <c r="R26" s="1">
+      <c r="R26" s="7">
         <v>16418228.732056851</v>
       </c>
-      <c r="S26" s="1">
+      <c r="S26" s="7">
         <v>19854143.964042392</v>
       </c>
-      <c r="T26" s="1">
+      <c r="T26" s="7">
         <v>21682033.999513011</v>
       </c>
-      <c r="U26" s="1">
+      <c r="U26" s="7">
         <v>22878271.354746394</v>
       </c>
-      <c r="V26" s="1">
+      <c r="V26" s="7">
         <v>23532651.2964877</v>
       </c>
-      <c r="W26" s="1">
+      <c r="W26" s="7">
         <v>23467458.951098278</v>
       </c>
-      <c r="X26" s="1">
+      <c r="X26" s="7">
         <v>22883156.392103262</v>
       </c>
-      <c r="Y26" s="1">
+      <c r="Y26" s="7">
         <v>21763713.955909982</v>
       </c>
-      <c r="Z26" s="1">
+      <c r="Z26" s="7">
         <v>20530080.597308073</v>
       </c>
-      <c r="AA26" s="1">
+      <c r="AA26" s="7">
         <v>15054143.082214948</v>
       </c>
-      <c r="AB26" s="1">
+      <c r="AB26" s="7">
         <v>18686516.473035902</v>
       </c>
-      <c r="AC26" s="1">
+      <c r="AC26" s="7">
         <v>21259200.52667113</v>
       </c>
-      <c r="AD26" s="1">
+      <c r="AD26" s="7">
         <v>22569470.169651326</v>
       </c>
-      <c r="AE26" s="1">
+      <c r="AE26" s="7">
         <v>23169120.018026371</v>
       </c>
-      <c r="AF26" s="1">
+      <c r="AF26" s="7">
         <v>23203359.663639918</v>
       </c>
-      <c r="AG26" s="1">
+      <c r="AG26" s="7">
         <v>22583498.550161485</v>
       </c>
-      <c r="AH26" s="1">
+      <c r="AH26" s="7">
         <v>21642848.017311852</v>
       </c>
-      <c r="AI26" s="1">
+      <c r="AI26" s="7">
         <v>20323380.728523735</v>
       </c>
     </row>
@@ -3377,7 +3418,7 @@
       <c r="D27" s="1">
         <v>35</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="2">
         <v>62.5</v>
       </c>
       <c r="F27" s="1">
@@ -3395,79 +3436,79 @@
       <c r="J27" s="1">
         <v>50</v>
       </c>
-      <c r="K27" s="1">
+      <c r="K27" s="7">
         <v>20.2227</v>
       </c>
-      <c r="L27" s="1">
+      <c r="L27" s="7">
         <v>9881043.4166893512</v>
       </c>
-      <c r="M27" s="1">
+      <c r="M27" s="7">
         <v>8625.9814266482063</v>
       </c>
-      <c r="N27" s="1">
+      <c r="N27" s="7">
         <v>2559.0751843862467</v>
       </c>
-      <c r="O27" s="1">
+      <c r="O27" s="7">
         <v>6066.9062422619572</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P27" s="7">
         <v>2.6127429196506191</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="Q27" s="7">
         <v>22.541901447098152</v>
       </c>
-      <c r="R27" s="1">
+      <c r="R27" s="7">
         <v>18336531.629250348</v>
       </c>
-      <c r="S27" s="1">
+      <c r="S27" s="7">
         <v>22790615.719253156</v>
       </c>
-      <c r="T27" s="1">
+      <c r="T27" s="7">
         <v>25033086.5890388</v>
       </c>
-      <c r="U27" s="1">
+      <c r="U27" s="7">
         <v>26010506.947258156</v>
       </c>
-      <c r="V27" s="1">
+      <c r="V27" s="7">
         <v>25971818.348270554</v>
       </c>
-      <c r="W27" s="1">
+      <c r="W27" s="7">
         <v>25488801.833207838</v>
       </c>
-      <c r="X27" s="1">
+      <c r="X27" s="7">
         <v>24340913.586255282</v>
       </c>
-      <c r="Y27" s="1">
+      <c r="Y27" s="7">
         <v>22636286.505660102</v>
       </c>
-      <c r="Z27" s="1">
+      <c r="Z27" s="7">
         <v>20956186.818461604</v>
       </c>
-      <c r="AA27" s="1">
+      <c r="AA27" s="7">
         <v>16635910.290045543</v>
       </c>
-      <c r="AB27" s="1">
+      <c r="AB27" s="7">
         <v>21167812.993295018</v>
       </c>
-      <c r="AC27" s="1">
+      <c r="AC27" s="7">
         <v>24294337.347477373</v>
       </c>
-      <c r="AD27" s="1">
+      <c r="AD27" s="7">
         <v>25493813.914020829</v>
       </c>
-      <c r="AE27" s="1">
+      <c r="AE27" s="7">
         <v>25747011.867134422</v>
       </c>
-      <c r="AF27" s="1">
+      <c r="AF27" s="7">
         <v>25129932.793784827</v>
       </c>
-      <c r="AG27" s="1">
+      <c r="AG27" s="7">
         <v>23978005.68883317</v>
       </c>
-      <c r="AH27" s="1">
+      <c r="AH27" s="7">
         <v>22522092.049515773</v>
       </c>
-      <c r="AI27" s="1">
+      <c r="AI27" s="7">
         <v>20693206.850758381</v>
       </c>
     </row>
@@ -3484,7 +3525,7 @@
       <c r="D28" s="1">
         <v>36</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28" s="2">
         <v>62.5</v>
       </c>
       <c r="F28" s="1">
@@ -3502,79 +3543,79 @@
       <c r="J28" s="1">
         <v>50</v>
       </c>
-      <c r="K28" s="1">
+      <c r="K28" s="7">
         <v>19.403700000000001</v>
       </c>
-      <c r="L28" s="1">
+      <c r="L28" s="7">
         <v>9708484.6838893015</v>
       </c>
-      <c r="M28" s="1">
+      <c r="M28" s="7">
         <v>8097.6271483294113</v>
       </c>
-      <c r="N28" s="1">
+      <c r="N28" s="7">
         <v>2468.7846454352939</v>
       </c>
-      <c r="O28" s="1">
+      <c r="O28" s="7">
         <v>5628.8425028941192</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="7">
         <v>2.3547350921580135</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="Q28" s="7">
         <v>19.410491762597481</v>
       </c>
-      <c r="R28" s="1">
+      <c r="R28" s="7">
         <v>16813016.51964765</v>
       </c>
-      <c r="S28" s="1">
+      <c r="S28" s="7">
         <v>21805816.197338138</v>
       </c>
-      <c r="T28" s="1">
+      <c r="T28" s="7">
         <v>24817533.991142493</v>
       </c>
-      <c r="U28" s="1">
+      <c r="U28" s="7">
         <v>25820063.664509341</v>
       </c>
-      <c r="V28" s="1">
+      <c r="V28" s="7">
         <v>26241810.925247014</v>
       </c>
-      <c r="W28" s="1">
+      <c r="W28" s="7">
         <v>26053789.072248079</v>
       </c>
-      <c r="X28" s="1">
+      <c r="X28" s="7">
         <v>25296209.37747816</v>
       </c>
-      <c r="Y28" s="1">
+      <c r="Y28" s="7">
         <v>23731353.760943539</v>
       </c>
-      <c r="Z28" s="1">
+      <c r="Z28" s="7">
         <v>21890589.605323039</v>
       </c>
-      <c r="AA28" s="1">
+      <c r="AA28" s="7">
         <v>15867608.81113652</v>
       </c>
-      <c r="AB28" s="1">
+      <c r="AB28" s="7">
         <v>20045740.632800311</v>
       </c>
-      <c r="AC28" s="1">
+      <c r="AC28" s="7">
         <v>23643765.28497038</v>
       </c>
-      <c r="AD28" s="1">
+      <c r="AD28" s="7">
         <v>25509807.683310311</v>
       </c>
-      <c r="AE28" s="1">
+      <c r="AE28" s="7">
         <v>25936399.825974971</v>
       </c>
-      <c r="AF28" s="1">
+      <c r="AF28" s="7">
         <v>25760335.368339386</v>
       </c>
-      <c r="AG28" s="1">
+      <c r="AG28" s="7">
         <v>24838401.58330572</v>
       </c>
-      <c r="AH28" s="1">
+      <c r="AH28" s="7">
         <v>23470502.343442742</v>
       </c>
-      <c r="AI28" s="1">
+      <c r="AI28" s="7">
         <v>21662491.675118409</v>
       </c>
     </row>
@@ -3591,7 +3632,7 @@
       <c r="D29" s="1">
         <v>37</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="2">
         <v>62.3</v>
       </c>
       <c r="F29" s="1">
@@ -3609,79 +3650,79 @@
       <c r="J29" s="1">
         <v>2</v>
       </c>
-      <c r="K29" s="1">
+      <c r="K29" s="7">
         <v>7.1063799999999997</v>
       </c>
-      <c r="L29" s="1">
+      <c r="L29" s="7">
         <v>3180514.4994760752</v>
       </c>
-      <c r="M29" s="1">
+      <c r="M29" s="7">
         <v>3177.7876714136255</v>
       </c>
-      <c r="N29" s="1">
+      <c r="N29" s="7">
         <v>1036.937101525667</v>
       </c>
-      <c r="O29" s="1">
+      <c r="O29" s="7">
         <v>2140.8505698879499</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P29" s="7">
         <v>2.7742505631067962</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="Q29" s="7">
         <v>27.306709130512989</v>
       </c>
-      <c r="R29" s="1">
+      <c r="R29" s="7">
         <v>4318934.3519322164</v>
       </c>
-      <c r="S29" s="1">
+      <c r="S29" s="7">
         <v>4578185.9026988624</v>
       </c>
-      <c r="T29" s="1">
+      <c r="T29" s="7">
         <v>4796405.0544131594</v>
       </c>
-      <c r="U29" s="1">
+      <c r="U29" s="7">
         <v>4738348.3031305475</v>
       </c>
-      <c r="V29" s="1">
+      <c r="V29" s="7">
         <v>4758238.1402506679</v>
       </c>
-      <c r="W29" s="1">
+      <c r="W29" s="7">
         <v>4809184.1376743373</v>
       </c>
-      <c r="X29" s="1">
+      <c r="X29" s="7">
         <v>4955750.7589634545</v>
       </c>
-      <c r="Y29" s="1">
+      <c r="Y29" s="7">
         <v>5389662.4111107877</v>
       </c>
-      <c r="Z29" s="1">
+      <c r="Z29" s="7">
         <v>5407009.4664117061</v>
       </c>
-      <c r="AA29" s="1">
+      <c r="AA29" s="7">
         <v>4188226.4406403704</v>
       </c>
-      <c r="AB29" s="1">
+      <c r="AB29" s="7">
         <v>4545164.5038836226</v>
       </c>
-      <c r="AC29" s="1">
+      <c r="AC29" s="7">
         <v>4656890.4110062495</v>
       </c>
-      <c r="AD29" s="1">
+      <c r="AD29" s="7">
         <v>4777245.3666811706</v>
       </c>
-      <c r="AE29" s="1">
+      <c r="AE29" s="7">
         <v>4773503.444890203</v>
       </c>
-      <c r="AF29" s="1">
+      <c r="AF29" s="7">
         <v>4854986.4570637532</v>
       </c>
-      <c r="AG29" s="1">
+      <c r="AG29" s="7">
         <v>5082904.0031043841</v>
       </c>
-      <c r="AH29" s="1">
+      <c r="AH29" s="7">
         <v>5171554.8143780995</v>
       </c>
-      <c r="AI29" s="1">
+      <c r="AI29" s="7">
         <v>5159718.6699212128</v>
       </c>
     </row>
@@ -3698,7 +3739,7 @@
       <c r="D30" s="1">
         <v>38</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="2">
         <v>61.8</v>
       </c>
       <c r="F30" s="1">
@@ -3716,84 +3757,84 @@
       <c r="J30" s="1">
         <v>2</v>
       </c>
-      <c r="K30" s="1">
+      <c r="K30" s="7">
         <v>7.0480999999999998</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L30" s="7">
         <v>2671610.7896518451</v>
       </c>
-      <c r="M30" s="1">
+      <c r="M30" s="7">
         <v>2883.8468138914518</v>
       </c>
-      <c r="N30" s="1">
+      <c r="N30" s="7">
         <v>966.17031868474498</v>
       </c>
-      <c r="O30" s="1">
+      <c r="O30" s="7">
         <v>1917.6764952067015</v>
       </c>
-      <c r="P30" s="1">
+      <c r="P30" s="7">
         <v>2.7570950271889401</v>
       </c>
-      <c r="Q30" s="1">
+      <c r="Q30" s="7">
         <v>29.083545392591557</v>
       </c>
-      <c r="R30" s="1">
+      <c r="R30" s="7">
         <v>5283158.7763407324</v>
       </c>
-      <c r="S30" s="1">
+      <c r="S30" s="7">
         <v>5548715.8281203741</v>
       </c>
-      <c r="T30" s="1">
+      <c r="T30" s="7">
         <v>5573674.1769550769</v>
       </c>
-      <c r="U30" s="1">
+      <c r="U30" s="7">
         <v>5531005.6530878795</v>
       </c>
-      <c r="V30" s="1">
+      <c r="V30" s="7">
         <v>5454108.4577146899</v>
       </c>
-      <c r="W30" s="1">
+      <c r="W30" s="7">
         <v>5508922.7923121676</v>
       </c>
-      <c r="X30" s="1">
+      <c r="X30" s="7">
         <v>5759951.3880557474</v>
       </c>
-      <c r="Y30" s="1">
+      <c r="Y30" s="7">
         <v>6211898.5091345217</v>
       </c>
-      <c r="Z30" s="1">
+      <c r="Z30" s="7">
         <v>6195702.6424887301</v>
       </c>
-      <c r="AA30" s="1">
+      <c r="AA30" s="7">
         <v>5156978.0663626641</v>
       </c>
-      <c r="AB30" s="1">
+      <c r="AB30" s="7">
         <v>5424529.5605298635</v>
       </c>
-      <c r="AC30" s="1">
+      <c r="AC30" s="7">
         <v>5539846.586353939</v>
       </c>
-      <c r="AD30" s="1">
+      <c r="AD30" s="7">
         <v>5513243.1380185578</v>
       </c>
-      <c r="AE30" s="1">
+      <c r="AE30" s="7">
         <v>5519942.136834953</v>
       </c>
-      <c r="AF30" s="1">
+      <c r="AF30" s="7">
         <v>5602859.2701811101</v>
       </c>
-      <c r="AG30" s="1">
+      <c r="AG30" s="7">
         <v>5839329.5828641783</v>
       </c>
-      <c r="AH30" s="1">
+      <c r="AH30" s="7">
         <v>5969886.0379214892</v>
       </c>
-      <c r="AI30" s="1">
+      <c r="AI30" s="7">
         <v>5911155.539062188</v>
       </c>
     </row>
     <row r="31" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="A31" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B31" s="3" t="s">
@@ -3805,7 +3846,7 @@
       <c r="D31" s="4">
         <v>39</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="5">
         <v>62</v>
       </c>
       <c r="F31" s="4">
@@ -3823,79 +3864,79 @@
       <c r="J31" s="4">
         <v>50</v>
       </c>
-      <c r="K31" s="4">
+      <c r="K31" s="8">
         <v>19.027699999999999</v>
       </c>
-      <c r="L31" s="4">
+      <c r="L31" s="8">
         <v>7022890.426079019</v>
       </c>
-      <c r="M31" s="4">
+      <c r="M31" s="8">
         <v>9354.1436324102906</v>
       </c>
-      <c r="N31" s="4">
+      <c r="N31" s="8">
         <v>2586.5636361310321</v>
       </c>
-      <c r="O31" s="4">
+      <c r="O31" s="8">
         <v>6767.5799962792607</v>
       </c>
-      <c r="P31" s="4">
+      <c r="P31" s="8">
         <v>3.2867379087858448</v>
       </c>
-      <c r="Q31" s="4">
+      <c r="Q31" s="8">
         <v>42.919340891968837</v>
       </c>
-      <c r="R31" s="4">
+      <c r="R31" s="8">
         <v>14564499.419269491</v>
       </c>
-      <c r="S31" s="4">
+      <c r="S31" s="8">
         <v>18372472.335616298</v>
       </c>
-      <c r="T31" s="4">
+      <c r="T31" s="8">
         <v>21426134.606720123</v>
       </c>
-      <c r="U31" s="4">
+      <c r="U31" s="8">
         <v>23235846.558729511</v>
       </c>
-      <c r="V31" s="4">
+      <c r="V31" s="8">
         <v>23740225.589244962</v>
       </c>
-      <c r="W31" s="4">
+      <c r="W31" s="8">
         <v>23784963.934820391</v>
       </c>
-      <c r="X31" s="4">
+      <c r="X31" s="8">
         <v>23414761.038740449</v>
       </c>
-      <c r="Y31" s="4">
+      <c r="Y31" s="8">
         <v>22406575.697432149</v>
       </c>
-      <c r="Z31" s="4">
+      <c r="Z31" s="8">
         <v>20818016.432474934</v>
       </c>
-      <c r="AA31" s="4">
+      <c r="AA31" s="8">
         <v>13600797.443530602</v>
       </c>
-      <c r="AB31" s="4">
+      <c r="AB31" s="8">
         <v>17341229.654994089</v>
       </c>
-      <c r="AC31" s="4">
+      <c r="AC31" s="8">
         <v>20519932.524978552</v>
       </c>
-      <c r="AD31" s="4">
+      <c r="AD31" s="8">
         <v>22523899.063910186</v>
       </c>
-      <c r="AE31" s="4">
+      <c r="AE31" s="8">
         <v>23507198.901652865</v>
       </c>
-      <c r="AF31" s="4">
+      <c r="AF31" s="8">
         <v>23576370.132954922</v>
       </c>
-      <c r="AG31" s="4">
+      <c r="AG31" s="8">
         <v>23075203.775807016</v>
       </c>
-      <c r="AH31" s="4">
+      <c r="AH31" s="8">
         <v>22040166.045832481</v>
       </c>
-      <c r="AI31" s="4">
+      <c r="AI31" s="8">
         <v>20746788.57311007</v>
       </c>
     </row>
@@ -3912,7 +3953,7 @@
       <c r="D32" s="1">
         <v>40</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="2">
         <v>62.7</v>
       </c>
       <c r="F32" s="1">
@@ -3930,79 +3971,79 @@
       <c r="J32" s="1">
         <v>2</v>
       </c>
-      <c r="K32" s="1">
+      <c r="K32" s="7">
         <v>8.7441300000000002</v>
       </c>
-      <c r="L32" s="1">
+      <c r="L32" s="7">
         <v>3339135.2905835654</v>
       </c>
-      <c r="M32" s="1">
+      <c r="M32" s="7">
         <v>3965.2160727218111</v>
       </c>
-      <c r="N32" s="1">
+      <c r="N32" s="7">
         <v>1070.1459313975897</v>
       </c>
-      <c r="O32" s="1">
+      <c r="O32" s="7">
         <v>2891.6261324561387</v>
       </c>
-      <c r="P32" s="1">
+      <c r="P32" s="7">
         <v>2.5230832964071852</v>
       </c>
-      <c r="Q32" s="1">
+      <c r="Q32" s="7">
         <v>29.705721858198711</v>
       </c>
-      <c r="R32" s="1">
+      <c r="R32" s="7">
         <v>7021189.5945427315</v>
       </c>
-      <c r="S32" s="1">
+      <c r="S32" s="7">
         <v>7032925.0437465506</v>
       </c>
-      <c r="T32" s="1">
+      <c r="T32" s="7">
         <v>6840096.5748538552</v>
       </c>
-      <c r="U32" s="1">
+      <c r="U32" s="7">
         <v>6976495.7249158211</v>
       </c>
-      <c r="V32" s="1">
+      <c r="V32" s="7">
         <v>7478858.8305687746</v>
       </c>
-      <c r="W32" s="1">
+      <c r="W32" s="7">
         <v>8254622.7000973616</v>
       </c>
-      <c r="X32" s="1">
+      <c r="X32" s="7">
         <v>8518642.9022301454</v>
       </c>
-      <c r="Y32" s="1">
+      <c r="Y32" s="7">
         <v>8265239.2023161482</v>
       </c>
-      <c r="Z32" s="1">
+      <c r="Z32" s="7">
         <v>8182685.6374641359</v>
       </c>
-      <c r="AA32" s="1">
+      <c r="AA32" s="7">
         <v>6722648.8452255893</v>
       </c>
-      <c r="AB32" s="1">
+      <c r="AB32" s="7">
         <v>6929460.1251453608</v>
       </c>
-      <c r="AC32" s="1">
+      <c r="AC32" s="7">
         <v>7004596.7369478894</v>
       </c>
-      <c r="AD32" s="1">
+      <c r="AD32" s="7">
         <v>7145230.2521196492</v>
       </c>
-      <c r="AE32" s="1">
+      <c r="AE32" s="7">
         <v>7561931.8780226074</v>
       </c>
-      <c r="AF32" s="1">
+      <c r="AF32" s="7">
         <v>7964959.6240624124</v>
       </c>
-      <c r="AG32" s="1">
+      <c r="AG32" s="7">
         <v>8259927.5398550127</v>
       </c>
-      <c r="AH32" s="1">
+      <c r="AH32" s="7">
         <v>8347285.2786644688</v>
       </c>
-      <c r="AI32" s="1">
+      <c r="AI32" s="7">
         <v>8448971.5412744824</v>
       </c>
     </row>
@@ -4019,7 +4060,7 @@
       <c r="D33" s="1">
         <v>41</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="2">
         <v>62.8</v>
       </c>
       <c r="F33" s="1">
@@ -4037,79 +4078,79 @@
       <c r="J33" s="1">
         <v>50</v>
       </c>
-      <c r="K33" s="1">
+      <c r="K33" s="7">
         <v>22.164100000000001</v>
       </c>
-      <c r="L33" s="1">
+      <c r="L33" s="7">
         <v>13774793.600500647</v>
       </c>
-      <c r="M33" s="1">
+      <c r="M33" s="7">
         <v>8414.5327556591092</v>
       </c>
-      <c r="N33" s="1">
+      <c r="N33" s="7">
         <v>2990.2252675081181</v>
       </c>
-      <c r="O33" s="1">
+      <c r="O33" s="7">
         <v>5424.307488150991</v>
       </c>
-      <c r="P33" s="1">
+      <c r="P33" s="7">
         <v>2.4872060338393824</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="Q33" s="7">
         <v>15.087748991812042</v>
       </c>
-      <c r="R33" s="1">
+      <c r="R33" s="7">
         <v>16520670.304294983</v>
       </c>
-      <c r="S33" s="1">
+      <c r="S33" s="7">
         <v>20389145.33495611</v>
       </c>
-      <c r="T33" s="1">
+      <c r="T33" s="7">
         <v>22268432.424956154</v>
       </c>
-      <c r="U33" s="1">
+      <c r="U33" s="7">
         <v>23261565.454005692</v>
       </c>
-      <c r="V33" s="1">
+      <c r="V33" s="7">
         <v>23768527.384456813</v>
       </c>
-      <c r="W33" s="1">
+      <c r="W33" s="7">
         <v>23799468.522658873</v>
       </c>
-      <c r="X33" s="1">
+      <c r="X33" s="7">
         <v>23498383.237800695</v>
       </c>
-      <c r="Y33" s="1">
+      <c r="Y33" s="7">
         <v>23036553.388083536</v>
       </c>
-      <c r="Z33" s="1">
+      <c r="Z33" s="7">
         <v>22299627.334620021</v>
       </c>
-      <c r="AA33" s="1">
+      <c r="AA33" s="7">
         <v>15051990.8544106</v>
       </c>
-      <c r="AB33" s="1">
+      <c r="AB33" s="7">
         <v>18968700.196756277</v>
       </c>
-      <c r="AC33" s="1">
+      <c r="AC33" s="7">
         <v>21730846.081903942</v>
       </c>
-      <c r="AD33" s="1">
+      <c r="AD33" s="7">
         <v>22994039.923256416</v>
       </c>
-      <c r="AE33" s="1">
+      <c r="AE33" s="7">
         <v>23527442.898296244</v>
       </c>
-      <c r="AF33" s="1">
+      <c r="AF33" s="7">
         <v>23632683.334930059</v>
       </c>
-      <c r="AG33" s="1">
+      <c r="AG33" s="7">
         <v>23411797.367209584</v>
       </c>
-      <c r="AH33" s="1">
+      <c r="AH33" s="7">
         <v>22883316.660247687</v>
       </c>
-      <c r="AI33" s="1">
+      <c r="AI33" s="7">
         <v>22039422.991631038</v>
       </c>
     </row>
@@ -4126,7 +4167,7 @@
       <c r="D34" s="1">
         <v>42</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="2">
         <v>62.3</v>
       </c>
       <c r="F34" s="1">
@@ -4144,79 +4185,79 @@
       <c r="J34" s="1">
         <v>50</v>
       </c>
-      <c r="K34" s="1">
+      <c r="K34" s="7">
         <v>20.457000000000001</v>
       </c>
-      <c r="L34" s="1">
+      <c r="L34" s="7">
         <v>10995121.388679709</v>
       </c>
-      <c r="M34" s="1">
+      <c r="M34" s="7">
         <v>8126.3637084317643</v>
       </c>
-      <c r="N34" s="1">
+      <c r="N34" s="7">
         <v>3219.0754260457793</v>
       </c>
-      <c r="O34" s="1">
+      <c r="O34" s="7">
         <v>4907.2882823859891</v>
       </c>
-      <c r="P34" s="1">
+      <c r="P34" s="7">
         <v>3.1948889312478208</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="Q34" s="7">
         <v>23.262060325958853</v>
       </c>
-      <c r="R34" s="1">
+      <c r="R34" s="7">
         <v>12384653.139527941</v>
       </c>
-      <c r="S34" s="1">
+      <c r="S34" s="7">
         <v>15157135.186150454</v>
       </c>
-      <c r="T34" s="1">
+      <c r="T34" s="7">
         <v>16851529.786245838</v>
       </c>
-      <c r="U34" s="1">
+      <c r="U34" s="7">
         <v>17948466.780685231</v>
       </c>
-      <c r="V34" s="1">
+      <c r="V34" s="7">
         <v>18653981.27758557</v>
       </c>
-      <c r="W34" s="1">
+      <c r="W34" s="7">
         <v>18763068.306787893</v>
       </c>
-      <c r="X34" s="1">
+      <c r="X34" s="7">
         <v>18427744.858686689</v>
       </c>
-      <c r="Y34" s="1">
+      <c r="Y34" s="7">
         <v>17748948.261641663</v>
       </c>
-      <c r="Z34" s="1">
+      <c r="Z34" s="7">
         <v>16689829.939260459</v>
       </c>
-      <c r="AA34" s="1">
+      <c r="AA34" s="7">
         <v>11641092.566934165</v>
       </c>
-      <c r="AB34" s="1">
+      <c r="AB34" s="7">
         <v>14276853.568944799</v>
       </c>
-      <c r="AC34" s="1">
+      <c r="AC34" s="7">
         <v>16435124.040427146</v>
       </c>
-      <c r="AD34" s="1">
+      <c r="AD34" s="7">
         <v>17707004.445939332</v>
       </c>
-      <c r="AE34" s="1">
+      <c r="AE34" s="7">
         <v>18346729.844213136</v>
       </c>
-      <c r="AF34" s="1">
+      <c r="AF34" s="7">
         <v>18540172.931476254</v>
       </c>
-      <c r="AG34" s="1">
+      <c r="AG34" s="7">
         <v>18241924.708961684</v>
       </c>
-      <c r="AH34" s="1">
+      <c r="AH34" s="7">
         <v>17515784.026950561</v>
       </c>
-      <c r="AI34" s="1">
+      <c r="AI34" s="7">
         <v>16413808.227992432</v>
       </c>
     </row>
@@ -4233,7 +4274,7 @@
       <c r="D35" s="1">
         <v>43</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="2">
         <v>62.3</v>
       </c>
       <c r="F35" s="1">
@@ -4251,79 +4292,79 @@
       <c r="J35" s="1">
         <v>50</v>
       </c>
-      <c r="K35" s="1">
+      <c r="K35" s="7">
         <v>17.249500000000001</v>
       </c>
-      <c r="L35" s="1">
+      <c r="L35" s="7">
         <v>9013676.9808660597</v>
       </c>
-      <c r="M35" s="1">
+      <c r="M35" s="7">
         <v>8672.807183723995</v>
       </c>
-      <c r="N35" s="1">
+      <c r="N35" s="7">
         <v>4104.6438593188395</v>
       </c>
-      <c r="O35" s="1">
+      <c r="O35" s="7">
         <v>4568.1633244051554</v>
       </c>
-      <c r="P35" s="1">
+      <c r="P35" s="7">
         <v>3.6856532988855113</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="Q35" s="7">
         <v>34.935612823879616</v>
       </c>
-      <c r="R35" s="1">
+      <c r="R35" s="7">
         <v>7716866.1178349247</v>
       </c>
-      <c r="S35" s="1">
+      <c r="S35" s="7">
         <v>9172026.3715508189</v>
       </c>
-      <c r="T35" s="1">
+      <c r="T35" s="7">
         <v>10346115.624764953</v>
       </c>
-      <c r="U35" s="1">
+      <c r="U35" s="7">
         <v>10734896.384647928</v>
       </c>
-      <c r="V35" s="1">
+      <c r="V35" s="7">
         <v>10509732.036857108</v>
       </c>
-      <c r="W35" s="1">
+      <c r="W35" s="7">
         <v>10081410.995680973</v>
       </c>
-      <c r="X35" s="1">
+      <c r="X35" s="7">
         <v>9408060.6709849462</v>
       </c>
-      <c r="Y35" s="1">
+      <c r="Y35" s="7">
         <v>8483100.8443030082</v>
       </c>
-      <c r="Z35" s="1">
+      <c r="Z35" s="7">
         <v>7778228.3498302968</v>
       </c>
-      <c r="AA35" s="1">
+      <c r="AA35" s="7">
         <v>7797727.6378363138</v>
       </c>
-      <c r="AB35" s="1">
+      <c r="AB35" s="7">
         <v>8840133.9550332241</v>
       </c>
-      <c r="AC35" s="1">
+      <c r="AC35" s="7">
         <v>9892111.7986653149</v>
       </c>
-      <c r="AD35" s="1">
+      <c r="AD35" s="7">
         <v>10427282.036462983</v>
       </c>
-      <c r="AE35" s="1">
+      <c r="AE35" s="7">
         <v>10397896.271646582</v>
       </c>
-      <c r="AF35" s="1">
+      <c r="AF35" s="7">
         <v>9928429.1275524944</v>
       </c>
-      <c r="AG35" s="1">
+      <c r="AG35" s="7">
         <v>9213452.7281273976</v>
       </c>
-      <c r="AH35" s="1">
+      <c r="AH35" s="7">
         <v>8515863.3302801624</v>
       </c>
-      <c r="AI35" s="1">
+      <c r="AI35" s="7">
         <v>7842072.6704272702</v>
       </c>
     </row>
@@ -4340,7 +4381,7 @@
       <c r="D36" s="1">
         <v>44</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="2">
         <v>62</v>
       </c>
       <c r="F36" s="1">
@@ -4358,84 +4399,84 @@
       <c r="J36" s="1">
         <v>2</v>
       </c>
-      <c r="K36" s="1">
+      <c r="K36" s="7">
         <v>7.0828699999999998</v>
       </c>
-      <c r="L36" s="1">
+      <c r="L36" s="7">
         <v>2621665.3560544425</v>
       </c>
-      <c r="M36" s="1">
+      <c r="M36" s="7">
         <v>3301.3312936395978</v>
       </c>
-      <c r="N36" s="1">
+      <c r="N36" s="7">
         <v>992.27166733108652</v>
       </c>
-      <c r="O36" s="1">
+      <c r="O36" s="7">
         <v>2309.059626308504</v>
       </c>
-      <c r="P36" s="1">
+      <c r="P36" s="7">
         <v>2.4776038326454293</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="Q36" s="7">
         <v>30.587469260541845</v>
       </c>
-      <c r="R36" s="1">
+      <c r="R36" s="7">
         <v>5716706.131627663</v>
       </c>
-      <c r="S36" s="1">
+      <c r="S36" s="7">
         <v>5964611.6265115701</v>
       </c>
-      <c r="T36" s="1">
+      <c r="T36" s="7">
         <v>5742306.9588942928</v>
       </c>
-      <c r="U36" s="1">
+      <c r="U36" s="7">
         <v>5424532.7341852449</v>
       </c>
-      <c r="V36" s="1">
+      <c r="V36" s="7">
         <v>5449155.4779389594</v>
       </c>
-      <c r="W36" s="1">
+      <c r="W36" s="7">
         <v>5429756.752494798</v>
       </c>
-      <c r="X36" s="1">
+      <c r="X36" s="7">
         <v>5444393.9839938236</v>
       </c>
-      <c r="Y36" s="1">
+      <c r="Y36" s="7">
         <v>5878981.5981488265</v>
       </c>
-      <c r="Z36" s="1">
+      <c r="Z36" s="7">
         <v>6110226.8800747246</v>
       </c>
-      <c r="AA36" s="1">
+      <c r="AA36" s="7">
         <v>5691630.5550467856</v>
       </c>
-      <c r="AB36" s="1">
+      <c r="AB36" s="7">
         <v>5729477.9475819478</v>
       </c>
-      <c r="AC36" s="1">
+      <c r="AC36" s="7">
         <v>5681766.775451486</v>
       </c>
-      <c r="AD36" s="1">
+      <c r="AD36" s="7">
         <v>5591891.7831653645</v>
       </c>
-      <c r="AE36" s="1">
+      <c r="AE36" s="7">
         <v>5427143.4862164054</v>
       </c>
-      <c r="AF36" s="1">
+      <c r="AF36" s="7">
         <v>5446773.6903586145</v>
       </c>
-      <c r="AG36" s="1">
+      <c r="AG36" s="7">
         <v>5645446.7404888682</v>
       </c>
-      <c r="AH36" s="1">
+      <c r="AH36" s="7">
         <v>5758126.1831212649</v>
       </c>
-      <c r="AI36" s="1">
+      <c r="AI36" s="7">
         <v>5651701.5540369945</v>
       </c>
     </row>
     <row r="37" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="A37" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -4447,7 +4488,7 @@
       <c r="D37" s="4">
         <v>45</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="5">
         <v>62.1</v>
       </c>
       <c r="F37" s="4">
@@ -4465,79 +4506,79 @@
       <c r="J37" s="4">
         <v>2</v>
       </c>
-      <c r="K37" s="4">
+      <c r="K37" s="8">
         <v>6.7699499999999997</v>
       </c>
-      <c r="L37" s="4">
+      <c r="L37" s="8">
         <v>2480867.1303816042</v>
       </c>
-      <c r="M37" s="4">
+      <c r="M37" s="8">
         <v>3520.064665857662</v>
       </c>
-      <c r="N37" s="4">
+      <c r="N37" s="8">
         <v>983.06536552299531</v>
       </c>
-      <c r="O37" s="4">
+      <c r="O37" s="8">
         <v>2435.4651205408782</v>
       </c>
-      <c r="P37" s="4">
+      <c r="P37" s="8">
         <v>2.6438321401746729</v>
       </c>
-      <c r="Q37" s="4">
+      <c r="Q37" s="8">
         <v>36.836703082358795</v>
       </c>
-      <c r="R37" s="4">
+      <c r="R37" s="8">
         <v>4624756.6842298191</v>
       </c>
-      <c r="S37" s="4">
+      <c r="S37" s="8">
         <v>5160991.6561363349</v>
       </c>
-      <c r="T37" s="4">
+      <c r="T37" s="8">
         <v>5092393.3664262835</v>
       </c>
-      <c r="U37" s="4">
+      <c r="U37" s="8">
         <v>4852262.1629199367</v>
       </c>
-      <c r="V37" s="4">
+      <c r="V37" s="8">
         <v>4880877.2410939373</v>
       </c>
-      <c r="W37" s="4">
+      <c r="W37" s="8">
         <v>4856901.695897256</v>
       </c>
-      <c r="X37" s="4">
+      <c r="X37" s="8">
         <v>4836744.5962215923</v>
       </c>
-      <c r="Y37" s="4">
+      <c r="Y37" s="8">
         <v>5123809.6243605334</v>
       </c>
-      <c r="Z37" s="4">
+      <c r="Z37" s="8">
         <v>5497617.1097832574</v>
       </c>
-      <c r="AA37" s="4">
+      <c r="AA37" s="8">
         <v>4616447.683808811</v>
       </c>
-      <c r="AB37" s="4">
+      <c r="AB37" s="8">
         <v>4847322.5456711715</v>
       </c>
-      <c r="AC37" s="4">
+      <c r="AC37" s="8">
         <v>5001867.5225344561</v>
       </c>
-      <c r="AD37" s="4">
+      <c r="AD37" s="8">
         <v>4984392.354930372</v>
       </c>
-      <c r="AE37" s="4">
+      <c r="AE37" s="8">
         <v>4854580.8209060226</v>
       </c>
-      <c r="AF37" s="4">
+      <c r="AF37" s="8">
         <v>4858710.7043061452</v>
       </c>
-      <c r="AG37" s="4">
+      <c r="AG37" s="8">
         <v>4986786.7841244377</v>
       </c>
-      <c r="AH37" s="4">
+      <c r="AH37" s="8">
         <v>5146049.7714897878</v>
       </c>
-      <c r="AI37" s="4">
+      <c r="AI37" s="8">
         <v>5158805.6665792083</v>
       </c>
     </row>
@@ -4554,7 +4595,7 @@
       <c r="D38" s="1">
         <v>46</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38" s="2">
         <v>62.3</v>
       </c>
       <c r="F38" s="1">
@@ -4572,79 +4613,79 @@
       <c r="J38" s="1">
         <v>2</v>
       </c>
-      <c r="K38" s="1">
+      <c r="K38" s="7">
         <v>8.4647900000000007</v>
       </c>
-      <c r="L38" s="1">
+      <c r="L38" s="7">
         <v>3803766.2860225569</v>
       </c>
-      <c r="M38" s="1">
+      <c r="M38" s="7">
         <v>3088.9976533113318</v>
       </c>
-      <c r="N38" s="1">
+      <c r="N38" s="7">
         <v>1049.1504922288079</v>
       </c>
-      <c r="O38" s="1">
+      <c r="O38" s="7">
         <v>2039.8471610825211</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P38" s="7">
         <v>2.3996702147163118</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="Q38" s="7">
         <v>19.197801634546156</v>
       </c>
-      <c r="R38" s="1">
+      <c r="R38" s="7">
         <v>6615639.3649493381</v>
       </c>
-      <c r="S38" s="1">
+      <c r="S38" s="7">
         <v>6612447.3190191519</v>
       </c>
-      <c r="T38" s="1">
+      <c r="T38" s="7">
         <v>6419622.468957888</v>
       </c>
-      <c r="U38" s="1">
+      <c r="U38" s="7">
         <v>6578706.7847090364</v>
       </c>
-      <c r="V38" s="1">
+      <c r="V38" s="7">
         <v>6774377.4661938148</v>
       </c>
-      <c r="W38" s="1">
+      <c r="W38" s="7">
         <v>7507132.8284019567</v>
       </c>
-      <c r="X38" s="1">
+      <c r="X38" s="7">
         <v>8154977.9727540379</v>
       </c>
-      <c r="Y38" s="1">
+      <c r="Y38" s="7">
         <v>7813406.2701453101</v>
       </c>
-      <c r="Z38" s="1">
+      <c r="Z38" s="7">
         <v>8027024.2358484566</v>
       </c>
-      <c r="AA38" s="1">
+      <c r="AA38" s="7">
         <v>6319199.8917948417</v>
       </c>
-      <c r="AB38" s="1">
+      <c r="AB38" s="7">
         <v>6516157.1213366296</v>
       </c>
-      <c r="AC38" s="1">
+      <c r="AC38" s="7">
         <v>6595533.9008385437</v>
       </c>
-      <c r="AD38" s="1">
+      <c r="AD38" s="7">
         <v>6592230.7122824453</v>
       </c>
-      <c r="AE38" s="1">
+      <c r="AE38" s="7">
         <v>7012322.5918248612</v>
       </c>
-      <c r="AF38" s="1">
+      <c r="AF38" s="7">
         <v>7400841.816895647</v>
       </c>
-      <c r="AG38" s="1">
+      <c r="AG38" s="7">
         <v>7657208.1876428854</v>
       </c>
-      <c r="AH38" s="1">
+      <c r="AH38" s="7">
         <v>8090495.2287434191</v>
       </c>
-      <c r="AI38" s="1">
+      <c r="AI38" s="7">
         <v>8004231.9579842826</v>
       </c>
     </row>
@@ -4661,7 +4702,7 @@
       <c r="D39" s="1">
         <v>47</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="2">
         <v>62.2</v>
       </c>
       <c r="F39" s="1">
@@ -4679,79 +4720,79 @@
       <c r="J39" s="1">
         <v>2</v>
       </c>
-      <c r="K39" s="1">
+      <c r="K39" s="7">
         <v>7.8396999999999997</v>
       </c>
-      <c r="L39" s="1">
+      <c r="L39" s="7">
         <v>3269378.5838507819</v>
       </c>
-      <c r="M39" s="1">
+      <c r="M39" s="7">
         <v>3479.901103998021</v>
       </c>
-      <c r="N39" s="1">
+      <c r="N39" s="7">
         <v>1145.1357865881992</v>
       </c>
-      <c r="O39" s="1">
+      <c r="O39" s="7">
         <v>2334.7653174098427</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P39" s="7">
         <v>2.6243921885574575</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="Q39" s="7">
         <v>27.474446268526243</v>
       </c>
-      <c r="R39" s="1">
+      <c r="R39" s="7">
         <v>4915335.6233765967</v>
       </c>
-      <c r="S39" s="1">
+      <c r="S39" s="7">
         <v>5046520.6806103829</v>
       </c>
-      <c r="T39" s="1">
+      <c r="T39" s="7">
         <v>5082922.3900978044</v>
       </c>
-      <c r="U39" s="1">
+      <c r="U39" s="7">
         <v>5158361.2292961301</v>
       </c>
-      <c r="V39" s="1">
+      <c r="V39" s="7">
         <v>5032038.9982632101</v>
       </c>
-      <c r="W39" s="1">
+      <c r="W39" s="7">
         <v>5163971.3951856038</v>
       </c>
-      <c r="X39" s="1">
+      <c r="X39" s="7">
         <v>5719994.1736042183</v>
       </c>
-      <c r="Y39" s="1">
+      <c r="Y39" s="7">
         <v>6025164.8664352242</v>
       </c>
-      <c r="Z39" s="1">
+      <c r="Z39" s="7">
         <v>5737105.7403750224</v>
       </c>
-      <c r="AA39" s="1">
+      <c r="AA39" s="7">
         <v>4428800.682120583</v>
       </c>
-      <c r="AB39" s="1">
+      <c r="AB39" s="7">
         <v>4997724.4958542939</v>
       </c>
-      <c r="AC39" s="1">
+      <c r="AC39" s="7">
         <v>5101828.0959098712</v>
       </c>
-      <c r="AD39" s="1">
+      <c r="AD39" s="7">
         <v>5057352.7095315708</v>
       </c>
-      <c r="AE39" s="1">
+      <c r="AE39" s="7">
         <v>5161164.7876842348</v>
       </c>
-      <c r="AF39" s="1">
+      <c r="AF39" s="7">
         <v>5354007.617224576</v>
       </c>
-      <c r="AG39" s="1">
+      <c r="AG39" s="7">
         <v>5561426.4218535358</v>
       </c>
-      <c r="AH39" s="1">
+      <c r="AH39" s="7">
         <v>5728537.1786373518</v>
       </c>
-      <c r="AI39" s="1">
+      <c r="AI39" s="7">
         <v>5920370.0864540292</v>
       </c>
     </row>
@@ -4768,7 +4809,7 @@
       <c r="D40" s="1">
         <v>48</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40" s="2">
         <v>62.1</v>
       </c>
       <c r="F40" s="1">
@@ -4786,79 +4827,79 @@
       <c r="J40" s="1">
         <v>50</v>
       </c>
-      <c r="K40" s="1">
+      <c r="K40" s="7">
         <v>22.236899999999999</v>
       </c>
-      <c r="L40" s="1">
+      <c r="L40" s="7">
         <v>12821434.540656574</v>
       </c>
-      <c r="M40" s="1">
+      <c r="M40" s="7">
         <v>8360.6408984512618</v>
       </c>
-      <c r="N40" s="1">
+      <c r="N40" s="7">
         <v>2789.7402537226467</v>
       </c>
-      <c r="O40" s="1">
+      <c r="O40" s="7">
         <v>5570.9006447286165</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P40" s="7">
         <v>2.2888512741369218</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="Q40" s="7">
         <v>14.656162230039023</v>
       </c>
-      <c r="R40" s="1">
+      <c r="R40" s="7">
         <v>20617189.041073393</v>
       </c>
-      <c r="S40" s="1">
+      <c r="S40" s="7">
         <v>24910485.821468063</v>
       </c>
-      <c r="T40" s="1">
+      <c r="T40" s="7">
         <v>26893948.200220492</v>
       </c>
-      <c r="U40" s="1">
+      <c r="U40" s="7">
         <v>28447559.581207551</v>
       </c>
-      <c r="V40" s="1">
+      <c r="V40" s="7">
         <v>29349756.03419983</v>
       </c>
-      <c r="W40" s="1">
+      <c r="W40" s="7">
         <v>28964469.200971235</v>
       </c>
-      <c r="X40" s="1">
+      <c r="X40" s="7">
         <v>28061015.521725744</v>
       </c>
-      <c r="Y40" s="1">
+      <c r="Y40" s="7">
         <v>26768499.768480044</v>
       </c>
-      <c r="Z40" s="1">
+      <c r="Z40" s="7">
         <v>24662731.174240571</v>
       </c>
-      <c r="AA40" s="1">
+      <c r="AA40" s="7">
         <v>19166604.184619717</v>
       </c>
-      <c r="AB40" s="1">
+      <c r="AB40" s="7">
         <v>23340953.144891765</v>
       </c>
-      <c r="AC40" s="1">
+      <c r="AC40" s="7">
         <v>26561787.421377473</v>
       </c>
-      <c r="AD40" s="1">
+      <c r="AD40" s="7">
         <v>28068237.297564771</v>
       </c>
-      <c r="AE40" s="1">
+      <c r="AE40" s="7">
         <v>28703687.391324084</v>
       </c>
-      <c r="AF40" s="1">
+      <c r="AF40" s="7">
         <v>28690921.139503136</v>
       </c>
-      <c r="AG40" s="1">
+      <c r="AG40" s="7">
         <v>27823222.104866788</v>
       </c>
-      <c r="AH40" s="1">
+      <c r="AH40" s="7">
         <v>26252355.936664149</v>
       </c>
-      <c r="AI40" s="1">
+      <c r="AI40" s="7">
         <v>24407998.83458082</v>
       </c>
     </row>
@@ -4875,7 +4916,7 @@
       <c r="D41" s="1">
         <v>49</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="2">
         <v>62.6</v>
       </c>
       <c r="F41" s="1">
@@ -4893,79 +4934,79 @@
       <c r="J41" s="1">
         <v>50</v>
       </c>
-      <c r="K41" s="1">
+      <c r="K41" s="7">
         <v>22.095300000000002</v>
       </c>
-      <c r="L41" s="1">
+      <c r="L41" s="7">
         <v>13239308.233491598</v>
       </c>
-      <c r="M41" s="1">
+      <c r="M41" s="7">
         <v>7402.1200787673069</v>
       </c>
-      <c r="N41" s="1">
+      <c r="N41" s="7">
         <v>2570.6141445718226</v>
       </c>
-      <c r="O41" s="1">
+      <c r="O41" s="7">
         <v>4831.5059341954848</v>
       </c>
-      <c r="P41" s="1">
+      <c r="P41" s="7">
         <v>2.182746226946878</v>
       </c>
-      <c r="Q41" s="1">
+      <c r="Q41" s="7">
         <v>12.080267487645834</v>
       </c>
-      <c r="R41" s="1">
+      <c r="R41" s="7">
         <v>23824186.721275944</v>
       </c>
-      <c r="S41" s="1">
+      <c r="S41" s="7">
         <v>26885271.884598233</v>
       </c>
-      <c r="T41" s="1">
+      <c r="T41" s="7">
         <v>29303825.280330651</v>
       </c>
-      <c r="U41" s="1">
+      <c r="U41" s="7">
         <v>30663130.797560215</v>
       </c>
-      <c r="V41" s="1">
+      <c r="V41" s="7">
         <v>30885504.639102306</v>
       </c>
-      <c r="W41" s="1">
+      <c r="W41" s="7">
         <v>30770489.46572924</v>
       </c>
-      <c r="X41" s="1">
+      <c r="X41" s="7">
         <v>29767757.696044758</v>
       </c>
-      <c r="Y41" s="1">
+      <c r="Y41" s="7">
         <v>28201675.209870659</v>
       </c>
-      <c r="Z41" s="1">
+      <c r="Z41" s="7">
         <v>26507470.010199651</v>
       </c>
-      <c r="AA41" s="1">
+      <c r="AA41" s="7">
         <v>21773189.002298653</v>
       </c>
-      <c r="AB41" s="1">
+      <c r="AB41" s="7">
         <v>26281420.246070266</v>
       </c>
-      <c r="AC41" s="1">
+      <c r="AC41" s="7">
         <v>28650199.480896659</v>
       </c>
-      <c r="AD41" s="1">
+      <c r="AD41" s="7">
         <v>30073882.957347352</v>
       </c>
-      <c r="AE41" s="1">
+      <c r="AE41" s="7">
         <v>30716716.32402293</v>
       </c>
-      <c r="AF41" s="1">
+      <c r="AF41" s="7">
         <v>30316331.983485036</v>
       </c>
-      <c r="AG41" s="1">
+      <c r="AG41" s="7">
         <v>29430133.851616666</v>
       </c>
-      <c r="AH41" s="1">
+      <c r="AH41" s="7">
         <v>28043171.980314881</v>
       </c>
-      <c r="AI41" s="1">
+      <c r="AI41" s="7">
         <v>25806179.783761524</v>
       </c>
     </row>
@@ -4982,7 +5023,7 @@
       <c r="D42" s="1">
         <v>50</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="2">
         <v>62.5</v>
       </c>
       <c r="F42" s="1">
@@ -5000,84 +5041,84 @@
       <c r="J42" s="1">
         <v>2</v>
       </c>
-      <c r="K42" s="1">
+      <c r="K42" s="7">
         <v>7.0903</v>
       </c>
-      <c r="L42" s="1">
+      <c r="L42" s="7">
         <v>2819389.5368008753</v>
       </c>
-      <c r="M42" s="1">
+      <c r="M42" s="7">
         <v>3098.927407558896</v>
       </c>
-      <c r="N42" s="1">
+      <c r="N42" s="7">
         <v>1091.2363029071307</v>
       </c>
-      <c r="O42" s="1">
+      <c r="O42" s="7">
         <v>2007.6911046517723</v>
       </c>
-      <c r="P42" s="1">
+      <c r="P42" s="7">
         <v>2.7379041903669723</v>
       </c>
-      <c r="Q42" s="1">
+      <c r="Q42" s="7">
         <v>29.741489978916533</v>
       </c>
-      <c r="R42" s="1">
+      <c r="R42" s="7">
         <v>3570255.9524934217</v>
       </c>
-      <c r="S42" s="1">
+      <c r="S42" s="7">
         <v>4139684.8328299583</v>
       </c>
-      <c r="T42" s="1">
+      <c r="T42" s="7">
         <v>4318807.4169193963</v>
       </c>
-      <c r="U42" s="1">
+      <c r="U42" s="7">
         <v>4539250.8112525865</v>
       </c>
-      <c r="V42" s="1">
+      <c r="V42" s="7">
         <v>4656418.9470688608</v>
       </c>
-      <c r="W42" s="1">
+      <c r="W42" s="7">
         <v>4835989.7395674232</v>
       </c>
-      <c r="X42" s="1">
+      <c r="X42" s="7">
         <v>5128336.2655317197</v>
       </c>
-      <c r="Y42" s="1">
+      <c r="Y42" s="7">
         <v>5491016.83402324</v>
       </c>
-      <c r="Z42" s="1">
+      <c r="Z42" s="7">
         <v>5417947.8042557938</v>
       </c>
-      <c r="AA42" s="1">
+      <c r="AA42" s="7">
         <v>3557015.7757092132</v>
       </c>
-      <c r="AB42" s="1">
+      <c r="AB42" s="7">
         <v>3909018.6416076068</v>
       </c>
-      <c r="AC42" s="1">
+      <c r="AC42" s="7">
         <v>4330270.0944822663</v>
       </c>
-      <c r="AD42" s="1">
+      <c r="AD42" s="7">
         <v>4481263.3953331932</v>
       </c>
-      <c r="AE42" s="1">
+      <c r="AE42" s="7">
         <v>4682924.183021755</v>
       </c>
-      <c r="AF42" s="1">
+      <c r="AF42" s="7">
         <v>4880997.3545399606</v>
       </c>
-      <c r="AG42" s="1">
+      <c r="AG42" s="7">
         <v>5142729.5760683306</v>
       </c>
-      <c r="AH42" s="1">
+      <c r="AH42" s="7">
         <v>5269165.5232235277</v>
       </c>
-      <c r="AI42" s="1">
+      <c r="AI42" s="7">
         <v>5158529.3078017952</v>
       </c>
     </row>
     <row r="43" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="A43" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
@@ -5089,7 +5130,7 @@
       <c r="D43" s="4">
         <v>51</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E43" s="5">
         <v>62.1</v>
       </c>
       <c r="F43" s="4">
@@ -5107,79 +5148,79 @@
       <c r="J43" s="4">
         <v>50</v>
       </c>
-      <c r="K43" s="4">
+      <c r="K43" s="8">
         <v>22.9084</v>
       </c>
-      <c r="L43" s="4">
+      <c r="L43" s="8">
         <v>14070910.20791259</v>
       </c>
-      <c r="M43" s="4">
+      <c r="M43" s="8">
         <v>7970.5635310402276</v>
       </c>
-      <c r="N43" s="4">
+      <c r="N43" s="8">
         <v>2872.6164016237276</v>
       </c>
-      <c r="O43" s="4">
+      <c r="O43" s="8">
         <v>5097.947129416496</v>
       </c>
-      <c r="P43" s="4">
+      <c r="P43" s="8">
         <v>2.2410779712801707</v>
       </c>
-      <c r="Q43" s="4">
+      <c r="Q43" s="8">
         <v>12.465897216980823</v>
       </c>
-      <c r="R43" s="4">
+      <c r="R43" s="8">
         <v>21329601.011923406</v>
       </c>
-      <c r="S43" s="4">
+      <c r="S43" s="8">
         <v>24806292.677894004</v>
       </c>
-      <c r="T43" s="4">
+      <c r="T43" s="8">
         <v>26600717.766339172</v>
       </c>
-      <c r="U43" s="4">
+      <c r="U43" s="8">
         <v>27862209.267208509</v>
       </c>
-      <c r="V43" s="4">
+      <c r="V43" s="8">
         <v>28471820.051205147</v>
       </c>
-      <c r="W43" s="4">
+      <c r="W43" s="8">
         <v>28223401.637579914</v>
       </c>
-      <c r="X43" s="4">
+      <c r="X43" s="8">
         <v>27601460.318577018</v>
       </c>
-      <c r="Y43" s="4">
+      <c r="Y43" s="8">
         <v>26238073.194407832</v>
       </c>
-      <c r="Z43" s="4">
+      <c r="Z43" s="8">
         <v>24396053.559813514</v>
       </c>
-      <c r="AA43" s="4">
+      <c r="AA43" s="8">
         <v>19512253.207675792</v>
       </c>
-      <c r="AB43" s="4">
+      <c r="AB43" s="8">
         <v>23675314.959270295</v>
       </c>
-      <c r="AC43" s="4">
+      <c r="AC43" s="8">
         <v>26245596.218229767</v>
       </c>
-      <c r="AD43" s="4">
+      <c r="AD43" s="8">
         <v>27504483.341053911</v>
       </c>
-      <c r="AE43" s="4">
+      <c r="AE43" s="8">
         <v>28041642.409625221</v>
       </c>
-      <c r="AF43" s="4">
+      <c r="AF43" s="8">
         <v>28029885.398483142</v>
       </c>
-      <c r="AG43" s="4">
+      <c r="AG43" s="8">
         <v>27194551.019651987</v>
       </c>
-      <c r="AH43" s="4">
+      <c r="AH43" s="8">
         <v>25899957.672434583</v>
       </c>
-      <c r="AI43" s="4">
+      <c r="AI43" s="8">
         <v>24208235.159901697</v>
       </c>
     </row>
@@ -5196,7 +5237,7 @@
       <c r="D44" s="1">
         <v>52</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="2">
         <v>63.7</v>
       </c>
       <c r="F44" s="1">
@@ -5214,79 +5255,79 @@
       <c r="J44" s="1">
         <v>50</v>
       </c>
-      <c r="K44" s="1">
+      <c r="K44" s="7">
         <v>12.171200000000001</v>
       </c>
-      <c r="L44" s="1">
+      <c r="L44" s="7">
         <v>2485373.5454068929</v>
       </c>
-      <c r="M44" s="1">
+      <c r="M44" s="7">
         <v>8945.1902284243679</v>
       </c>
-      <c r="N44" s="1">
+      <c r="N44" s="7">
         <v>2351.5274025478657</v>
       </c>
-      <c r="O44" s="1">
+      <c r="O44" s="7">
         <v>6593.6628258765022</v>
       </c>
-      <c r="P44" s="1">
+      <c r="P44" s="7">
         <v>4.0880093770462791</v>
       </c>
-      <c r="Q44" s="1">
+      <c r="Q44" s="7">
         <v>148.20312585529925</v>
       </c>
-      <c r="R44" s="1">
+      <c r="R44" s="7">
         <v>7368595.0827067113</v>
       </c>
-      <c r="S44" s="1">
+      <c r="S44" s="7">
         <v>8104622.0805955464</v>
       </c>
-      <c r="T44" s="1">
+      <c r="T44" s="7">
         <v>9089755.8051330578</v>
       </c>
-      <c r="U44" s="1">
+      <c r="U44" s="7">
         <v>10286241.580829632</v>
       </c>
-      <c r="V44" s="1">
+      <c r="V44" s="7">
         <v>11097463.275339933</v>
       </c>
-      <c r="W44" s="1">
+      <c r="W44" s="7">
         <v>11406329.323549455</v>
       </c>
-      <c r="X44" s="1">
+      <c r="X44" s="7">
         <v>11240890.845652014</v>
       </c>
-      <c r="Y44" s="1">
+      <c r="Y44" s="7">
         <v>10624966.16747372</v>
       </c>
-      <c r="Z44" s="1">
+      <c r="Z44" s="7">
         <v>9759611.9420525935</v>
       </c>
-      <c r="AA44" s="1">
+      <c r="AA44" s="7">
         <v>7391345.617284487</v>
       </c>
-      <c r="AB44" s="1">
+      <c r="AB44" s="7">
         <v>8139178.753102825</v>
       </c>
-      <c r="AC44" s="1">
+      <c r="AC44" s="7">
         <v>9066034.328468455</v>
       </c>
-      <c r="AD44" s="1">
+      <c r="AD44" s="7">
         <v>9993771.8838001117</v>
       </c>
-      <c r="AE44" s="1">
+      <c r="AE44" s="7">
         <v>10817367.797456006</v>
       </c>
-      <c r="AF44" s="1">
+      <c r="AF44" s="7">
         <v>11168716.608758701</v>
       </c>
-      <c r="AG44" s="1">
+      <c r="AG44" s="7">
         <v>11001791.810849883</v>
       </c>
-      <c r="AH44" s="1">
+      <c r="AH44" s="7">
         <v>10448010.092478953</v>
       </c>
-      <c r="AI44" s="1">
+      <c r="AI44" s="7">
         <v>9410458.6199755426</v>
       </c>
     </row>
@@ -5303,7 +5344,7 @@
       <c r="D45" s="1">
         <v>53</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45" s="2">
         <v>64</v>
       </c>
       <c r="F45" s="1">
@@ -5321,79 +5362,79 @@
       <c r="J45" s="1">
         <v>2</v>
       </c>
-      <c r="K45" s="1">
+      <c r="K45" s="7">
         <v>4.1768099999999997</v>
       </c>
-      <c r="L45" s="1">
+      <c r="L45" s="7">
         <v>688115.20423775527</v>
       </c>
-      <c r="M45" s="1">
+      <c r="M45" s="7">
         <v>3110.3176470119352</v>
       </c>
-      <c r="N45" s="1">
+      <c r="N45" s="7">
         <v>734.60217659986904</v>
       </c>
-      <c r="O45" s="1">
+      <c r="O45" s="7">
         <v>2237.2946566467467</v>
       </c>
-      <c r="P45" s="1">
+      <c r="P45" s="7">
         <v>3.7774116000000002</v>
       </c>
-      <c r="Q45" s="1">
+      <c r="Q45" s="7">
         <v>172.79294750851892</v>
       </c>
-      <c r="R45" s="1">
+      <c r="R45" s="7">
         <v>3289154.9958040938</v>
       </c>
-      <c r="S45" s="1">
+      <c r="S45" s="7">
         <v>3302493.2577868439</v>
       </c>
-      <c r="T45" s="1">
+      <c r="T45" s="7">
         <v>3375564.5642253975</v>
       </c>
-      <c r="U45" s="1">
+      <c r="U45" s="7">
         <v>3521495.3771428051</v>
       </c>
-      <c r="V45" s="1">
+      <c r="V45" s="7">
         <v>3617634.9236298907</v>
       </c>
-      <c r="W45" s="1">
+      <c r="W45" s="7">
         <v>3503560.9846564014</v>
       </c>
-      <c r="X45" s="1">
+      <c r="X45" s="7">
         <v>3204250.3611923382</v>
       </c>
-      <c r="Y45" s="1">
+      <c r="Y45" s="7">
         <v>3097233.7390528522</v>
       </c>
-      <c r="Z45" s="1">
+      <c r="Z45" s="7">
         <v>2928586.8324428592</v>
       </c>
-      <c r="AA45" s="1">
+      <c r="AA45" s="7">
         <v>3236211.350756248</v>
       </c>
-      <c r="AB45" s="1">
+      <c r="AB45" s="7">
         <v>3331799.6203975626</v>
       </c>
-      <c r="AC45" s="1">
+      <c r="AC45" s="7">
         <v>3408480.1023299326</v>
       </c>
-      <c r="AD45" s="1">
+      <c r="AD45" s="7">
         <v>3492410.0980435261</v>
       </c>
-      <c r="AE45" s="1">
+      <c r="AE45" s="7">
         <v>3512505.2883833521</v>
       </c>
-      <c r="AF45" s="1">
+      <c r="AF45" s="7">
         <v>3398417.7472152151</v>
       </c>
-      <c r="AG45" s="1">
+      <c r="AG45" s="7">
         <v>3287891.1533274371</v>
       </c>
-      <c r="AH45" s="1">
+      <c r="AH45" s="7">
         <v>3060223.2276366362</v>
       </c>
-      <c r="AI45" s="1">
+      <c r="AI45" s="7">
         <v>2834733.4732353063</v>
       </c>
     </row>
@@ -5410,7 +5451,7 @@
       <c r="D46" s="1">
         <v>54</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="2">
         <v>64.2</v>
       </c>
       <c r="F46" s="1">
@@ -5428,79 +5469,79 @@
       <c r="J46" s="1">
         <v>2</v>
       </c>
-      <c r="K46" s="1">
+      <c r="K46" s="7">
         <v>4.4995399999999997</v>
       </c>
-      <c r="L46" s="1">
+      <c r="L46" s="7">
         <v>912048.01434086659</v>
       </c>
-      <c r="M46" s="1">
+      <c r="M46" s="7">
         <v>3659.9706429863072</v>
       </c>
-      <c r="N46" s="1">
+      <c r="N46" s="7">
         <v>953.53942130542521</v>
       </c>
-      <c r="O46" s="1">
+      <c r="O46" s="7">
         <v>2706.4312216808748</v>
       </c>
-      <c r="P46" s="1">
+      <c r="P46" s="7">
         <v>4.3668016979695423</v>
       </c>
-      <c r="Q46" s="1">
+      <c r="Q46" s="7">
         <v>177.89614499610326</v>
       </c>
-      <c r="R46" s="1">
+      <c r="R46" s="7">
         <v>2911948.4198610731</v>
       </c>
-      <c r="S46" s="1">
+      <c r="S46" s="7">
         <v>3084781.1672399244</v>
       </c>
-      <c r="T46" s="1">
+      <c r="T46" s="7">
         <v>3257852.4132065098</v>
       </c>
-      <c r="U46" s="1">
+      <c r="U46" s="7">
         <v>3226025.6896725707</v>
       </c>
-      <c r="V46" s="1">
+      <c r="V46" s="7">
         <v>3182281.2275018408</v>
       </c>
-      <c r="W46" s="1">
+      <c r="W46" s="7">
         <v>3149070.8329087184</v>
       </c>
-      <c r="X46" s="1">
+      <c r="X46" s="7">
         <v>3066204.1829323946</v>
       </c>
-      <c r="Y46" s="1">
+      <c r="Y46" s="7">
         <v>2905750.1969258063</v>
       </c>
-      <c r="Z46" s="1">
+      <c r="Z46" s="7">
         <v>2646148.4262643871</v>
       </c>
-      <c r="AA46" s="1">
+      <c r="AA46" s="7">
         <v>2961635.3500916837</v>
       </c>
-      <c r="AB46" s="1">
+      <c r="AB46" s="7">
         <v>3075204.0279590543</v>
       </c>
-      <c r="AC46" s="1">
+      <c r="AC46" s="7">
         <v>3153822.8052832074</v>
       </c>
-      <c r="AD46" s="1">
+      <c r="AD46" s="7">
         <v>3219623.4286151663</v>
       </c>
-      <c r="AE46" s="1">
+      <c r="AE46" s="7">
         <v>3187083.7938148533</v>
       </c>
-      <c r="AF46" s="1">
+      <c r="AF46" s="7">
         <v>3123164.5335170226</v>
       </c>
-      <c r="AG46" s="1">
+      <c r="AG46" s="7">
         <v>3022521.4412680664</v>
       </c>
-      <c r="AH46" s="1">
+      <c r="AH46" s="7">
         <v>2840731.9814988454</v>
       </c>
-      <c r="AI46" s="1">
+      <c r="AI46" s="7">
         <v>2638966.0101114721</v>
       </c>
     </row>
@@ -5517,7 +5558,7 @@
       <c r="D47" s="1">
         <v>55</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="2">
         <v>63.9</v>
       </c>
       <c r="F47" s="1">
@@ -5535,79 +5576,79 @@
       <c r="J47" s="1">
         <v>50</v>
       </c>
-      <c r="K47" s="1">
+      <c r="K47" s="7">
         <v>10.9636</v>
       </c>
-      <c r="L47" s="1">
+      <c r="L47" s="7">
         <v>1785082.4133718868</v>
       </c>
-      <c r="M47" s="1">
+      <c r="M47" s="7">
         <v>8736.0134118096594</v>
       </c>
-      <c r="N47" s="1">
+      <c r="N47" s="7">
         <v>2012.1472284042168</v>
       </c>
-      <c r="O47" s="1">
+      <c r="O47" s="7">
         <v>6723.866183405441</v>
       </c>
-      <c r="P47" s="1">
+      <c r="P47" s="7">
         <v>4.2474981800331353</v>
       </c>
-      <c r="Q47" s="1">
+      <c r="Q47" s="7">
         <v>210.03768315917927</v>
       </c>
-      <c r="R47" s="1">
+      <c r="R47" s="7">
         <v>6674574.4053165913</v>
       </c>
-      <c r="S47" s="1">
+      <c r="S47" s="7">
         <v>7160457.3228066321</v>
       </c>
-      <c r="T47" s="1">
+      <c r="T47" s="7">
         <v>7728808.7218564879</v>
       </c>
-      <c r="U47" s="1">
+      <c r="U47" s="7">
         <v>8486416.826967882</v>
       </c>
-      <c r="V47" s="1">
+      <c r="V47" s="7">
         <v>9367437.7245363146</v>
       </c>
-      <c r="W47" s="1">
+      <c r="W47" s="7">
         <v>9949648.82957552</v>
       </c>
-      <c r="X47" s="1">
+      <c r="X47" s="7">
         <v>10163319.462646458</v>
       </c>
-      <c r="Y47" s="1">
+      <c r="Y47" s="7">
         <v>9857397.5546569899</v>
       </c>
-      <c r="Z47" s="1">
+      <c r="Z47" s="7">
         <v>9052160.8614019658</v>
       </c>
-      <c r="AA47" s="1">
+      <c r="AA47" s="7">
         <v>6712909.1773715196</v>
       </c>
-      <c r="AB47" s="1">
+      <c r="AB47" s="7">
         <v>7163110.0031171255</v>
       </c>
-      <c r="AC47" s="1">
+      <c r="AC47" s="7">
         <v>7767254.3322561709</v>
       </c>
-      <c r="AD47" s="1">
+      <c r="AD47" s="7">
         <v>8469594.1432359871</v>
       </c>
-      <c r="AE47" s="1">
+      <c r="AE47" s="7">
         <v>9159965.9952135514</v>
       </c>
-      <c r="AF47" s="1">
+      <c r="AF47" s="7">
         <v>9749162.4342539255</v>
       </c>
-      <c r="AG47" s="1">
+      <c r="AG47" s="7">
         <v>9903308.362061359</v>
       </c>
-      <c r="AH47" s="1">
+      <c r="AH47" s="7">
         <v>9575613.1109097414</v>
       </c>
-      <c r="AI47" s="1">
+      <c r="AI47" s="7">
         <v>8833693.1389480382</v>
       </c>
     </row>
@@ -5624,7 +5665,7 @@
       <c r="D48" s="1">
         <v>56</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="2">
         <v>64</v>
       </c>
       <c r="F48" s="1">
@@ -5642,84 +5683,84 @@
       <c r="J48" s="1">
         <v>50</v>
       </c>
-      <c r="K48" s="1">
+      <c r="K48" s="7">
         <v>11.0039</v>
       </c>
-      <c r="L48" s="1">
+      <c r="L48" s="7">
         <v>2019588.0576748007</v>
       </c>
-      <c r="M48" s="1">
+      <c r="M48" s="7">
         <v>8827.3102934627768</v>
       </c>
-      <c r="N48" s="1">
+      <c r="N48" s="7">
         <v>2201.0851653530945</v>
       </c>
-      <c r="O48" s="1">
+      <c r="O48" s="7">
         <v>6626.2251281096833</v>
       </c>
-      <c r="P48" s="1">
+      <c r="P48" s="7">
         <v>4.4880375757575761</v>
       </c>
-      <c r="Q48" s="1">
+      <c r="Q48" s="7">
         <v>198.52271048898456</v>
       </c>
-      <c r="R48" s="1">
+      <c r="R48" s="7">
         <v>5857856.9245789368</v>
       </c>
-      <c r="S48" s="1">
+      <c r="S48" s="7">
         <v>6404749.804121892</v>
       </c>
-      <c r="T48" s="1">
+      <c r="T48" s="7">
         <v>7056616.3187402152</v>
       </c>
-      <c r="U48" s="1">
+      <c r="U48" s="7">
         <v>7788487.7426890507</v>
       </c>
-      <c r="V48" s="1">
+      <c r="V48" s="7">
         <v>8640697.414637696</v>
       </c>
-      <c r="W48" s="1">
+      <c r="W48" s="7">
         <v>9168888.3523143362</v>
       </c>
-      <c r="X48" s="1">
+      <c r="X48" s="7">
         <v>9168745.8980706763</v>
       </c>
-      <c r="Y48" s="1">
+      <c r="Y48" s="7">
         <v>8892208.0190559421</v>
       </c>
-      <c r="Z48" s="1">
+      <c r="Z48" s="7">
         <v>8195927.2120691827</v>
       </c>
-      <c r="AA48" s="1">
+      <c r="AA48" s="7">
         <v>5879046.7046695622</v>
       </c>
-      <c r="AB48" s="1">
+      <c r="AB48" s="7">
         <v>6401600.4351107627</v>
       </c>
-      <c r="AC48" s="1">
+      <c r="AC48" s="7">
         <v>7029166.5562381372</v>
       </c>
-      <c r="AD48" s="1">
+      <c r="AD48" s="7">
         <v>7768728.7668560501</v>
       </c>
-      <c r="AE48" s="1">
+      <c r="AE48" s="7">
         <v>8422502.8855881318</v>
       </c>
-      <c r="AF48" s="1">
+      <c r="AF48" s="7">
         <v>8896893.3599846736</v>
       </c>
-      <c r="AG48" s="1">
+      <c r="AG48" s="7">
         <v>9028428.9343053252</v>
       </c>
-      <c r="AH48" s="1">
+      <c r="AH48" s="7">
         <v>8655086.5115525238</v>
       </c>
-      <c r="AI48" s="1">
+      <c r="AI48" s="7">
         <v>7971190.5652309479</v>
       </c>
     </row>
     <row r="49" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+      <c r="A49" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B49" s="3" t="s">
@@ -5731,7 +5772,7 @@
       <c r="D49" s="4">
         <v>57</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E49" s="5">
         <v>63.9</v>
       </c>
       <c r="F49" s="4">
@@ -5749,79 +5790,79 @@
       <c r="J49" s="4">
         <v>2</v>
       </c>
-      <c r="K49" s="4">
+      <c r="K49" s="8">
         <v>4.6298199999999996</v>
       </c>
-      <c r="L49" s="4">
+      <c r="L49" s="8">
         <v>776263.12351100077</v>
       </c>
-      <c r="M49" s="4">
+      <c r="M49" s="8">
         <v>3842.9439826472712</v>
       </c>
-      <c r="N49" s="4">
+      <c r="N49" s="8">
         <v>960.94955522083546</v>
       </c>
-      <c r="O49" s="4">
+      <c r="O49" s="8">
         <v>2881.9944274264294</v>
       </c>
-      <c r="P49" s="4">
+      <c r="P49" s="8">
         <v>4.3120537641434264</v>
       </c>
-      <c r="Q49" s="4">
+      <c r="Q49" s="8">
         <v>215.69906499829435</v>
       </c>
-      <c r="R49" s="4">
+      <c r="R49" s="8">
         <v>3365634.740204799</v>
       </c>
-      <c r="S49" s="4">
+      <c r="S49" s="8">
         <v>3437040.1495567886</v>
       </c>
-      <c r="T49" s="4">
+      <c r="T49" s="8">
         <v>3642249.6737439493</v>
       </c>
-      <c r="U49" s="4">
+      <c r="U49" s="8">
         <v>3730747.1594998809</v>
       </c>
-      <c r="V49" s="4">
+      <c r="V49" s="8">
         <v>3690649.7113418775</v>
       </c>
-      <c r="W49" s="4">
+      <c r="W49" s="8">
         <v>3537069.6860901746</v>
       </c>
-      <c r="X49" s="4">
+      <c r="X49" s="8">
         <v>3433019.193265717</v>
       </c>
-      <c r="Y49" s="4">
+      <c r="Y49" s="8">
         <v>3228361.4068440427</v>
       </c>
-      <c r="Z49" s="4">
+      <c r="Z49" s="8">
         <v>2915944.2667282093</v>
       </c>
-      <c r="AA49" s="4">
+      <c r="AA49" s="8">
         <v>3365320.2884954405</v>
       </c>
-      <c r="AB49" s="4">
+      <c r="AB49" s="8">
         <v>3498482.9401730723</v>
       </c>
-      <c r="AC49" s="4">
+      <c r="AC49" s="8">
         <v>3577876.1902837749</v>
       </c>
-      <c r="AD49" s="4">
+      <c r="AD49" s="8">
         <v>3666289.9628428002</v>
       </c>
-      <c r="AE49" s="4">
+      <c r="AE49" s="8">
         <v>3631327.8016467993</v>
       </c>
-      <c r="AF49" s="4">
+      <c r="AF49" s="8">
         <v>3557175.7936313497</v>
       </c>
-      <c r="AG49" s="4">
+      <c r="AG49" s="8">
         <v>3375672.3292377852</v>
       </c>
-      <c r="AH49" s="4">
+      <c r="AH49" s="8">
         <v>3153425.8142290981</v>
       </c>
-      <c r="AI49" s="4">
+      <c r="AI49" s="8">
         <v>2886978.4577496885</v>
       </c>
     </row>
@@ -5838,7 +5879,7 @@
       <c r="D50" s="1">
         <v>58</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50" s="2">
         <v>64.2</v>
       </c>
       <c r="F50" s="1">
@@ -5856,79 +5897,79 @@
       <c r="J50" s="1">
         <v>50</v>
       </c>
-      <c r="K50" s="1">
+      <c r="K50" s="7">
         <v>12.588699999999999</v>
       </c>
-      <c r="L50" s="1">
+      <c r="L50" s="7">
         <v>2748323.6973567917</v>
       </c>
-      <c r="M50" s="1">
+      <c r="M50" s="7">
         <v>9736.4194256444061</v>
       </c>
-      <c r="N50" s="1">
+      <c r="N50" s="7">
         <v>2682.3734409076792</v>
       </c>
-      <c r="O50" s="1">
+      <c r="O50" s="7">
         <v>7054.0459847367265</v>
       </c>
-      <c r="P50" s="1">
+      <c r="P50" s="7">
         <v>4.655502860468574</v>
       </c>
-      <c r="Q50" s="1">
+      <c r="Q50" s="7">
         <v>167.43303755329131</v>
       </c>
-      <c r="R50" s="1">
+      <c r="R50" s="7">
         <v>7048940.4029311212</v>
       </c>
-      <c r="S50" s="1">
+      <c r="S50" s="7">
         <v>7697968.3631641818</v>
       </c>
-      <c r="T50" s="1">
+      <c r="T50" s="7">
         <v>8378047.0591737097</v>
       </c>
-      <c r="U50" s="1">
+      <c r="U50" s="7">
         <v>9315455.3486778531</v>
       </c>
-      <c r="V50" s="1">
+      <c r="V50" s="7">
         <v>10328685.019173292</v>
       </c>
-      <c r="W50" s="1">
+      <c r="W50" s="7">
         <v>10674170.660385175</v>
       </c>
-      <c r="X50" s="1">
+      <c r="X50" s="7">
         <v>10353877.251995847</v>
       </c>
-      <c r="Y50" s="1">
+      <c r="Y50" s="7">
         <v>9637642.3155780807</v>
       </c>
-      <c r="Z50" s="1">
+      <c r="Z50" s="7">
         <v>8579496.3841408193</v>
       </c>
-      <c r="AA50" s="1">
+      <c r="AA50" s="7">
         <v>6938789.211552226</v>
       </c>
-      <c r="AB50" s="1">
+      <c r="AB50" s="7">
         <v>7656239.3737772945</v>
       </c>
-      <c r="AC50" s="1">
+      <c r="AC50" s="7">
         <v>8429823.6236457862</v>
       </c>
-      <c r="AD50" s="1">
+      <c r="AD50" s="7">
         <v>9251664.9928588532</v>
       </c>
-      <c r="AE50" s="1">
+      <c r="AE50" s="7">
         <v>9948636.3702755533</v>
       </c>
-      <c r="AF50" s="1">
+      <c r="AF50" s="7">
         <v>10341265.792983728</v>
       </c>
-      <c r="AG50" s="1">
+      <c r="AG50" s="7">
         <v>10129459.045528805</v>
       </c>
-      <c r="AH50" s="1">
+      <c r="AH50" s="7">
         <v>9383541.9035719335</v>
       </c>
-      <c r="AI50" s="1">
+      <c r="AI50" s="7">
         <v>8406125.0635228977</v>
       </c>
     </row>
@@ -5945,7 +5986,7 @@
       <c r="D51" s="1">
         <v>59</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E51" s="2">
         <v>64.8</v>
       </c>
       <c r="F51" s="1">
@@ -5963,79 +6004,79 @@
       <c r="J51" s="1">
         <v>50</v>
       </c>
-      <c r="K51" s="1">
+      <c r="K51" s="7">
         <v>13.505599999999999</v>
       </c>
-      <c r="L51" s="1">
+      <c r="L51" s="7">
         <v>3151138.0544159459</v>
       </c>
-      <c r="M51" s="1">
+      <c r="M51" s="7">
         <v>9823.6477044276544</v>
       </c>
-      <c r="N51" s="1">
+      <c r="N51" s="7">
         <v>2845.871450251906</v>
       </c>
-      <c r="O51" s="1">
+      <c r="O51" s="7">
         <v>6977.7762541757484</v>
       </c>
-      <c r="P51" s="1">
+      <c r="P51" s="7">
         <v>4.5472587747709348</v>
       </c>
-      <c r="Q51" s="1">
+      <c r="Q51" s="7">
         <v>145.25736551694516</v>
       </c>
-      <c r="R51" s="1">
+      <c r="R51" s="7">
         <v>5000090.4604094662</v>
       </c>
-      <c r="S51" s="1">
+      <c r="S51" s="7">
         <v>5965137.6266403161</v>
       </c>
-      <c r="T51" s="1">
+      <c r="T51" s="7">
         <v>7908412.6892561046</v>
       </c>
-      <c r="U51" s="1">
+      <c r="U51" s="7">
         <v>9828248.2067883685</v>
       </c>
-      <c r="V51" s="1">
+      <c r="V51" s="7">
         <v>10865617.472910354</v>
       </c>
-      <c r="W51" s="1">
+      <c r="W51" s="7">
         <v>11193350.826557351</v>
       </c>
-      <c r="X51" s="1">
+      <c r="X51" s="7">
         <v>10698618.027187722</v>
       </c>
-      <c r="Y51" s="1">
+      <c r="Y51" s="7">
         <v>9706673.6066958997</v>
       </c>
-      <c r="Z51" s="1">
+      <c r="Z51" s="7">
         <v>8697874.6534075122</v>
       </c>
-      <c r="AA51" s="1">
+      <c r="AA51" s="7">
         <v>5363256.8320690813</v>
       </c>
-      <c r="AB51" s="1">
+      <c r="AB51" s="7">
         <v>6126624.9674432753</v>
       </c>
-      <c r="AC51" s="1">
+      <c r="AC51" s="7">
         <v>7424228.5727209179</v>
       </c>
-      <c r="AD51" s="1">
+      <c r="AD51" s="7">
         <v>7424228.5727209179</v>
       </c>
-      <c r="AE51" s="1">
+      <c r="AE51" s="7">
         <v>10466475.934067557</v>
       </c>
-      <c r="AF51" s="1">
+      <c r="AF51" s="7">
         <v>10781471.104939092</v>
       </c>
-      <c r="AG51" s="1">
+      <c r="AG51" s="7">
         <v>10397136.461310798</v>
       </c>
-      <c r="AH51" s="1">
+      <c r="AH51" s="7">
         <v>9595058.2507382575</v>
       </c>
-      <c r="AI51" s="1">
+      <c r="AI51" s="7">
         <v>8580346.0451476425</v>
       </c>
     </row>
@@ -6052,7 +6093,7 @@
       <c r="D52" s="1">
         <v>60</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E52" s="2">
         <v>65.099999999999994</v>
       </c>
       <c r="F52" s="1">
@@ -6070,79 +6111,79 @@
       <c r="J52" s="1">
         <v>2</v>
       </c>
-      <c r="K52" s="1">
+      <c r="K52" s="7">
         <v>6.0233100000000004</v>
       </c>
-      <c r="L52" s="1">
+      <c r="L52" s="7">
         <v>1100981.0809674349</v>
       </c>
-      <c r="M52" s="1">
+      <c r="M52" s="7">
         <v>4106.9938537829103</v>
       </c>
-      <c r="N52" s="1">
+      <c r="N52" s="7">
         <v>1064.25601816125</v>
       </c>
-      <c r="O52" s="1">
+      <c r="O52" s="7">
         <v>3042.7378356216618</v>
       </c>
-      <c r="P52" s="1">
+      <c r="P52" s="7">
         <v>3.6053393764243618</v>
       </c>
-      <c r="Q52" s="1">
+      <c r="Q52" s="7">
         <v>138.44570138693834</v>
       </c>
-      <c r="R52" s="1">
+      <c r="R52" s="7">
         <v>4046592.4679476391</v>
       </c>
-      <c r="S52" s="1">
+      <c r="S52" s="7">
         <v>4142012.3369523399</v>
       </c>
-      <c r="T52" s="1">
+      <c r="T52" s="7">
         <v>4190112.3190193595</v>
       </c>
-      <c r="U52" s="1">
+      <c r="U52" s="7">
         <v>4311968.0786288753</v>
       </c>
-      <c r="V52" s="1">
+      <c r="V52" s="7">
         <v>4332956.8835555259</v>
       </c>
-      <c r="W52" s="1">
+      <c r="W52" s="7">
         <v>4162431.2227751757</v>
       </c>
-      <c r="X52" s="1">
+      <c r="X52" s="7">
         <v>4121570.1873064684</v>
       </c>
-      <c r="Y52" s="1">
+      <c r="Y52" s="7">
         <v>4138516.9795440705</v>
       </c>
-      <c r="Z52" s="1">
+      <c r="Z52" s="7">
         <v>4109864.0699648233</v>
       </c>
-      <c r="AA52" s="1">
+      <c r="AA52" s="7">
         <v>4093718.6357319625</v>
       </c>
-      <c r="AB52" s="1">
+      <c r="AB52" s="7">
         <v>4117102.0179884201</v>
       </c>
-      <c r="AC52" s="1">
+      <c r="AC52" s="7">
         <v>4225281.8436408872</v>
       </c>
-      <c r="AD52" s="1">
+      <c r="AD52" s="7">
         <v>4260337.5812273826</v>
       </c>
-      <c r="AE52" s="1">
+      <c r="AE52" s="7">
         <v>4235880.3081466835</v>
       </c>
-      <c r="AF52" s="1">
+      <c r="AF52" s="7">
         <v>4224620.9077017009</v>
       </c>
-      <c r="AG52" s="1">
+      <c r="AG52" s="7">
         <v>4150439.6538281022</v>
       </c>
-      <c r="AH52" s="1">
+      <c r="AH52" s="7">
         <v>4115708.8048624774</v>
       </c>
-      <c r="AI52" s="1">
+      <c r="AI52" s="7">
         <v>4104381.8286810089</v>
       </c>
     </row>
@@ -6159,7 +6200,7 @@
       <c r="D53" s="1">
         <v>61</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="2">
         <v>65</v>
       </c>
       <c r="F53" s="1">
@@ -6177,79 +6218,79 @@
       <c r="J53" s="1">
         <v>2</v>
       </c>
-      <c r="K53" s="1">
+      <c r="K53" s="7">
         <v>5.1953899999999997</v>
       </c>
-      <c r="L53" s="1">
+      <c r="L53" s="7">
         <v>1009753.6702942313</v>
       </c>
-      <c r="M53" s="1">
+      <c r="M53" s="7">
         <v>4049.6978244505726</v>
       </c>
-      <c r="N53" s="1">
+      <c r="N53" s="7">
         <v>1255.511061573507</v>
       </c>
-      <c r="O53" s="1">
+      <c r="O53" s="7">
         <v>2794.1867628770683</v>
       </c>
-      <c r="P53" s="1">
+      <c r="P53" s="7">
         <v>4.4072017155612242</v>
       </c>
-      <c r="Q53" s="1">
+      <c r="Q53" s="7">
         <v>181.67350795735874</v>
       </c>
-      <c r="R53" s="1">
+      <c r="R53" s="7">
         <v>3555630.5703979447</v>
       </c>
-      <c r="S53" s="1">
+      <c r="S53" s="7">
         <v>3574862.9929103451</v>
       </c>
-      <c r="T53" s="1">
+      <c r="T53" s="7">
         <v>3553273.6152057135</v>
       </c>
-      <c r="U53" s="1">
+      <c r="U53" s="7">
         <v>3606243.8497469896</v>
       </c>
-      <c r="V53" s="1">
+      <c r="V53" s="7">
         <v>3571698.5641839816</v>
       </c>
-      <c r="W53" s="1">
+      <c r="W53" s="7">
         <v>3520836.8280765861</v>
       </c>
-      <c r="X53" s="1">
+      <c r="X53" s="7">
         <v>3490670.0080380449</v>
       </c>
-      <c r="Y53" s="1">
+      <c r="Y53" s="7">
         <v>3123437.5211406988</v>
       </c>
-      <c r="Z53" s="1">
+      <c r="Z53" s="7">
         <v>2902474.1826540013</v>
       </c>
-      <c r="AA53" s="1">
+      <c r="AA53" s="7">
         <v>3492550.8605607529</v>
       </c>
-      <c r="AB53" s="1">
+      <c r="AB53" s="7">
         <v>3554451.7020779122</v>
       </c>
-      <c r="AC53" s="1">
+      <c r="AC53" s="7">
         <v>3590484.8554238994</v>
       </c>
-      <c r="AD53" s="1">
+      <c r="AD53" s="7">
         <v>3562462.2665320123</v>
       </c>
-      <c r="AE53" s="1">
+      <c r="AE53" s="7">
         <v>3563028.6034845947</v>
       </c>
-      <c r="AF53" s="1">
+      <c r="AF53" s="7">
         <v>3530719.4543166971</v>
       </c>
-      <c r="AG53" s="1">
+      <c r="AG53" s="7">
         <v>3310252.7910888884</v>
       </c>
-      <c r="AH53" s="1">
+      <c r="AH53" s="7">
         <v>3169513.8655705289</v>
       </c>
-      <c r="AI53" s="1">
+      <c r="AI53" s="7">
         <v>2887908.0695628477</v>
       </c>
     </row>
@@ -6266,7 +6307,7 @@
       <c r="D54" s="1">
         <v>62</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E54" s="2">
         <v>64.8</v>
       </c>
       <c r="F54" s="1">
@@ -6284,84 +6325,84 @@
       <c r="J54" s="1">
         <v>50</v>
       </c>
-      <c r="K54" s="1">
+      <c r="K54" s="7">
         <v>13.949</v>
       </c>
-      <c r="L54" s="1">
+      <c r="L54" s="7">
         <v>3693578.7332728188</v>
       </c>
-      <c r="M54" s="1">
+      <c r="M54" s="7">
         <v>8355.4626171843229</v>
       </c>
-      <c r="N54" s="1">
+      <c r="N54" s="7">
         <v>2492.6829947260808</v>
       </c>
-      <c r="O54" s="1">
+      <c r="O54" s="7">
         <v>5862.7796224582398</v>
       </c>
-      <c r="P54" s="1">
+      <c r="P54" s="7">
         <v>3.7414758267716537</v>
       </c>
-      <c r="Q54" s="1">
+      <c r="Q54" s="7">
         <v>86.72598233768646</v>
       </c>
-      <c r="R54" s="1">
+      <c r="R54" s="7">
         <v>8983902.8796135411</v>
       </c>
-      <c r="S54" s="1">
+      <c r="S54" s="7">
         <v>10580413.634655213</v>
       </c>
-      <c r="T54" s="1">
+      <c r="T54" s="7">
         <v>12501799.6780168</v>
       </c>
-      <c r="U54" s="1">
+      <c r="U54" s="7">
         <v>13907356.111677531</v>
       </c>
-      <c r="V54" s="1">
+      <c r="V54" s="7">
         <v>14584496.123570306</v>
       </c>
-      <c r="W54" s="1">
+      <c r="W54" s="7">
         <v>14521485.420606609</v>
       </c>
-      <c r="X54" s="1">
+      <c r="X54" s="7">
         <v>13712981.339631088</v>
       </c>
-      <c r="Y54" s="1">
+      <c r="Y54" s="7">
         <v>12681465.715754366</v>
       </c>
-      <c r="Z54" s="1">
+      <c r="Z54" s="7">
         <v>11512794.145534391</v>
       </c>
-      <c r="AA54" s="1">
+      <c r="AA54" s="7">
         <v>8952219.9842314962</v>
       </c>
-      <c r="AB54" s="1">
+      <c r="AB54" s="7">
         <v>10454855.160209758</v>
       </c>
-      <c r="AC54" s="1">
+      <c r="AC54" s="7">
         <v>12017883.355672665</v>
       </c>
-      <c r="AD54" s="1">
+      <c r="AD54" s="7">
         <v>13463077.437927475</v>
       </c>
-      <c r="AE54" s="1">
+      <c r="AE54" s="7">
         <v>14207787.45314447</v>
       </c>
-      <c r="AF54" s="1">
+      <c r="AF54" s="7">
         <v>14135318.135725813</v>
       </c>
-      <c r="AG54" s="1">
+      <c r="AG54" s="7">
         <v>13539245.692876277</v>
       </c>
-      <c r="AH54" s="1">
+      <c r="AH54" s="7">
         <v>12516937.794643303</v>
       </c>
-      <c r="AI54" s="1">
+      <c r="AI54" s="7">
         <v>11287990.943224482</v>
       </c>
     </row>
     <row r="55" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+      <c r="A55" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B55" s="3" t="s">
@@ -6373,7 +6414,7 @@
       <c r="D55" s="4">
         <v>63</v>
       </c>
-      <c r="E55" s="4">
+      <c r="E55" s="5">
         <v>65.3</v>
       </c>
       <c r="F55" s="4">
@@ -6391,79 +6432,79 @@
       <c r="J55" s="4">
         <v>2</v>
       </c>
-      <c r="K55" s="4">
+      <c r="K55" s="8">
         <v>4.9371600000000004</v>
       </c>
-      <c r="L55" s="4">
+      <c r="L55" s="8">
         <v>951238.85925376404</v>
       </c>
-      <c r="M55" s="4">
+      <c r="M55" s="8">
         <v>3719.5461367934699</v>
       </c>
-      <c r="N55" s="4">
+      <c r="N55" s="8">
         <v>1141.2520202911985</v>
       </c>
-      <c r="O55" s="4">
+      <c r="O55" s="8">
         <v>2578.2941165022589</v>
       </c>
-      <c r="P55" s="4">
+      <c r="P55" s="8">
         <v>4.4694785000000001</v>
       </c>
-      <c r="Q55" s="4">
+      <c r="Q55" s="8">
         <v>180.45899695032924</v>
       </c>
-      <c r="R55" s="4">
+      <c r="R55" s="8">
         <v>3018522.7015658095</v>
       </c>
-      <c r="S55" s="4">
+      <c r="S55" s="8">
         <v>3194199.2209821269</v>
       </c>
-      <c r="T55" s="4">
+      <c r="T55" s="8">
         <v>3301687.6539268354</v>
       </c>
-      <c r="U55" s="4">
+      <c r="U55" s="8">
         <v>3282008.1059928373</v>
       </c>
-      <c r="V55" s="4">
+      <c r="V55" s="8">
         <v>3086866.6809711768</v>
       </c>
-      <c r="W55" s="4">
+      <c r="W55" s="8">
         <v>3094502.8599404916</v>
       </c>
-      <c r="X55" s="4">
+      <c r="X55" s="8">
         <v>3085642.9998180601</v>
       </c>
-      <c r="Y55" s="4">
+      <c r="Y55" s="8">
         <v>2841343.6971145184</v>
       </c>
-      <c r="Z55" s="4">
+      <c r="Z55" s="8">
         <v>2613329.2918845643</v>
       </c>
-      <c r="AA55" s="4">
+      <c r="AA55" s="8">
         <v>2972979.813298027</v>
       </c>
-      <c r="AB55" s="4">
+      <c r="AB55" s="8">
         <v>3153761.8453463227</v>
       </c>
-      <c r="AC55" s="4">
+      <c r="AC55" s="8">
         <v>3237508.3767789551</v>
       </c>
-      <c r="AD55" s="4">
+      <c r="AD55" s="8">
         <v>3190665.391763737</v>
       </c>
-      <c r="AE55" s="4">
+      <c r="AE55" s="8">
         <v>3185498.6291413526</v>
       </c>
-      <c r="AF55" s="4">
+      <c r="AF55" s="8">
         <v>3086254.719099097</v>
       </c>
-      <c r="AG55" s="4">
+      <c r="AG55" s="8">
         <v>2962524.7594530373</v>
       </c>
-      <c r="AH55" s="4">
+      <c r="AH55" s="8">
         <v>2829914.1750394278</v>
       </c>
-      <c r="AI55" s="4">
+      <c r="AI55" s="8">
         <v>2613363.0526854228</v>
       </c>
     </row>
@@ -6480,7 +6521,7 @@
       <c r="D56" s="1">
         <v>64</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56" s="2">
         <v>65.099999999999994</v>
       </c>
       <c r="F56" s="1">
@@ -6498,79 +6539,79 @@
       <c r="J56" s="1">
         <v>2</v>
       </c>
-      <c r="K56" s="1">
+      <c r="K56" s="7">
         <v>5.92089</v>
       </c>
-      <c r="L56" s="1">
+      <c r="L56" s="7">
         <v>1073076.9627657351</v>
       </c>
-      <c r="M56" s="1">
+      <c r="M56" s="7">
         <v>4009.8626658631342</v>
       </c>
-      <c r="N56" s="1">
+      <c r="N56" s="7">
         <v>1073.4668630959</v>
       </c>
-      <c r="O56" s="1">
+      <c r="O56" s="7">
         <v>2936.3958027672415</v>
       </c>
-      <c r="P56" s="1">
+      <c r="P56" s="7">
         <v>3.7509712488636362</v>
       </c>
-      <c r="Q56" s="1">
+      <c r="Q56" s="7">
         <v>144.28842403405736</v>
       </c>
-      <c r="R56" s="1">
+      <c r="R56" s="7">
         <v>4041528.6740989173</v>
       </c>
-      <c r="S56" s="1">
+      <c r="S56" s="7">
         <v>4128492.229603163</v>
       </c>
-      <c r="T56" s="1">
+      <c r="T56" s="7">
         <v>3977672.3945107087</v>
       </c>
-      <c r="U56" s="1">
+      <c r="U56" s="7">
         <v>3943674.4732645079</v>
       </c>
-      <c r="V56" s="1">
+      <c r="V56" s="7">
         <v>4021225.9726468772</v>
       </c>
-      <c r="W56" s="1">
+      <c r="W56" s="7">
         <v>3807417.1703510131</v>
       </c>
-      <c r="X56" s="1">
+      <c r="X56" s="7">
         <v>3666223.5051992116</v>
       </c>
-      <c r="Y56" s="1">
+      <c r="Y56" s="7">
         <v>3629653.4133091643</v>
       </c>
-      <c r="Z56" s="1">
+      <c r="Z56" s="7">
         <v>3688490.0037282514</v>
       </c>
-      <c r="AA56" s="1">
+      <c r="AA56" s="7">
         <v>4022946.9648679434</v>
       </c>
-      <c r="AB56" s="1">
+      <c r="AB56" s="7">
         <v>4009346.292990251</v>
       </c>
-      <c r="AC56" s="1">
+      <c r="AC56" s="7">
         <v>4033967.5872087278</v>
       </c>
-      <c r="AD56" s="1">
+      <c r="AD56" s="7">
         <v>3999330.6101152115</v>
       </c>
-      <c r="AE56" s="1">
+      <c r="AE56" s="7">
         <v>3874348.1806592033</v>
       </c>
-      <c r="AF56" s="1">
+      <c r="AF56" s="7">
         <v>3835527.8231412158</v>
       </c>
-      <c r="AG56" s="1">
+      <c r="AG56" s="7">
         <v>3716410.8025596049</v>
       </c>
-      <c r="AH56" s="1">
+      <c r="AH56" s="7">
         <v>3677323.0483950898</v>
       </c>
-      <c r="AI56" s="1">
+      <c r="AI56" s="7">
         <v>3710699.9045705218</v>
       </c>
     </row>
@@ -6587,7 +6628,7 @@
       <c r="D57" s="1">
         <v>65</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E57" s="2">
         <v>64.2</v>
       </c>
       <c r="F57" s="1">
@@ -6605,79 +6646,79 @@
       <c r="J57" s="1">
         <v>50</v>
       </c>
-      <c r="K57" s="1">
+      <c r="K57" s="7">
         <v>13.5677</v>
       </c>
-      <c r="L57" s="1">
+      <c r="L57" s="7">
         <v>3141116.0435126564</v>
       </c>
-      <c r="M57" s="1">
+      <c r="M57" s="7">
         <v>9107.8648992054168</v>
       </c>
-      <c r="N57" s="1">
+      <c r="N57" s="7">
         <v>2485.500645331952</v>
       </c>
-      <c r="O57" s="1">
+      <c r="O57" s="7">
         <v>6622.3642538734657</v>
       </c>
-      <c r="P57" s="1">
+      <c r="P57" s="7">
         <v>3.9258138578016424</v>
       </c>
-      <c r="Q57" s="1">
+      <c r="Q57" s="7">
         <v>115.5594508655284</v>
       </c>
-      <c r="R57" s="1">
+      <c r="R57" s="7">
         <v>8355751.871879261</v>
       </c>
-      <c r="S57" s="1">
+      <c r="S57" s="7">
         <v>9737408.6030726954</v>
       </c>
-      <c r="T57" s="1">
+      <c r="T57" s="7">
         <v>11356550.153691269</v>
       </c>
-      <c r="U57" s="1">
+      <c r="U57" s="7">
         <v>12662156.114109743</v>
       </c>
-      <c r="V57" s="1">
+      <c r="V57" s="7">
         <v>13385930.794561546</v>
       </c>
-      <c r="W57" s="1">
+      <c r="W57" s="7">
         <v>13359559.969875427</v>
       </c>
-      <c r="X57" s="1">
+      <c r="X57" s="7">
         <v>12665973.360455019</v>
       </c>
-      <c r="Y57" s="1">
+      <c r="Y57" s="7">
         <v>11744613.596825529</v>
       </c>
-      <c r="Z57" s="1">
+      <c r="Z57" s="7">
         <v>10683408.522564493</v>
       </c>
-      <c r="AA57" s="1">
+      <c r="AA57" s="7">
         <v>8357171.6389736123</v>
       </c>
-      <c r="AB57" s="1">
+      <c r="AB57" s="7">
         <v>9627745.6668128613</v>
       </c>
-      <c r="AC57" s="1">
+      <c r="AC57" s="7">
         <v>11008837.844460646</v>
       </c>
-      <c r="AD57" s="1">
+      <c r="AD57" s="7">
         <v>12288015.477527393</v>
       </c>
-      <c r="AE57" s="1">
+      <c r="AE57" s="7">
         <v>13001512.53732896</v>
       </c>
-      <c r="AF57" s="1">
+      <c r="AF57" s="7">
         <v>13016003.88516424</v>
       </c>
-      <c r="AG57" s="1">
+      <c r="AG57" s="7">
         <v>12500142.197704241</v>
       </c>
-      <c r="AH57" s="1">
+      <c r="AH57" s="7">
         <v>11590522.474949656</v>
       </c>
-      <c r="AI57" s="1">
+      <c r="AI57" s="7">
         <v>10506504.442837363</v>
       </c>
     </row>
@@ -6694,7 +6735,7 @@
       <c r="D58" s="1">
         <v>66</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E58" s="2">
         <v>65.400000000000006</v>
       </c>
       <c r="F58" s="1">
@@ -6712,79 +6753,79 @@
       <c r="J58" s="1">
         <v>2</v>
       </c>
-      <c r="K58" s="1">
+      <c r="K58" s="7">
         <v>5.3853200000000001</v>
       </c>
-      <c r="L58" s="1">
+      <c r="L58" s="7">
         <v>951258.31551125133</v>
       </c>
-      <c r="M58" s="1">
+      <c r="M58" s="7">
         <v>3712.5144359712522</v>
       </c>
-      <c r="N58" s="1">
+      <c r="N58" s="7">
         <v>1005.2611476864914</v>
       </c>
-      <c r="O58" s="1">
+      <c r="O58" s="7">
         <v>2707.2532882847645</v>
       </c>
-      <c r="P58" s="1">
+      <c r="P58" s="7">
         <v>3.840934962962963</v>
       </c>
-      <c r="Q58" s="1">
+      <c r="Q58" s="7">
         <v>155.02171080075163</v>
       </c>
-      <c r="R58" s="1">
+      <c r="R58" s="7">
         <v>3728546.8679197994</v>
       </c>
-      <c r="S58" s="1">
+      <c r="S58" s="7">
         <v>3641686.9383456162</v>
       </c>
-      <c r="T58" s="1">
+      <c r="T58" s="7">
         <v>3595370.727849599</v>
       </c>
-      <c r="U58" s="1">
+      <c r="U58" s="7">
         <v>3529806.7231428311</v>
       </c>
-      <c r="V58" s="1">
+      <c r="V58" s="7">
         <v>3674299.1377394181</v>
       </c>
-      <c r="W58" s="1">
+      <c r="W58" s="7">
         <v>3834214.650212252</v>
       </c>
-      <c r="X58" s="1">
+      <c r="X58" s="7">
         <v>3644625.5628350764</v>
       </c>
-      <c r="Y58" s="1">
+      <c r="Y58" s="7">
         <v>3453347.2414757567</v>
       </c>
-      <c r="Z58" s="1">
+      <c r="Z58" s="7">
         <v>3324842.9212827925</v>
       </c>
-      <c r="AA58" s="1">
+      <c r="AA58" s="7">
         <v>3649454.9610852837</v>
       </c>
-      <c r="AB58" s="1">
+      <c r="AB58" s="7">
         <v>3660747.9783982644</v>
       </c>
-      <c r="AC58" s="1">
+      <c r="AC58" s="7">
         <v>3584874.1267341063</v>
       </c>
-      <c r="AD58" s="1">
+      <c r="AD58" s="7">
         <v>3634406.4612130667</v>
       </c>
-      <c r="AE58" s="1">
+      <c r="AE58" s="7">
         <v>3675719.0030060369</v>
       </c>
-      <c r="AF58" s="1">
+      <c r="AF58" s="7">
         <v>3659402.196570436</v>
       </c>
-      <c r="AG58" s="1">
+      <c r="AG58" s="7">
         <v>3633828.3728714786</v>
       </c>
-      <c r="AH58" s="1">
+      <c r="AH58" s="7">
         <v>3477397.8907954781</v>
       </c>
-      <c r="AI58" s="1">
+      <c r="AI58" s="7">
         <v>3314851.1303187655</v>
       </c>
     </row>
@@ -6801,7 +6842,7 @@
       <c r="D59" s="1">
         <v>67</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59" s="2">
         <v>64.900000000000006</v>
       </c>
       <c r="F59" s="1">
@@ -6819,79 +6860,79 @@
       <c r="J59" s="1">
         <v>2</v>
       </c>
-      <c r="K59" s="1">
+      <c r="K59" s="7">
         <v>5.8415600000000003</v>
       </c>
-      <c r="L59" s="1">
+      <c r="L59" s="7">
         <v>1200718.3922679368</v>
       </c>
-      <c r="M59" s="1">
+      <c r="M59" s="7">
         <v>4226.2772512595529</v>
       </c>
-      <c r="N59" s="1">
+      <c r="N59" s="7">
         <v>1082.2409492519373</v>
       </c>
-      <c r="O59" s="1">
+      <c r="O59" s="7">
         <v>3144.0363020076061</v>
       </c>
-      <c r="P59" s="1">
+      <c r="P59" s="7">
         <v>3.8141056784689003</v>
       </c>
-      <c r="Q59" s="1">
+      <c r="Q59" s="7">
         <v>137.7724490714134</v>
       </c>
-      <c r="R59" s="1">
+      <c r="R59" s="7">
         <v>4342900.743199015</v>
       </c>
-      <c r="S59" s="1">
+      <c r="S59" s="7">
         <v>4492036.7705228878</v>
       </c>
-      <c r="T59" s="1">
+      <c r="T59" s="7">
         <v>4624156.9176937155</v>
       </c>
-      <c r="U59" s="1">
+      <c r="U59" s="7">
         <v>4447748.7034174222</v>
       </c>
-      <c r="V59" s="1">
+      <c r="V59" s="7">
         <v>4255068.6590863252</v>
       </c>
-      <c r="W59" s="1">
+      <c r="W59" s="7">
         <v>4046088.8657134105</v>
       </c>
-      <c r="X59" s="1">
+      <c r="X59" s="7">
         <v>3837049.144880475</v>
       </c>
-      <c r="Y59" s="1">
+      <c r="Y59" s="7">
         <v>3689450.4763660175</v>
       </c>
-      <c r="Z59" s="1">
+      <c r="Z59" s="7">
         <v>3565881.5076775081</v>
       </c>
-      <c r="AA59" s="1">
+      <c r="AA59" s="7">
         <v>4329030.8373930342</v>
       </c>
-      <c r="AB59" s="1">
+      <c r="AB59" s="7">
         <v>4479117.9613138745</v>
       </c>
-      <c r="AC59" s="1">
+      <c r="AC59" s="7">
         <v>4469783.0345117645</v>
       </c>
-      <c r="AD59" s="1">
+      <c r="AD59" s="7">
         <v>4431941.7284837337</v>
       </c>
-      <c r="AE59" s="1">
+      <c r="AE59" s="7">
         <v>4237421.8625963209</v>
       </c>
-      <c r="AF59" s="1">
+      <c r="AF59" s="7">
         <v>4035261.9562091287</v>
       </c>
-      <c r="AG59" s="1">
+      <c r="AG59" s="7">
         <v>3859548.4640151164</v>
       </c>
-      <c r="AH59" s="1">
+      <c r="AH59" s="7">
         <v>3696498.9223696948</v>
       </c>
-      <c r="AI59" s="1">
+      <c r="AI59" s="7">
         <v>3664688.2811688054</v>
       </c>
     </row>
@@ -6908,7 +6949,7 @@
       <c r="D60" s="1">
         <v>68</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E60" s="2">
         <v>64.599999999999994</v>
       </c>
       <c r="F60" s="1">
@@ -6926,84 +6967,84 @@
       <c r="J60" s="1">
         <v>50</v>
       </c>
-      <c r="K60" s="1">
+      <c r="K60" s="7">
         <v>13.5901</v>
       </c>
-      <c r="L60" s="1">
+      <c r="L60" s="7">
         <v>3289064.4461280904</v>
       </c>
-      <c r="M60" s="1">
+      <c r="M60" s="7">
         <v>9032.1854347851404</v>
       </c>
-      <c r="N60" s="1">
+      <c r="N60" s="7">
         <v>2283.2440711825761</v>
       </c>
-      <c r="O60" s="1">
+      <c r="O60" s="7">
         <v>6748.9413636025647</v>
       </c>
-      <c r="P60" s="1">
+      <c r="P60" s="7">
         <v>4.1703012133582762</v>
       </c>
-      <c r="Q60" s="1">
+      <c r="Q60" s="7">
         <v>116.98455927803464</v>
       </c>
-      <c r="R60" s="1">
+      <c r="R60" s="7">
         <v>7706485.9784410615</v>
       </c>
-      <c r="S60" s="1">
+      <c r="S60" s="7">
         <v>9031122.0686489176</v>
       </c>
-      <c r="T60" s="1">
+      <c r="T60" s="7">
         <v>10486729.63280822</v>
       </c>
-      <c r="U60" s="1">
+      <c r="U60" s="7">
         <v>11892092.086363558</v>
       </c>
-      <c r="V60" s="1">
+      <c r="V60" s="7">
         <v>12583897.365025036</v>
       </c>
-      <c r="W60" s="1">
+      <c r="W60" s="7">
         <v>12531913.804305356</v>
       </c>
-      <c r="X60" s="1">
+      <c r="X60" s="7">
         <v>12181863.536114134</v>
       </c>
-      <c r="Y60" s="1">
+      <c r="Y60" s="7">
         <v>11395262.110001881</v>
       </c>
-      <c r="Z60" s="1">
+      <c r="Z60" s="7">
         <v>10453817.657563008</v>
       </c>
-      <c r="AA60" s="1">
+      <c r="AA60" s="7">
         <v>7568346.8003986226</v>
       </c>
-      <c r="AB60" s="1">
+      <c r="AB60" s="7">
         <v>8884172.7160061412</v>
       </c>
-      <c r="AC60" s="1">
+      <c r="AC60" s="7">
         <v>10266007.362720037</v>
       </c>
-      <c r="AD60" s="1">
+      <c r="AD60" s="7">
         <v>11439995.055740712</v>
       </c>
-      <c r="AE60" s="1">
+      <c r="AE60" s="7">
         <v>12203622.423470384</v>
       </c>
-      <c r="AF60" s="1">
+      <c r="AF60" s="7">
         <v>12379617.251828508</v>
       </c>
-      <c r="AG60" s="1">
+      <c r="AG60" s="7">
         <v>11936589.846745811</v>
       </c>
-      <c r="AH60" s="1">
+      <c r="AH60" s="7">
         <v>11251879.636069877</v>
       </c>
-      <c r="AI60" s="1">
+      <c r="AI60" s="7">
         <v>10379838.61255276</v>
       </c>
     </row>
     <row r="61" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+      <c r="A61" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B61" s="3" t="s">
@@ -7015,7 +7056,7 @@
       <c r="D61" s="4">
         <v>69</v>
       </c>
-      <c r="E61" s="4">
+      <c r="E61" s="5">
         <v>64.5</v>
       </c>
       <c r="F61" s="4">
@@ -7033,118 +7074,2010 @@
       <c r="J61" s="4">
         <v>50</v>
       </c>
-      <c r="K61" s="4">
+      <c r="K61" s="8">
         <v>14.009499999999999</v>
       </c>
-      <c r="L61" s="4">
+      <c r="L61" s="8">
         <v>3571750.1628045174</v>
       </c>
-      <c r="M61" s="4">
+      <c r="M61" s="8">
         <v>9218.5028993657706</v>
       </c>
-      <c r="N61" s="4">
+      <c r="N61" s="8">
         <v>2745.0549043323308</v>
       </c>
-      <c r="O61" s="4">
+      <c r="O61" s="8">
         <v>6473.4479950334426</v>
       </c>
-      <c r="P61" s="4">
+      <c r="P61" s="8">
         <v>3.9995886757957075</v>
       </c>
-      <c r="Q61" s="4">
+      <c r="Q61" s="8">
         <v>105.28403160200644</v>
       </c>
-      <c r="R61" s="4">
+      <c r="R61" s="8">
         <v>8462123.4132440556</v>
       </c>
-      <c r="S61" s="4">
+      <c r="S61" s="8">
         <v>10045483.716069195</v>
       </c>
-      <c r="T61" s="4">
+      <c r="T61" s="8">
         <v>11848379.099573268</v>
       </c>
-      <c r="U61" s="4">
+      <c r="U61" s="8">
         <v>13287754.38539663</v>
       </c>
-      <c r="V61" s="4">
+      <c r="V61" s="8">
         <v>13710215.337688386</v>
       </c>
-      <c r="W61" s="4">
+      <c r="W61" s="8">
         <v>13569071.740315659</v>
       </c>
-      <c r="X61" s="4">
+      <c r="X61" s="8">
         <v>12697490.577262221</v>
       </c>
-      <c r="Y61" s="4">
+      <c r="Y61" s="8">
         <v>11434715.262409432</v>
       </c>
-      <c r="Z61" s="4">
+      <c r="Z61" s="8">
         <v>10238974.306030538</v>
       </c>
-      <c r="AA61" s="4">
+      <c r="AA61" s="8">
         <v>8264173.5681853974</v>
       </c>
-      <c r="AB61" s="4">
+      <c r="AB61" s="8">
         <v>9872965.587554317</v>
       </c>
-      <c r="AC61" s="4">
+      <c r="AC61" s="8">
         <v>11441354.150776302</v>
       </c>
-      <c r="AD61" s="4">
+      <c r="AD61" s="8">
         <v>12711483.744261811</v>
       </c>
-      <c r="AE61" s="4">
+      <c r="AE61" s="8">
         <v>13426939.704578286</v>
       </c>
-      <c r="AF61" s="4">
+      <c r="AF61" s="8">
         <v>13184434.166542018</v>
       </c>
-      <c r="AG61" s="4">
+      <c r="AG61" s="8">
         <v>12410797.749061428</v>
       </c>
-      <c r="AH61" s="4">
+      <c r="AH61" s="8">
         <v>11336470.588050675</v>
       </c>
-      <c r="AI61" s="4">
+      <c r="AI61" s="8">
         <v>10049209.063895488</v>
       </c>
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
-      <c r="R62" s="1"/>
-      <c r="S62" s="1"/>
-      <c r="T62" s="1"/>
-      <c r="U62" s="1"/>
-      <c r="V62" s="1"/>
-      <c r="W62" s="1"/>
-      <c r="X62" s="1"/>
-      <c r="Y62" s="1"/>
-      <c r="Z62" s="1"/>
-      <c r="AA62" s="1"/>
-      <c r="AB62" s="1"/>
-      <c r="AC62" s="1"/>
-      <c r="AD62" s="1"/>
-      <c r="AE62" s="1"/>
-      <c r="AF62" s="1"/>
-      <c r="AG62" s="1"/>
-      <c r="AH62" s="1"/>
-      <c r="AI62" s="1"/>
+      <c r="A62" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" t="s">
+        <v>34</v>
+      </c>
+      <c r="C62" t="s">
+        <v>36</v>
+      </c>
+      <c r="D62" s="1">
+        <v>70</v>
+      </c>
+      <c r="E62" s="2">
+        <v>64.5</v>
+      </c>
+      <c r="F62" s="1">
+        <v>102</v>
+      </c>
+      <c r="G62" s="1">
+        <v>2.3570000000000002</v>
+      </c>
+      <c r="H62" s="1">
+        <v>2289</v>
+      </c>
+      <c r="I62" s="1">
+        <v>3151</v>
+      </c>
+      <c r="J62" s="1">
+        <v>50</v>
+      </c>
+      <c r="K62" s="7">
+        <v>12.566599999999999</v>
+      </c>
+      <c r="L62" s="7">
+        <v>2108933.637019034</v>
+      </c>
+      <c r="M62" s="7">
+        <v>9864.3762529659525</v>
+      </c>
+      <c r="N62" s="7">
+        <v>2035.0661295885398</v>
+      </c>
+      <c r="O62" s="7">
+        <v>7829.310123377415</v>
+      </c>
+      <c r="P62" s="7">
+        <v>3.6777978447361082</v>
+      </c>
+      <c r="Q62" s="7">
+        <v>175.45365614966161</v>
+      </c>
+      <c r="R62" s="7">
+        <v>8203556.9511615559</v>
+      </c>
+      <c r="S62" s="7">
+        <v>8988156.7546107396</v>
+      </c>
+      <c r="T62" s="7">
+        <v>10013906.678868396</v>
+      </c>
+      <c r="U62" s="7">
+        <v>11334795.277426388</v>
+      </c>
+      <c r="V62" s="7">
+        <v>12328133.001263691</v>
+      </c>
+      <c r="W62" s="7">
+        <v>12831731.670598242</v>
+      </c>
+      <c r="X62" s="7">
+        <v>12940700.354219455</v>
+      </c>
+      <c r="Y62" s="7">
+        <v>12418943.463139182</v>
+      </c>
+      <c r="Z62" s="7">
+        <v>11458794.221517023</v>
+      </c>
+      <c r="AA62" s="7">
+        <v>8206291.725171471</v>
+      </c>
+      <c r="AB62" s="7">
+        <v>9018780.5955925919</v>
+      </c>
+      <c r="AC62" s="7">
+        <v>10025995.886259817</v>
+      </c>
+      <c r="AD62" s="7">
+        <v>11051164.0984251</v>
+      </c>
+      <c r="AE62" s="7">
+        <v>12036901.442554057</v>
+      </c>
+      <c r="AF62" s="7">
+        <v>12626991.745283704</v>
+      </c>
+      <c r="AG62" s="7">
+        <v>12621963.5164064</v>
+      </c>
+      <c r="AH62" s="7">
+        <v>12154745.417453988</v>
+      </c>
+      <c r="AI62" s="7">
+        <v>11314416.424508194</v>
+      </c>
+    </row>
+    <row r="63" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" t="s">
+        <v>34</v>
+      </c>
+      <c r="C63" t="s">
+        <v>36</v>
+      </c>
+      <c r="D63" s="1">
+        <v>71</v>
+      </c>
+      <c r="E63" s="2">
+        <v>64.5</v>
+      </c>
+      <c r="F63" s="1">
+        <v>102</v>
+      </c>
+      <c r="G63" s="1">
+        <v>2.3660000000000001</v>
+      </c>
+      <c r="H63" s="1">
+        <v>2631</v>
+      </c>
+      <c r="I63" s="1">
+        <v>3133</v>
+      </c>
+      <c r="J63" s="1">
+        <v>50</v>
+      </c>
+      <c r="K63" s="7">
+        <v>13.736700000000001</v>
+      </c>
+      <c r="L63" s="7">
+        <v>2816897.1982053262</v>
+      </c>
+      <c r="M63" s="7">
+        <v>10038.343378842814</v>
+      </c>
+      <c r="N63" s="7">
+        <v>3116.6814612185526</v>
+      </c>
+      <c r="O63" s="7">
+        <v>6921.6619176242566</v>
+      </c>
+      <c r="P63" s="7">
+        <v>4.7505292902979379</v>
+      </c>
+      <c r="Q63" s="7">
+        <v>172.66364432054371</v>
+      </c>
+      <c r="R63" s="7">
+        <v>8230695.3747049887</v>
+      </c>
+      <c r="S63" s="7">
+        <v>9538173.0741112418</v>
+      </c>
+      <c r="T63" s="7">
+        <v>11098437.139468929</v>
+      </c>
+      <c r="U63" s="7">
+        <v>12319558.161569972</v>
+      </c>
+      <c r="V63" s="7">
+        <v>12746641.887890739</v>
+      </c>
+      <c r="W63" s="7">
+        <v>12799274.609815672</v>
+      </c>
+      <c r="X63" s="7">
+        <v>12358379.09318772</v>
+      </c>
+      <c r="Y63" s="7">
+        <v>11669202.576415919</v>
+      </c>
+      <c r="Z63" s="7">
+        <v>10821137.256861998</v>
+      </c>
+      <c r="AA63" s="7">
+        <v>8234376.679268023</v>
+      </c>
+      <c r="AB63" s="7">
+        <v>9451831.8567371015</v>
+      </c>
+      <c r="AC63" s="7">
+        <v>10751900.705029592</v>
+      </c>
+      <c r="AD63" s="7">
+        <v>11865576.421009786</v>
+      </c>
+      <c r="AE63" s="7">
+        <v>12554835.602166535</v>
+      </c>
+      <c r="AF63" s="7">
+        <v>12549508.142963734</v>
+      </c>
+      <c r="AG63" s="7">
+        <v>12208142.510573501</v>
+      </c>
+      <c r="AH63" s="7">
+        <v>11538784.021214591</v>
+      </c>
+      <c r="AI63" s="7">
+        <v>10548922.531340584</v>
+      </c>
+    </row>
+    <row r="64" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" t="s">
+        <v>34</v>
+      </c>
+      <c r="C64" t="s">
+        <v>36</v>
+      </c>
+      <c r="D64" s="1">
+        <v>72</v>
+      </c>
+      <c r="E64" s="2">
+        <v>65.5</v>
+      </c>
+      <c r="F64" s="1">
+        <v>102</v>
+      </c>
+      <c r="G64" s="1">
+        <v>2.3559999999999999</v>
+      </c>
+      <c r="H64" s="1">
+        <v>2433</v>
+      </c>
+      <c r="I64" s="1">
+        <v>3487</v>
+      </c>
+      <c r="J64" s="1">
+        <v>50</v>
+      </c>
+      <c r="K64" s="7">
+        <v>13.4582</v>
+      </c>
+      <c r="L64" s="7">
+        <v>3156073.0267511434</v>
+      </c>
+      <c r="M64" s="7">
+        <v>10188.792347679693</v>
+      </c>
+      <c r="N64" s="7">
+        <v>2604.7876877560243</v>
+      </c>
+      <c r="O64" s="7">
+        <v>7584.0046599236666</v>
+      </c>
+      <c r="P64" s="7">
+        <v>4.392825507095881</v>
+      </c>
+      <c r="Q64" s="7">
+        <v>146.88216281724678</v>
+      </c>
+      <c r="R64" s="7">
+        <v>7984067.2564927926</v>
+      </c>
+      <c r="S64" s="7">
+        <v>9459088.8131622672</v>
+      </c>
+      <c r="T64" s="7">
+        <v>11048927.692542644</v>
+      </c>
+      <c r="U64" s="7">
+        <v>12587178.832838461</v>
+      </c>
+      <c r="V64" s="7">
+        <v>13453044.211885437</v>
+      </c>
+      <c r="W64" s="7">
+        <v>13518728.106880231</v>
+      </c>
+      <c r="X64" s="7">
+        <v>13021844.284655264</v>
+      </c>
+      <c r="Y64" s="7">
+        <v>12062981.75991039</v>
+      </c>
+      <c r="Z64" s="7">
+        <v>10905221.815022003</v>
+      </c>
+      <c r="AA64" s="7">
+        <v>8014343.9906189367</v>
+      </c>
+      <c r="AB64" s="7">
+        <v>9269732.0674544517</v>
+      </c>
+      <c r="AC64" s="7">
+        <v>10801215.371126428</v>
+      </c>
+      <c r="AD64" s="7">
+        <v>12133040.82801911</v>
+      </c>
+      <c r="AE64" s="7">
+        <v>13036333.015876045</v>
+      </c>
+      <c r="AF64" s="7">
+        <v>13233932.743825909</v>
+      </c>
+      <c r="AG64" s="7">
+        <v>12749434.765670963</v>
+      </c>
+      <c r="AH64" s="7">
+        <v>11869913.325207688</v>
+      </c>
+      <c r="AI64" s="7">
+        <v>10468586.503397355</v>
+      </c>
+    </row>
+    <row r="65" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>44</v>
+      </c>
+      <c r="B65" t="s">
+        <v>34</v>
+      </c>
+      <c r="C65" t="s">
+        <v>36</v>
+      </c>
+      <c r="D65" s="1">
+        <v>73</v>
+      </c>
+      <c r="E65" s="2">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="F65" s="1">
+        <v>102</v>
+      </c>
+      <c r="G65" s="1">
+        <v>2.3559999999999999</v>
+      </c>
+      <c r="H65" s="1">
+        <v>2801</v>
+      </c>
+      <c r="I65" s="1">
+        <v>3235</v>
+      </c>
+      <c r="J65" s="1">
+        <v>2</v>
+      </c>
+      <c r="K65" s="7">
+        <v>5.4879499999999997</v>
+      </c>
+      <c r="L65" s="7">
+        <v>1151014.6273658371</v>
+      </c>
+      <c r="M65" s="7">
+        <v>4548.1945407276326</v>
+      </c>
+      <c r="N65" s="7">
+        <v>1197.9145323927883</v>
+      </c>
+      <c r="O65" s="7">
+        <v>3350.2800083348475</v>
+      </c>
+      <c r="P65" s="7">
+        <v>4.256475068712871</v>
+      </c>
+      <c r="Q65" s="7">
+        <v>171.81019885093946</v>
+      </c>
+      <c r="R65" s="7">
+        <v>2884448.3002249151</v>
+      </c>
+      <c r="S65" s="7">
+        <v>3091907.2405840326</v>
+      </c>
+      <c r="T65" s="7">
+        <v>3122289.9295745655</v>
+      </c>
+      <c r="U65" s="7">
+        <v>3265030.8025081935</v>
+      </c>
+      <c r="V65" s="7">
+        <v>3312507.5594288446</v>
+      </c>
+      <c r="W65" s="7">
+        <v>3308528.395834967</v>
+      </c>
+      <c r="X65" s="7">
+        <v>3337313.5390242366</v>
+      </c>
+      <c r="Y65" s="7">
+        <v>3156667.8267808207</v>
+      </c>
+      <c r="Z65" s="7">
+        <v>3173029.3659618753</v>
+      </c>
+      <c r="AA65" s="7">
+        <v>2864235.2796415794</v>
+      </c>
+      <c r="AB65" s="7">
+        <v>2998660.3496358357</v>
+      </c>
+      <c r="AC65" s="7">
+        <v>3176111.6155520529</v>
+      </c>
+      <c r="AD65" s="7">
+        <v>3214587.2537928512</v>
+      </c>
+      <c r="AE65" s="7">
+        <v>3286635.6862190892</v>
+      </c>
+      <c r="AF65" s="7">
+        <v>3324864.2820702833</v>
+      </c>
+      <c r="AG65" s="7">
+        <v>3230814.5898462576</v>
+      </c>
+      <c r="AH65" s="7">
+        <v>3253098.6515736058</v>
+      </c>
+      <c r="AI65" s="7">
+        <v>3190275.3501116652</v>
+      </c>
+    </row>
+    <row r="66" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>44</v>
+      </c>
+      <c r="B66" t="s">
+        <v>34</v>
+      </c>
+      <c r="C66" t="s">
+        <v>36</v>
+      </c>
+      <c r="D66" s="1">
+        <v>74</v>
+      </c>
+      <c r="E66" s="2">
+        <v>65.7</v>
+      </c>
+      <c r="F66" s="1">
+        <v>102</v>
+      </c>
+      <c r="G66" s="1">
+        <v>2.33</v>
+      </c>
+      <c r="H66" s="1">
+        <v>2281</v>
+      </c>
+      <c r="I66" s="1">
+        <v>3881</v>
+      </c>
+      <c r="J66" s="1">
+        <v>2</v>
+      </c>
+      <c r="K66" s="7">
+        <v>5.8254099999999998</v>
+      </c>
+      <c r="L66" s="7">
+        <v>829864.2010776446</v>
+      </c>
+      <c r="M66" s="7">
+        <v>4539.6704380624597</v>
+      </c>
+      <c r="N66" s="7">
+        <v>1179.7221689977921</v>
+      </c>
+      <c r="O66" s="7">
+        <v>3359.9482690646742</v>
+      </c>
+      <c r="P66" s="7">
+        <v>4.4867796673189826</v>
+      </c>
+      <c r="Q66" s="7">
+        <v>254.99140805170379</v>
+      </c>
+      <c r="R66" s="7">
+        <v>3755318.6845111861</v>
+      </c>
+      <c r="S66" s="7">
+        <v>3908731.7452109726</v>
+      </c>
+      <c r="T66" s="7">
+        <v>3895466.6198228477</v>
+      </c>
+      <c r="U66" s="7">
+        <v>3892075.6515512802</v>
+      </c>
+      <c r="V66" s="7">
+        <v>3807562.3334328248</v>
+      </c>
+      <c r="W66" s="7">
+        <v>3625862.617746505</v>
+      </c>
+      <c r="X66" s="7">
+        <v>3552951.6085832324</v>
+      </c>
+      <c r="Y66" s="7">
+        <v>3482268.8614537069</v>
+      </c>
+      <c r="Z66" s="7">
+        <v>3519551.026214873</v>
+      </c>
+      <c r="AA66" s="7">
+        <v>3728959.4538289481</v>
+      </c>
+      <c r="AB66" s="7">
+        <v>3824109.0294413213</v>
+      </c>
+      <c r="AC66" s="7">
+        <v>3900385.9165386907</v>
+      </c>
+      <c r="AD66" s="7">
+        <v>3851012.9100614488</v>
+      </c>
+      <c r="AE66" s="7">
+        <v>3754255.7826081505</v>
+      </c>
+      <c r="AF66" s="7">
+        <v>3675853.2960935375</v>
+      </c>
+      <c r="AG66" s="7">
+        <v>3552615.3467010288</v>
+      </c>
+      <c r="AH66" s="7">
+        <v>3536172.4486477664</v>
+      </c>
+      <c r="AI66" s="7">
+        <v>3436741.7130575506</v>
+      </c>
+    </row>
+    <row r="67" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A67" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D67" s="4">
+        <v>75</v>
+      </c>
+      <c r="E67" s="5">
+        <v>66.2</v>
+      </c>
+      <c r="F67" s="4">
+        <v>102</v>
+      </c>
+      <c r="G67" s="4">
+        <v>2.3340000000000001</v>
+      </c>
+      <c r="H67" s="4">
+        <v>2751</v>
+      </c>
+      <c r="I67" s="4">
+        <v>3786</v>
+      </c>
+      <c r="J67" s="4">
+        <v>2</v>
+      </c>
+      <c r="K67" s="8">
+        <v>6.7766000000000002</v>
+      </c>
+      <c r="L67" s="8">
+        <v>1160437.0679055045</v>
+      </c>
+      <c r="M67" s="8">
+        <v>5008.2668655035741</v>
+      </c>
+      <c r="N67" s="8">
+        <v>1217.9005746403288</v>
+      </c>
+      <c r="O67" s="8">
+        <v>3790.3662908632396</v>
+      </c>
+      <c r="P67" s="8">
+        <v>3.8677552694214881</v>
+      </c>
+      <c r="Q67" s="8">
+        <v>174.73945780519253</v>
+      </c>
+      <c r="R67" s="8">
+        <v>4397064.6852285871</v>
+      </c>
+      <c r="S67" s="8">
+        <v>4539560.0097320471</v>
+      </c>
+      <c r="T67" s="8">
+        <v>4528811.6882654009</v>
+      </c>
+      <c r="U67" s="8">
+        <v>4478379.049930891</v>
+      </c>
+      <c r="V67" s="8">
+        <v>4353493.703547772</v>
+      </c>
+      <c r="W67" s="8">
+        <v>4334574.8164821649</v>
+      </c>
+      <c r="X67" s="8">
+        <v>4502017.0045491429</v>
+      </c>
+      <c r="Y67" s="8">
+        <v>4597360.3817105191</v>
+      </c>
+      <c r="Z67" s="8">
+        <v>4260879.024304809</v>
+      </c>
+      <c r="AA67" s="8">
+        <v>4232538.0296263658</v>
+      </c>
+      <c r="AB67" s="8">
+        <v>4461965.8859844198</v>
+      </c>
+      <c r="AC67" s="8">
+        <v>4508761.9929531738</v>
+      </c>
+      <c r="AD67" s="8">
+        <v>4439422.4921807731</v>
+      </c>
+      <c r="AE67" s="8">
+        <v>4405303.6797281122</v>
+      </c>
+      <c r="AF67" s="8">
+        <v>4426509.8487542132</v>
+      </c>
+      <c r="AG67" s="8">
+        <v>4462101.9052819517</v>
+      </c>
+      <c r="AH67" s="8">
+        <v>4378130.1886006258</v>
+      </c>
+      <c r="AI67" s="8">
+        <v>4346072.6784139648</v>
+      </c>
+    </row>
+    <row r="68" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68" t="s">
+        <v>34</v>
+      </c>
+      <c r="C68" t="s">
+        <v>37</v>
+      </c>
+      <c r="D68" s="1">
+        <v>76</v>
+      </c>
+      <c r="E68" s="2">
+        <v>66.3</v>
+      </c>
+      <c r="F68" s="1">
+        <v>102</v>
+      </c>
+      <c r="G68" s="1">
+        <v>2.2909999999999999</v>
+      </c>
+      <c r="H68" s="1">
+        <v>2111</v>
+      </c>
+      <c r="I68" s="1">
+        <v>3532</v>
+      </c>
+      <c r="J68" s="1">
+        <v>2</v>
+      </c>
+      <c r="K68" s="7">
+        <v>4.6527000000000003</v>
+      </c>
+      <c r="L68" s="7">
+        <v>1020949.5628362276</v>
+      </c>
+      <c r="M68" s="7">
+        <v>4318.2823152684923</v>
+      </c>
+      <c r="N68" s="7">
+        <v>1521.347440899907</v>
+      </c>
+      <c r="O68" s="7">
+        <v>2796.9348743685891</v>
+      </c>
+      <c r="P68" s="7">
+        <v>5.7915149467213105</v>
+      </c>
+      <c r="Q68" s="7">
+        <v>256.81512211479895</v>
+      </c>
+      <c r="R68" s="7">
+        <v>2074581.3820029823</v>
+      </c>
+      <c r="S68" s="7">
+        <v>2025895.5325133214</v>
+      </c>
+      <c r="T68" s="7">
+        <v>2009588.5265845361</v>
+      </c>
+      <c r="U68" s="7">
+        <v>2031369.368610455</v>
+      </c>
+      <c r="V68" s="7">
+        <v>1935044.7198747774</v>
+      </c>
+      <c r="W68" s="7">
+        <v>1669735.5217451532</v>
+      </c>
+      <c r="X68" s="7">
+        <v>1496678.1436847176</v>
+      </c>
+      <c r="Y68" s="7">
+        <v>1543664.5561650405</v>
+      </c>
+      <c r="Z68" s="7">
+        <v>1420800.9360080655</v>
+      </c>
+      <c r="AA68" s="7">
+        <v>2047640.9906974805</v>
+      </c>
+      <c r="AB68" s="7">
+        <v>2041567.827025552</v>
+      </c>
+      <c r="AC68" s="7">
+        <v>2028628.7580643129</v>
+      </c>
+      <c r="AD68" s="7">
+        <v>1971612.2764917477</v>
+      </c>
+      <c r="AE68" s="7">
+        <v>1832884.8779143929</v>
+      </c>
+      <c r="AF68" s="7">
+        <v>1687863.0672904199</v>
+      </c>
+      <c r="AG68" s="7">
+        <v>1604226.9749143692</v>
+      </c>
+      <c r="AH68" s="7">
+        <v>1457752.8402870221</v>
+      </c>
+      <c r="AI68" s="7">
+        <v>1403447.2767509099</v>
+      </c>
+    </row>
+    <row r="69" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>44</v>
+      </c>
+      <c r="B69" t="s">
+        <v>34</v>
+      </c>
+      <c r="C69" t="s">
+        <v>37</v>
+      </c>
+      <c r="D69" s="1">
+        <v>77</v>
+      </c>
+      <c r="E69" s="2">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="F69" s="1">
+        <v>102</v>
+      </c>
+      <c r="G69" s="1">
+        <v>2.3170000000000002</v>
+      </c>
+      <c r="H69" s="1">
+        <v>2709</v>
+      </c>
+      <c r="I69" s="1">
+        <v>3922</v>
+      </c>
+      <c r="J69" s="1">
+        <v>2</v>
+      </c>
+      <c r="K69" s="7">
+        <v>6.5720799999999997</v>
+      </c>
+      <c r="L69" s="7">
+        <v>1013124.7153204391</v>
+      </c>
+      <c r="M69" s="7">
+        <v>4739.0321903993272</v>
+      </c>
+      <c r="N69" s="7">
+        <v>1322.3960331668925</v>
+      </c>
+      <c r="O69" s="7">
+        <v>3416.6361572324395</v>
+      </c>
+      <c r="P69" s="7">
+        <v>4.2786538666666667</v>
+      </c>
+      <c r="Q69" s="7">
+        <v>208.5582895287765</v>
+      </c>
+      <c r="R69" s="7">
+        <v>3790126.2225320097</v>
+      </c>
+      <c r="S69" s="7">
+        <v>3890923.129794511</v>
+      </c>
+      <c r="T69" s="7">
+        <v>4125478.9244336151</v>
+      </c>
+      <c r="U69" s="7">
+        <v>4205264.3793105781</v>
+      </c>
+      <c r="V69" s="7">
+        <v>4037518.348741963</v>
+      </c>
+      <c r="W69" s="7">
+        <v>4077415.7422948801</v>
+      </c>
+      <c r="X69" s="7">
+        <v>4383677.0704330197</v>
+      </c>
+      <c r="Y69" s="7">
+        <v>4664277.8992124097</v>
+      </c>
+      <c r="Z69" s="7">
+        <v>4265057.7321245829</v>
+      </c>
+      <c r="AA69" s="7">
+        <v>3740060.3044540528</v>
+      </c>
+      <c r="AB69" s="7">
+        <v>3950698.7935073916</v>
+      </c>
+      <c r="AC69" s="7">
+        <v>4041991.4736310486</v>
+      </c>
+      <c r="AD69" s="7">
+        <v>4081024.7259262339</v>
+      </c>
+      <c r="AE69" s="7">
+        <v>4140353.3467351324</v>
+      </c>
+      <c r="AF69" s="7">
+        <v>4203483.1697485307</v>
+      </c>
+      <c r="AG69" s="7">
+        <v>4351147.7094975272</v>
+      </c>
+      <c r="AH69" s="7">
+        <v>4323553.9558592141</v>
+      </c>
+      <c r="AI69" s="7">
+        <v>4203584.6169810332</v>
+      </c>
+    </row>
+    <row r="70" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" t="s">
+        <v>34</v>
+      </c>
+      <c r="C70" t="s">
+        <v>37</v>
+      </c>
+      <c r="D70" s="1">
+        <v>78</v>
+      </c>
+      <c r="E70" s="2">
+        <v>65</v>
+      </c>
+      <c r="F70" s="1">
+        <v>102</v>
+      </c>
+      <c r="G70" s="1">
+        <v>2.3439999999999999</v>
+      </c>
+      <c r="H70" s="1">
+        <v>2341</v>
+      </c>
+      <c r="I70" s="1">
+        <v>3430</v>
+      </c>
+      <c r="J70" s="1">
+        <v>50</v>
+      </c>
+      <c r="K70" s="7">
+        <v>13.179</v>
+      </c>
+      <c r="L70" s="7">
+        <v>2701928.4775373684</v>
+      </c>
+      <c r="M70" s="7">
+        <v>9322.6515421826098</v>
+      </c>
+      <c r="N70" s="7">
+        <v>2909.0549379978434</v>
+      </c>
+      <c r="O70" s="7">
+        <v>6413.5966041847669</v>
+      </c>
+      <c r="P70" s="7">
+        <v>4.7888263398619673</v>
+      </c>
+      <c r="Q70" s="7">
+        <v>169.83069489706077</v>
+      </c>
+      <c r="R70" s="7">
+        <v>7102012.2562517617</v>
+      </c>
+      <c r="S70" s="7">
+        <v>8415898.9111962672</v>
+      </c>
+      <c r="T70" s="7">
+        <v>9818632.5469664652</v>
+      </c>
+      <c r="U70" s="7">
+        <v>10832717.093716698</v>
+      </c>
+      <c r="V70" s="7">
+        <v>11266111.181369718</v>
+      </c>
+      <c r="W70" s="7">
+        <v>11101909.626634283</v>
+      </c>
+      <c r="X70" s="7">
+        <v>10528730.523021366</v>
+      </c>
+      <c r="Y70" s="7">
+        <v>9760389.1663357522</v>
+      </c>
+      <c r="Z70" s="7">
+        <v>8847907.6129424926</v>
+      </c>
+      <c r="AA70" s="7">
+        <v>7123275.4039001344</v>
+      </c>
+      <c r="AB70" s="7">
+        <v>8242244.8434028449</v>
+      </c>
+      <c r="AC70" s="7">
+        <v>9472582.545263337</v>
+      </c>
+      <c r="AD70" s="7">
+        <v>10492686.783238269</v>
+      </c>
+      <c r="AE70" s="7">
+        <v>10965661.528560061</v>
+      </c>
+      <c r="AF70" s="7">
+        <v>10884947.023693344</v>
+      </c>
+      <c r="AG70" s="7">
+        <v>10388017.113622546</v>
+      </c>
+      <c r="AH70" s="7">
+        <v>9615417.7309382651</v>
+      </c>
+      <c r="AI70" s="7">
+        <v>8699075.6066776216</v>
+      </c>
+    </row>
+    <row r="71" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" t="s">
+        <v>34</v>
+      </c>
+      <c r="C71" t="s">
+        <v>37</v>
+      </c>
+      <c r="D71" s="1">
+        <v>79</v>
+      </c>
+      <c r="E71" s="2">
+        <v>65.8</v>
+      </c>
+      <c r="F71" s="1">
+        <v>102</v>
+      </c>
+      <c r="G71" s="1">
+        <v>2.302</v>
+      </c>
+      <c r="H71" s="1">
+        <v>2449</v>
+      </c>
+      <c r="I71" s="1">
+        <v>3352</v>
+      </c>
+      <c r="J71" s="1">
+        <v>2</v>
+      </c>
+      <c r="K71" s="7">
+        <v>5.5578700000000003</v>
+      </c>
+      <c r="L71" s="7">
+        <v>807749.49012524239</v>
+      </c>
+      <c r="M71" s="7">
+        <v>5483.5344796121071</v>
+      </c>
+      <c r="N71" s="7">
+        <v>1736.2019488072226</v>
+      </c>
+      <c r="O71" s="7">
+        <v>3747.3325308048852</v>
+      </c>
+      <c r="P71" s="7">
+        <v>5.8276025178684812</v>
+      </c>
+      <c r="Q71" s="7">
+        <v>411.63077873400141</v>
+      </c>
+      <c r="R71" s="7">
+        <v>2668609.1321958737</v>
+      </c>
+      <c r="S71" s="7">
+        <v>2679402.9671900682</v>
+      </c>
+      <c r="T71" s="7">
+        <v>2700949.7248871387</v>
+      </c>
+      <c r="U71" s="7">
+        <v>2592205.8871506322</v>
+      </c>
+      <c r="V71" s="7">
+        <v>2556165.5560429902</v>
+      </c>
+      <c r="W71" s="7">
+        <v>2545547.261298134</v>
+      </c>
+      <c r="X71" s="7">
+        <v>2282954.7943807943</v>
+      </c>
+      <c r="Y71" s="7">
+        <v>2060003.9676997671</v>
+      </c>
+      <c r="Z71" s="7">
+        <v>1965050.4971607281</v>
+      </c>
+      <c r="AA71" s="7">
+        <v>2624155.5080683902</v>
+      </c>
+      <c r="AB71" s="7">
+        <v>2684682.0356305186</v>
+      </c>
+      <c r="AC71" s="7">
+        <v>2635083.2686988576</v>
+      </c>
+      <c r="AD71" s="7">
+        <v>2626563.9182022172</v>
+      </c>
+      <c r="AE71" s="7">
+        <v>2568664.7085212693</v>
+      </c>
+      <c r="AF71" s="7">
+        <v>2411847.6040333826</v>
+      </c>
+      <c r="AG71" s="7">
+        <v>2277181.2525826194</v>
+      </c>
+      <c r="AH71" s="7">
+        <v>2112107.2813285119</v>
+      </c>
+      <c r="AI71" s="7">
+        <v>1976132.0672013799</v>
+      </c>
+    </row>
+    <row r="72" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" t="s">
+        <v>34</v>
+      </c>
+      <c r="C72" t="s">
+        <v>37</v>
+      </c>
+      <c r="D72" s="1">
+        <v>80</v>
+      </c>
+      <c r="E72" s="2">
+        <v>65.5</v>
+      </c>
+      <c r="F72" s="1">
+        <v>102</v>
+      </c>
+      <c r="G72" s="1">
+        <v>2.3410000000000002</v>
+      </c>
+      <c r="H72" s="1">
+        <v>2611</v>
+      </c>
+      <c r="I72" s="1">
+        <v>3612</v>
+      </c>
+      <c r="J72" s="1">
+        <v>50</v>
+      </c>
+      <c r="K72" s="7">
+        <v>13.413500000000001</v>
+      </c>
+      <c r="L72" s="7">
+        <v>3017000.3292398504</v>
+      </c>
+      <c r="M72" s="7">
+        <v>9986.1020950719012</v>
+      </c>
+      <c r="N72" s="7">
+        <v>2854.4064674631641</v>
+      </c>
+      <c r="O72" s="7">
+        <v>7131.6956276087431</v>
+      </c>
+      <c r="P72" s="7">
+        <v>4.8933022323739195</v>
+      </c>
+      <c r="Q72" s="7">
+        <v>167.75370609134796</v>
+      </c>
+      <c r="R72" s="7">
+        <v>8259780.153861667</v>
+      </c>
+      <c r="S72" s="7">
+        <v>9485289.4677612018</v>
+      </c>
+      <c r="T72" s="7">
+        <v>10622803.974049468</v>
+      </c>
+      <c r="U72" s="7">
+        <v>11365492.370510038</v>
+      </c>
+      <c r="V72" s="7">
+        <v>11416510.441143354</v>
+      </c>
+      <c r="W72" s="7">
+        <v>11054894.192467518</v>
+      </c>
+      <c r="X72" s="7">
+        <v>10341517.134555725</v>
+      </c>
+      <c r="Y72" s="7">
+        <v>9291853.6538337599</v>
+      </c>
+      <c r="Z72" s="7">
+        <v>8187736.433232381</v>
+      </c>
+      <c r="AA72" s="7">
+        <v>8169360.4732299624</v>
+      </c>
+      <c r="AB72" s="7">
+        <v>9293434.0817813687</v>
+      </c>
+      <c r="AC72" s="7">
+        <v>10340618.007910384</v>
+      </c>
+      <c r="AD72" s="7">
+        <v>11005365.248598985</v>
+      </c>
+      <c r="AE72" s="7">
+        <v>11208041.863895411</v>
+      </c>
+      <c r="AF72" s="7">
+        <v>10852457.828096578</v>
+      </c>
+      <c r="AG72" s="7">
+        <v>10096990.415468082</v>
+      </c>
+      <c r="AH72" s="7">
+        <v>9139452.5211418513</v>
+      </c>
+      <c r="AI72" s="7">
+        <v>8053420.6140141198</v>
+      </c>
+    </row>
+    <row r="73" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A73" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D73" s="4">
+        <v>81</v>
+      </c>
+      <c r="E73" s="5">
+        <v>64.8</v>
+      </c>
+      <c r="F73" s="4">
+        <v>102</v>
+      </c>
+      <c r="G73" s="4">
+        <v>2.359</v>
+      </c>
+      <c r="H73" s="4">
+        <v>3262</v>
+      </c>
+      <c r="I73" s="4">
+        <v>4253</v>
+      </c>
+      <c r="J73" s="4">
+        <v>50</v>
+      </c>
+      <c r="K73" s="8">
+        <v>14.408300000000001</v>
+      </c>
+      <c r="L73" s="8">
+        <v>3021503.9234796325</v>
+      </c>
+      <c r="M73" s="8">
+        <v>11242.595396331264</v>
+      </c>
+      <c r="N73" s="8">
+        <v>3186.0599703664147</v>
+      </c>
+      <c r="O73" s="8">
+        <v>8056.5354259648448</v>
+      </c>
+      <c r="P73" s="8">
+        <v>5.1131158576271183</v>
+      </c>
+      <c r="Q73" s="8">
+        <v>194.94504315990326</v>
+      </c>
+      <c r="R73" s="8">
+        <v>8428337.7357779127</v>
+      </c>
+      <c r="S73" s="8">
+        <v>10106794.687398391</v>
+      </c>
+      <c r="T73" s="8">
+        <v>11719149.317784833</v>
+      </c>
+      <c r="U73" s="8">
+        <v>12585691.598319387</v>
+      </c>
+      <c r="V73" s="8">
+        <v>12990470.587748043</v>
+      </c>
+      <c r="W73" s="8">
+        <v>12833287.183445068</v>
+      </c>
+      <c r="X73" s="8">
+        <v>12200143.402406527</v>
+      </c>
+      <c r="Y73" s="8">
+        <v>11403986.00115549</v>
+      </c>
+      <c r="Z73" s="8">
+        <v>10316168.876796452</v>
+      </c>
+      <c r="AA73" s="8">
+        <v>8301756.3745862553</v>
+      </c>
+      <c r="AB73" s="8">
+        <v>9804989.3928419761</v>
+      </c>
+      <c r="AC73" s="8">
+        <v>11210847.448054807</v>
+      </c>
+      <c r="AD73" s="8">
+        <v>12322104.921737228</v>
+      </c>
+      <c r="AE73" s="8">
+        <v>12708283.528634572</v>
+      </c>
+      <c r="AF73" s="8">
+        <v>12582909.181746218</v>
+      </c>
+      <c r="AG73" s="8">
+        <v>12076492.786474129</v>
+      </c>
+      <c r="AH73" s="8">
+        <v>11179338.614574844</v>
+      </c>
+      <c r="AI73" s="8">
+        <v>9990636.458056353</v>
+      </c>
+    </row>
+    <row r="74" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>44</v>
+      </c>
+      <c r="B74" t="s">
+        <v>34</v>
+      </c>
+      <c r="C74" t="s">
+        <v>38</v>
+      </c>
+      <c r="D74" s="1">
+        <v>82</v>
+      </c>
+      <c r="E74" s="2">
+        <v>66.5</v>
+      </c>
+      <c r="F74" s="1">
+        <v>102</v>
+      </c>
+      <c r="G74" s="1">
+        <v>2.3079999999999998</v>
+      </c>
+      <c r="H74" s="1">
+        <v>3130</v>
+      </c>
+      <c r="I74" s="1">
+        <v>3991</v>
+      </c>
+      <c r="J74" s="1">
+        <v>2</v>
+      </c>
+      <c r="K74" s="7">
+        <v>6.9010699999999998</v>
+      </c>
+      <c r="L74" s="7">
+        <v>1269921.8385419014</v>
+      </c>
+      <c r="M74" s="7">
+        <v>4875.2565857940945</v>
+      </c>
+      <c r="N74" s="7">
+        <v>1291.0842986814714</v>
+      </c>
+      <c r="O74" s="7">
+        <v>3584.1722871126321</v>
+      </c>
+      <c r="P74" s="7">
+        <v>4.2405902608695651</v>
+      </c>
+      <c r="Q74" s="7">
+        <v>171.18928639231294</v>
+      </c>
+      <c r="R74" s="7">
+        <v>4242901.0481925011</v>
+      </c>
+      <c r="S74" s="7">
+        <v>4289450.2657636721</v>
+      </c>
+      <c r="T74" s="7">
+        <v>4316965.3704233123</v>
+      </c>
+      <c r="U74" s="7">
+        <v>4401948.4115863536</v>
+      </c>
+      <c r="V74" s="7">
+        <v>4348636.7831268245</v>
+      </c>
+      <c r="W74" s="7">
+        <v>4433860.0437347302</v>
+      </c>
+      <c r="X74" s="7">
+        <v>4728988.1015359452</v>
+      </c>
+      <c r="Y74" s="7">
+        <v>4696431.8848801842</v>
+      </c>
+      <c r="Z74" s="7">
+        <v>4279013.7134188004</v>
+      </c>
+      <c r="AA74" s="7">
+        <v>4051637.1027000817</v>
+      </c>
+      <c r="AB74" s="7">
+        <v>4279612.7881962191</v>
+      </c>
+      <c r="AC74" s="7">
+        <v>4344971.2721529622</v>
+      </c>
+      <c r="AD74" s="7">
+        <v>4332743.199759434</v>
+      </c>
+      <c r="AE74" s="7">
+        <v>4417846.6012264965</v>
+      </c>
+      <c r="AF74" s="7">
+        <v>4530844.1066018492</v>
+      </c>
+      <c r="AG74" s="7">
+        <v>4561370.402019769</v>
+      </c>
+      <c r="AH74" s="7">
+        <v>4492762.1802812237</v>
+      </c>
+      <c r="AI74" s="7">
+        <v>4435957.0110770138</v>
+      </c>
+    </row>
+    <row r="75" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>44</v>
+      </c>
+      <c r="B75" t="s">
+        <v>34</v>
+      </c>
+      <c r="C75" t="s">
+        <v>38</v>
+      </c>
+      <c r="D75" s="1">
+        <v>83</v>
+      </c>
+      <c r="E75" s="2">
+        <v>67.2</v>
+      </c>
+      <c r="F75" s="1">
+        <v>102</v>
+      </c>
+      <c r="G75" s="1">
+        <v>2.3210000000000002</v>
+      </c>
+      <c r="H75" s="1">
+        <v>3724</v>
+      </c>
+      <c r="I75" s="1">
+        <v>4687</v>
+      </c>
+      <c r="J75" s="1">
+        <v>50</v>
+      </c>
+      <c r="K75" s="7">
+        <v>15.5212</v>
+      </c>
+      <c r="L75" s="7">
+        <v>4038821.2392434534</v>
+      </c>
+      <c r="M75" s="7">
+        <v>10521.021519435029</v>
+      </c>
+      <c r="N75" s="7">
+        <v>2484.7078541280789</v>
+      </c>
+      <c r="O75" s="7">
+        <v>8036.3136653069514</v>
+      </c>
+      <c r="P75" s="7">
+        <v>4.641698949950932</v>
+      </c>
+      <c r="Q75" s="7">
+        <v>128.48654731222763</v>
+      </c>
+      <c r="R75" s="7">
+        <v>11268315.269053299</v>
+      </c>
+      <c r="S75" s="7">
+        <v>13217242.340792764</v>
+      </c>
+      <c r="T75" s="7">
+        <v>14934660.83687561</v>
+      </c>
+      <c r="U75" s="7">
+        <v>15758139.893250328</v>
+      </c>
+      <c r="V75" s="7">
+        <v>15754909.737499053</v>
+      </c>
+      <c r="W75" s="7">
+        <v>15178027.112061063</v>
+      </c>
+      <c r="X75" s="7">
+        <v>14274963.206530932</v>
+      </c>
+      <c r="Y75" s="7">
+        <v>13283572.743293528</v>
+      </c>
+      <c r="Z75" s="7">
+        <v>11777908.814972773</v>
+      </c>
+      <c r="AA75" s="7">
+        <v>10951630.292714601</v>
+      </c>
+      <c r="AB75" s="7">
+        <v>12844988.757457927</v>
+      </c>
+      <c r="AC75" s="7">
+        <v>14376283.434459563</v>
+      </c>
+      <c r="AD75" s="7">
+        <v>15333823.774100279</v>
+      </c>
+      <c r="AE75" s="7">
+        <v>15462644.386057293</v>
+      </c>
+      <c r="AF75" s="7">
+        <v>14978468.756373856</v>
+      </c>
+      <c r="AG75" s="7">
+        <v>14167750.812842187</v>
+      </c>
+      <c r="AH75" s="7">
+        <v>12906770.113087032</v>
+      </c>
+      <c r="AI75" s="7">
+        <v>11519063.238606704</v>
+      </c>
+    </row>
+    <row r="76" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>44</v>
+      </c>
+      <c r="B76" t="s">
+        <v>34</v>
+      </c>
+      <c r="C76" t="s">
+        <v>38</v>
+      </c>
+      <c r="D76" s="1">
+        <v>84</v>
+      </c>
+      <c r="E76" s="2">
+        <v>66.900000000000006</v>
+      </c>
+      <c r="F76" s="1">
+        <v>102</v>
+      </c>
+      <c r="G76" s="1">
+        <v>2.3119999999999998</v>
+      </c>
+      <c r="H76" s="1">
+        <v>2765</v>
+      </c>
+      <c r="I76" s="1">
+        <v>3499</v>
+      </c>
+      <c r="J76" s="1">
+        <v>2</v>
+      </c>
+      <c r="K76" s="9">
+        <v>6.1210899999999997</v>
+      </c>
+      <c r="L76" s="11">
+        <v>1206675.8793196818</v>
+      </c>
+      <c r="M76" s="11">
+        <v>4992.7333605269741</v>
+      </c>
+      <c r="N76" s="11">
+        <v>1764.3685767407994</v>
+      </c>
+      <c r="O76" s="11">
+        <v>3228.3647837861686</v>
+      </c>
+      <c r="P76" s="11">
+        <v>6.8454060260309273</v>
+      </c>
+      <c r="Q76" s="11">
+        <v>299.62718268091146</v>
+      </c>
+      <c r="R76" s="10">
+        <v>1163620.5307454816</v>
+      </c>
+      <c r="S76" s="10">
+        <v>1255202.5363488451</v>
+      </c>
+      <c r="T76" s="10">
+        <v>1421993.2084577514</v>
+      </c>
+      <c r="U76" s="10">
+        <v>1569925.1431572591</v>
+      </c>
+      <c r="V76" s="10">
+        <v>2234242.2267258377</v>
+      </c>
+      <c r="W76" s="10">
+        <v>3362565.6067209137</v>
+      </c>
+      <c r="X76" s="10">
+        <v>3249236.7911550105</v>
+      </c>
+      <c r="Y76" s="10">
+        <v>2972058.9687339873</v>
+      </c>
+      <c r="Z76" s="10">
+        <v>2813086.6974220942</v>
+      </c>
+      <c r="AA76" s="10">
+        <v>973341.40005220741</v>
+      </c>
+      <c r="AB76" s="10">
+        <v>1279897.6636409499</v>
+      </c>
+      <c r="AC76" s="10">
+        <v>1395033.6021013507</v>
+      </c>
+      <c r="AD76" s="10">
+        <v>1737895.3455135669</v>
+      </c>
+      <c r="AE76" s="10">
+        <v>2140491.1065012706</v>
+      </c>
+      <c r="AF76" s="10">
+        <v>2647801.5215366804</v>
+      </c>
+      <c r="AG76" s="10">
+        <v>3155275.6285304138</v>
+      </c>
+      <c r="AH76" s="10">
+        <v>3015472.470644407</v>
+      </c>
+      <c r="AI76" s="10">
+        <v>2845375.4467195841</v>
+      </c>
+    </row>
+    <row r="77" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>44</v>
+      </c>
+      <c r="B77" t="s">
+        <v>34</v>
+      </c>
+      <c r="C77" t="s">
+        <v>38</v>
+      </c>
+      <c r="D77" s="1">
+        <v>85</v>
+      </c>
+      <c r="E77" s="2">
+        <v>65.8</v>
+      </c>
+      <c r="F77" s="1">
+        <v>102</v>
+      </c>
+      <c r="G77" s="1">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="H77" s="1">
+        <v>3728</v>
+      </c>
+      <c r="I77" s="1">
+        <v>4383</v>
+      </c>
+      <c r="J77" s="1">
+        <v>50</v>
+      </c>
+      <c r="K77" s="7">
+        <v>15.0379</v>
+      </c>
+      <c r="L77" s="7">
+        <v>3585534.0727804699</v>
+      </c>
+      <c r="M77" s="7">
+        <v>10496.418007944452</v>
+      </c>
+      <c r="N77" s="7">
+        <v>2909.3105736091265</v>
+      </c>
+      <c r="O77" s="7">
+        <v>7587.107434335333</v>
+      </c>
+      <c r="P77" s="7">
+        <v>4.7816678260238161</v>
+      </c>
+      <c r="Q77" s="7">
+        <v>145.64671685748391</v>
+      </c>
+      <c r="R77" s="7">
+        <v>6141939.7206837069</v>
+      </c>
+      <c r="S77" s="7">
+        <v>7428940.4894149238</v>
+      </c>
+      <c r="T77" s="7">
+        <v>8856841.998911947</v>
+      </c>
+      <c r="U77" s="7">
+        <v>9973398.6949927825</v>
+      </c>
+      <c r="V77" s="7">
+        <v>10616766.244712193</v>
+      </c>
+      <c r="W77" s="7">
+        <v>10836802.497070855</v>
+      </c>
+      <c r="X77" s="7">
+        <v>10669132.346404443</v>
+      </c>
+      <c r="Y77" s="7">
+        <v>10261093.256145814</v>
+      </c>
+      <c r="Z77" s="7">
+        <v>9699484.414150428</v>
+      </c>
+      <c r="AA77" s="7">
+        <v>6235014.5045778276</v>
+      </c>
+      <c r="AB77" s="7">
+        <v>7253681.0908937566</v>
+      </c>
+      <c r="AC77" s="7">
+        <v>8515152.4283235688</v>
+      </c>
+      <c r="AD77" s="7">
+        <v>9657277.6850006059</v>
+      </c>
+      <c r="AE77" s="7">
+        <v>10387189.521588983</v>
+      </c>
+      <c r="AF77" s="7">
+        <v>10642884.881819928</v>
+      </c>
+      <c r="AG77" s="7">
+        <v>10541093.038050892</v>
+      </c>
+      <c r="AH77" s="7">
+        <v>10161228.337003576</v>
+      </c>
+      <c r="AI77" s="7">
+        <v>9592554.8086781595</v>
+      </c>
+    </row>
+    <row r="78" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>44</v>
+      </c>
+      <c r="B78" t="s">
+        <v>34</v>
+      </c>
+      <c r="C78" t="s">
+        <v>38</v>
+      </c>
+      <c r="D78" s="1">
+        <v>86</v>
+      </c>
+      <c r="E78" s="2">
+        <v>66.3</v>
+      </c>
+      <c r="F78" s="1">
+        <v>102</v>
+      </c>
+      <c r="G78" s="1">
+        <v>2.3180000000000001</v>
+      </c>
+      <c r="H78" s="1">
+        <v>3716</v>
+      </c>
+      <c r="I78" s="1">
+        <v>4209</v>
+      </c>
+      <c r="J78" s="1">
+        <v>50</v>
+      </c>
+      <c r="K78" s="7">
+        <v>15.1938</v>
+      </c>
+      <c r="L78" s="7">
+        <v>4071618.064604742</v>
+      </c>
+      <c r="M78" s="7">
+        <v>10423.498481771294</v>
+      </c>
+      <c r="N78" s="7">
+        <v>3572.3914954265365</v>
+      </c>
+      <c r="O78" s="7">
+        <v>6851.1069863447483</v>
+      </c>
+      <c r="P78" s="7">
+        <v>4.061993260980592</v>
+      </c>
+      <c r="Q78" s="7">
+        <v>109.02029193323285</v>
+      </c>
+      <c r="R78" s="7">
+        <v>10330503.963502156</v>
+      </c>
+      <c r="S78" s="7">
+        <v>12299553.880710576</v>
+      </c>
+      <c r="T78" s="7">
+        <v>13965151.044152563</v>
+      </c>
+      <c r="U78" s="7">
+        <v>14682399.547353981</v>
+      </c>
+      <c r="V78" s="7">
+        <v>14850336.943615744</v>
+      </c>
+      <c r="W78" s="7">
+        <v>14280051.81094683</v>
+      </c>
+      <c r="X78" s="7">
+        <v>13214111.293560712</v>
+      </c>
+      <c r="Y78" s="7">
+        <v>12073126.248628555</v>
+      </c>
+      <c r="Z78" s="7">
+        <v>10653307.205838492</v>
+      </c>
+      <c r="AA78" s="7">
+        <v>10146545.622867808</v>
+      </c>
+      <c r="AB78" s="7">
+        <v>11875954.623744104</v>
+      </c>
+      <c r="AC78" s="7">
+        <v>13385759.100967698</v>
+      </c>
+      <c r="AD78" s="7">
+        <v>14394147.936150532</v>
+      </c>
+      <c r="AE78" s="7">
+        <v>14478430.962311881</v>
+      </c>
+      <c r="AF78" s="7">
+        <v>13984526.149341295</v>
+      </c>
+      <c r="AG78" s="7">
+        <v>13084180.432490559</v>
+      </c>
+      <c r="AH78" s="7">
+        <v>11796331.225849643</v>
+      </c>
+      <c r="AI78" s="7">
+        <v>10314866.900941689</v>
+      </c>
+    </row>
+    <row r="79" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A79" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D79" s="4">
+        <v>87</v>
+      </c>
+      <c r="E79" s="5">
+        <v>66.5</v>
+      </c>
+      <c r="F79" s="4">
+        <v>102</v>
+      </c>
+      <c r="G79" s="4">
+        <v>2.3090000000000002</v>
+      </c>
+      <c r="H79" s="4">
+        <v>3188</v>
+      </c>
+      <c r="I79" s="4">
+        <v>3736</v>
+      </c>
+      <c r="J79" s="4">
+        <v>2</v>
+      </c>
+      <c r="K79" s="8">
+        <v>8.1847799999999999</v>
+      </c>
+      <c r="L79" s="8">
+        <v>1783882.5972697779</v>
+      </c>
+      <c r="M79" s="8">
+        <v>6016.0070791490389</v>
+      </c>
+      <c r="N79" s="8">
+        <v>1869.6104458186428</v>
+      </c>
+      <c r="O79" s="8">
+        <v>4146.3966333303961</v>
+      </c>
+      <c r="P79" s="8">
+        <v>4.2915705919480516</v>
+      </c>
+      <c r="Q79" s="8">
+        <v>152.19069998990179</v>
+      </c>
+      <c r="R79" s="8">
+        <v>3353807.2266779765</v>
+      </c>
+      <c r="S79" s="8">
+        <v>4008455.3942691307</v>
+      </c>
+      <c r="T79" s="8">
+        <v>4104075.4363839338</v>
+      </c>
+      <c r="U79" s="8">
+        <v>4448912.7641885774</v>
+      </c>
+      <c r="V79" s="8">
+        <v>5093956.1107698251</v>
+      </c>
+      <c r="W79" s="8">
+        <v>5134418.876687739</v>
+      </c>
+      <c r="X79" s="8">
+        <v>4944748.9084658902</v>
+      </c>
+      <c r="Y79" s="8">
+        <v>4646056.2269365368</v>
+      </c>
+      <c r="Z79" s="8">
+        <v>4559025.5339102643</v>
+      </c>
+      <c r="AA79" s="8">
+        <v>3036491.0528198271</v>
+      </c>
+      <c r="AB79" s="8">
+        <v>3691202.5783266863</v>
+      </c>
+      <c r="AC79" s="8">
+        <v>4217214.6308684712</v>
+      </c>
+      <c r="AD79" s="8">
+        <v>4545750.9122584881</v>
+      </c>
+      <c r="AE79" s="8">
+        <v>4767148.3223548541</v>
+      </c>
+      <c r="AF79" s="8">
+        <v>5018243.6619539056</v>
+      </c>
+      <c r="AG79" s="8">
+        <v>4878044.9908605926</v>
+      </c>
+      <c r="AH79" s="8">
+        <v>4744059.6721137231</v>
+      </c>
+      <c r="AI79" s="8">
+        <v>4430359.1002791366</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI61" xr:uid="{F6820742-B6BB-224A-B3FC-2A5B149FF72F}"/>
+  <autoFilter ref="A1:AI79" xr:uid="{F6820742-B6BB-224A-B3FC-2A5B149FF72F}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davitt/Desktop/Analisis_Asfalto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB0AA89-6904-2048-9625-D73E6BD35753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C499961F-3776-B849-990A-D27AED9B7694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{FC2B8901-ED9E-184C-BCB1-2CFD191E8EE2}"/>
+    <workbookView xWindow="28800" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{FC2B8901-ED9E-184C-BCB1-2CFD191E8EE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="46">
   <si>
     <t>Mezcla</t>
   </si>
@@ -178,6 +178,9 @@
   <si>
     <t>SMA16</t>
   </si>
+  <si>
+    <t>lpeak</t>
+  </si>
 </sst>
 </file>
 
@@ -242,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -257,7 +260,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -273,7 +275,15 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -728,6 +738,9 @@
       <c r="AI1" t="s">
         <v>26</v>
       </c>
+      <c r="AJ1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -760,80 +773,83 @@
       <c r="J2" s="1">
         <v>50</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="6">
         <v>14.1927</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="6">
         <v>8253403.0808814485</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="6">
         <v>5597.4518901650481</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="6">
         <v>2128.1711928904156</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="6">
         <v>3469.2806972746257</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="6">
         <v>2.6147409980476923</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="6">
         <v>17.465246584084589</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="6">
         <v>8116282.1562428633</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="6">
         <v>8878277.5150890499</v>
       </c>
-      <c r="T2" s="7">
+      <c r="T2" s="6">
         <v>9824307.8994215354</v>
       </c>
-      <c r="U2" s="7">
+      <c r="U2" s="6">
         <v>11166257.477405874</v>
       </c>
-      <c r="V2" s="7">
+      <c r="V2" s="6">
         <v>12603732.951070141</v>
       </c>
-      <c r="W2" s="7">
+      <c r="W2" s="6">
         <v>13336407.271943403</v>
       </c>
-      <c r="X2" s="7">
+      <c r="X2" s="6">
         <v>13474679.314941157</v>
       </c>
-      <c r="Y2" s="7">
+      <c r="Y2" s="6">
         <v>13110828.453251969</v>
       </c>
-      <c r="Z2" s="7">
+      <c r="Z2" s="6">
         <v>12451426.432672478</v>
       </c>
-      <c r="AA2" s="7">
+      <c r="AA2" s="6">
         <v>8132758.3531402349</v>
       </c>
-      <c r="AB2" s="7">
+      <c r="AB2" s="6">
         <v>8888989.119545199</v>
       </c>
-      <c r="AC2" s="7">
+      <c r="AC2" s="6">
         <v>9891686.9587113392</v>
       </c>
-      <c r="AD2" s="7">
+      <c r="AD2" s="6">
         <v>11041798.436057637</v>
       </c>
-      <c r="AE2" s="7">
+      <c r="AE2" s="6">
         <v>12155229.559350107</v>
       </c>
-      <c r="AF2" s="7">
+      <c r="AF2" s="6">
         <v>13024662.541145021</v>
       </c>
-      <c r="AG2" s="7">
+      <c r="AG2" s="6">
         <v>13222655.837606285</v>
       </c>
-      <c r="AH2" s="7">
+      <c r="AH2" s="6">
         <v>12942859.974972261</v>
       </c>
-      <c r="AI2" s="7">
+      <c r="AI2" s="6">
         <v>12354682.163536195</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.2">
@@ -867,80 +883,83 @@
       <c r="J3" s="1">
         <v>50</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="6">
         <v>15.768000000000001</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="6">
         <v>8789429.3118240349</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="6">
         <v>5690.0782768158087</v>
       </c>
-      <c r="N3" s="7">
+      <c r="N3" s="6">
         <v>1899.3769994293334</v>
       </c>
-      <c r="O3" s="7">
+      <c r="O3" s="6">
         <v>3790.7012773864762</v>
       </c>
-      <c r="P3" s="7">
+      <c r="P3" s="6">
         <v>2.4702870525150269</v>
       </c>
-      <c r="Q3" s="7">
+      <c r="Q3" s="6">
         <v>15.66561681983154</v>
       </c>
-      <c r="R3" s="7">
+      <c r="R3" s="6">
         <v>10468682.089332411</v>
       </c>
-      <c r="S3" s="7">
+      <c r="S3" s="6">
         <v>12255277.26305341</v>
       </c>
-      <c r="T3" s="7">
+      <c r="T3" s="6">
         <v>15119471.332628476</v>
       </c>
-      <c r="U3" s="7">
+      <c r="U3" s="6">
         <v>18087434.280043613</v>
       </c>
-      <c r="V3" s="7">
+      <c r="V3" s="6">
         <v>19520508.738511011</v>
       </c>
-      <c r="W3" s="7">
+      <c r="W3" s="6">
         <v>20010668.958849277</v>
       </c>
-      <c r="X3" s="7">
+      <c r="X3" s="6">
         <v>19662812.469710197</v>
       </c>
-      <c r="Y3" s="7">
+      <c r="Y3" s="6">
         <v>18966333.773282584</v>
       </c>
-      <c r="Z3" s="7">
+      <c r="Z3" s="6">
         <v>17523151.416949309</v>
       </c>
-      <c r="AA3" s="7">
+      <c r="AA3" s="6">
         <v>10612251.670412583</v>
       </c>
-      <c r="AB3" s="7">
+      <c r="AB3" s="6">
         <v>12371423.301238989</v>
       </c>
-      <c r="AC3" s="7">
+      <c r="AC3" s="6">
         <v>14610857.817657402</v>
       </c>
-      <c r="AD3" s="7">
+      <c r="AD3" s="6">
         <v>17040412.359598234</v>
       </c>
-      <c r="AE3" s="7">
+      <c r="AE3" s="6">
         <v>19000508.105264552</v>
       </c>
-      <c r="AF3" s="7">
+      <c r="AF3" s="6">
         <v>19591402.198859483</v>
       </c>
-      <c r="AG3" s="7">
+      <c r="AG3" s="6">
         <v>19474510.60352182</v>
       </c>
-      <c r="AH3" s="7">
+      <c r="AH3" s="6">
         <v>18531424.45036472</v>
       </c>
-      <c r="AI3" s="7">
+      <c r="AI3" s="6">
         <v>17194937.548380703</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.2">
@@ -974,80 +993,83 @@
       <c r="J4" s="1">
         <v>50</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="6">
         <v>15.273899999999999</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="6">
         <v>7913410.9089839282</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="6">
         <v>6690.1798944189095</v>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="6">
         <v>2456.2263835372701</v>
       </c>
-      <c r="O4" s="7">
+      <c r="O4" s="6">
         <v>4233.953510881639</v>
       </c>
-      <c r="P4" s="7">
+      <c r="P4" s="6">
         <v>2.9232069449492566</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="Q4" s="6">
         <v>24.079400243145951</v>
       </c>
-      <c r="R4" s="7">
+      <c r="R4" s="6">
         <v>8578140.1392299365</v>
       </c>
-      <c r="S4" s="7">
+      <c r="S4" s="6">
         <v>9988192.8045357447</v>
       </c>
-      <c r="T4" s="7">
+      <c r="T4" s="6">
         <v>11911929.180443261</v>
       </c>
-      <c r="U4" s="7">
+      <c r="U4" s="6">
         <v>14192253.023745121</v>
       </c>
-      <c r="V4" s="7">
+      <c r="V4" s="6">
         <v>15938918.156161731</v>
       </c>
-      <c r="W4" s="7">
+      <c r="W4" s="6">
         <v>16523471.919830203</v>
       </c>
-      <c r="X4" s="7">
+      <c r="X4" s="6">
         <v>16477651.868992524</v>
       </c>
-      <c r="Y4" s="7">
+      <c r="Y4" s="6">
         <v>15830724.003693346</v>
       </c>
-      <c r="Z4" s="7">
+      <c r="Z4" s="6">
         <v>14762869.141178906</v>
       </c>
-      <c r="AA4" s="7">
+      <c r="AA4" s="6">
         <v>8634395.350003954</v>
       </c>
-      <c r="AB4" s="7">
+      <c r="AB4" s="6">
         <v>9973826.4662985951</v>
       </c>
-      <c r="AC4" s="7">
+      <c r="AC4" s="6">
         <v>11724759.794637742</v>
       </c>
-      <c r="AD4" s="7">
+      <c r="AD4" s="6">
         <v>13634289.97289704</v>
       </c>
-      <c r="AE4" s="7">
+      <c r="AE4" s="6">
         <v>15269396.685102707</v>
       </c>
-      <c r="AF4" s="7">
+      <c r="AF4" s="6">
         <v>16203808.38205892</v>
       </c>
-      <c r="AG4" s="7">
+      <c r="AG4" s="6">
         <v>16169681.618044775</v>
       </c>
-      <c r="AH4" s="7">
+      <c r="AH4" s="6">
         <v>15573198.553035514</v>
       </c>
-      <c r="AI4" s="7">
+      <c r="AI4" s="6">
         <v>14589574.436153652</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -1081,80 +1103,83 @@
       <c r="J5" s="4">
         <v>50</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="7">
         <v>15.7704</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="7">
         <v>8944177.9844431132</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="7">
         <v>6116.8621965284747</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N5" s="7">
         <v>2279.8813875796895</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O5" s="7">
         <v>3836.9808089487856</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P5" s="7">
         <v>2.7536702060301508</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="Q5" s="7">
         <v>18.488148060099267</v>
       </c>
-      <c r="R5" s="8">
+      <c r="R5" s="7">
         <v>9362952.6494312733</v>
       </c>
-      <c r="S5" s="8">
+      <c r="S5" s="7">
         <v>10928055.385490295</v>
       </c>
-      <c r="T5" s="8">
+      <c r="T5" s="7">
         <v>12923269.719718838</v>
       </c>
-      <c r="U5" s="8">
+      <c r="U5" s="7">
         <v>15055989.753165269</v>
       </c>
-      <c r="V5" s="8">
+      <c r="V5" s="7">
         <v>16406809.288429121</v>
       </c>
-      <c r="W5" s="8">
+      <c r="W5" s="7">
         <v>16654540.050857287</v>
       </c>
-      <c r="X5" s="8">
+      <c r="X5" s="7">
         <v>16484364.798766017</v>
       </c>
-      <c r="Y5" s="8">
+      <c r="Y5" s="7">
         <v>15776595.003160853</v>
       </c>
-      <c r="Z5" s="8">
+      <c r="Z5" s="7">
         <v>14734301.297375673</v>
       </c>
-      <c r="AA5" s="8">
+      <c r="AA5" s="7">
         <v>9358374.0784872025</v>
       </c>
-      <c r="AB5" s="8">
+      <c r="AB5" s="7">
         <v>10858723.426277183</v>
       </c>
-      <c r="AC5" s="8">
+      <c r="AC5" s="7">
         <v>12664132.087824523</v>
       </c>
-      <c r="AD5" s="8">
+      <c r="AD5" s="7">
         <v>14458169.145432957</v>
       </c>
-      <c r="AE5" s="8">
+      <c r="AE5" s="7">
         <v>15814972.874882689</v>
       </c>
-      <c r="AF5" s="8">
+      <c r="AF5" s="7">
         <v>16445495.607865181</v>
       </c>
-      <c r="AG5" s="8">
+      <c r="AG5" s="7">
         <v>16203684.077578595</v>
       </c>
-      <c r="AH5" s="8">
+      <c r="AH5" s="7">
         <v>15560280.307485027</v>
       </c>
-      <c r="AI5" s="8">
+      <c r="AI5" s="7">
         <v>14611906.308258634</v>
+      </c>
+      <c r="AJ5" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.2">
@@ -1188,84 +1213,87 @@
       <c r="J6" s="1">
         <v>50</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="6">
         <v>16.014500000000002</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="6">
         <v>8111695.1342813419</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="6">
         <v>6243.9978933404227</v>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="6">
         <v>2197.0567111308114</v>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="6">
         <v>4046.9411822096122</v>
       </c>
-      <c r="P6" s="7">
+      <c r="P6" s="6">
         <v>3.0783491596413595</v>
       </c>
-      <c r="Q6" s="7">
+      <c r="Q6" s="6">
         <v>23.529122156420371</v>
       </c>
-      <c r="R6" s="7">
+      <c r="R6" s="6">
         <v>9865417.1981567629</v>
       </c>
-      <c r="S6" s="7">
+      <c r="S6" s="6">
         <v>12077628.95750919</v>
       </c>
-      <c r="T6" s="7">
+      <c r="T6" s="6">
         <v>15021329.747639183</v>
       </c>
-      <c r="U6" s="7">
+      <c r="U6" s="6">
         <v>17330475.373862516</v>
       </c>
-      <c r="V6" s="7">
+      <c r="V6" s="6">
         <v>18313313.321357608</v>
       </c>
-      <c r="W6" s="7">
+      <c r="W6" s="6">
         <v>18482086.959576812</v>
       </c>
-      <c r="X6" s="7">
+      <c r="X6" s="6">
         <v>17936492.156640351</v>
       </c>
-      <c r="Y6" s="7">
+      <c r="Y6" s="6">
         <v>17286195.783378057</v>
       </c>
-      <c r="Z6" s="7">
+      <c r="Z6" s="6">
         <v>16088334.537685303</v>
       </c>
-      <c r="AA6" s="7">
+      <c r="AA6" s="6">
         <v>9950937.7242692802</v>
       </c>
-      <c r="AB6" s="7">
+      <c r="AB6" s="6">
         <v>11909285.303885572</v>
       </c>
-      <c r="AC6" s="7">
+      <c r="AC6" s="6">
         <v>14234923.058231598</v>
       </c>
-      <c r="AD6" s="7">
+      <c r="AD6" s="6">
         <v>16504770.583717238</v>
       </c>
-      <c r="AE6" s="7">
+      <c r="AE6" s="6">
         <v>17887765.188555308</v>
       </c>
-      <c r="AF6" s="7">
+      <c r="AF6" s="6">
         <v>18122944.187934961</v>
       </c>
-      <c r="AG6" s="7">
+      <c r="AG6" s="6">
         <v>17864149.41777382</v>
       </c>
-      <c r="AH6" s="7">
+      <c r="AH6" s="6">
         <v>16962219.313623913</v>
       </c>
-      <c r="AI6" s="7">
+      <c r="AI6" s="6">
         <v>15804649.634190621</v>
+      </c>
+      <c r="AJ6" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+      <c r="A7" t="s">
         <v>31</v>
       </c>
       <c r="B7" t="s">
@@ -1295,84 +1323,87 @@
       <c r="J7" s="1">
         <v>50</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="6">
         <v>14.924799999999999</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="6">
         <v>6273760.7870711759</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="6">
         <v>7127.3163245055412</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7" s="6">
         <v>2709.393711608278</v>
       </c>
-      <c r="O7" s="7">
+      <c r="O7" s="6">
         <v>4417.9226128972659</v>
       </c>
-      <c r="P7" s="7">
+      <c r="P7" s="6">
         <v>3.3287539392198369</v>
       </c>
-      <c r="Q7" s="7">
+      <c r="Q7" s="6">
         <v>36.91244481633305</v>
       </c>
-      <c r="R7" s="7">
+      <c r="R7" s="6">
         <v>6460189.0363154514</v>
       </c>
-      <c r="S7" s="7">
+      <c r="S7" s="6">
         <v>7749499.0685391221</v>
       </c>
-      <c r="T7" s="7">
+      <c r="T7" s="6">
         <v>9285195.7630087845</v>
       </c>
-      <c r="U7" s="7">
+      <c r="U7" s="6">
         <v>11014177.363848913</v>
       </c>
-      <c r="V7" s="7">
+      <c r="V7" s="6">
         <v>12651060.172161458</v>
       </c>
-      <c r="W7" s="7">
+      <c r="W7" s="6">
         <v>13656140.392693788</v>
       </c>
-      <c r="X7" s="7">
+      <c r="X7" s="6">
         <v>13793928.437193971</v>
       </c>
-      <c r="Y7" s="7">
+      <c r="Y7" s="6">
         <v>13378262.180143071</v>
       </c>
-      <c r="Z7" s="7">
+      <c r="Z7" s="6">
         <v>12670033.961652769</v>
       </c>
-      <c r="AA7" s="7">
+      <c r="AA7" s="6">
         <v>6475476.5298331073</v>
       </c>
-      <c r="AB7" s="7">
+      <c r="AB7" s="6">
         <v>7619263.7566795377</v>
       </c>
-      <c r="AC7" s="7">
+      <c r="AC7" s="6">
         <v>9097828.7255626973</v>
       </c>
-      <c r="AD7" s="7">
+      <c r="AD7" s="6">
         <v>10709901.512389617</v>
       </c>
-      <c r="AE7" s="7">
+      <c r="AE7" s="6">
         <v>12193693.966577375</v>
       </c>
-      <c r="AF7" s="7">
+      <c r="AF7" s="6">
         <v>13197798.739659464</v>
       </c>
-      <c r="AG7" s="7">
+      <c r="AG7" s="6">
         <v>13515773.174574597</v>
       </c>
-      <c r="AH7" s="7">
+      <c r="AH7" s="6">
         <v>13208115.937428305</v>
       </c>
-      <c r="AI7" s="7">
+      <c r="AI7" s="6">
         <v>12442672.642323911</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+      <c r="A8" t="s">
         <v>31</v>
       </c>
       <c r="B8" t="s">
@@ -1402,80 +1433,83 @@
       <c r="J8" s="1">
         <v>50</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="6">
         <v>13.9833</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="6">
         <v>7571076.8242832934</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="6">
         <v>6184.5960701349904</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N8" s="6">
         <v>2710.3631637385506</v>
       </c>
-      <c r="O8" s="7">
+      <c r="O8" s="6">
         <v>3474.2329063964398</v>
       </c>
-      <c r="P8" s="7">
+      <c r="P8" s="6">
         <v>3.0953688849031691</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="Q8" s="6">
         <v>24.677036043217715</v>
       </c>
-      <c r="R8" s="7">
+      <c r="R8" s="6">
         <v>7384175.4387683533</v>
       </c>
-      <c r="S8" s="7">
+      <c r="S8" s="6">
         <v>7924095.5919207064</v>
       </c>
-      <c r="T8" s="7">
+      <c r="T8" s="6">
         <v>8608824.1952788234</v>
       </c>
-      <c r="U8" s="7">
+      <c r="U8" s="6">
         <v>9605269.6153139547</v>
       </c>
-      <c r="V8" s="7">
+      <c r="V8" s="6">
         <v>10747675.286966439</v>
       </c>
-      <c r="W8" s="7">
+      <c r="W8" s="6">
         <v>11457469.742690034</v>
       </c>
-      <c r="X8" s="7">
+      <c r="X8" s="6">
         <v>11530840.182773625</v>
       </c>
-      <c r="Y8" s="7">
+      <c r="Y8" s="6">
         <v>11211938.295527047</v>
       </c>
-      <c r="Z8" s="7">
+      <c r="Z8" s="6">
         <v>10656890.087780597</v>
       </c>
-      <c r="AA8" s="7">
+      <c r="AA8" s="6">
         <v>7370493.7827976895</v>
       </c>
-      <c r="AB8" s="7">
+      <c r="AB8" s="6">
         <v>7949611.6593564739</v>
       </c>
-      <c r="AC8" s="7">
+      <c r="AC8" s="6">
         <v>8684065.1350576077</v>
       </c>
-      <c r="AD8" s="7">
+      <c r="AD8" s="6">
         <v>9560080.5443469062</v>
       </c>
-      <c r="AE8" s="7">
+      <c r="AE8" s="6">
         <v>10449930.953166261</v>
       </c>
-      <c r="AF8" s="7">
+      <c r="AF8" s="6">
         <v>11125492.292220641</v>
       </c>
-      <c r="AG8" s="7">
+      <c r="AG8" s="6">
         <v>11333374.348491549</v>
       </c>
-      <c r="AH8" s="7">
+      <c r="AH8" s="6">
         <v>11076653.172646755</v>
       </c>
-      <c r="AI8" s="7">
+      <c r="AI8" s="6">
         <v>10441497.973194702</v>
+      </c>
+      <c r="AJ8" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -1509,80 +1543,83 @@
       <c r="J9" s="4">
         <v>50</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="7">
         <v>16.6934</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="7">
         <v>9911499.7145404145</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="7">
         <v>7551.6044203584561</v>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="7">
         <v>2641.8583913251564</v>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="7">
         <v>4909.7460290332974</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="7">
         <v>2.8511422328511848</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9" s="7">
         <v>21.135840314234844</v>
       </c>
-      <c r="R9" s="8">
+      <c r="R9" s="7">
         <v>8381420.0087174885</v>
       </c>
-      <c r="S9" s="8">
+      <c r="S9" s="7">
         <v>10259507.907906407</v>
       </c>
-      <c r="T9" s="8">
+      <c r="T9" s="7">
         <v>12366368.942383677</v>
       </c>
-      <c r="U9" s="8">
+      <c r="U9" s="7">
         <v>13921313.206846157</v>
       </c>
-      <c r="V9" s="8">
+      <c r="V9" s="7">
         <v>14630828.776472708</v>
       </c>
-      <c r="W9" s="8">
+      <c r="W9" s="7">
         <v>14670234.946231553</v>
       </c>
-      <c r="X9" s="8">
+      <c r="X9" s="7">
         <v>14250304.057113729</v>
       </c>
-      <c r="Y9" s="8">
+      <c r="Y9" s="7">
         <v>13609802.473399473</v>
       </c>
-      <c r="Z9" s="8">
+      <c r="Z9" s="7">
         <v>12846952.963085955</v>
       </c>
-      <c r="AA9" s="8">
+      <c r="AA9" s="7">
         <v>8366291.9984124228</v>
       </c>
-      <c r="AB9" s="8">
+      <c r="AB9" s="7">
         <v>9991207.4807736166</v>
       </c>
-      <c r="AC9" s="8">
+      <c r="AC9" s="7">
         <v>11813149.128086716</v>
       </c>
-      <c r="AD9" s="8">
+      <c r="AD9" s="7">
         <v>13403630.144645233</v>
       </c>
-      <c r="AE9" s="8">
+      <c r="AE9" s="7">
         <v>14285965.517577283</v>
       </c>
-      <c r="AF9" s="8">
+      <c r="AF9" s="7">
         <v>14438059.606155328</v>
       </c>
-      <c r="AG9" s="8">
+      <c r="AG9" s="7">
         <v>14120136.893310981</v>
       </c>
-      <c r="AH9" s="8">
+      <c r="AH9" s="7">
         <v>13512289.143874677</v>
       </c>
-      <c r="AI9" s="8">
+      <c r="AI9" s="7">
         <v>12719837.964141108</v>
+      </c>
+      <c r="AJ9" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.2">
@@ -1616,84 +1653,87 @@
       <c r="J10" s="1">
         <v>50</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="6">
         <v>16.994199999999999</v>
       </c>
-      <c r="L10" s="7">
+      <c r="L10" s="6">
         <v>11256583.311405884</v>
       </c>
-      <c r="M10" s="7">
+      <c r="M10" s="6">
         <v>6220.9752091130476</v>
       </c>
-      <c r="N10" s="7">
+      <c r="N10" s="6">
         <v>2526.8089521856846</v>
       </c>
-      <c r="O10" s="7">
+      <c r="O10" s="6">
         <v>3694.1662569273658</v>
       </c>
-      <c r="P10" s="7">
+      <c r="P10" s="6">
         <v>2.9932713650719927</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="Q10" s="6">
         <v>16.214298554959448</v>
       </c>
-      <c r="R10" s="7">
+      <c r="R10" s="6">
         <v>8417552.7149950992</v>
       </c>
-      <c r="S10" s="7">
+      <c r="S10" s="6">
         <v>9943246.269822685</v>
       </c>
-      <c r="T10" s="7">
+      <c r="T10" s="6">
         <v>11859346.962977584</v>
       </c>
-      <c r="U10" s="7">
+      <c r="U10" s="6">
         <v>13330467.469250569</v>
       </c>
-      <c r="V10" s="7">
+      <c r="V10" s="6">
         <v>13756738.40840229</v>
       </c>
-      <c r="W10" s="7">
+      <c r="W10" s="6">
         <v>13434611.188394597</v>
       </c>
-      <c r="X10" s="7">
+      <c r="X10" s="6">
         <v>12863670.033315104</v>
       </c>
-      <c r="Y10" s="7">
+      <c r="Y10" s="6">
         <v>12211995.669127366</v>
       </c>
-      <c r="Z10" s="7">
+      <c r="Z10" s="6">
         <v>11736444.177228887</v>
       </c>
-      <c r="AA10" s="7">
+      <c r="AA10" s="6">
         <v>8495358.0328350514</v>
       </c>
-      <c r="AB10" s="7">
+      <c r="AB10" s="6">
         <v>9846345.3300728351</v>
       </c>
-      <c r="AC10" s="7">
+      <c r="AC10" s="6">
         <v>11390371.336920666</v>
       </c>
-      <c r="AD10" s="7">
+      <c r="AD10" s="6">
         <v>12737772.497154551</v>
       </c>
-      <c r="AE10" s="7">
+      <c r="AE10" s="6">
         <v>13382336.715664297</v>
       </c>
-      <c r="AF10" s="7">
+      <c r="AF10" s="6">
         <v>13295223.775980717</v>
       </c>
-      <c r="AG10" s="7">
+      <c r="AG10" s="6">
         <v>12794161.392228482</v>
       </c>
-      <c r="AH10" s="7">
+      <c r="AH10" s="6">
         <v>12274231.246909015</v>
       </c>
-      <c r="AI10" s="7">
+      <c r="AI10" s="6">
         <v>11846978.692702495</v>
+      </c>
+      <c r="AJ10" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+      <c r="A11" t="s">
         <v>31</v>
       </c>
       <c r="B11" t="s">
@@ -1723,84 +1763,87 @@
       <c r="J11" s="1">
         <v>50</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="6">
         <v>18.105899999999998</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="6">
         <v>8946455.3314072825</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="6">
         <v>7732.2667338139372</v>
       </c>
-      <c r="N11" s="7">
+      <c r="N11" s="6">
         <v>2401.7498037468645</v>
       </c>
-      <c r="O11" s="7">
+      <c r="O11" s="6">
         <v>5330.5169300670723</v>
       </c>
-      <c r="P11" s="7">
+      <c r="P11" s="6">
         <v>2.7451325131233597</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q11" s="6">
         <v>23.522704328826023</v>
       </c>
-      <c r="R11" s="7">
+      <c r="R11" s="6">
         <v>11524228.794649191</v>
       </c>
-      <c r="S11" s="7">
+      <c r="S11" s="6">
         <v>15021460.929348191</v>
       </c>
-      <c r="T11" s="7">
+      <c r="T11" s="6">
         <v>18417759.35253739</v>
       </c>
-      <c r="U11" s="7">
+      <c r="U11" s="6">
         <v>20704505.210122034</v>
       </c>
-      <c r="V11" s="7">
+      <c r="V11" s="6">
         <v>22007020.388973594</v>
       </c>
-      <c r="W11" s="7">
+      <c r="W11" s="6">
         <v>22308442.812791545</v>
       </c>
-      <c r="X11" s="7">
+      <c r="X11" s="6">
         <v>22050919.210792053</v>
       </c>
-      <c r="Y11" s="7">
+      <c r="Y11" s="6">
         <v>21173858.523779295</v>
       </c>
-      <c r="Z11" s="7">
+      <c r="Z11" s="6">
         <v>19995317.826049808</v>
       </c>
-      <c r="AA11" s="7">
+      <c r="AA11" s="6">
         <v>11348018.075095564</v>
       </c>
-      <c r="AB11" s="7">
+      <c r="AB11" s="6">
         <v>14177446.842879364</v>
       </c>
-      <c r="AC11" s="7">
+      <c r="AC11" s="6">
         <v>17410973.00832554</v>
       </c>
-      <c r="AD11" s="7">
+      <c r="AD11" s="6">
         <v>20053047.075691968</v>
       </c>
-      <c r="AE11" s="7">
+      <c r="AE11" s="6">
         <v>21476568.878798984</v>
       </c>
-      <c r="AF11" s="7">
+      <c r="AF11" s="6">
         <v>22028947.929743472</v>
       </c>
-      <c r="AG11" s="7">
+      <c r="AG11" s="6">
         <v>21726348.306527823</v>
       </c>
-      <c r="AH11" s="7">
+      <c r="AH11" s="6">
         <v>20972870.299427498</v>
       </c>
-      <c r="AI11" s="7">
+      <c r="AI11" s="6">
         <v>19808839.116337959</v>
+      </c>
+      <c r="AJ11" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+      <c r="A12" t="s">
         <v>31</v>
       </c>
       <c r="B12" t="s">
@@ -1830,80 +1873,83 @@
       <c r="J12" s="1">
         <v>50</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="6">
         <v>16.671600000000002</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="6">
         <v>8415507.9126979895</v>
       </c>
-      <c r="M12" s="7">
+      <c r="M12" s="6">
         <v>7185.2264613329589</v>
       </c>
-      <c r="N12" s="7">
+      <c r="N12" s="6">
         <v>3202.6662596253855</v>
       </c>
-      <c r="O12" s="7">
+      <c r="O12" s="6">
         <v>3982.5602017075757</v>
       </c>
-      <c r="P12" s="7">
+      <c r="P12" s="6">
         <v>3.3458298350646594</v>
       </c>
-      <c r="Q12" s="7">
+      <c r="Q12" s="6">
         <v>28.214457831854208</v>
       </c>
-      <c r="R12" s="7">
+      <c r="R12" s="6">
         <v>7362095.3492581462</v>
       </c>
-      <c r="S12" s="7">
+      <c r="S12" s="6">
         <v>8326904.2360911313</v>
       </c>
-      <c r="T12" s="7">
+      <c r="T12" s="6">
         <v>10010307.115174383</v>
       </c>
-      <c r="U12" s="7">
+      <c r="U12" s="6">
         <v>12087713.219503308</v>
       </c>
-      <c r="V12" s="7">
+      <c r="V12" s="6">
         <v>13210951.193914106</v>
       </c>
-      <c r="W12" s="7">
+      <c r="W12" s="6">
         <v>13372201.393686485</v>
       </c>
-      <c r="X12" s="7">
+      <c r="X12" s="6">
         <v>13055250.774885729</v>
       </c>
-      <c r="Y12" s="7">
+      <c r="Y12" s="6">
         <v>12372111.017264126</v>
       </c>
-      <c r="Z12" s="7">
+      <c r="Z12" s="6">
         <v>11382339.536538474</v>
       </c>
-      <c r="AA12" s="7">
+      <c r="AA12" s="6">
         <v>7470135.4495948404</v>
       </c>
-      <c r="AB12" s="7">
+      <c r="AB12" s="6">
         <v>8484357.3717745282</v>
       </c>
-      <c r="AC12" s="7">
+      <c r="AC12" s="6">
         <v>9860898.0188902579</v>
       </c>
-      <c r="AD12" s="7">
+      <c r="AD12" s="6">
         <v>11390052.767545391</v>
       </c>
-      <c r="AE12" s="7">
+      <c r="AE12" s="6">
         <v>12697555.197344268</v>
       </c>
-      <c r="AF12" s="7">
+      <c r="AF12" s="6">
         <v>13132639.505033499</v>
       </c>
-      <c r="AG12" s="7">
+      <c r="AG12" s="6">
         <v>12852730.929223081</v>
       </c>
-      <c r="AH12" s="7">
+      <c r="AH12" s="6">
         <v>12161534.35430485</v>
       </c>
-      <c r="AI12" s="7">
+      <c r="AI12" s="6">
         <v>11144888.490922293</v>
+      </c>
+      <c r="AJ12" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -1937,80 +1983,83 @@
       <c r="J13" s="4">
         <v>50</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="7">
         <v>19.2285</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="7">
         <v>13459696.741385918</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M13" s="7">
         <v>6654.0145631889818</v>
       </c>
-      <c r="N13" s="8">
+      <c r="N13" s="7">
         <v>2651.2676735578229</v>
       </c>
-      <c r="O13" s="8">
+      <c r="O13" s="7">
         <v>4002.7468896311602</v>
       </c>
-      <c r="P13" s="8">
+      <c r="P13" s="7">
         <v>2.5420997287855074</v>
       </c>
-      <c r="Q13" s="8">
+      <c r="Q13" s="7">
         <v>12.120042824849866</v>
       </c>
-      <c r="R13" s="8">
+      <c r="R13" s="7">
         <v>13737411.018187204</v>
       </c>
-      <c r="S13" s="8">
+      <c r="S13" s="7">
         <v>17567337.585628234</v>
       </c>
-      <c r="T13" s="8">
+      <c r="T13" s="7">
         <v>20712337.1270684</v>
       </c>
-      <c r="U13" s="8">
+      <c r="U13" s="7">
         <v>22503025.707681414</v>
       </c>
-      <c r="V13" s="8">
+      <c r="V13" s="7">
         <v>22989585.765568115</v>
       </c>
-      <c r="W13" s="8">
+      <c r="W13" s="7">
         <v>23000397.713554658</v>
       </c>
-      <c r="X13" s="8">
+      <c r="X13" s="7">
         <v>22470684.503705516</v>
       </c>
-      <c r="Y13" s="8">
+      <c r="Y13" s="7">
         <v>21595202.27037067</v>
       </c>
-      <c r="Z13" s="8">
+      <c r="Z13" s="7">
         <v>20562082.525530171</v>
       </c>
-      <c r="AA13" s="8">
+      <c r="AA13" s="7">
         <v>13136203.429165399</v>
       </c>
-      <c r="AB13" s="8">
+      <c r="AB13" s="7">
         <v>16518779.008895783</v>
       </c>
-      <c r="AC13" s="8">
+      <c r="AC13" s="7">
         <v>19731203.653494921</v>
       </c>
-      <c r="AD13" s="8">
+      <c r="AD13" s="7">
         <v>21791629.258873224</v>
       </c>
-      <c r="AE13" s="8">
+      <c r="AE13" s="7">
         <v>22748993.465553962</v>
       </c>
-      <c r="AF13" s="8">
+      <c r="AF13" s="7">
         <v>22727173.663906794</v>
       </c>
-      <c r="AG13" s="8">
+      <c r="AG13" s="7">
         <v>22275661.325432144</v>
       </c>
-      <c r="AH13" s="8">
+      <c r="AH13" s="7">
         <v>21474058.075625971</v>
       </c>
-      <c r="AI13" s="8">
+      <c r="AI13" s="7">
         <v>20146751.329910308</v>
+      </c>
+      <c r="AJ13" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.2">
@@ -2044,84 +2093,87 @@
       <c r="J14" s="1">
         <v>50</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="6">
         <v>16.172699999999999</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L14" s="6">
         <v>6462609.4981648158</v>
       </c>
-      <c r="M14" s="7">
+      <c r="M14" s="6">
         <v>8507.7956141772902</v>
       </c>
-      <c r="N14" s="7">
+      <c r="N14" s="6">
         <v>3375.7890852202636</v>
       </c>
-      <c r="O14" s="7">
+      <c r="O14" s="6">
         <v>5132.0065289570266</v>
       </c>
-      <c r="P14" s="7">
+      <c r="P14" s="6">
         <v>3.6316822420154589</v>
       </c>
-      <c r="Q14" s="7">
+      <c r="Q14" s="6">
         <v>47.388942297550457</v>
       </c>
-      <c r="R14" s="7">
+      <c r="R14" s="6">
         <v>8795190.4367636088</v>
       </c>
-      <c r="S14" s="7">
+      <c r="S14" s="6">
         <v>9838200.9052775539</v>
       </c>
-      <c r="T14" s="7">
+      <c r="T14" s="6">
         <v>11017771.024783209</v>
       </c>
-      <c r="U14" s="7">
+      <c r="U14" s="6">
         <v>11908699.044573504</v>
       </c>
-      <c r="V14" s="7">
+      <c r="V14" s="6">
         <v>12264212.436163494</v>
       </c>
-      <c r="W14" s="7">
+      <c r="W14" s="6">
         <v>12237497.009407902</v>
       </c>
-      <c r="X14" s="7">
+      <c r="X14" s="6">
         <v>12006713.921825461</v>
       </c>
-      <c r="Y14" s="7">
+      <c r="Y14" s="6">
         <v>11524857.169104319</v>
       </c>
-      <c r="Z14" s="7">
+      <c r="Z14" s="6">
         <v>10535907.217635749</v>
       </c>
-      <c r="AA14" s="7">
+      <c r="AA14" s="6">
         <v>8791029.355404431</v>
       </c>
-      <c r="AB14" s="7">
+      <c r="AB14" s="6">
         <v>9781818.28493388</v>
       </c>
-      <c r="AC14" s="7">
+      <c r="AC14" s="6">
         <v>10774885.063266536</v>
       </c>
-      <c r="AD14" s="7">
+      <c r="AD14" s="6">
         <v>11607626.527834803</v>
       </c>
-      <c r="AE14" s="7">
+      <c r="AE14" s="6">
         <v>12070859.411404265</v>
       </c>
-      <c r="AF14" s="7">
+      <c r="AF14" s="6">
         <v>12134097.234326601</v>
       </c>
-      <c r="AG14" s="7">
+      <c r="AG14" s="6">
         <v>11870490.952306617</v>
       </c>
-      <c r="AH14" s="7">
+      <c r="AH14" s="6">
         <v>11223328.741270946</v>
       </c>
-      <c r="AI14" s="7">
+      <c r="AI14" s="6">
         <v>10133937.446832882</v>
+      </c>
+      <c r="AJ14" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
+      <c r="A15" t="s">
         <v>31</v>
       </c>
       <c r="B15" t="s">
@@ -2151,84 +2203,87 @@
       <c r="J15" s="1">
         <v>50</v>
       </c>
-      <c r="K15" s="7">
+      <c r="K15" s="6">
         <v>19.677900000000001</v>
       </c>
-      <c r="L15" s="7">
+      <c r="L15" s="6">
         <v>14866769.439705364</v>
       </c>
-      <c r="M15" s="7">
+      <c r="M15" s="6">
         <v>6836.8251558970578</v>
       </c>
-      <c r="N15" s="7">
+      <c r="N15" s="6">
         <v>2804.0443380015849</v>
       </c>
-      <c r="O15" s="7">
+      <c r="O15" s="6">
         <v>4032.7808178954751</v>
       </c>
-      <c r="P15" s="7">
+      <c r="P15" s="6">
         <v>3.5279799848075628</v>
       </c>
-      <c r="Q15" s="7">
+      <c r="Q15" s="6">
         <v>15.825154366205851</v>
       </c>
-      <c r="R15" s="7">
+      <c r="R15" s="6">
         <v>14368966.97085502</v>
       </c>
-      <c r="S15" s="7">
+      <c r="S15" s="6">
         <v>18908248.170906004</v>
       </c>
-      <c r="T15" s="7">
+      <c r="T15" s="6">
         <v>22530608.537433799</v>
       </c>
-      <c r="U15" s="7">
+      <c r="U15" s="6">
         <v>24668045.127362002</v>
       </c>
-      <c r="V15" s="7">
+      <c r="V15" s="6">
         <v>25303827.976420153</v>
       </c>
-      <c r="W15" s="7">
+      <c r="W15" s="6">
         <v>25272604.632300254</v>
       </c>
-      <c r="X15" s="7">
+      <c r="X15" s="6">
         <v>24598899.263474327</v>
       </c>
-      <c r="Y15" s="7">
+      <c r="Y15" s="6">
         <v>23654862.901020207</v>
       </c>
-      <c r="Z15" s="7">
+      <c r="Z15" s="6">
         <v>21891817.426759005</v>
       </c>
-      <c r="AA15" s="7">
+      <c r="AA15" s="6">
         <v>13239551.666400462</v>
       </c>
-      <c r="AB15" s="7">
+      <c r="AB15" s="6">
         <v>17547170.418528404</v>
       </c>
-      <c r="AC15" s="7">
+      <c r="AC15" s="6">
         <v>21407489.433150485</v>
       </c>
-      <c r="AD15" s="7">
+      <c r="AD15" s="6">
         <v>23836829.03717998</v>
       </c>
-      <c r="AE15" s="7">
+      <c r="AE15" s="6">
         <v>24966665.614315256</v>
       </c>
-      <c r="AF15" s="7">
+      <c r="AF15" s="6">
         <v>24946384.688756298</v>
       </c>
-      <c r="AG15" s="7">
+      <c r="AG15" s="6">
         <v>24436989.1951438</v>
       </c>
-      <c r="AH15" s="7">
+      <c r="AH15" s="6">
         <v>23166543.771021131</v>
       </c>
-      <c r="AI15" s="7">
+      <c r="AI15" s="6">
         <v>21521424.223709635</v>
+      </c>
+      <c r="AJ15" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A16" s="12" t="s">
+      <c r="A16" t="s">
         <v>31</v>
       </c>
       <c r="B16" t="s">
@@ -2258,84 +2313,86 @@
       <c r="J16" s="1">
         <v>50</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K16" s="6">
         <v>19.732600000000001</v>
       </c>
-      <c r="L16" s="7">
+      <c r="L16" s="6">
         <v>13426636.579512706</v>
       </c>
-      <c r="M16" s="7">
+      <c r="M16" s="6">
         <v>6400.692472397639</v>
       </c>
-      <c r="N16" s="7">
+      <c r="N16" s="6">
         <v>2777.3000104016801</v>
       </c>
-      <c r="O16" s="7">
+      <c r="O16" s="6">
         <v>3623.3924619959557</v>
       </c>
-      <c r="P16" s="7">
+      <c r="P16" s="6">
         <v>2.6247226721059111</v>
       </c>
-      <c r="Q16" s="7">
+      <c r="Q16" s="6">
         <v>12.237916529035209</v>
       </c>
-      <c r="R16" s="7">
+      <c r="R16" s="6">
         <v>12434964.802015029</v>
       </c>
-      <c r="S16" s="7">
+      <c r="S16" s="6">
         <v>15306907.20428703</v>
       </c>
-      <c r="T16" s="7">
+      <c r="T16" s="6">
         <v>17653205.109771222</v>
       </c>
-      <c r="U16" s="7">
+      <c r="U16" s="6">
         <v>18783327.662235521</v>
       </c>
-      <c r="V16" s="7">
+      <c r="V16" s="6">
         <v>19005314.73292622</v>
       </c>
-      <c r="W16" s="7">
+      <c r="W16" s="6">
         <v>18718973.91477257</v>
       </c>
-      <c r="X16" s="7">
+      <c r="X16" s="6">
         <v>18181671.331191737</v>
       </c>
-      <c r="Y16" s="7">
+      <c r="Y16" s="6">
         <v>17496927.023271821</v>
       </c>
-      <c r="Z16" s="7">
+      <c r="Z16" s="6">
         <v>16640419.41947584</v>
       </c>
-      <c r="AA16" s="7">
+      <c r="AA16" s="6">
         <v>12136558.424164921</v>
       </c>
-      <c r="AB16" s="7">
+      <c r="AB16" s="6">
         <v>14591580.998535041</v>
       </c>
-      <c r="AC16" s="7">
+      <c r="AC16" s="6">
         <v>16867859.939322576</v>
       </c>
-      <c r="AD16" s="7">
+      <c r="AD16" s="6">
         <v>18304324.375111815</v>
       </c>
-      <c r="AE16" s="7">
+      <c r="AE16" s="6">
         <v>18751095.573162075</v>
       </c>
-      <c r="AF16" s="7">
+      <c r="AF16" s="6">
         <v>18584371.716714263</v>
       </c>
-      <c r="AG16" s="7">
+      <c r="AG16" s="6">
         <v>18087332.472971492</v>
       </c>
-      <c r="AH16" s="7">
+      <c r="AH16" s="6">
         <v>17376936.891262908</v>
       </c>
-      <c r="AI16" s="7">
+      <c r="AI16" s="6">
         <v>16452570.457583116</v>
       </c>
-      <c r="AJ16" s="6"/>
+      <c r="AJ16" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="17" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>31</v>
       </c>
@@ -2366,83 +2423,86 @@
       <c r="J17" s="4">
         <v>50</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="7">
         <v>23.551100000000002</v>
       </c>
-      <c r="L17" s="8">
+      <c r="L17" s="7">
         <v>19125589.134683296</v>
       </c>
-      <c r="M17" s="8">
+      <c r="M17" s="7">
         <v>7793.7355038013447</v>
       </c>
-      <c r="N17" s="8">
+      <c r="N17" s="7">
         <v>3810.6172970179778</v>
       </c>
-      <c r="O17" s="8">
+      <c r="O17" s="7">
         <v>3983.1182067833665</v>
       </c>
-      <c r="P17" s="8">
+      <c r="P17" s="7">
         <v>2.9255963372380953</v>
       </c>
-      <c r="Q17" s="8">
+      <c r="Q17" s="7">
         <v>11.571114610628989</v>
       </c>
-      <c r="R17" s="8">
+      <c r="R17" s="7">
         <v>18902186.644834843</v>
       </c>
-      <c r="S17" s="8">
+      <c r="S17" s="7">
         <v>22550149.880342484</v>
       </c>
-      <c r="T17" s="8">
+      <c r="T17" s="7">
         <v>24654361.60708141</v>
       </c>
-      <c r="U17" s="8">
+      <c r="U17" s="7">
         <v>25542657.420510616</v>
       </c>
-      <c r="V17" s="8">
+      <c r="V17" s="7">
         <v>25512034.566040333</v>
       </c>
-      <c r="W17" s="8">
+      <c r="W17" s="7">
         <v>25090284.114149973</v>
       </c>
-      <c r="X17" s="8">
+      <c r="X17" s="7">
         <v>23848009.819196973</v>
       </c>
-      <c r="Y17" s="8">
+      <c r="Y17" s="7">
         <v>22166354.4283958</v>
       </c>
-      <c r="Z17" s="8">
+      <c r="Z17" s="7">
         <v>20487976.479211565</v>
       </c>
-      <c r="AA17" s="8">
+      <c r="AA17" s="7">
         <v>17366289.761913434</v>
       </c>
-      <c r="AB17" s="8">
+      <c r="AB17" s="7">
         <v>21398451.594970025</v>
       </c>
-      <c r="AC17" s="8">
+      <c r="AC17" s="7">
         <v>23953301.35633564</v>
       </c>
-      <c r="AD17" s="8">
+      <c r="AD17" s="7">
         <v>25075866.456618879</v>
       </c>
-      <c r="AE17" s="8">
+      <c r="AE17" s="7">
         <v>25314449.932651278</v>
       </c>
-      <c r="AF17" s="8">
+      <c r="AF17" s="7">
         <v>24651973.409512866</v>
       </c>
-      <c r="AG17" s="8">
+      <c r="AG17" s="7">
         <v>23537862.511430167</v>
       </c>
-      <c r="AH17" s="8">
+      <c r="AH17" s="7">
         <v>22040671.925652072</v>
       </c>
-      <c r="AI17" s="8">
+      <c r="AI17" s="7">
         <v>20150158.797653325</v>
       </c>
+      <c r="AJ17" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -2473,84 +2533,87 @@
       <c r="J18" s="1">
         <v>50</v>
       </c>
-      <c r="K18" s="7">
+      <c r="K18" s="6">
         <v>27.1968</v>
       </c>
-      <c r="L18" s="7">
+      <c r="L18" s="6">
         <v>20183633.2041215</v>
       </c>
-      <c r="M18" s="7">
+      <c r="M18" s="6">
         <v>8153.3668276810804</v>
       </c>
-      <c r="N18" s="7">
+      <c r="N18" s="6">
         <v>3031.8201769108482</v>
       </c>
-      <c r="O18" s="7">
+      <c r="O18" s="6">
         <v>5121.5466507702358</v>
       </c>
-      <c r="P18" s="7">
+      <c r="P18" s="6">
         <v>2.3220290642160748</v>
       </c>
-      <c r="Q18" s="7">
+      <c r="Q18" s="6">
         <v>9.1719247980580523</v>
       </c>
-      <c r="R18" s="7">
+      <c r="R18" s="6">
         <v>28026234.04195375</v>
       </c>
-      <c r="S18" s="7">
+      <c r="S18" s="6">
         <v>32143831.404388312</v>
       </c>
-      <c r="T18" s="7">
+      <c r="T18" s="6">
         <v>34248460.823753662</v>
       </c>
-      <c r="U18" s="7">
+      <c r="U18" s="6">
         <v>35124512.806481704</v>
       </c>
-      <c r="V18" s="7">
+      <c r="V18" s="6">
         <v>35238151.880997516</v>
       </c>
-      <c r="W18" s="7">
+      <c r="W18" s="6">
         <v>34668073.98994419</v>
       </c>
-      <c r="X18" s="7">
+      <c r="X18" s="6">
         <v>33843471.284417614</v>
       </c>
-      <c r="Y18" s="7">
+      <c r="Y18" s="6">
         <v>32856847.162292738</v>
       </c>
-      <c r="Z18" s="7">
+      <c r="Z18" s="6">
         <v>30921135.983414505</v>
       </c>
-      <c r="AA18" s="7">
+      <c r="AA18" s="6">
         <v>25807913.041817181</v>
       </c>
-      <c r="AB18" s="7">
+      <c r="AB18" s="6">
         <v>30826498.008319087</v>
       </c>
-      <c r="AC18" s="7">
+      <c r="AC18" s="6">
         <v>33568134.642160043</v>
       </c>
-      <c r="AD18" s="7">
+      <c r="AD18" s="6">
         <v>34736258.315705925</v>
       </c>
-      <c r="AE18" s="7">
+      <c r="AE18" s="6">
         <v>34894800.858655341</v>
       </c>
-      <c r="AF18" s="7">
+      <c r="AF18" s="6">
         <v>34526733.0631437</v>
       </c>
-      <c r="AG18" s="7">
+      <c r="AG18" s="6">
         <v>33738169.228826046</v>
       </c>
-      <c r="AH18" s="7">
+      <c r="AH18" s="6">
         <v>32316372.224989485</v>
       </c>
-      <c r="AI18" s="7">
+      <c r="AI18" s="6">
         <v>30381041.003094517</v>
       </c>
+      <c r="AJ18" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A19" s="12" t="s">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>31</v>
       </c>
       <c r="B19" t="s">
@@ -2580,84 +2643,87 @@
       <c r="J19" s="1">
         <v>50</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K19" s="6">
         <v>21.612100000000002</v>
       </c>
-      <c r="L19" s="7">
+      <c r="L19" s="6">
         <v>14445044.039830649</v>
       </c>
-      <c r="M19" s="7">
+      <c r="M19" s="6">
         <v>7819.6855564675834</v>
       </c>
-      <c r="N19" s="7">
+      <c r="N19" s="6">
         <v>3635.6827417094873</v>
       </c>
-      <c r="O19" s="7">
+      <c r="O19" s="6">
         <v>4184.002814758097</v>
       </c>
-      <c r="P19" s="7">
+      <c r="P19" s="6">
         <v>2.8780401345844813</v>
       </c>
-      <c r="Q19" s="7">
+      <c r="Q19" s="6">
         <v>15.201933787082577</v>
       </c>
-      <c r="R19" s="7">
+      <c r="R19" s="6">
         <v>12063512.182029223</v>
       </c>
-      <c r="S19" s="7">
+      <c r="S19" s="6">
         <v>14747362.896105697</v>
       </c>
-      <c r="T19" s="7">
+      <c r="T19" s="6">
         <v>15876711.24979955</v>
       </c>
-      <c r="U19" s="7">
+      <c r="U19" s="6">
         <v>15979328.4507076</v>
       </c>
-      <c r="V19" s="7">
+      <c r="V19" s="6">
         <v>15889230.334371746</v>
       </c>
-      <c r="W19" s="7">
+      <c r="W19" s="6">
         <v>15861071.808531517</v>
       </c>
-      <c r="X19" s="7">
+      <c r="X19" s="6">
         <v>15718323.09321606</v>
       </c>
-      <c r="Y19" s="7">
+      <c r="Y19" s="6">
         <v>15280094.41293785</v>
       </c>
-      <c r="Z19" s="7">
+      <c r="Z19" s="6">
         <v>14694880.655699167</v>
       </c>
-      <c r="AA19" s="7">
+      <c r="AA19" s="6">
         <v>11247780.179828193</v>
       </c>
-      <c r="AB19" s="7">
+      <c r="AB19" s="6">
         <v>13709904.649819842</v>
       </c>
-      <c r="AC19" s="7">
+      <c r="AC19" s="6">
         <v>15338648.267646382</v>
       </c>
-      <c r="AD19" s="7">
+      <c r="AD19" s="6">
         <v>15882968.32517501</v>
       </c>
-      <c r="AE19" s="7">
+      <c r="AE19" s="6">
         <v>15919980.524443353</v>
       </c>
-      <c r="AF19" s="7">
+      <c r="AF19" s="6">
         <v>15803314.652009426</v>
       </c>
-      <c r="AG19" s="7">
+      <c r="AG19" s="6">
         <v>15565163.680842586</v>
       </c>
-      <c r="AH19" s="7">
+      <c r="AH19" s="6">
         <v>15189381.813862257</v>
       </c>
-      <c r="AI19" s="7">
+      <c r="AI19" s="6">
         <v>14652670.000708176</v>
       </c>
+      <c r="AJ19" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>31</v>
       </c>
       <c r="B20" t="s">
@@ -2687,83 +2753,86 @@
       <c r="J20" s="1">
         <v>50</v>
       </c>
-      <c r="K20" s="7">
+      <c r="K20" s="6">
         <v>25.642800000000001</v>
       </c>
-      <c r="L20" s="7">
+      <c r="L20" s="6">
         <v>17819576.179180816</v>
       </c>
-      <c r="M20" s="7">
+      <c r="M20" s="6">
         <v>8627.627361269615</v>
       </c>
-      <c r="N20" s="7">
+      <c r="N20" s="6">
         <v>3522.9458062131903</v>
       </c>
-      <c r="O20" s="7">
+      <c r="O20" s="6">
         <v>5104.6815550564288</v>
       </c>
-      <c r="P20" s="7">
+      <c r="P20" s="6">
         <v>2.5554317472545485</v>
       </c>
-      <c r="Q20" s="7">
+      <c r="Q20" s="6">
         <v>11.982437090646577</v>
       </c>
-      <c r="R20" s="7">
+      <c r="R20" s="6">
         <v>22819030.945934437</v>
       </c>
-      <c r="S20" s="7">
+      <c r="S20" s="6">
         <v>26741615.337891877</v>
       </c>
-      <c r="T20" s="7">
+      <c r="T20" s="6">
         <v>29085038.038137883</v>
       </c>
-      <c r="U20" s="7">
+      <c r="U20" s="6">
         <v>30092413.93621349</v>
       </c>
-      <c r="V20" s="7">
+      <c r="V20" s="6">
         <v>30470633.479616378</v>
       </c>
-      <c r="W20" s="7">
+      <c r="W20" s="6">
         <v>30138624.205490906</v>
       </c>
-      <c r="X20" s="7">
+      <c r="X20" s="6">
         <v>29292772.088935249</v>
       </c>
-      <c r="Y20" s="7">
+      <c r="Y20" s="6">
         <v>28230373.148913082</v>
       </c>
-      <c r="Z20" s="7">
+      <c r="Z20" s="6">
         <v>26345575.304769173</v>
       </c>
-      <c r="AA20" s="7">
+      <c r="AA20" s="6">
         <v>21060370.355055209</v>
       </c>
-      <c r="AB20" s="7">
+      <c r="AB20" s="6">
         <v>25573809.377434909</v>
       </c>
-      <c r="AC20" s="7">
+      <c r="AC20" s="6">
         <v>28318237.096643195</v>
       </c>
-      <c r="AD20" s="7">
+      <c r="AD20" s="6">
         <v>29761717.439004991</v>
       </c>
-      <c r="AE20" s="7">
+      <c r="AE20" s="6">
         <v>30115501.344202843</v>
       </c>
-      <c r="AF20" s="7">
+      <c r="AF20" s="6">
         <v>29870095.702630628</v>
       </c>
-      <c r="AG20" s="7">
+      <c r="AG20" s="6">
         <v>29153305.558766015</v>
       </c>
-      <c r="AH20" s="7">
+      <c r="AH20" s="6">
         <v>27741116.302164193</v>
       </c>
-      <c r="AI20" s="7">
+      <c r="AI20" s="6">
         <v>25953927.425724126</v>
       </c>
+      <c r="AJ20" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="21" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>31</v>
       </c>
@@ -2794,83 +2863,86 @@
       <c r="J21" s="4">
         <v>50</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21" s="7">
         <v>23.185500000000001</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L21" s="7">
         <v>17138330.513733305</v>
       </c>
-      <c r="M21" s="8">
+      <c r="M21" s="7">
         <v>5863.4578150916941</v>
       </c>
-      <c r="N21" s="8">
+      <c r="N21" s="7">
         <v>2683.6797137876292</v>
       </c>
-      <c r="O21" s="8">
+      <c r="O21" s="7">
         <v>3179.7781013040658</v>
       </c>
-      <c r="P21" s="8">
+      <c r="P21" s="7">
         <v>2.3597334411486699</v>
       </c>
-      <c r="Q21" s="8">
+      <c r="Q21" s="7">
         <v>7.9549407519239361</v>
       </c>
-      <c r="R21" s="8">
+      <c r="R21" s="7">
         <v>21954020.576787651</v>
       </c>
-      <c r="S21" s="8">
+      <c r="S21" s="7">
         <v>25740782.020151533</v>
       </c>
-      <c r="T21" s="8">
+      <c r="T21" s="7">
         <v>27081482.326011539</v>
       </c>
-      <c r="U21" s="8">
+      <c r="U21" s="7">
         <v>27884011.599201165</v>
       </c>
-      <c r="V21" s="8">
+      <c r="V21" s="7">
         <v>27981163.971325677</v>
       </c>
-      <c r="W21" s="8">
+      <c r="W21" s="7">
         <v>27432581.443124358</v>
       </c>
-      <c r="X21" s="8">
+      <c r="X21" s="7">
         <v>26722574.028892163</v>
       </c>
-      <c r="Y21" s="8">
+      <c r="Y21" s="7">
         <v>25755570.075274117</v>
       </c>
-      <c r="Z21" s="8">
+      <c r="Z21" s="7">
         <v>24307784.982681435</v>
       </c>
-      <c r="AA21" s="8">
+      <c r="AA21" s="7">
         <v>19766572.192563768</v>
       </c>
-      <c r="AB21" s="8">
+      <c r="AB21" s="7">
         <v>24249671.56607784</v>
       </c>
-      <c r="AC21" s="8">
+      <c r="AC21" s="7">
         <v>26769567.43245656</v>
       </c>
-      <c r="AD21" s="8">
+      <c r="AD21" s="7">
         <v>27523973.092711031</v>
       </c>
-      <c r="AE21" s="8">
+      <c r="AE21" s="7">
         <v>27656454.49533825</v>
       </c>
-      <c r="AF21" s="8">
+      <c r="AF21" s="7">
         <v>27337390.568642419</v>
       </c>
-      <c r="AG21" s="8">
+      <c r="AG21" s="7">
         <v>26567637.849179689</v>
       </c>
-      <c r="AH21" s="8">
+      <c r="AH21" s="7">
         <v>25458044.828991983</v>
       </c>
-      <c r="AI21" s="8">
+      <c r="AI21" s="7">
         <v>24063165.530871075</v>
       </c>
+      <c r="AJ21" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -2901,84 +2973,87 @@
       <c r="J22" s="1">
         <v>50</v>
       </c>
-      <c r="K22" s="7">
+      <c r="K22" s="6">
         <v>24.927499999999998</v>
       </c>
-      <c r="L22" s="7">
+      <c r="L22" s="6">
         <v>22170841.725542035</v>
       </c>
-      <c r="M22" s="7">
+      <c r="M22" s="6">
         <v>8105.8364181028874</v>
       </c>
-      <c r="N22" s="7">
+      <c r="N22" s="6">
         <v>3772.9795098664299</v>
       </c>
-      <c r="O22" s="7">
+      <c r="O22" s="6">
         <v>4332.8569082364538</v>
       </c>
-      <c r="P22" s="7">
+      <c r="P22" s="6">
         <v>2.6376883356510361</v>
       </c>
-      <c r="Q22" s="7">
+      <c r="Q22" s="6">
         <v>9.5616895001190745</v>
       </c>
-      <c r="R22" s="7">
+      <c r="R22" s="6">
         <v>19723328.894795854</v>
       </c>
-      <c r="S22" s="7">
+      <c r="S22" s="6">
         <v>21802230.696893044</v>
       </c>
-      <c r="T22" s="7">
+      <c r="T22" s="6">
         <v>22381838.538321029</v>
       </c>
-      <c r="U22" s="7">
+      <c r="U22" s="6">
         <v>22272780.66408851</v>
       </c>
-      <c r="V22" s="7">
+      <c r="V22" s="6">
         <v>21644847.226970162</v>
       </c>
-      <c r="W22" s="7">
+      <c r="W22" s="6">
         <v>20899529.608433697</v>
       </c>
-      <c r="X22" s="7">
+      <c r="X22" s="6">
         <v>20210219.242029969</v>
       </c>
-      <c r="Y22" s="7">
+      <c r="Y22" s="6">
         <v>19489829.562064055</v>
       </c>
-      <c r="Z22" s="7">
+      <c r="Z22" s="6">
         <v>18703042.038104396</v>
       </c>
-      <c r="AA22" s="7">
+      <c r="AA22" s="6">
         <v>18061798.4107127</v>
       </c>
-      <c r="AB22" s="7">
+      <c r="AB22" s="6">
         <v>20968654.902643342</v>
       </c>
-      <c r="AC22" s="7">
+      <c r="AC22" s="6">
         <v>22034993.857296746</v>
       </c>
-      <c r="AD22" s="7">
+      <c r="AD22" s="6">
         <v>22007174.394334868</v>
       </c>
-      <c r="AE22" s="7">
+      <c r="AE22" s="6">
         <v>21564314.534612119</v>
       </c>
-      <c r="AF22" s="7">
+      <c r="AF22" s="6">
         <v>20902946.51622669</v>
       </c>
-      <c r="AG22" s="7">
+      <c r="AG22" s="6">
         <v>20170078.375158545</v>
       </c>
-      <c r="AH22" s="7">
+      <c r="AH22" s="6">
         <v>19427442.863852795</v>
       </c>
-      <c r="AI22" s="7">
+      <c r="AI22" s="6">
         <v>18545278.578721382</v>
       </c>
+      <c r="AJ22" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A23" s="12" t="s">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>31</v>
       </c>
       <c r="B23" t="s">
@@ -3008,84 +3083,87 @@
       <c r="J23" s="1">
         <v>50</v>
       </c>
-      <c r="K23" s="7">
+      <c r="K23" s="6">
         <v>26.137499999999999</v>
       </c>
-      <c r="L23" s="7">
+      <c r="L23" s="6">
         <v>19490655.066456571</v>
       </c>
-      <c r="M23" s="7">
+      <c r="M23" s="6">
         <v>7576.7937977969968</v>
       </c>
-      <c r="N23" s="7">
+      <c r="N23" s="6">
         <v>3062.4107935250122</v>
       </c>
-      <c r="O23" s="7">
+      <c r="O23" s="6">
         <v>4514.3830042719819</v>
       </c>
-      <c r="P23" s="7">
+      <c r="P23" s="6">
         <v>2.3027344601451962</v>
       </c>
-      <c r="Q23" s="7">
+      <c r="Q23" s="6">
         <v>8.8185717944715964</v>
       </c>
-      <c r="R23" s="7">
+      <c r="R23" s="6">
         <v>20399276.196271483</v>
       </c>
-      <c r="S23" s="7">
+      <c r="S23" s="6">
         <v>23975022.214020494</v>
       </c>
-      <c r="T23" s="7">
+      <c r="T23" s="6">
         <v>26841544.038064789</v>
       </c>
-      <c r="U23" s="7">
+      <c r="U23" s="6">
         <v>28732699.492918812</v>
       </c>
-      <c r="V23" s="7">
+      <c r="V23" s="6">
         <v>29807425.998950582</v>
       </c>
-      <c r="W23" s="7">
+      <c r="W23" s="6">
         <v>30441067.195630118</v>
       </c>
-      <c r="X23" s="7">
+      <c r="X23" s="6">
         <v>30417827.538020916</v>
       </c>
-      <c r="Y23" s="7">
+      <c r="Y23" s="6">
         <v>29873301.434443958</v>
       </c>
-      <c r="Z23" s="7">
+      <c r="Z23" s="6">
         <v>28836202.17174292</v>
       </c>
-      <c r="AA23" s="7">
+      <c r="AA23" s="6">
         <v>19038003.995269224</v>
       </c>
-      <c r="AB23" s="7">
+      <c r="AB23" s="6">
         <v>23181141.548803631</v>
       </c>
-      <c r="AC23" s="7">
+      <c r="AC23" s="6">
         <v>26139134.316663515</v>
       </c>
-      <c r="AD23" s="7">
+      <c r="AD23" s="6">
         <v>28246844.985510089</v>
       </c>
-      <c r="AE23" s="7">
+      <c r="AE23" s="6">
         <v>29562222.752503891</v>
       </c>
-      <c r="AF23" s="7">
+      <c r="AF23" s="6">
         <v>30109533.464456145</v>
       </c>
-      <c r="AG23" s="7">
+      <c r="AG23" s="6">
         <v>30154512.000239607</v>
       </c>
-      <c r="AH23" s="7">
+      <c r="AH23" s="6">
         <v>29605906.258458119</v>
       </c>
-      <c r="AI23" s="7">
+      <c r="AI23" s="6">
         <v>28328542.512437902</v>
       </c>
+      <c r="AJ23" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A24" s="12" t="s">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>31</v>
       </c>
       <c r="B24" t="s">
@@ -3115,83 +3193,86 @@
       <c r="J24" s="1">
         <v>50</v>
       </c>
-      <c r="K24" s="7">
+      <c r="K24" s="6">
         <v>25.952200000000001</v>
       </c>
-      <c r="L24" s="7">
+      <c r="L24" s="6">
         <v>24849323.480220713</v>
       </c>
-      <c r="M24" s="7">
+      <c r="M24" s="6">
         <v>6021.5910541267149</v>
       </c>
-      <c r="N24" s="7">
+      <c r="N24" s="6">
         <v>2893.4510873188074</v>
       </c>
-      <c r="O24" s="7">
+      <c r="O24" s="6">
         <v>3128.139966807908</v>
       </c>
-      <c r="P24" s="7">
+      <c r="P24" s="6">
         <v>2.1274384482329212</v>
       </c>
-      <c r="Q24" s="7">
+      <c r="Q24" s="6">
         <v>5.0953650048961165</v>
       </c>
-      <c r="R24" s="7">
+      <c r="R24" s="6">
         <v>24825225.32747291</v>
       </c>
-      <c r="S24" s="7">
+      <c r="S24" s="6">
         <v>29241285.363728955</v>
       </c>
-      <c r="T24" s="7">
+      <c r="T24" s="6">
         <v>31893841.835492283</v>
       </c>
-      <c r="U24" s="7">
+      <c r="U24" s="6">
         <v>32984449.969104163</v>
       </c>
-      <c r="V24" s="7">
+      <c r="V24" s="6">
         <v>33493400.846528765</v>
       </c>
-      <c r="W24" s="7">
+      <c r="W24" s="6">
         <v>33278647.744484402</v>
       </c>
-      <c r="X24" s="7">
+      <c r="X24" s="6">
         <v>32698840.337061882</v>
       </c>
-      <c r="Y24" s="7">
+      <c r="Y24" s="6">
         <v>31762978.151851851</v>
       </c>
-      <c r="Z24" s="7">
+      <c r="Z24" s="6">
         <v>29855976.950598363</v>
       </c>
-      <c r="AA24" s="7">
+      <c r="AA24" s="6">
         <v>23073946.217075173</v>
       </c>
-      <c r="AB24" s="7">
+      <c r="AB24" s="6">
         <v>27919070.243167426</v>
       </c>
-      <c r="AC24" s="7">
+      <c r="AC24" s="6">
         <v>31000283.369999729</v>
       </c>
-      <c r="AD24" s="7">
+      <c r="AD24" s="6">
         <v>32674056.446354922</v>
       </c>
-      <c r="AE24" s="7">
+      <c r="AE24" s="6">
         <v>33130895.760772325</v>
       </c>
-      <c r="AF24" s="7">
+      <c r="AF24" s="6">
         <v>33091351.706561081</v>
       </c>
-      <c r="AG24" s="7">
+      <c r="AG24" s="6">
         <v>32503153.070494615</v>
       </c>
-      <c r="AH24" s="7">
+      <c r="AH24" s="6">
         <v>31212810.323632576</v>
       </c>
-      <c r="AI24" s="7">
+      <c r="AI24" s="6">
         <v>29408628.258093428</v>
       </c>
+      <c r="AJ24" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="25" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>31</v>
       </c>
@@ -3222,83 +3303,86 @@
       <c r="J25" s="4">
         <v>50</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="7">
         <v>24.7196</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="7">
         <v>16961165.030899476</v>
       </c>
-      <c r="M25" s="8">
+      <c r="M25" s="7">
         <v>8353.6458812873116</v>
       </c>
-      <c r="N25" s="8">
+      <c r="N25" s="7">
         <v>3779.596577448187</v>
       </c>
-      <c r="O25" s="8">
+      <c r="O25" s="7">
         <v>4574.049303839126</v>
       </c>
-      <c r="P25" s="8">
+      <c r="P25" s="7">
         <v>3.2661391420203572</v>
       </c>
-      <c r="Q25" s="8">
+      <c r="Q25" s="7">
         <v>15.5678577509637</v>
       </c>
-      <c r="R25" s="8">
+      <c r="R25" s="7">
         <v>16227241.024887826</v>
       </c>
-      <c r="S25" s="8">
+      <c r="S25" s="7">
         <v>19696972.480273023</v>
       </c>
-      <c r="T25" s="8">
+      <c r="T25" s="7">
         <v>21775607.914163094</v>
       </c>
-      <c r="U25" s="8">
+      <c r="U25" s="7">
         <v>23020387.679041855</v>
       </c>
-      <c r="V25" s="8">
+      <c r="V25" s="7">
         <v>23818255.588281136</v>
       </c>
-      <c r="W25" s="8">
+      <c r="W25" s="7">
         <v>24310067.354904823</v>
       </c>
-      <c r="X25" s="8">
+      <c r="X25" s="7">
         <v>24379003.112845901</v>
       </c>
-      <c r="Y25" s="8">
+      <c r="Y25" s="7">
         <v>23917978.869199421</v>
       </c>
-      <c r="Z25" s="8">
+      <c r="Z25" s="7">
         <v>22768409.92634562</v>
       </c>
-      <c r="AA25" s="8">
+      <c r="AA25" s="7">
         <v>14314805.132985387</v>
       </c>
-      <c r="AB25" s="8">
+      <c r="AB25" s="7">
         <v>18596397.267652016</v>
       </c>
-      <c r="AC25" s="8">
+      <c r="AC25" s="7">
         <v>21229399.050326332</v>
       </c>
-      <c r="AD25" s="8">
+      <c r="AD25" s="7">
         <v>22751175.489303712</v>
       </c>
-      <c r="AE25" s="8">
+      <c r="AE25" s="7">
         <v>23647656.65625437</v>
       </c>
-      <c r="AF25" s="8">
+      <c r="AF25" s="7">
         <v>24095367.362280581</v>
       </c>
-      <c r="AG25" s="8">
+      <c r="AG25" s="7">
         <v>24112429.294837259</v>
       </c>
-      <c r="AH25" s="8">
+      <c r="AH25" s="7">
         <v>23546196.946480423</v>
       </c>
-      <c r="AI25" s="8">
+      <c r="AI25" s="7">
         <v>22231435.672014918</v>
       </c>
+      <c r="AJ25" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -3329,83 +3413,86 @@
       <c r="J26" s="1">
         <v>50</v>
       </c>
-      <c r="K26" s="7">
+      <c r="K26" s="6">
         <v>22.279699999999998</v>
       </c>
-      <c r="L26" s="7">
+      <c r="L26" s="6">
         <v>10522831.506272467</v>
       </c>
-      <c r="M26" s="7">
+      <c r="M26" s="6">
         <v>9501.8792857954577</v>
       </c>
-      <c r="N26" s="7">
+      <c r="N26" s="6">
         <v>3300.419956011739</v>
       </c>
-      <c r="O26" s="7">
+      <c r="O26" s="6">
         <v>6201.4593297837182</v>
       </c>
-      <c r="P26" s="7">
+      <c r="P26" s="6">
         <v>4.0663833672884335</v>
       </c>
-      <c r="Q26" s="7">
+      <c r="Q26" s="6">
         <v>36.346925812752147</v>
       </c>
-      <c r="R26" s="7">
+      <c r="R26" s="6">
         <v>16418228.732056851</v>
       </c>
-      <c r="S26" s="7">
+      <c r="S26" s="6">
         <v>19854143.964042392</v>
       </c>
-      <c r="T26" s="7">
+      <c r="T26" s="6">
         <v>21682033.999513011</v>
       </c>
-      <c r="U26" s="7">
+      <c r="U26" s="6">
         <v>22878271.354746394</v>
       </c>
-      <c r="V26" s="7">
+      <c r="V26" s="6">
         <v>23532651.2964877</v>
       </c>
-      <c r="W26" s="7">
+      <c r="W26" s="6">
         <v>23467458.951098278</v>
       </c>
-      <c r="X26" s="7">
+      <c r="X26" s="6">
         <v>22883156.392103262</v>
       </c>
-      <c r="Y26" s="7">
+      <c r="Y26" s="6">
         <v>21763713.955909982</v>
       </c>
-      <c r="Z26" s="7">
+      <c r="Z26" s="6">
         <v>20530080.597308073</v>
       </c>
-      <c r="AA26" s="7">
+      <c r="AA26" s="6">
         <v>15054143.082214948</v>
       </c>
-      <c r="AB26" s="7">
+      <c r="AB26" s="6">
         <v>18686516.473035902</v>
       </c>
-      <c r="AC26" s="7">
+      <c r="AC26" s="6">
         <v>21259200.52667113</v>
       </c>
-      <c r="AD26" s="7">
+      <c r="AD26" s="6">
         <v>22569470.169651326</v>
       </c>
-      <c r="AE26" s="7">
+      <c r="AE26" s="6">
         <v>23169120.018026371</v>
       </c>
-      <c r="AF26" s="7">
+      <c r="AF26" s="6">
         <v>23203359.663639918</v>
       </c>
-      <c r="AG26" s="7">
+      <c r="AG26" s="6">
         <v>22583498.550161485</v>
       </c>
-      <c r="AH26" s="7">
+      <c r="AH26" s="6">
         <v>21642848.017311852</v>
       </c>
-      <c r="AI26" s="7">
+      <c r="AI26" s="6">
         <v>20323380.728523735</v>
       </c>
+      <c r="AJ26" s="6">
+        <v>3.2462049999999998</v>
+      </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -3436,83 +3523,86 @@
       <c r="J27" s="1">
         <v>50</v>
       </c>
-      <c r="K27" s="7">
+      <c r="K27" s="6">
         <v>20.2227</v>
       </c>
-      <c r="L27" s="7">
+      <c r="L27" s="6">
         <v>9881043.4166893512</v>
       </c>
-      <c r="M27" s="7">
+      <c r="M27" s="6">
         <v>8625.9814266482063</v>
       </c>
-      <c r="N27" s="7">
+      <c r="N27" s="6">
         <v>2559.0751843862467</v>
       </c>
-      <c r="O27" s="7">
+      <c r="O27" s="6">
         <v>6066.9062422619572</v>
       </c>
-      <c r="P27" s="7">
+      <c r="P27" s="6">
         <v>2.6127429196506191</v>
       </c>
-      <c r="Q27" s="7">
+      <c r="Q27" s="6">
         <v>22.541901447098152</v>
       </c>
-      <c r="R27" s="7">
+      <c r="R27" s="6">
         <v>18336531.629250348</v>
       </c>
-      <c r="S27" s="7">
+      <c r="S27" s="6">
         <v>22790615.719253156</v>
       </c>
-      <c r="T27" s="7">
+      <c r="T27" s="6">
         <v>25033086.5890388</v>
       </c>
-      <c r="U27" s="7">
+      <c r="U27" s="6">
         <v>26010506.947258156</v>
       </c>
-      <c r="V27" s="7">
+      <c r="V27" s="6">
         <v>25971818.348270554</v>
       </c>
-      <c r="W27" s="7">
+      <c r="W27" s="6">
         <v>25488801.833207838</v>
       </c>
-      <c r="X27" s="7">
+      <c r="X27" s="6">
         <v>24340913.586255282</v>
       </c>
-      <c r="Y27" s="7">
+      <c r="Y27" s="6">
         <v>22636286.505660102</v>
       </c>
-      <c r="Z27" s="7">
+      <c r="Z27" s="6">
         <v>20956186.818461604</v>
       </c>
-      <c r="AA27" s="7">
+      <c r="AA27" s="6">
         <v>16635910.290045543</v>
       </c>
-      <c r="AB27" s="7">
+      <c r="AB27" s="6">
         <v>21167812.993295018</v>
       </c>
-      <c r="AC27" s="7">
+      <c r="AC27" s="6">
         <v>24294337.347477373</v>
       </c>
-      <c r="AD27" s="7">
+      <c r="AD27" s="6">
         <v>25493813.914020829</v>
       </c>
-      <c r="AE27" s="7">
+      <c r="AE27" s="6">
         <v>25747011.867134422</v>
       </c>
-      <c r="AF27" s="7">
+      <c r="AF27" s="6">
         <v>25129932.793784827</v>
       </c>
-      <c r="AG27" s="7">
+      <c r="AG27" s="6">
         <v>23978005.68883317</v>
       </c>
-      <c r="AH27" s="7">
+      <c r="AH27" s="6">
         <v>22522092.049515773</v>
       </c>
-      <c r="AI27" s="7">
+      <c r="AI27" s="6">
         <v>20693206.850758381</v>
       </c>
+      <c r="AJ27" s="6">
+        <v>1.8057576000000002</v>
+      </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -3543,83 +3633,86 @@
       <c r="J28" s="1">
         <v>50</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K28" s="6">
         <v>19.403700000000001</v>
       </c>
-      <c r="L28" s="7">
+      <c r="L28" s="6">
         <v>9708484.6838893015</v>
       </c>
-      <c r="M28" s="7">
+      <c r="M28" s="6">
         <v>8097.6271483294113</v>
       </c>
-      <c r="N28" s="7">
+      <c r="N28" s="6">
         <v>2468.7846454352939</v>
       </c>
-      <c r="O28" s="7">
+      <c r="O28" s="6">
         <v>5628.8425028941192</v>
       </c>
-      <c r="P28" s="7">
+      <c r="P28" s="6">
         <v>2.3547350921580135</v>
       </c>
-      <c r="Q28" s="7">
+      <c r="Q28" s="6">
         <v>19.410491762597481</v>
       </c>
-      <c r="R28" s="7">
+      <c r="R28" s="6">
         <v>16813016.51964765</v>
       </c>
-      <c r="S28" s="7">
+      <c r="S28" s="6">
         <v>21805816.197338138</v>
       </c>
-      <c r="T28" s="7">
+      <c r="T28" s="6">
         <v>24817533.991142493</v>
       </c>
-      <c r="U28" s="7">
+      <c r="U28" s="6">
         <v>25820063.664509341</v>
       </c>
-      <c r="V28" s="7">
+      <c r="V28" s="6">
         <v>26241810.925247014</v>
       </c>
-      <c r="W28" s="7">
+      <c r="W28" s="6">
         <v>26053789.072248079</v>
       </c>
-      <c r="X28" s="7">
+      <c r="X28" s="6">
         <v>25296209.37747816</v>
       </c>
-      <c r="Y28" s="7">
+      <c r="Y28" s="6">
         <v>23731353.760943539</v>
       </c>
-      <c r="Z28" s="7">
+      <c r="Z28" s="6">
         <v>21890589.605323039</v>
       </c>
-      <c r="AA28" s="7">
+      <c r="AA28" s="6">
         <v>15867608.81113652</v>
       </c>
-      <c r="AB28" s="7">
+      <c r="AB28" s="6">
         <v>20045740.632800311</v>
       </c>
-      <c r="AC28" s="7">
+      <c r="AC28" s="6">
         <v>23643765.28497038</v>
       </c>
-      <c r="AD28" s="7">
+      <c r="AD28" s="6">
         <v>25509807.683310311</v>
       </c>
-      <c r="AE28" s="7">
+      <c r="AE28" s="6">
         <v>25936399.825974971</v>
       </c>
-      <c r="AF28" s="7">
+      <c r="AF28" s="6">
         <v>25760335.368339386</v>
       </c>
-      <c r="AG28" s="7">
+      <c r="AG28" s="6">
         <v>24838401.58330572</v>
       </c>
-      <c r="AH28" s="7">
+      <c r="AH28" s="6">
         <v>23470502.343442742</v>
       </c>
-      <c r="AI28" s="7">
+      <c r="AI28" s="6">
         <v>21662491.675118409</v>
       </c>
+      <c r="AJ28" s="6">
+        <v>1.5343400000000003</v>
+      </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -3650,83 +3743,86 @@
       <c r="J29" s="1">
         <v>2</v>
       </c>
-      <c r="K29" s="7">
+      <c r="K29" s="6">
         <v>7.1063799999999997</v>
       </c>
-      <c r="L29" s="7">
+      <c r="L29" s="6">
         <v>3180514.4994760752</v>
       </c>
-      <c r="M29" s="7">
+      <c r="M29" s="6">
         <v>3177.7876714136255</v>
       </c>
-      <c r="N29" s="7">
+      <c r="N29" s="6">
         <v>1036.937101525667</v>
       </c>
-      <c r="O29" s="7">
+      <c r="O29" s="6">
         <v>2140.8505698879499</v>
       </c>
-      <c r="P29" s="7">
+      <c r="P29" s="6">
         <v>2.7742505631067962</v>
       </c>
-      <c r="Q29" s="7">
+      <c r="Q29" s="6">
         <v>27.306709130512989</v>
       </c>
-      <c r="R29" s="7">
+      <c r="R29" s="6">
         <v>4318934.3519322164</v>
       </c>
-      <c r="S29" s="7">
+      <c r="S29" s="6">
         <v>4578185.9026988624</v>
       </c>
-      <c r="T29" s="7">
+      <c r="T29" s="6">
         <v>4796405.0544131594</v>
       </c>
-      <c r="U29" s="7">
+      <c r="U29" s="6">
         <v>4738348.3031305475</v>
       </c>
-      <c r="V29" s="7">
+      <c r="V29" s="6">
         <v>4758238.1402506679</v>
       </c>
-      <c r="W29" s="7">
+      <c r="W29" s="6">
         <v>4809184.1376743373</v>
       </c>
-      <c r="X29" s="7">
+      <c r="X29" s="6">
         <v>4955750.7589634545</v>
       </c>
-      <c r="Y29" s="7">
+      <c r="Y29" s="6">
         <v>5389662.4111107877</v>
       </c>
-      <c r="Z29" s="7">
+      <c r="Z29" s="6">
         <v>5407009.4664117061</v>
       </c>
-      <c r="AA29" s="7">
+      <c r="AA29" s="6">
         <v>4188226.4406403704</v>
       </c>
-      <c r="AB29" s="7">
+      <c r="AB29" s="6">
         <v>4545164.5038836226</v>
       </c>
-      <c r="AC29" s="7">
+      <c r="AC29" s="6">
         <v>4656890.4110062495</v>
       </c>
-      <c r="AD29" s="7">
+      <c r="AD29" s="6">
         <v>4777245.3666811706</v>
       </c>
-      <c r="AE29" s="7">
+      <c r="AE29" s="6">
         <v>4773503.444890203</v>
       </c>
-      <c r="AF29" s="7">
+      <c r="AF29" s="6">
         <v>4854986.4570637532</v>
       </c>
-      <c r="AG29" s="7">
+      <c r="AG29" s="6">
         <v>5082904.0031043841</v>
       </c>
-      <c r="AH29" s="7">
+      <c r="AH29" s="6">
         <v>5171554.8143780995</v>
       </c>
-      <c r="AI29" s="7">
+      <c r="AI29" s="6">
         <v>5159718.6699212128</v>
       </c>
+      <c r="AJ29" s="6">
+        <v>2.0508009999999999</v>
+      </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -3757,83 +3853,86 @@
       <c r="J30" s="1">
         <v>2</v>
       </c>
-      <c r="K30" s="7">
+      <c r="K30" s="6">
         <v>7.0480999999999998</v>
       </c>
-      <c r="L30" s="7">
+      <c r="L30" s="6">
         <v>2671610.7896518451</v>
       </c>
-      <c r="M30" s="7">
+      <c r="M30" s="6">
         <v>2883.8468138914518</v>
       </c>
-      <c r="N30" s="7">
+      <c r="N30" s="6">
         <v>966.17031868474498</v>
       </c>
-      <c r="O30" s="7">
+      <c r="O30" s="6">
         <v>1917.6764952067015</v>
       </c>
-      <c r="P30" s="7">
+      <c r="P30" s="6">
         <v>2.7570950271889401</v>
       </c>
-      <c r="Q30" s="7">
+      <c r="Q30" s="6">
         <v>29.083545392591557</v>
       </c>
-      <c r="R30" s="7">
+      <c r="R30" s="6">
         <v>5283158.7763407324</v>
       </c>
-      <c r="S30" s="7">
+      <c r="S30" s="6">
         <v>5548715.8281203741</v>
       </c>
-      <c r="T30" s="7">
+      <c r="T30" s="6">
         <v>5573674.1769550769</v>
       </c>
-      <c r="U30" s="7">
+      <c r="U30" s="6">
         <v>5531005.6530878795</v>
       </c>
-      <c r="V30" s="7">
+      <c r="V30" s="6">
         <v>5454108.4577146899</v>
       </c>
-      <c r="W30" s="7">
+      <c r="W30" s="6">
         <v>5508922.7923121676</v>
       </c>
-      <c r="X30" s="7">
+      <c r="X30" s="6">
         <v>5759951.3880557474</v>
       </c>
-      <c r="Y30" s="7">
+      <c r="Y30" s="6">
         <v>6211898.5091345217</v>
       </c>
-      <c r="Z30" s="7">
+      <c r="Z30" s="6">
         <v>6195702.6424887301</v>
       </c>
-      <c r="AA30" s="7">
+      <c r="AA30" s="6">
         <v>5156978.0663626641</v>
       </c>
-      <c r="AB30" s="7">
+      <c r="AB30" s="6">
         <v>5424529.5605298635</v>
       </c>
-      <c r="AC30" s="7">
+      <c r="AC30" s="6">
         <v>5539846.586353939</v>
       </c>
-      <c r="AD30" s="7">
+      <c r="AD30" s="6">
         <v>5513243.1380185578</v>
       </c>
-      <c r="AE30" s="7">
+      <c r="AE30" s="6">
         <v>5519942.136834953</v>
       </c>
-      <c r="AF30" s="7">
+      <c r="AF30" s="6">
         <v>5602859.2701811101</v>
       </c>
-      <c r="AG30" s="7">
+      <c r="AG30" s="6">
         <v>5839329.5828641783</v>
       </c>
-      <c r="AH30" s="7">
+      <c r="AH30" s="6">
         <v>5969886.0379214892</v>
       </c>
-      <c r="AI30" s="7">
+      <c r="AI30" s="6">
         <v>5911155.539062188</v>
       </c>
+      <c r="AJ30" s="6">
+        <v>1.9448177</v>
+      </c>
     </row>
-    <row r="31" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>42</v>
       </c>
@@ -3864,83 +3963,86 @@
       <c r="J31" s="4">
         <v>50</v>
       </c>
-      <c r="K31" s="8">
+      <c r="K31" s="7">
         <v>19.027699999999999</v>
       </c>
-      <c r="L31" s="8">
+      <c r="L31" s="7">
         <v>7022890.426079019</v>
       </c>
-      <c r="M31" s="8">
+      <c r="M31" s="7">
         <v>9354.1436324102906</v>
       </c>
-      <c r="N31" s="8">
+      <c r="N31" s="7">
         <v>2586.5636361310321</v>
       </c>
-      <c r="O31" s="8">
+      <c r="O31" s="7">
         <v>6767.5799962792607</v>
       </c>
-      <c r="P31" s="8">
+      <c r="P31" s="7">
         <v>3.2867379087858448</v>
       </c>
-      <c r="Q31" s="8">
+      <c r="Q31" s="7">
         <v>42.919340891968837</v>
       </c>
-      <c r="R31" s="8">
+      <c r="R31" s="7">
         <v>14564499.419269491</v>
       </c>
-      <c r="S31" s="8">
+      <c r="S31" s="7">
         <v>18372472.335616298</v>
       </c>
-      <c r="T31" s="8">
+      <c r="T31" s="7">
         <v>21426134.606720123</v>
       </c>
-      <c r="U31" s="8">
+      <c r="U31" s="7">
         <v>23235846.558729511</v>
       </c>
-      <c r="V31" s="8">
+      <c r="V31" s="7">
         <v>23740225.589244962</v>
       </c>
-      <c r="W31" s="8">
+      <c r="W31" s="7">
         <v>23784963.934820391</v>
       </c>
-      <c r="X31" s="8">
+      <c r="X31" s="7">
         <v>23414761.038740449</v>
       </c>
-      <c r="Y31" s="8">
+      <c r="Y31" s="7">
         <v>22406575.697432149</v>
       </c>
-      <c r="Z31" s="8">
+      <c r="Z31" s="7">
         <v>20818016.432474934</v>
       </c>
-      <c r="AA31" s="8">
+      <c r="AA31" s="7">
         <v>13600797.443530602</v>
       </c>
-      <c r="AB31" s="8">
+      <c r="AB31" s="7">
         <v>17341229.654994089</v>
       </c>
-      <c r="AC31" s="8">
+      <c r="AC31" s="7">
         <v>20519932.524978552</v>
       </c>
-      <c r="AD31" s="8">
+      <c r="AD31" s="7">
         <v>22523899.063910186</v>
       </c>
-      <c r="AE31" s="8">
+      <c r="AE31" s="7">
         <v>23507198.901652865</v>
       </c>
-      <c r="AF31" s="8">
+      <c r="AF31" s="7">
         <v>23576370.132954922</v>
       </c>
-      <c r="AG31" s="8">
+      <c r="AG31" s="7">
         <v>23075203.775807016</v>
       </c>
-      <c r="AH31" s="8">
+      <c r="AH31" s="7">
         <v>22040166.045832481</v>
       </c>
-      <c r="AI31" s="8">
+      <c r="AI31" s="7">
         <v>20746788.57311007</v>
       </c>
+      <c r="AJ31" s="7">
+        <v>2.3474759999999999</v>
+      </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>42</v>
       </c>
@@ -3971,83 +4073,86 @@
       <c r="J32" s="1">
         <v>2</v>
       </c>
-      <c r="K32" s="7">
+      <c r="K32" s="6">
         <v>8.7441300000000002</v>
       </c>
-      <c r="L32" s="7">
+      <c r="L32" s="6">
         <v>3339135.2905835654</v>
       </c>
-      <c r="M32" s="7">
+      <c r="M32" s="6">
         <v>3965.2160727218111</v>
       </c>
-      <c r="N32" s="7">
+      <c r="N32" s="6">
         <v>1070.1459313975897</v>
       </c>
-      <c r="O32" s="7">
+      <c r="O32" s="6">
         <v>2891.6261324561387</v>
       </c>
-      <c r="P32" s="7">
+      <c r="P32" s="6">
         <v>2.5230832964071852</v>
       </c>
-      <c r="Q32" s="7">
+      <c r="Q32" s="6">
         <v>29.705721858198711</v>
       </c>
-      <c r="R32" s="7">
+      <c r="R32" s="6">
         <v>7021189.5945427315</v>
       </c>
-      <c r="S32" s="7">
+      <c r="S32" s="6">
         <v>7032925.0437465506</v>
       </c>
-      <c r="T32" s="7">
+      <c r="T32" s="6">
         <v>6840096.5748538552</v>
       </c>
-      <c r="U32" s="7">
+      <c r="U32" s="6">
         <v>6976495.7249158211</v>
       </c>
-      <c r="V32" s="7">
+      <c r="V32" s="6">
         <v>7478858.8305687746</v>
       </c>
-      <c r="W32" s="7">
+      <c r="W32" s="6">
         <v>8254622.7000973616</v>
       </c>
-      <c r="X32" s="7">
+      <c r="X32" s="6">
         <v>8518642.9022301454</v>
       </c>
-      <c r="Y32" s="7">
+      <c r="Y32" s="6">
         <v>8265239.2023161482</v>
       </c>
-      <c r="Z32" s="7">
+      <c r="Z32" s="6">
         <v>8182685.6374641359</v>
       </c>
-      <c r="AA32" s="7">
+      <c r="AA32" s="6">
         <v>6722648.8452255893</v>
       </c>
-      <c r="AB32" s="7">
+      <c r="AB32" s="6">
         <v>6929460.1251453608</v>
       </c>
-      <c r="AC32" s="7">
+      <c r="AC32" s="6">
         <v>7004596.7369478894</v>
       </c>
-      <c r="AD32" s="7">
+      <c r="AD32" s="6">
         <v>7145230.2521196492</v>
       </c>
-      <c r="AE32" s="7">
+      <c r="AE32" s="6">
         <v>7561931.8780226074</v>
       </c>
-      <c r="AF32" s="7">
+      <c r="AF32" s="6">
         <v>7964959.6240624124</v>
       </c>
-      <c r="AG32" s="7">
+      <c r="AG32" s="6">
         <v>8259927.5398550127</v>
       </c>
-      <c r="AH32" s="7">
+      <c r="AH32" s="6">
         <v>8347285.2786644688</v>
       </c>
-      <c r="AI32" s="7">
+      <c r="AI32" s="6">
         <v>8448971.5412744824</v>
       </c>
+      <c r="AJ32" s="12">
+        <v>1.6823039999999998</v>
+      </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -4078,83 +4183,86 @@
       <c r="J33" s="1">
         <v>50</v>
       </c>
-      <c r="K33" s="7">
+      <c r="K33" s="6">
         <v>22.164100000000001</v>
       </c>
-      <c r="L33" s="7">
+      <c r="L33" s="6">
         <v>13774793.600500647</v>
       </c>
-      <c r="M33" s="7">
+      <c r="M33" s="6">
         <v>8414.5327556591092</v>
       </c>
-      <c r="N33" s="7">
+      <c r="N33" s="6">
         <v>2990.2252675081181</v>
       </c>
-      <c r="O33" s="7">
+      <c r="O33" s="6">
         <v>5424.307488150991</v>
       </c>
-      <c r="P33" s="7">
+      <c r="P33" s="6">
         <v>2.4872060338393824</v>
       </c>
-      <c r="Q33" s="7">
+      <c r="Q33" s="6">
         <v>15.087748991812042</v>
       </c>
-      <c r="R33" s="7">
+      <c r="R33" s="6">
         <v>16520670.304294983</v>
       </c>
-      <c r="S33" s="7">
+      <c r="S33" s="6">
         <v>20389145.33495611</v>
       </c>
-      <c r="T33" s="7">
+      <c r="T33" s="6">
         <v>22268432.424956154</v>
       </c>
-      <c r="U33" s="7">
+      <c r="U33" s="6">
         <v>23261565.454005692</v>
       </c>
-      <c r="V33" s="7">
+      <c r="V33" s="6">
         <v>23768527.384456813</v>
       </c>
-      <c r="W33" s="7">
+      <c r="W33" s="6">
         <v>23799468.522658873</v>
       </c>
-      <c r="X33" s="7">
+      <c r="X33" s="6">
         <v>23498383.237800695</v>
       </c>
-      <c r="Y33" s="7">
+      <c r="Y33" s="6">
         <v>23036553.388083536</v>
       </c>
-      <c r="Z33" s="7">
+      <c r="Z33" s="6">
         <v>22299627.334620021</v>
       </c>
-      <c r="AA33" s="7">
+      <c r="AA33" s="6">
         <v>15051990.8544106</v>
       </c>
-      <c r="AB33" s="7">
+      <c r="AB33" s="6">
         <v>18968700.196756277</v>
       </c>
-      <c r="AC33" s="7">
+      <c r="AC33" s="6">
         <v>21730846.081903942</v>
       </c>
-      <c r="AD33" s="7">
+      <c r="AD33" s="6">
         <v>22994039.923256416</v>
       </c>
-      <c r="AE33" s="7">
+      <c r="AE33" s="6">
         <v>23527442.898296244</v>
       </c>
-      <c r="AF33" s="7">
+      <c r="AF33" s="6">
         <v>23632683.334930059</v>
       </c>
-      <c r="AG33" s="7">
+      <c r="AG33" s="6">
         <v>23411797.367209584</v>
       </c>
-      <c r="AH33" s="7">
+      <c r="AH33" s="6">
         <v>22883316.660247687</v>
       </c>
-      <c r="AI33" s="7">
+      <c r="AI33" s="6">
         <v>22039422.991631038</v>
       </c>
+      <c r="AJ33" s="6">
+        <v>1.8442699999999999</v>
+      </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -4185,83 +4293,86 @@
       <c r="J34" s="1">
         <v>50</v>
       </c>
-      <c r="K34" s="7">
+      <c r="K34" s="6">
         <v>20.457000000000001</v>
       </c>
-      <c r="L34" s="7">
+      <c r="L34" s="6">
         <v>10995121.388679709</v>
       </c>
-      <c r="M34" s="7">
+      <c r="M34" s="6">
         <v>8126.3637084317643</v>
       </c>
-      <c r="N34" s="7">
+      <c r="N34" s="6">
         <v>3219.0754260457793</v>
       </c>
-      <c r="O34" s="7">
+      <c r="O34" s="6">
         <v>4907.2882823859891</v>
       </c>
-      <c r="P34" s="7">
+      <c r="P34" s="6">
         <v>3.1948889312478208</v>
       </c>
-      <c r="Q34" s="7">
+      <c r="Q34" s="6">
         <v>23.262060325958853</v>
       </c>
-      <c r="R34" s="7">
+      <c r="R34" s="6">
         <v>12384653.139527941</v>
       </c>
-      <c r="S34" s="7">
+      <c r="S34" s="6">
         <v>15157135.186150454</v>
       </c>
-      <c r="T34" s="7">
+      <c r="T34" s="6">
         <v>16851529.786245838</v>
       </c>
-      <c r="U34" s="7">
+      <c r="U34" s="6">
         <v>17948466.780685231</v>
       </c>
-      <c r="V34" s="7">
+      <c r="V34" s="6">
         <v>18653981.27758557</v>
       </c>
-      <c r="W34" s="7">
+      <c r="W34" s="6">
         <v>18763068.306787893</v>
       </c>
-      <c r="X34" s="7">
+      <c r="X34" s="6">
         <v>18427744.858686689</v>
       </c>
-      <c r="Y34" s="7">
+      <c r="Y34" s="6">
         <v>17748948.261641663</v>
       </c>
-      <c r="Z34" s="7">
+      <c r="Z34" s="6">
         <v>16689829.939260459</v>
       </c>
-      <c r="AA34" s="7">
+      <c r="AA34" s="6">
         <v>11641092.566934165</v>
       </c>
-      <c r="AB34" s="7">
+      <c r="AB34" s="6">
         <v>14276853.568944799</v>
       </c>
-      <c r="AC34" s="7">
+      <c r="AC34" s="6">
         <v>16435124.040427146</v>
       </c>
-      <c r="AD34" s="7">
+      <c r="AD34" s="6">
         <v>17707004.445939332</v>
       </c>
-      <c r="AE34" s="7">
+      <c r="AE34" s="6">
         <v>18346729.844213136</v>
       </c>
-      <c r="AF34" s="7">
+      <c r="AF34" s="6">
         <v>18540172.931476254</v>
       </c>
-      <c r="AG34" s="7">
+      <c r="AG34" s="6">
         <v>18241924.708961684</v>
       </c>
-      <c r="AH34" s="7">
+      <c r="AH34" s="6">
         <v>17515784.026950561</v>
       </c>
-      <c r="AI34" s="7">
+      <c r="AI34" s="6">
         <v>16413808.227992432</v>
       </c>
+      <c r="AJ34" s="6">
+        <v>2.45418</v>
+      </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -4292,83 +4403,86 @@
       <c r="J35" s="1">
         <v>50</v>
       </c>
-      <c r="K35" s="7">
+      <c r="K35" s="6">
         <v>17.249500000000001</v>
       </c>
-      <c r="L35" s="7">
+      <c r="L35" s="6">
         <v>9013676.9808660597</v>
       </c>
-      <c r="M35" s="7">
+      <c r="M35" s="6">
         <v>8672.807183723995</v>
       </c>
-      <c r="N35" s="7">
+      <c r="N35" s="6">
         <v>4104.6438593188395</v>
       </c>
-      <c r="O35" s="7">
+      <c r="O35" s="6">
         <v>4568.1633244051554</v>
       </c>
-      <c r="P35" s="7">
+      <c r="P35" s="6">
         <v>3.6856532988855113</v>
       </c>
-      <c r="Q35" s="7">
+      <c r="Q35" s="6">
         <v>34.935612823879616</v>
       </c>
-      <c r="R35" s="7">
+      <c r="R35" s="6">
         <v>7716866.1178349247</v>
       </c>
-      <c r="S35" s="7">
+      <c r="S35" s="6">
         <v>9172026.3715508189</v>
       </c>
-      <c r="T35" s="7">
+      <c r="T35" s="6">
         <v>10346115.624764953</v>
       </c>
-      <c r="U35" s="7">
+      <c r="U35" s="6">
         <v>10734896.384647928</v>
       </c>
-      <c r="V35" s="7">
+      <c r="V35" s="6">
         <v>10509732.036857108</v>
       </c>
-      <c r="W35" s="7">
+      <c r="W35" s="6">
         <v>10081410.995680973</v>
       </c>
-      <c r="X35" s="7">
+      <c r="X35" s="6">
         <v>9408060.6709849462</v>
       </c>
-      <c r="Y35" s="7">
+      <c r="Y35" s="6">
         <v>8483100.8443030082</v>
       </c>
-      <c r="Z35" s="7">
+      <c r="Z35" s="6">
         <v>7778228.3498302968</v>
       </c>
-      <c r="AA35" s="7">
+      <c r="AA35" s="6">
         <v>7797727.6378363138</v>
       </c>
-      <c r="AB35" s="7">
+      <c r="AB35" s="6">
         <v>8840133.9550332241</v>
       </c>
-      <c r="AC35" s="7">
+      <c r="AC35" s="6">
         <v>9892111.7986653149</v>
       </c>
-      <c r="AD35" s="7">
+      <c r="AD35" s="6">
         <v>10427282.036462983</v>
       </c>
-      <c r="AE35" s="7">
+      <c r="AE35" s="6">
         <v>10397896.271646582</v>
       </c>
-      <c r="AF35" s="7">
+      <c r="AF35" s="6">
         <v>9928429.1275524944</v>
       </c>
-      <c r="AG35" s="7">
+      <c r="AG35" s="6">
         <v>9213452.7281273976</v>
       </c>
-      <c r="AH35" s="7">
+      <c r="AH35" s="6">
         <v>8515863.3302801624</v>
       </c>
-      <c r="AI35" s="7">
+      <c r="AI35" s="6">
         <v>7842072.6704272702</v>
       </c>
+      <c r="AJ35" s="6">
+        <v>3.018958</v>
+      </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>42</v>
       </c>
@@ -4399,83 +4513,86 @@
       <c r="J36" s="1">
         <v>2</v>
       </c>
-      <c r="K36" s="7">
+      <c r="K36" s="6">
         <v>7.0828699999999998</v>
       </c>
-      <c r="L36" s="7">
+      <c r="L36" s="6">
         <v>2621665.3560544425</v>
       </c>
-      <c r="M36" s="7">
+      <c r="M36" s="6">
         <v>3301.3312936395978</v>
       </c>
-      <c r="N36" s="7">
+      <c r="N36" s="6">
         <v>992.27166733108652</v>
       </c>
-      <c r="O36" s="7">
+      <c r="O36" s="6">
         <v>2309.059626308504</v>
       </c>
-      <c r="P36" s="7">
+      <c r="P36" s="6">
         <v>2.4776038326454293</v>
       </c>
-      <c r="Q36" s="7">
+      <c r="Q36" s="6">
         <v>30.587469260541845</v>
       </c>
-      <c r="R36" s="7">
+      <c r="R36" s="6">
         <v>5716706.131627663</v>
       </c>
-      <c r="S36" s="7">
+      <c r="S36" s="6">
         <v>5964611.6265115701</v>
       </c>
-      <c r="T36" s="7">
+      <c r="T36" s="6">
         <v>5742306.9588942928</v>
       </c>
-      <c r="U36" s="7">
+      <c r="U36" s="6">
         <v>5424532.7341852449</v>
       </c>
-      <c r="V36" s="7">
+      <c r="V36" s="6">
         <v>5449155.4779389594</v>
       </c>
-      <c r="W36" s="7">
+      <c r="W36" s="6">
         <v>5429756.752494798</v>
       </c>
-      <c r="X36" s="7">
+      <c r="X36" s="6">
         <v>5444393.9839938236</v>
       </c>
-      <c r="Y36" s="7">
+      <c r="Y36" s="6">
         <v>5878981.5981488265</v>
       </c>
-      <c r="Z36" s="7">
+      <c r="Z36" s="6">
         <v>6110226.8800747246</v>
       </c>
-      <c r="AA36" s="7">
+      <c r="AA36" s="6">
         <v>5691630.5550467856</v>
       </c>
-      <c r="AB36" s="7">
+      <c r="AB36" s="6">
         <v>5729477.9475819478</v>
       </c>
-      <c r="AC36" s="7">
+      <c r="AC36" s="6">
         <v>5681766.775451486</v>
       </c>
-      <c r="AD36" s="7">
+      <c r="AD36" s="6">
         <v>5591891.7831653645</v>
       </c>
-      <c r="AE36" s="7">
+      <c r="AE36" s="6">
         <v>5427143.4862164054</v>
       </c>
-      <c r="AF36" s="7">
+      <c r="AF36" s="6">
         <v>5446773.6903586145</v>
       </c>
-      <c r="AG36" s="7">
+      <c r="AG36" s="6">
         <v>5645446.7404888682</v>
       </c>
-      <c r="AH36" s="7">
+      <c r="AH36" s="6">
         <v>5758126.1831212649</v>
       </c>
-      <c r="AI36" s="7">
+      <c r="AI36" s="6">
         <v>5651701.5540369945</v>
       </c>
+      <c r="AJ36" s="6">
+        <v>1.6784727349999999</v>
+      </c>
     </row>
-    <row r="37" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>42</v>
       </c>
@@ -4506,83 +4623,86 @@
       <c r="J37" s="4">
         <v>2</v>
       </c>
-      <c r="K37" s="8">
+      <c r="K37" s="7">
         <v>6.7699499999999997</v>
       </c>
-      <c r="L37" s="8">
+      <c r="L37" s="7">
         <v>2480867.1303816042</v>
       </c>
-      <c r="M37" s="8">
+      <c r="M37" s="7">
         <v>3520.064665857662</v>
       </c>
-      <c r="N37" s="8">
+      <c r="N37" s="7">
         <v>983.06536552299531</v>
       </c>
-      <c r="O37" s="8">
+      <c r="O37" s="7">
         <v>2435.4651205408782</v>
       </c>
-      <c r="P37" s="8">
+      <c r="P37" s="7">
         <v>2.6438321401746729</v>
       </c>
-      <c r="Q37" s="8">
+      <c r="Q37" s="7">
         <v>36.836703082358795</v>
       </c>
-      <c r="R37" s="8">
+      <c r="R37" s="7">
         <v>4624756.6842298191</v>
       </c>
-      <c r="S37" s="8">
+      <c r="S37" s="7">
         <v>5160991.6561363349</v>
       </c>
-      <c r="T37" s="8">
+      <c r="T37" s="7">
         <v>5092393.3664262835</v>
       </c>
-      <c r="U37" s="8">
+      <c r="U37" s="7">
         <v>4852262.1629199367</v>
       </c>
-      <c r="V37" s="8">
+      <c r="V37" s="7">
         <v>4880877.2410939373</v>
       </c>
-      <c r="W37" s="8">
+      <c r="W37" s="7">
         <v>4856901.695897256</v>
       </c>
-      <c r="X37" s="8">
+      <c r="X37" s="7">
         <v>4836744.5962215923</v>
       </c>
-      <c r="Y37" s="8">
+      <c r="Y37" s="7">
         <v>5123809.6243605334</v>
       </c>
-      <c r="Z37" s="8">
+      <c r="Z37" s="7">
         <v>5497617.1097832574</v>
       </c>
-      <c r="AA37" s="8">
+      <c r="AA37" s="7">
         <v>4616447.683808811</v>
       </c>
-      <c r="AB37" s="8">
+      <c r="AB37" s="7">
         <v>4847322.5456711715</v>
       </c>
-      <c r="AC37" s="8">
+      <c r="AC37" s="7">
         <v>5001867.5225344561</v>
       </c>
-      <c r="AD37" s="8">
+      <c r="AD37" s="7">
         <v>4984392.354930372</v>
       </c>
-      <c r="AE37" s="8">
+      <c r="AE37" s="7">
         <v>4854580.8209060226</v>
       </c>
-      <c r="AF37" s="8">
+      <c r="AF37" s="7">
         <v>4858710.7043061452</v>
       </c>
-      <c r="AG37" s="8">
+      <c r="AG37" s="7">
         <v>4986786.7841244377</v>
       </c>
-      <c r="AH37" s="8">
+      <c r="AH37" s="7">
         <v>5146049.7714897878</v>
       </c>
-      <c r="AI37" s="8">
+      <c r="AI37" s="7">
         <v>5158805.6665792083</v>
       </c>
+      <c r="AJ37" s="7">
+        <v>1.8380694000000002</v>
+      </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -4613,83 +4733,86 @@
       <c r="J38" s="1">
         <v>2</v>
       </c>
-      <c r="K38" s="7">
+      <c r="K38" s="6">
         <v>8.4647900000000007</v>
       </c>
-      <c r="L38" s="7">
+      <c r="L38" s="6">
         <v>3803766.2860225569</v>
       </c>
-      <c r="M38" s="7">
+      <c r="M38" s="6">
         <v>3088.9976533113318</v>
       </c>
-      <c r="N38" s="7">
+      <c r="N38" s="6">
         <v>1049.1504922288079</v>
       </c>
-      <c r="O38" s="7">
+      <c r="O38" s="6">
         <v>2039.8471610825211</v>
       </c>
-      <c r="P38" s="7">
+      <c r="P38" s="6">
         <v>2.3996702147163118</v>
       </c>
-      <c r="Q38" s="7">
+      <c r="Q38" s="6">
         <v>19.197801634546156</v>
       </c>
-      <c r="R38" s="7">
+      <c r="R38" s="6">
         <v>6615639.3649493381</v>
       </c>
-      <c r="S38" s="7">
+      <c r="S38" s="6">
         <v>6612447.3190191519</v>
       </c>
-      <c r="T38" s="7">
+      <c r="T38" s="6">
         <v>6419622.468957888</v>
       </c>
-      <c r="U38" s="7">
+      <c r="U38" s="6">
         <v>6578706.7847090364</v>
       </c>
-      <c r="V38" s="7">
+      <c r="V38" s="6">
         <v>6774377.4661938148</v>
       </c>
-      <c r="W38" s="7">
+      <c r="W38" s="6">
         <v>7507132.8284019567</v>
       </c>
-      <c r="X38" s="7">
+      <c r="X38" s="6">
         <v>8154977.9727540379</v>
       </c>
-      <c r="Y38" s="7">
+      <c r="Y38" s="6">
         <v>7813406.2701453101</v>
       </c>
-      <c r="Z38" s="7">
+      <c r="Z38" s="6">
         <v>8027024.2358484566</v>
       </c>
-      <c r="AA38" s="7">
+      <c r="AA38" s="6">
         <v>6319199.8917948417</v>
       </c>
-      <c r="AB38" s="7">
+      <c r="AB38" s="6">
         <v>6516157.1213366296</v>
       </c>
-      <c r="AC38" s="7">
+      <c r="AC38" s="6">
         <v>6595533.9008385437</v>
       </c>
-      <c r="AD38" s="7">
+      <c r="AD38" s="6">
         <v>6592230.7122824453</v>
       </c>
-      <c r="AE38" s="7">
+      <c r="AE38" s="6">
         <v>7012322.5918248612</v>
       </c>
-      <c r="AF38" s="7">
+      <c r="AF38" s="6">
         <v>7400841.816895647</v>
       </c>
-      <c r="AG38" s="7">
+      <c r="AG38" s="6">
         <v>7657208.1876428854</v>
       </c>
-      <c r="AH38" s="7">
+      <c r="AH38" s="6">
         <v>8090495.2287434191</v>
       </c>
-      <c r="AI38" s="7">
+      <c r="AI38" s="6">
         <v>8004231.9579842826</v>
       </c>
+      <c r="AJ38" s="6">
+        <v>1.6713574</v>
+      </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -4720,83 +4843,86 @@
       <c r="J39" s="1">
         <v>2</v>
       </c>
-      <c r="K39" s="7">
+      <c r="K39" s="6">
         <v>7.8396999999999997</v>
       </c>
-      <c r="L39" s="7">
+      <c r="L39" s="6">
         <v>3269378.5838507819</v>
       </c>
-      <c r="M39" s="7">
+      <c r="M39" s="6">
         <v>3479.901103998021</v>
       </c>
-      <c r="N39" s="7">
+      <c r="N39" s="6">
         <v>1145.1357865881992</v>
       </c>
-      <c r="O39" s="7">
+      <c r="O39" s="6">
         <v>2334.7653174098427</v>
       </c>
-      <c r="P39" s="7">
+      <c r="P39" s="6">
         <v>2.6243921885574575</v>
       </c>
-      <c r="Q39" s="7">
+      <c r="Q39" s="6">
         <v>27.474446268526243</v>
       </c>
-      <c r="R39" s="7">
+      <c r="R39" s="6">
         <v>4915335.6233765967</v>
       </c>
-      <c r="S39" s="7">
+      <c r="S39" s="6">
         <v>5046520.6806103829</v>
       </c>
-      <c r="T39" s="7">
+      <c r="T39" s="6">
         <v>5082922.3900978044</v>
       </c>
-      <c r="U39" s="7">
+      <c r="U39" s="6">
         <v>5158361.2292961301</v>
       </c>
-      <c r="V39" s="7">
+      <c r="V39" s="6">
         <v>5032038.9982632101</v>
       </c>
-      <c r="W39" s="7">
+      <c r="W39" s="6">
         <v>5163971.3951856038</v>
       </c>
-      <c r="X39" s="7">
+      <c r="X39" s="6">
         <v>5719994.1736042183</v>
       </c>
-      <c r="Y39" s="7">
+      <c r="Y39" s="6">
         <v>6025164.8664352242</v>
       </c>
-      <c r="Z39" s="7">
+      <c r="Z39" s="6">
         <v>5737105.7403750224</v>
       </c>
-      <c r="AA39" s="7">
+      <c r="AA39" s="6">
         <v>4428800.682120583</v>
       </c>
-      <c r="AB39" s="7">
+      <c r="AB39" s="6">
         <v>4997724.4958542939</v>
       </c>
-      <c r="AC39" s="7">
+      <c r="AC39" s="6">
         <v>5101828.0959098712</v>
       </c>
-      <c r="AD39" s="7">
+      <c r="AD39" s="6">
         <v>5057352.7095315708</v>
       </c>
-      <c r="AE39" s="7">
+      <c r="AE39" s="6">
         <v>5161164.7876842348</v>
       </c>
-      <c r="AF39" s="7">
+      <c r="AF39" s="6">
         <v>5354007.617224576</v>
       </c>
-      <c r="AG39" s="7">
+      <c r="AG39" s="6">
         <v>5561426.4218535358</v>
       </c>
-      <c r="AH39" s="7">
+      <c r="AH39" s="6">
         <v>5728537.1786373518</v>
       </c>
-      <c r="AI39" s="7">
+      <c r="AI39" s="6">
         <v>5920370.0864540292</v>
       </c>
+      <c r="AJ39" s="6">
+        <v>1.90668868</v>
+      </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -4827,83 +4953,86 @@
       <c r="J40" s="1">
         <v>50</v>
       </c>
-      <c r="K40" s="7">
+      <c r="K40" s="6">
         <v>22.236899999999999</v>
       </c>
-      <c r="L40" s="7">
+      <c r="L40" s="6">
         <v>12821434.540656574</v>
       </c>
-      <c r="M40" s="7">
+      <c r="M40" s="6">
         <v>8360.6408984512618</v>
       </c>
-      <c r="N40" s="7">
+      <c r="N40" s="6">
         <v>2789.7402537226467</v>
       </c>
-      <c r="O40" s="7">
+      <c r="O40" s="6">
         <v>5570.9006447286165</v>
       </c>
-      <c r="P40" s="7">
+      <c r="P40" s="6">
         <v>2.2888512741369218</v>
       </c>
-      <c r="Q40" s="7">
+      <c r="Q40" s="6">
         <v>14.656162230039023</v>
       </c>
-      <c r="R40" s="7">
+      <c r="R40" s="6">
         <v>20617189.041073393</v>
       </c>
-      <c r="S40" s="7">
+      <c r="S40" s="6">
         <v>24910485.821468063</v>
       </c>
-      <c r="T40" s="7">
+      <c r="T40" s="6">
         <v>26893948.200220492</v>
       </c>
-      <c r="U40" s="7">
+      <c r="U40" s="6">
         <v>28447559.581207551</v>
       </c>
-      <c r="V40" s="7">
+      <c r="V40" s="6">
         <v>29349756.03419983</v>
       </c>
-      <c r="W40" s="7">
+      <c r="W40" s="6">
         <v>28964469.200971235</v>
       </c>
-      <c r="X40" s="7">
+      <c r="X40" s="6">
         <v>28061015.521725744</v>
       </c>
-      <c r="Y40" s="7">
+      <c r="Y40" s="6">
         <v>26768499.768480044</v>
       </c>
-      <c r="Z40" s="7">
+      <c r="Z40" s="6">
         <v>24662731.174240571</v>
       </c>
-      <c r="AA40" s="7">
+      <c r="AA40" s="6">
         <v>19166604.184619717</v>
       </c>
-      <c r="AB40" s="7">
+      <c r="AB40" s="6">
         <v>23340953.144891765</v>
       </c>
-      <c r="AC40" s="7">
+      <c r="AC40" s="6">
         <v>26561787.421377473</v>
       </c>
-      <c r="AD40" s="7">
+      <c r="AD40" s="6">
         <v>28068237.297564771</v>
       </c>
-      <c r="AE40" s="7">
+      <c r="AE40" s="6">
         <v>28703687.391324084</v>
       </c>
-      <c r="AF40" s="7">
+      <c r="AF40" s="6">
         <v>28690921.139503136</v>
       </c>
-      <c r="AG40" s="7">
+      <c r="AG40" s="6">
         <v>27823222.104866788</v>
       </c>
-      <c r="AH40" s="7">
+      <c r="AH40" s="6">
         <v>26252355.936664149</v>
       </c>
-      <c r="AI40" s="7">
+      <c r="AI40" s="6">
         <v>24407998.83458082</v>
       </c>
+      <c r="AJ40" s="6">
+        <v>1.6478199999999994</v>
+      </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -4934,83 +5063,86 @@
       <c r="J41" s="1">
         <v>50</v>
       </c>
-      <c r="K41" s="7">
+      <c r="K41" s="6">
         <v>22.095300000000002</v>
       </c>
-      <c r="L41" s="7">
+      <c r="L41" s="6">
         <v>13239308.233491598</v>
       </c>
-      <c r="M41" s="7">
+      <c r="M41" s="6">
         <v>7402.1200787673069</v>
       </c>
-      <c r="N41" s="7">
+      <c r="N41" s="6">
         <v>2570.6141445718226</v>
       </c>
-      <c r="O41" s="7">
+      <c r="O41" s="6">
         <v>4831.5059341954848</v>
       </c>
-      <c r="P41" s="7">
+      <c r="P41" s="6">
         <v>2.182746226946878</v>
       </c>
-      <c r="Q41" s="7">
+      <c r="Q41" s="6">
         <v>12.080267487645834</v>
       </c>
-      <c r="R41" s="7">
+      <c r="R41" s="6">
         <v>23824186.721275944</v>
       </c>
-      <c r="S41" s="7">
+      <c r="S41" s="6">
         <v>26885271.884598233</v>
       </c>
-      <c r="T41" s="7">
+      <c r="T41" s="6">
         <v>29303825.280330651</v>
       </c>
-      <c r="U41" s="7">
+      <c r="U41" s="6">
         <v>30663130.797560215</v>
       </c>
-      <c r="V41" s="7">
+      <c r="V41" s="6">
         <v>30885504.639102306</v>
       </c>
-      <c r="W41" s="7">
+      <c r="W41" s="6">
         <v>30770489.46572924</v>
       </c>
-      <c r="X41" s="7">
+      <c r="X41" s="6">
         <v>29767757.696044758</v>
       </c>
-      <c r="Y41" s="7">
+      <c r="Y41" s="6">
         <v>28201675.209870659</v>
       </c>
-      <c r="Z41" s="7">
+      <c r="Z41" s="6">
         <v>26507470.010199651</v>
       </c>
-      <c r="AA41" s="7">
+      <c r="AA41" s="6">
         <v>21773189.002298653</v>
       </c>
-      <c r="AB41" s="7">
+      <c r="AB41" s="6">
         <v>26281420.246070266</v>
       </c>
-      <c r="AC41" s="7">
+      <c r="AC41" s="6">
         <v>28650199.480896659</v>
       </c>
-      <c r="AD41" s="7">
+      <c r="AD41" s="6">
         <v>30073882.957347352</v>
       </c>
-      <c r="AE41" s="7">
+      <c r="AE41" s="6">
         <v>30716716.32402293</v>
       </c>
-      <c r="AF41" s="7">
+      <c r="AF41" s="6">
         <v>30316331.983485036</v>
       </c>
-      <c r="AG41" s="7">
+      <c r="AG41" s="6">
         <v>29430133.851616666</v>
       </c>
-      <c r="AH41" s="7">
+      <c r="AH41" s="6">
         <v>28043171.980314881</v>
       </c>
-      <c r="AI41" s="7">
+      <c r="AI41" s="6">
         <v>25806179.783761524</v>
       </c>
+      <c r="AJ41" s="6">
+        <v>1.5340599999999998</v>
+      </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -5041,83 +5173,86 @@
       <c r="J42" s="1">
         <v>2</v>
       </c>
-      <c r="K42" s="7">
+      <c r="K42" s="6">
         <v>7.0903</v>
       </c>
-      <c r="L42" s="7">
+      <c r="L42" s="6">
         <v>2819389.5368008753</v>
       </c>
-      <c r="M42" s="7">
+      <c r="M42" s="6">
         <v>3098.927407558896</v>
       </c>
-      <c r="N42" s="7">
+      <c r="N42" s="6">
         <v>1091.2363029071307</v>
       </c>
-      <c r="O42" s="7">
+      <c r="O42" s="6">
         <v>2007.6911046517723</v>
       </c>
-      <c r="P42" s="7">
+      <c r="P42" s="6">
         <v>2.7379041903669723</v>
       </c>
-      <c r="Q42" s="7">
+      <c r="Q42" s="6">
         <v>29.741489978916533</v>
       </c>
-      <c r="R42" s="7">
+      <c r="R42" s="6">
         <v>3570255.9524934217</v>
       </c>
-      <c r="S42" s="7">
+      <c r="S42" s="6">
         <v>4139684.8328299583</v>
       </c>
-      <c r="T42" s="7">
+      <c r="T42" s="6">
         <v>4318807.4169193963</v>
       </c>
-      <c r="U42" s="7">
+      <c r="U42" s="6">
         <v>4539250.8112525865</v>
       </c>
-      <c r="V42" s="7">
+      <c r="V42" s="6">
         <v>4656418.9470688608</v>
       </c>
-      <c r="W42" s="7">
+      <c r="W42" s="6">
         <v>4835989.7395674232</v>
       </c>
-      <c r="X42" s="7">
+      <c r="X42" s="6">
         <v>5128336.2655317197</v>
       </c>
-      <c r="Y42" s="7">
+      <c r="Y42" s="6">
         <v>5491016.83402324</v>
       </c>
-      <c r="Z42" s="7">
+      <c r="Z42" s="6">
         <v>5417947.8042557938</v>
       </c>
-      <c r="AA42" s="7">
+      <c r="AA42" s="6">
         <v>3557015.7757092132</v>
       </c>
-      <c r="AB42" s="7">
+      <c r="AB42" s="6">
         <v>3909018.6416076068</v>
       </c>
-      <c r="AC42" s="7">
+      <c r="AC42" s="6">
         <v>4330270.0944822663</v>
       </c>
-      <c r="AD42" s="7">
+      <c r="AD42" s="6">
         <v>4481263.3953331932</v>
       </c>
-      <c r="AE42" s="7">
+      <c r="AE42" s="6">
         <v>4682924.183021755</v>
       </c>
-      <c r="AF42" s="7">
+      <c r="AF42" s="6">
         <v>4880997.3545399606</v>
       </c>
-      <c r="AG42" s="7">
+      <c r="AG42" s="6">
         <v>5142729.5760683306</v>
       </c>
-      <c r="AH42" s="7">
+      <c r="AH42" s="6">
         <v>5269165.5232235277</v>
       </c>
-      <c r="AI42" s="7">
+      <c r="AI42" s="6">
         <v>5158529.3078017952</v>
       </c>
+      <c r="AJ42" s="6">
+        <v>1.95892325</v>
+      </c>
     </row>
-    <row r="43" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>42</v>
       </c>
@@ -5148,83 +5283,86 @@
       <c r="J43" s="4">
         <v>50</v>
       </c>
-      <c r="K43" s="8">
+      <c r="K43" s="7">
         <v>22.9084</v>
       </c>
-      <c r="L43" s="8">
+      <c r="L43" s="7">
         <v>14070910.20791259</v>
       </c>
-      <c r="M43" s="8">
+      <c r="M43" s="7">
         <v>7970.5635310402276</v>
       </c>
-      <c r="N43" s="8">
+      <c r="N43" s="7">
         <v>2872.6164016237276</v>
       </c>
-      <c r="O43" s="8">
+      <c r="O43" s="7">
         <v>5097.947129416496</v>
       </c>
-      <c r="P43" s="8">
+      <c r="P43" s="7">
         <v>2.2410779712801707</v>
       </c>
-      <c r="Q43" s="8">
+      <c r="Q43" s="7">
         <v>12.465897216980823</v>
       </c>
-      <c r="R43" s="8">
+      <c r="R43" s="7">
         <v>21329601.011923406</v>
       </c>
-      <c r="S43" s="8">
+      <c r="S43" s="7">
         <v>24806292.677894004</v>
       </c>
-      <c r="T43" s="8">
+      <c r="T43" s="7">
         <v>26600717.766339172</v>
       </c>
-      <c r="U43" s="8">
+      <c r="U43" s="7">
         <v>27862209.267208509</v>
       </c>
-      <c r="V43" s="8">
+      <c r="V43" s="7">
         <v>28471820.051205147</v>
       </c>
-      <c r="W43" s="8">
+      <c r="W43" s="7">
         <v>28223401.637579914</v>
       </c>
-      <c r="X43" s="8">
+      <c r="X43" s="7">
         <v>27601460.318577018</v>
       </c>
-      <c r="Y43" s="8">
+      <c r="Y43" s="7">
         <v>26238073.194407832</v>
       </c>
-      <c r="Z43" s="8">
+      <c r="Z43" s="7">
         <v>24396053.559813514</v>
       </c>
-      <c r="AA43" s="8">
+      <c r="AA43" s="7">
         <v>19512253.207675792</v>
       </c>
-      <c r="AB43" s="8">
+      <c r="AB43" s="7">
         <v>23675314.959270295</v>
       </c>
-      <c r="AC43" s="8">
+      <c r="AC43" s="7">
         <v>26245596.218229767</v>
       </c>
-      <c r="AD43" s="8">
+      <c r="AD43" s="7">
         <v>27504483.341053911</v>
       </c>
-      <c r="AE43" s="8">
+      <c r="AE43" s="7">
         <v>28041642.409625221</v>
       </c>
-      <c r="AF43" s="8">
+      <c r="AF43" s="7">
         <v>28029885.398483142</v>
       </c>
-      <c r="AG43" s="8">
+      <c r="AG43" s="7">
         <v>27194551.019651987</v>
       </c>
-      <c r="AH43" s="8">
+      <c r="AH43" s="7">
         <v>25899957.672434583</v>
       </c>
-      <c r="AI43" s="8">
+      <c r="AI43" s="7">
         <v>24208235.159901697</v>
       </c>
+      <c r="AJ43" s="7">
+        <v>1.6421600000000005</v>
+      </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -5255,83 +5393,86 @@
       <c r="J44" s="1">
         <v>50</v>
       </c>
-      <c r="K44" s="7">
+      <c r="K44" s="6">
         <v>12.171200000000001</v>
       </c>
-      <c r="L44" s="7">
+      <c r="L44" s="6">
         <v>2485373.5454068929</v>
       </c>
-      <c r="M44" s="7">
+      <c r="M44" s="6">
         <v>8945.1902284243679</v>
       </c>
-      <c r="N44" s="7">
+      <c r="N44" s="6">
         <v>2351.5274025478657</v>
       </c>
-      <c r="O44" s="7">
+      <c r="O44" s="6">
         <v>6593.6628258765022</v>
       </c>
-      <c r="P44" s="7">
+      <c r="P44" s="6">
         <v>4.0880093770462791</v>
       </c>
-      <c r="Q44" s="7">
+      <c r="Q44" s="6">
         <v>148.20312585529925</v>
       </c>
-      <c r="R44" s="7">
+      <c r="R44" s="6">
         <v>7368595.0827067113</v>
       </c>
-      <c r="S44" s="7">
+      <c r="S44" s="6">
         <v>8104622.0805955464</v>
       </c>
-      <c r="T44" s="7">
+      <c r="T44" s="6">
         <v>9089755.8051330578</v>
       </c>
-      <c r="U44" s="7">
+      <c r="U44" s="6">
         <v>10286241.580829632</v>
       </c>
-      <c r="V44" s="7">
+      <c r="V44" s="6">
         <v>11097463.275339933</v>
       </c>
-      <c r="W44" s="7">
+      <c r="W44" s="6">
         <v>11406329.323549455</v>
       </c>
-      <c r="X44" s="7">
+      <c r="X44" s="6">
         <v>11240890.845652014</v>
       </c>
-      <c r="Y44" s="7">
+      <c r="Y44" s="6">
         <v>10624966.16747372</v>
       </c>
-      <c r="Z44" s="7">
+      <c r="Z44" s="6">
         <v>9759611.9420525935</v>
       </c>
-      <c r="AA44" s="7">
+      <c r="AA44" s="6">
         <v>7391345.617284487</v>
       </c>
-      <c r="AB44" s="7">
+      <c r="AB44" s="6">
         <v>8139178.753102825</v>
       </c>
-      <c r="AC44" s="7">
+      <c r="AC44" s="6">
         <v>9066034.328468455</v>
       </c>
-      <c r="AD44" s="7">
+      <c r="AD44" s="6">
         <v>9993771.8838001117</v>
       </c>
-      <c r="AE44" s="7">
+      <c r="AE44" s="6">
         <v>10817367.797456006</v>
       </c>
-      <c r="AF44" s="7">
+      <c r="AF44" s="6">
         <v>11168716.608758701</v>
       </c>
-      <c r="AG44" s="7">
+      <c r="AG44" s="6">
         <v>11001791.810849883</v>
       </c>
-      <c r="AH44" s="7">
+      <c r="AH44" s="6">
         <v>10448010.092478953</v>
       </c>
-      <c r="AI44" s="7">
+      <c r="AI44" s="6">
         <v>9410458.6199755426</v>
       </c>
+      <c r="AJ44" s="6">
+        <v>2.3968100000000003</v>
+      </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -5362,83 +5503,86 @@
       <c r="J45" s="1">
         <v>2</v>
       </c>
-      <c r="K45" s="7">
+      <c r="K45" s="6">
         <v>4.1768099999999997</v>
       </c>
-      <c r="L45" s="7">
+      <c r="L45" s="6">
         <v>688115.20423775527</v>
       </c>
-      <c r="M45" s="7">
+      <c r="M45" s="6">
         <v>3110.3176470119352</v>
       </c>
-      <c r="N45" s="7">
+      <c r="N45" s="6">
         <v>734.60217659986904</v>
       </c>
-      <c r="O45" s="7">
+      <c r="O45" s="6">
         <v>2237.2946566467467</v>
       </c>
-      <c r="P45" s="7">
+      <c r="P45" s="6">
         <v>3.7774116000000002</v>
       </c>
-      <c r="Q45" s="7">
+      <c r="Q45" s="6">
         <v>172.79294750851892</v>
       </c>
-      <c r="R45" s="7">
+      <c r="R45" s="6">
         <v>3289154.9958040938</v>
       </c>
-      <c r="S45" s="7">
+      <c r="S45" s="6">
         <v>3302493.2577868439</v>
       </c>
-      <c r="T45" s="7">
+      <c r="T45" s="6">
         <v>3375564.5642253975</v>
       </c>
-      <c r="U45" s="7">
+      <c r="U45" s="6">
         <v>3521495.3771428051</v>
       </c>
-      <c r="V45" s="7">
+      <c r="V45" s="6">
         <v>3617634.9236298907</v>
       </c>
-      <c r="W45" s="7">
+      <c r="W45" s="6">
         <v>3503560.9846564014</v>
       </c>
-      <c r="X45" s="7">
+      <c r="X45" s="6">
         <v>3204250.3611923382</v>
       </c>
-      <c r="Y45" s="7">
+      <c r="Y45" s="6">
         <v>3097233.7390528522</v>
       </c>
-      <c r="Z45" s="7">
+      <c r="Z45" s="6">
         <v>2928586.8324428592</v>
       </c>
-      <c r="AA45" s="7">
+      <c r="AA45" s="6">
         <v>3236211.350756248</v>
       </c>
-      <c r="AB45" s="7">
+      <c r="AB45" s="6">
         <v>3331799.6203975626</v>
       </c>
-      <c r="AC45" s="7">
+      <c r="AC45" s="6">
         <v>3408480.1023299326</v>
       </c>
-      <c r="AD45" s="7">
+      <c r="AD45" s="6">
         <v>3492410.0980435261</v>
       </c>
-      <c r="AE45" s="7">
+      <c r="AE45" s="6">
         <v>3512505.2883833521</v>
       </c>
-      <c r="AF45" s="7">
+      <c r="AF45" s="6">
         <v>3398417.7472152151</v>
       </c>
-      <c r="AG45" s="7">
+      <c r="AG45" s="6">
         <v>3287891.1533274371</v>
       </c>
-      <c r="AH45" s="7">
+      <c r="AH45" s="6">
         <v>3060223.2276366362</v>
       </c>
-      <c r="AI45" s="7">
+      <c r="AI45" s="6">
         <v>2834733.4732353063</v>
       </c>
+      <c r="AJ45" s="6">
+        <v>1.9465766</v>
+      </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>43</v>
       </c>
@@ -5469,83 +5613,86 @@
       <c r="J46" s="1">
         <v>2</v>
       </c>
-      <c r="K46" s="7">
+      <c r="K46" s="6">
         <v>4.4995399999999997</v>
       </c>
-      <c r="L46" s="7">
+      <c r="L46" s="6">
         <v>912048.01434086659</v>
       </c>
-      <c r="M46" s="7">
+      <c r="M46" s="6">
         <v>3659.9706429863072</v>
       </c>
-      <c r="N46" s="7">
+      <c r="N46" s="6">
         <v>953.53942130542521</v>
       </c>
-      <c r="O46" s="7">
+      <c r="O46" s="6">
         <v>2706.4312216808748</v>
       </c>
-      <c r="P46" s="7">
+      <c r="P46" s="6">
         <v>4.3668016979695423</v>
       </c>
-      <c r="Q46" s="7">
+      <c r="Q46" s="6">
         <v>177.89614499610326</v>
       </c>
-      <c r="R46" s="7">
+      <c r="R46" s="6">
         <v>2911948.4198610731</v>
       </c>
-      <c r="S46" s="7">
+      <c r="S46" s="6">
         <v>3084781.1672399244</v>
       </c>
-      <c r="T46" s="7">
+      <c r="T46" s="6">
         <v>3257852.4132065098</v>
       </c>
-      <c r="U46" s="7">
+      <c r="U46" s="6">
         <v>3226025.6896725707</v>
       </c>
-      <c r="V46" s="7">
+      <c r="V46" s="6">
         <v>3182281.2275018408</v>
       </c>
-      <c r="W46" s="7">
+      <c r="W46" s="6">
         <v>3149070.8329087184</v>
       </c>
-      <c r="X46" s="7">
+      <c r="X46" s="6">
         <v>3066204.1829323946</v>
       </c>
-      <c r="Y46" s="7">
+      <c r="Y46" s="6">
         <v>2905750.1969258063</v>
       </c>
-      <c r="Z46" s="7">
+      <c r="Z46" s="6">
         <v>2646148.4262643871</v>
       </c>
-      <c r="AA46" s="7">
+      <c r="AA46" s="6">
         <v>2961635.3500916837</v>
       </c>
-      <c r="AB46" s="7">
+      <c r="AB46" s="6">
         <v>3075204.0279590543</v>
       </c>
-      <c r="AC46" s="7">
+      <c r="AC46" s="6">
         <v>3153822.8052832074</v>
       </c>
-      <c r="AD46" s="7">
+      <c r="AD46" s="6">
         <v>3219623.4286151663</v>
       </c>
-      <c r="AE46" s="7">
+      <c r="AE46" s="6">
         <v>3187083.7938148533</v>
       </c>
-      <c r="AF46" s="7">
+      <c r="AF46" s="6">
         <v>3123164.5335170226</v>
       </c>
-      <c r="AG46" s="7">
+      <c r="AG46" s="6">
         <v>3022521.4412680664</v>
       </c>
-      <c r="AH46" s="7">
+      <c r="AH46" s="6">
         <v>2840731.9814988454</v>
       </c>
-      <c r="AI46" s="7">
+      <c r="AI46" s="6">
         <v>2638966.0101114721</v>
       </c>
+      <c r="AJ46" s="6">
+        <v>2.4656009999999999</v>
+      </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>43</v>
       </c>
@@ -5576,83 +5723,86 @@
       <c r="J47" s="1">
         <v>50</v>
       </c>
-      <c r="K47" s="7">
+      <c r="K47" s="6">
         <v>10.9636</v>
       </c>
-      <c r="L47" s="7">
+      <c r="L47" s="6">
         <v>1785082.4133718868</v>
       </c>
-      <c r="M47" s="7">
+      <c r="M47" s="6">
         <v>8736.0134118096594</v>
       </c>
-      <c r="N47" s="7">
+      <c r="N47" s="6">
         <v>2012.1472284042168</v>
       </c>
-      <c r="O47" s="7">
+      <c r="O47" s="6">
         <v>6723.866183405441</v>
       </c>
-      <c r="P47" s="7">
+      <c r="P47" s="6">
         <v>4.2474981800331353</v>
       </c>
-      <c r="Q47" s="7">
+      <c r="Q47" s="6">
         <v>210.03768315917927</v>
       </c>
-      <c r="R47" s="7">
+      <c r="R47" s="6">
         <v>6674574.4053165913</v>
       </c>
-      <c r="S47" s="7">
+      <c r="S47" s="6">
         <v>7160457.3228066321</v>
       </c>
-      <c r="T47" s="7">
+      <c r="T47" s="6">
         <v>7728808.7218564879</v>
       </c>
-      <c r="U47" s="7">
+      <c r="U47" s="6">
         <v>8486416.826967882</v>
       </c>
-      <c r="V47" s="7">
+      <c r="V47" s="6">
         <v>9367437.7245363146</v>
       </c>
-      <c r="W47" s="7">
+      <c r="W47" s="6">
         <v>9949648.82957552</v>
       </c>
-      <c r="X47" s="7">
+      <c r="X47" s="6">
         <v>10163319.462646458</v>
       </c>
-      <c r="Y47" s="7">
+      <c r="Y47" s="6">
         <v>9857397.5546569899</v>
       </c>
-      <c r="Z47" s="7">
+      <c r="Z47" s="6">
         <v>9052160.8614019658</v>
       </c>
-      <c r="AA47" s="7">
+      <c r="AA47" s="6">
         <v>6712909.1773715196</v>
       </c>
-      <c r="AB47" s="7">
+      <c r="AB47" s="6">
         <v>7163110.0031171255</v>
       </c>
-      <c r="AC47" s="7">
+      <c r="AC47" s="6">
         <v>7767254.3322561709</v>
       </c>
-      <c r="AD47" s="7">
+      <c r="AD47" s="6">
         <v>8469594.1432359871</v>
       </c>
-      <c r="AE47" s="7">
+      <c r="AE47" s="6">
         <v>9159965.9952135514</v>
       </c>
-      <c r="AF47" s="7">
+      <c r="AF47" s="6">
         <v>9749162.4342539255</v>
       </c>
-      <c r="AG47" s="7">
+      <c r="AG47" s="6">
         <v>9903308.362061359</v>
       </c>
-      <c r="AH47" s="7">
+      <c r="AH47" s="6">
         <v>9575613.1109097414</v>
       </c>
-      <c r="AI47" s="7">
+      <c r="AI47" s="6">
         <v>8833693.1389480382</v>
       </c>
+      <c r="AJ47" s="6">
+        <v>2.20296</v>
+      </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>43</v>
       </c>
@@ -5683,83 +5833,86 @@
       <c r="J48" s="1">
         <v>50</v>
       </c>
-      <c r="K48" s="7">
+      <c r="K48" s="6">
         <v>11.0039</v>
       </c>
-      <c r="L48" s="7">
+      <c r="L48" s="6">
         <v>2019588.0576748007</v>
       </c>
-      <c r="M48" s="7">
+      <c r="M48" s="6">
         <v>8827.3102934627768</v>
       </c>
-      <c r="N48" s="7">
+      <c r="N48" s="6">
         <v>2201.0851653530945</v>
       </c>
-      <c r="O48" s="7">
+      <c r="O48" s="6">
         <v>6626.2251281096833</v>
       </c>
-      <c r="P48" s="7">
+      <c r="P48" s="6">
         <v>4.4880375757575761</v>
       </c>
-      <c r="Q48" s="7">
+      <c r="Q48" s="6">
         <v>198.52271048898456</v>
       </c>
-      <c r="R48" s="7">
+      <c r="R48" s="6">
         <v>5857856.9245789368</v>
       </c>
-      <c r="S48" s="7">
+      <c r="S48" s="6">
         <v>6404749.804121892</v>
       </c>
-      <c r="T48" s="7">
+      <c r="T48" s="6">
         <v>7056616.3187402152</v>
       </c>
-      <c r="U48" s="7">
+      <c r="U48" s="6">
         <v>7788487.7426890507</v>
       </c>
-      <c r="V48" s="7">
+      <c r="V48" s="6">
         <v>8640697.414637696</v>
       </c>
-      <c r="W48" s="7">
+      <c r="W48" s="6">
         <v>9168888.3523143362</v>
       </c>
-      <c r="X48" s="7">
+      <c r="X48" s="6">
         <v>9168745.8980706763</v>
       </c>
-      <c r="Y48" s="7">
+      <c r="Y48" s="6">
         <v>8892208.0190559421</v>
       </c>
-      <c r="Z48" s="7">
+      <c r="Z48" s="6">
         <v>8195927.2120691827</v>
       </c>
-      <c r="AA48" s="7">
+      <c r="AA48" s="6">
         <v>5879046.7046695622</v>
       </c>
-      <c r="AB48" s="7">
+      <c r="AB48" s="6">
         <v>6401600.4351107627</v>
       </c>
-      <c r="AC48" s="7">
+      <c r="AC48" s="6">
         <v>7029166.5562381372</v>
       </c>
-      <c r="AD48" s="7">
+      <c r="AD48" s="6">
         <v>7768728.7668560501</v>
       </c>
-      <c r="AE48" s="7">
+      <c r="AE48" s="6">
         <v>8422502.8855881318</v>
       </c>
-      <c r="AF48" s="7">
+      <c r="AF48" s="6">
         <v>8896893.3599846736</v>
       </c>
-      <c r="AG48" s="7">
+      <c r="AG48" s="6">
         <v>9028428.9343053252</v>
       </c>
-      <c r="AH48" s="7">
+      <c r="AH48" s="6">
         <v>8655086.5115525238</v>
       </c>
-      <c r="AI48" s="7">
+      <c r="AI48" s="6">
         <v>7971190.5652309479</v>
       </c>
+      <c r="AJ48" s="6">
+        <v>2.62575</v>
+      </c>
     </row>
-    <row r="49" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>43</v>
       </c>
@@ -5790,83 +5943,86 @@
       <c r="J49" s="4">
         <v>2</v>
       </c>
-      <c r="K49" s="8">
+      <c r="K49" s="7">
         <v>4.6298199999999996</v>
       </c>
-      <c r="L49" s="8">
+      <c r="L49" s="7">
         <v>776263.12351100077</v>
       </c>
-      <c r="M49" s="8">
+      <c r="M49" s="7">
         <v>3842.9439826472712</v>
       </c>
-      <c r="N49" s="8">
+      <c r="N49" s="7">
         <v>960.94955522083546</v>
       </c>
-      <c r="O49" s="8">
+      <c r="O49" s="7">
         <v>2881.9944274264294</v>
       </c>
-      <c r="P49" s="8">
+      <c r="P49" s="7">
         <v>4.3120537641434264</v>
       </c>
-      <c r="Q49" s="8">
+      <c r="Q49" s="7">
         <v>215.69906499829435</v>
       </c>
-      <c r="R49" s="8">
+      <c r="R49" s="7">
         <v>3365634.740204799</v>
       </c>
-      <c r="S49" s="8">
+      <c r="S49" s="7">
         <v>3437040.1495567886</v>
       </c>
-      <c r="T49" s="8">
+      <c r="T49" s="7">
         <v>3642249.6737439493</v>
       </c>
-      <c r="U49" s="8">
+      <c r="U49" s="7">
         <v>3730747.1594998809</v>
       </c>
-      <c r="V49" s="8">
+      <c r="V49" s="7">
         <v>3690649.7113418775</v>
       </c>
-      <c r="W49" s="8">
+      <c r="W49" s="7">
         <v>3537069.6860901746</v>
       </c>
-      <c r="X49" s="8">
+      <c r="X49" s="7">
         <v>3433019.193265717</v>
       </c>
-      <c r="Y49" s="8">
+      <c r="Y49" s="7">
         <v>3228361.4068440427</v>
       </c>
-      <c r="Z49" s="8">
+      <c r="Z49" s="7">
         <v>2915944.2667282093</v>
       </c>
-      <c r="AA49" s="8">
+      <c r="AA49" s="7">
         <v>3365320.2884954405</v>
       </c>
-      <c r="AB49" s="8">
+      <c r="AB49" s="7">
         <v>3498482.9401730723</v>
       </c>
-      <c r="AC49" s="8">
+      <c r="AC49" s="7">
         <v>3577876.1902837749</v>
       </c>
-      <c r="AD49" s="8">
+      <c r="AD49" s="7">
         <v>3666289.9628428002</v>
       </c>
-      <c r="AE49" s="8">
+      <c r="AE49" s="7">
         <v>3631327.8016467993</v>
       </c>
-      <c r="AF49" s="8">
+      <c r="AF49" s="7">
         <v>3557175.7936313497</v>
       </c>
-      <c r="AG49" s="8">
+      <c r="AG49" s="7">
         <v>3375672.3292377852</v>
       </c>
-      <c r="AH49" s="8">
+      <c r="AH49" s="7">
         <v>3153425.8142290981</v>
       </c>
-      <c r="AI49" s="8">
+      <c r="AI49" s="7">
         <v>2886978.4577496885</v>
       </c>
+      <c r="AJ49" s="7">
+        <v>2.2312623</v>
+      </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>43</v>
       </c>
@@ -5897,83 +6053,86 @@
       <c r="J50" s="1">
         <v>50</v>
       </c>
-      <c r="K50" s="7">
+      <c r="K50" s="6">
         <v>12.588699999999999</v>
       </c>
-      <c r="L50" s="7">
+      <c r="L50" s="6">
         <v>2748323.6973567917</v>
       </c>
-      <c r="M50" s="7">
+      <c r="M50" s="6">
         <v>9736.4194256444061</v>
       </c>
-      <c r="N50" s="7">
+      <c r="N50" s="6">
         <v>2682.3734409076792</v>
       </c>
-      <c r="O50" s="7">
+      <c r="O50" s="6">
         <v>7054.0459847367265</v>
       </c>
-      <c r="P50" s="7">
+      <c r="P50" s="6">
         <v>4.655502860468574</v>
       </c>
-      <c r="Q50" s="7">
+      <c r="Q50" s="6">
         <v>167.43303755329131</v>
       </c>
-      <c r="R50" s="7">
+      <c r="R50" s="6">
         <v>7048940.4029311212</v>
       </c>
-      <c r="S50" s="7">
+      <c r="S50" s="6">
         <v>7697968.3631641818</v>
       </c>
-      <c r="T50" s="7">
+      <c r="T50" s="6">
         <v>8378047.0591737097</v>
       </c>
-      <c r="U50" s="7">
+      <c r="U50" s="6">
         <v>9315455.3486778531</v>
       </c>
-      <c r="V50" s="7">
+      <c r="V50" s="6">
         <v>10328685.019173292</v>
       </c>
-      <c r="W50" s="7">
+      <c r="W50" s="6">
         <v>10674170.660385175</v>
       </c>
-      <c r="X50" s="7">
+      <c r="X50" s="6">
         <v>10353877.251995847</v>
       </c>
-      <c r="Y50" s="7">
+      <c r="Y50" s="6">
         <v>9637642.3155780807</v>
       </c>
-      <c r="Z50" s="7">
+      <c r="Z50" s="6">
         <v>8579496.3841408193</v>
       </c>
-      <c r="AA50" s="7">
+      <c r="AA50" s="6">
         <v>6938789.211552226</v>
       </c>
-      <c r="AB50" s="7">
+      <c r="AB50" s="6">
         <v>7656239.3737772945</v>
       </c>
-      <c r="AC50" s="7">
+      <c r="AC50" s="6">
         <v>8429823.6236457862</v>
       </c>
-      <c r="AD50" s="7">
+      <c r="AD50" s="6">
         <v>9251664.9928588532</v>
       </c>
-      <c r="AE50" s="7">
+      <c r="AE50" s="6">
         <v>9948636.3702755533</v>
       </c>
-      <c r="AF50" s="7">
+      <c r="AF50" s="6">
         <v>10341265.792983728</v>
       </c>
-      <c r="AG50" s="7">
+      <c r="AG50" s="6">
         <v>10129459.045528805</v>
       </c>
-      <c r="AH50" s="7">
+      <c r="AH50" s="6">
         <v>9383541.9035719335</v>
       </c>
-      <c r="AI50" s="7">
+      <c r="AI50" s="6">
         <v>8406125.0635228977</v>
       </c>
+      <c r="AJ50" s="6">
+        <v>3.0268383999999999</v>
+      </c>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>43</v>
       </c>
@@ -6004,83 +6163,86 @@
       <c r="J51" s="1">
         <v>50</v>
       </c>
-      <c r="K51" s="7">
+      <c r="K51" s="6">
         <v>13.505599999999999</v>
       </c>
-      <c r="L51" s="7">
+      <c r="L51" s="6">
         <v>3151138.0544159459</v>
       </c>
-      <c r="M51" s="7">
+      <c r="M51" s="6">
         <v>9823.6477044276544</v>
       </c>
-      <c r="N51" s="7">
+      <c r="N51" s="6">
         <v>2845.871450251906</v>
       </c>
-      <c r="O51" s="7">
+      <c r="O51" s="6">
         <v>6977.7762541757484</v>
       </c>
-      <c r="P51" s="7">
+      <c r="P51" s="6">
         <v>4.5472587747709348</v>
       </c>
-      <c r="Q51" s="7">
+      <c r="Q51" s="6">
         <v>145.25736551694516</v>
       </c>
-      <c r="R51" s="7">
+      <c r="R51" s="6">
         <v>5000090.4604094662</v>
       </c>
-      <c r="S51" s="7">
+      <c r="S51" s="6">
         <v>5965137.6266403161</v>
       </c>
-      <c r="T51" s="7">
+      <c r="T51" s="6">
         <v>7908412.6892561046</v>
       </c>
-      <c r="U51" s="7">
+      <c r="U51" s="6">
         <v>9828248.2067883685</v>
       </c>
-      <c r="V51" s="7">
+      <c r="V51" s="6">
         <v>10865617.472910354</v>
       </c>
-      <c r="W51" s="7">
+      <c r="W51" s="6">
         <v>11193350.826557351</v>
       </c>
-      <c r="X51" s="7">
+      <c r="X51" s="6">
         <v>10698618.027187722</v>
       </c>
-      <c r="Y51" s="7">
+      <c r="Y51" s="6">
         <v>9706673.6066958997</v>
       </c>
-      <c r="Z51" s="7">
+      <c r="Z51" s="6">
         <v>8697874.6534075122</v>
       </c>
-      <c r="AA51" s="7">
+      <c r="AA51" s="6">
         <v>5363256.8320690813</v>
       </c>
-      <c r="AB51" s="7">
+      <c r="AB51" s="6">
         <v>6126624.9674432753</v>
       </c>
-      <c r="AC51" s="7">
+      <c r="AC51" s="6">
         <v>7424228.5727209179</v>
       </c>
-      <c r="AD51" s="7">
+      <c r="AD51" s="6">
         <v>7424228.5727209179</v>
       </c>
-      <c r="AE51" s="7">
+      <c r="AE51" s="6">
         <v>10466475.934067557</v>
       </c>
-      <c r="AF51" s="7">
+      <c r="AF51" s="6">
         <v>10781471.104939092</v>
       </c>
-      <c r="AG51" s="7">
+      <c r="AG51" s="6">
         <v>10397136.461310798</v>
       </c>
-      <c r="AH51" s="7">
+      <c r="AH51" s="6">
         <v>9595058.2507382575</v>
       </c>
-      <c r="AI51" s="7">
+      <c r="AI51" s="6">
         <v>8580346.0451476425</v>
       </c>
+      <c r="AJ51" s="6">
+        <v>2.9406199999999996</v>
+      </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>43</v>
       </c>
@@ -6111,83 +6273,86 @@
       <c r="J52" s="1">
         <v>2</v>
       </c>
-      <c r="K52" s="7">
+      <c r="K52" s="6">
         <v>6.0233100000000004</v>
       </c>
-      <c r="L52" s="7">
+      <c r="L52" s="6">
         <v>1100981.0809674349</v>
       </c>
-      <c r="M52" s="7">
+      <c r="M52" s="6">
         <v>4106.9938537829103</v>
       </c>
-      <c r="N52" s="7">
+      <c r="N52" s="6">
         <v>1064.25601816125</v>
       </c>
-      <c r="O52" s="7">
+      <c r="O52" s="6">
         <v>3042.7378356216618</v>
       </c>
-      <c r="P52" s="7">
+      <c r="P52" s="6">
         <v>3.6053393764243618</v>
       </c>
-      <c r="Q52" s="7">
+      <c r="Q52" s="6">
         <v>138.44570138693834</v>
       </c>
-      <c r="R52" s="7">
+      <c r="R52" s="6">
         <v>4046592.4679476391</v>
       </c>
-      <c r="S52" s="7">
+      <c r="S52" s="6">
         <v>4142012.3369523399</v>
       </c>
-      <c r="T52" s="7">
+      <c r="T52" s="6">
         <v>4190112.3190193595</v>
       </c>
-      <c r="U52" s="7">
+      <c r="U52" s="6">
         <v>4311968.0786288753</v>
       </c>
-      <c r="V52" s="7">
+      <c r="V52" s="6">
         <v>4332956.8835555259</v>
       </c>
-      <c r="W52" s="7">
+      <c r="W52" s="6">
         <v>4162431.2227751757</v>
       </c>
-      <c r="X52" s="7">
+      <c r="X52" s="6">
         <v>4121570.1873064684</v>
       </c>
-      <c r="Y52" s="7">
+      <c r="Y52" s="6">
         <v>4138516.9795440705</v>
       </c>
-      <c r="Z52" s="7">
+      <c r="Z52" s="6">
         <v>4109864.0699648233</v>
       </c>
-      <c r="AA52" s="7">
+      <c r="AA52" s="6">
         <v>4093718.6357319625</v>
       </c>
-      <c r="AB52" s="7">
+      <c r="AB52" s="6">
         <v>4117102.0179884201</v>
       </c>
-      <c r="AC52" s="7">
+      <c r="AC52" s="6">
         <v>4225281.8436408872</v>
       </c>
-      <c r="AD52" s="7">
+      <c r="AD52" s="6">
         <v>4260337.5812273826</v>
       </c>
-      <c r="AE52" s="7">
+      <c r="AE52" s="6">
         <v>4235880.3081466835</v>
       </c>
-      <c r="AF52" s="7">
+      <c r="AF52" s="6">
         <v>4224620.9077017009</v>
       </c>
-      <c r="AG52" s="7">
+      <c r="AG52" s="6">
         <v>4150439.6538281022</v>
       </c>
-      <c r="AH52" s="7">
+      <c r="AH52" s="6">
         <v>4115708.8048624774</v>
       </c>
-      <c r="AI52" s="7">
+      <c r="AI52" s="6">
         <v>4104381.8286810089</v>
       </c>
+      <c r="AJ52" s="6">
+        <v>2.0150014000000001</v>
+      </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>43</v>
       </c>
@@ -6218,83 +6383,86 @@
       <c r="J53" s="1">
         <v>2</v>
       </c>
-      <c r="K53" s="7">
+      <c r="K53" s="6">
         <v>5.1953899999999997</v>
       </c>
-      <c r="L53" s="7">
+      <c r="L53" s="6">
         <v>1009753.6702942313</v>
       </c>
-      <c r="M53" s="7">
+      <c r="M53" s="6">
         <v>4049.6978244505726</v>
       </c>
-      <c r="N53" s="7">
+      <c r="N53" s="6">
         <v>1255.511061573507</v>
       </c>
-      <c r="O53" s="7">
+      <c r="O53" s="6">
         <v>2794.1867628770683</v>
       </c>
-      <c r="P53" s="7">
+      <c r="P53" s="6">
         <v>4.4072017155612242</v>
       </c>
-      <c r="Q53" s="7">
+      <c r="Q53" s="6">
         <v>181.67350795735874</v>
       </c>
-      <c r="R53" s="7">
+      <c r="R53" s="6">
         <v>3555630.5703979447</v>
       </c>
-      <c r="S53" s="7">
+      <c r="S53" s="6">
         <v>3574862.9929103451</v>
       </c>
-      <c r="T53" s="7">
+      <c r="T53" s="6">
         <v>3553273.6152057135</v>
       </c>
-      <c r="U53" s="7">
+      <c r="U53" s="6">
         <v>3606243.8497469896</v>
       </c>
-      <c r="V53" s="7">
+      <c r="V53" s="6">
         <v>3571698.5641839816</v>
       </c>
-      <c r="W53" s="7">
+      <c r="W53" s="6">
         <v>3520836.8280765861</v>
       </c>
-      <c r="X53" s="7">
+      <c r="X53" s="6">
         <v>3490670.0080380449</v>
       </c>
-      <c r="Y53" s="7">
+      <c r="Y53" s="6">
         <v>3123437.5211406988</v>
       </c>
-      <c r="Z53" s="7">
+      <c r="Z53" s="6">
         <v>2902474.1826540013</v>
       </c>
-      <c r="AA53" s="7">
+      <c r="AA53" s="6">
         <v>3492550.8605607529</v>
       </c>
-      <c r="AB53" s="7">
+      <c r="AB53" s="6">
         <v>3554451.7020779122</v>
       </c>
-      <c r="AC53" s="7">
+      <c r="AC53" s="6">
         <v>3590484.8554238994</v>
       </c>
-      <c r="AD53" s="7">
+      <c r="AD53" s="6">
         <v>3562462.2665320123</v>
       </c>
-      <c r="AE53" s="7">
+      <c r="AE53" s="6">
         <v>3563028.6034845947</v>
       </c>
-      <c r="AF53" s="7">
+      <c r="AF53" s="6">
         <v>3530719.4543166971</v>
       </c>
-      <c r="AG53" s="7">
+      <c r="AG53" s="6">
         <v>3310252.7910888884</v>
       </c>
-      <c r="AH53" s="7">
+      <c r="AH53" s="6">
         <v>3169513.8655705289</v>
       </c>
-      <c r="AI53" s="7">
+      <c r="AI53" s="6">
         <v>2887908.0695628477</v>
       </c>
+      <c r="AJ53" s="6">
+        <v>2.5249200000000003</v>
+      </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>43</v>
       </c>
@@ -6325,83 +6493,86 @@
       <c r="J54" s="1">
         <v>50</v>
       </c>
-      <c r="K54" s="7">
+      <c r="K54" s="6">
         <v>13.949</v>
       </c>
-      <c r="L54" s="7">
+      <c r="L54" s="6">
         <v>3693578.7332728188</v>
       </c>
-      <c r="M54" s="7">
+      <c r="M54" s="6">
         <v>8355.4626171843229</v>
       </c>
-      <c r="N54" s="7">
+      <c r="N54" s="6">
         <v>2492.6829947260808</v>
       </c>
-      <c r="O54" s="7">
+      <c r="O54" s="6">
         <v>5862.7796224582398</v>
       </c>
-      <c r="P54" s="7">
+      <c r="P54" s="6">
         <v>3.7414758267716537</v>
       </c>
-      <c r="Q54" s="7">
+      <c r="Q54" s="6">
         <v>86.72598233768646</v>
       </c>
-      <c r="R54" s="7">
+      <c r="R54" s="6">
         <v>8983902.8796135411</v>
       </c>
-      <c r="S54" s="7">
+      <c r="S54" s="6">
         <v>10580413.634655213</v>
       </c>
-      <c r="T54" s="7">
+      <c r="T54" s="6">
         <v>12501799.6780168</v>
       </c>
-      <c r="U54" s="7">
+      <c r="U54" s="6">
         <v>13907356.111677531</v>
       </c>
-      <c r="V54" s="7">
+      <c r="V54" s="6">
         <v>14584496.123570306</v>
       </c>
-      <c r="W54" s="7">
+      <c r="W54" s="6">
         <v>14521485.420606609</v>
       </c>
-      <c r="X54" s="7">
+      <c r="X54" s="6">
         <v>13712981.339631088</v>
       </c>
-      <c r="Y54" s="7">
+      <c r="Y54" s="6">
         <v>12681465.715754366</v>
       </c>
-      <c r="Z54" s="7">
+      <c r="Z54" s="6">
         <v>11512794.145534391</v>
       </c>
-      <c r="AA54" s="7">
+      <c r="AA54" s="6">
         <v>8952219.9842314962</v>
       </c>
-      <c r="AB54" s="7">
+      <c r="AB54" s="6">
         <v>10454855.160209758</v>
       </c>
-      <c r="AC54" s="7">
+      <c r="AC54" s="6">
         <v>12017883.355672665</v>
       </c>
-      <c r="AD54" s="7">
+      <c r="AD54" s="6">
         <v>13463077.437927475</v>
       </c>
-      <c r="AE54" s="7">
+      <c r="AE54" s="6">
         <v>14207787.45314447</v>
       </c>
-      <c r="AF54" s="7">
+      <c r="AF54" s="6">
         <v>14135318.135725813</v>
       </c>
-      <c r="AG54" s="7">
+      <c r="AG54" s="6">
         <v>13539245.692876277</v>
       </c>
-      <c r="AH54" s="7">
+      <c r="AH54" s="6">
         <v>12516937.794643303</v>
       </c>
-      <c r="AI54" s="7">
+      <c r="AI54" s="6">
         <v>11287990.943224482</v>
       </c>
+      <c r="AJ54" s="6">
+        <v>2.4934399999999997</v>
+      </c>
     </row>
-    <row r="55" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>43</v>
       </c>
@@ -6432,83 +6603,86 @@
       <c r="J55" s="4">
         <v>2</v>
       </c>
-      <c r="K55" s="8">
+      <c r="K55" s="7">
         <v>4.9371600000000004</v>
       </c>
-      <c r="L55" s="8">
+      <c r="L55" s="7">
         <v>951238.85925376404</v>
       </c>
-      <c r="M55" s="8">
+      <c r="M55" s="7">
         <v>3719.5461367934699</v>
       </c>
-      <c r="N55" s="8">
+      <c r="N55" s="7">
         <v>1141.2520202911985</v>
       </c>
-      <c r="O55" s="8">
+      <c r="O55" s="7">
         <v>2578.2941165022589</v>
       </c>
-      <c r="P55" s="8">
+      <c r="P55" s="7">
         <v>4.4694785000000001</v>
       </c>
-      <c r="Q55" s="8">
+      <c r="Q55" s="7">
         <v>180.45899695032924</v>
       </c>
-      <c r="R55" s="8">
+      <c r="R55" s="7">
         <v>3018522.7015658095</v>
       </c>
-      <c r="S55" s="8">
+      <c r="S55" s="7">
         <v>3194199.2209821269</v>
       </c>
-      <c r="T55" s="8">
+      <c r="T55" s="7">
         <v>3301687.6539268354</v>
       </c>
-      <c r="U55" s="8">
+      <c r="U55" s="7">
         <v>3282008.1059928373</v>
       </c>
-      <c r="V55" s="8">
+      <c r="V55" s="7">
         <v>3086866.6809711768</v>
       </c>
-      <c r="W55" s="8">
+      <c r="W55" s="7">
         <v>3094502.8599404916</v>
       </c>
-      <c r="X55" s="8">
+      <c r="X55" s="7">
         <v>3085642.9998180601</v>
       </c>
-      <c r="Y55" s="8">
+      <c r="Y55" s="7">
         <v>2841343.6971145184</v>
       </c>
-      <c r="Z55" s="8">
+      <c r="Z55" s="7">
         <v>2613329.2918845643</v>
       </c>
-      <c r="AA55" s="8">
+      <c r="AA55" s="7">
         <v>2972979.813298027</v>
       </c>
-      <c r="AB55" s="8">
+      <c r="AB55" s="7">
         <v>3153761.8453463227</v>
       </c>
-      <c r="AC55" s="8">
+      <c r="AC55" s="7">
         <v>3237508.3767789551</v>
       </c>
-      <c r="AD55" s="8">
+      <c r="AD55" s="7">
         <v>3190665.391763737</v>
       </c>
-      <c r="AE55" s="8">
+      <c r="AE55" s="7">
         <v>3185498.6291413526</v>
       </c>
-      <c r="AF55" s="8">
+      <c r="AF55" s="7">
         <v>3086254.719099097</v>
       </c>
-      <c r="AG55" s="8">
+      <c r="AG55" s="7">
         <v>2962524.7594530373</v>
       </c>
-      <c r="AH55" s="8">
+      <c r="AH55" s="7">
         <v>2829914.1750394278</v>
       </c>
-      <c r="AI55" s="8">
+      <c r="AI55" s="7">
         <v>2613363.0526854228</v>
       </c>
+      <c r="AJ55" s="7">
+        <v>2.6765534999999998</v>
+      </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>43</v>
       </c>
@@ -6539,83 +6713,86 @@
       <c r="J56" s="1">
         <v>2</v>
       </c>
-      <c r="K56" s="7">
+      <c r="K56" s="6">
         <v>5.92089</v>
       </c>
-      <c r="L56" s="7">
+      <c r="L56" s="6">
         <v>1073076.9627657351</v>
       </c>
-      <c r="M56" s="7">
+      <c r="M56" s="6">
         <v>4009.8626658631342</v>
       </c>
-      <c r="N56" s="7">
+      <c r="N56" s="6">
         <v>1073.4668630959</v>
       </c>
-      <c r="O56" s="7">
+      <c r="O56" s="6">
         <v>2936.3958027672415</v>
       </c>
-      <c r="P56" s="7">
+      <c r="P56" s="6">
         <v>3.7509712488636362</v>
       </c>
-      <c r="Q56" s="7">
+      <c r="Q56" s="6">
         <v>144.28842403405736</v>
       </c>
-      <c r="R56" s="7">
+      <c r="R56" s="6">
         <v>4041528.6740989173</v>
       </c>
-      <c r="S56" s="7">
+      <c r="S56" s="6">
         <v>4128492.229603163</v>
       </c>
-      <c r="T56" s="7">
+      <c r="T56" s="6">
         <v>3977672.3945107087</v>
       </c>
-      <c r="U56" s="7">
+      <c r="U56" s="6">
         <v>3943674.4732645079</v>
       </c>
-      <c r="V56" s="7">
+      <c r="V56" s="6">
         <v>4021225.9726468772</v>
       </c>
-      <c r="W56" s="7">
+      <c r="W56" s="6">
         <v>3807417.1703510131</v>
       </c>
-      <c r="X56" s="7">
+      <c r="X56" s="6">
         <v>3666223.5051992116</v>
       </c>
-      <c r="Y56" s="7">
+      <c r="Y56" s="6">
         <v>3629653.4133091643</v>
       </c>
-      <c r="Z56" s="7">
+      <c r="Z56" s="6">
         <v>3688490.0037282514</v>
       </c>
-      <c r="AA56" s="7">
+      <c r="AA56" s="6">
         <v>4022946.9648679434</v>
       </c>
-      <c r="AB56" s="7">
+      <c r="AB56" s="6">
         <v>4009346.292990251</v>
       </c>
-      <c r="AC56" s="7">
+      <c r="AC56" s="6">
         <v>4033967.5872087278</v>
       </c>
-      <c r="AD56" s="7">
+      <c r="AD56" s="6">
         <v>3999330.6101152115</v>
       </c>
-      <c r="AE56" s="7">
+      <c r="AE56" s="6">
         <v>3874348.1806592033</v>
       </c>
-      <c r="AF56" s="7">
+      <c r="AF56" s="6">
         <v>3835527.8231412158</v>
       </c>
-      <c r="AG56" s="7">
+      <c r="AG56" s="6">
         <v>3716410.8025596049</v>
       </c>
-      <c r="AH56" s="7">
+      <c r="AH56" s="6">
         <v>3677323.0483950898</v>
       </c>
-      <c r="AI56" s="7">
+      <c r="AI56" s="6">
         <v>3710699.9045705218</v>
       </c>
+      <c r="AJ56" s="6">
+        <v>2.0973885499999998</v>
+      </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>43</v>
       </c>
@@ -6646,83 +6823,86 @@
       <c r="J57" s="1">
         <v>50</v>
       </c>
-      <c r="K57" s="7">
+      <c r="K57" s="6">
         <v>13.5677</v>
       </c>
-      <c r="L57" s="7">
+      <c r="L57" s="6">
         <v>3141116.0435126564</v>
       </c>
-      <c r="M57" s="7">
+      <c r="M57" s="6">
         <v>9107.8648992054168</v>
       </c>
-      <c r="N57" s="7">
+      <c r="N57" s="6">
         <v>2485.500645331952</v>
       </c>
-      <c r="O57" s="7">
+      <c r="O57" s="6">
         <v>6622.3642538734657</v>
       </c>
-      <c r="P57" s="7">
+      <c r="P57" s="6">
         <v>3.9258138578016424</v>
       </c>
-      <c r="Q57" s="7">
+      <c r="Q57" s="6">
         <v>115.5594508655284</v>
       </c>
-      <c r="R57" s="7">
+      <c r="R57" s="6">
         <v>8355751.871879261</v>
       </c>
-      <c r="S57" s="7">
+      <c r="S57" s="6">
         <v>9737408.6030726954</v>
       </c>
-      <c r="T57" s="7">
+      <c r="T57" s="6">
         <v>11356550.153691269</v>
       </c>
-      <c r="U57" s="7">
+      <c r="U57" s="6">
         <v>12662156.114109743</v>
       </c>
-      <c r="V57" s="7">
+      <c r="V57" s="6">
         <v>13385930.794561546</v>
       </c>
-      <c r="W57" s="7">
+      <c r="W57" s="6">
         <v>13359559.969875427</v>
       </c>
-      <c r="X57" s="7">
+      <c r="X57" s="6">
         <v>12665973.360455019</v>
       </c>
-      <c r="Y57" s="7">
+      <c r="Y57" s="6">
         <v>11744613.596825529</v>
       </c>
-      <c r="Z57" s="7">
+      <c r="Z57" s="6">
         <v>10683408.522564493</v>
       </c>
-      <c r="AA57" s="7">
+      <c r="AA57" s="6">
         <v>8357171.6389736123</v>
       </c>
-      <c r="AB57" s="7">
+      <c r="AB57" s="6">
         <v>9627745.6668128613</v>
       </c>
-      <c r="AC57" s="7">
+      <c r="AC57" s="6">
         <v>11008837.844460646</v>
       </c>
-      <c r="AD57" s="7">
+      <c r="AD57" s="6">
         <v>12288015.477527393</v>
       </c>
-      <c r="AE57" s="7">
+      <c r="AE57" s="6">
         <v>13001512.53732896</v>
       </c>
-      <c r="AF57" s="7">
+      <c r="AF57" s="6">
         <v>13016003.88516424</v>
       </c>
-      <c r="AG57" s="7">
+      <c r="AG57" s="6">
         <v>12500142.197704241</v>
       </c>
-      <c r="AH57" s="7">
+      <c r="AH57" s="6">
         <v>11590522.474949656</v>
       </c>
-      <c r="AI57" s="7">
+      <c r="AI57" s="6">
         <v>10506504.442837363</v>
       </c>
+      <c r="AJ57" s="6">
+        <v>2.4370467999999996</v>
+      </c>
     </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>43</v>
       </c>
@@ -6753,83 +6933,86 @@
       <c r="J58" s="1">
         <v>2</v>
       </c>
-      <c r="K58" s="7">
+      <c r="K58" s="6">
         <v>5.3853200000000001</v>
       </c>
-      <c r="L58" s="7">
+      <c r="L58" s="6">
         <v>951258.31551125133</v>
       </c>
-      <c r="M58" s="7">
+      <c r="M58" s="6">
         <v>3712.5144359712522</v>
       </c>
-      <c r="N58" s="7">
+      <c r="N58" s="6">
         <v>1005.2611476864914</v>
       </c>
-      <c r="O58" s="7">
+      <c r="O58" s="6">
         <v>2707.2532882847645</v>
       </c>
-      <c r="P58" s="7">
+      <c r="P58" s="6">
         <v>3.840934962962963</v>
       </c>
-      <c r="Q58" s="7">
+      <c r="Q58" s="6">
         <v>155.02171080075163</v>
       </c>
-      <c r="R58" s="7">
+      <c r="R58" s="6">
         <v>3728546.8679197994</v>
       </c>
-      <c r="S58" s="7">
+      <c r="S58" s="6">
         <v>3641686.9383456162</v>
       </c>
-      <c r="T58" s="7">
+      <c r="T58" s="6">
         <v>3595370.727849599</v>
       </c>
-      <c r="U58" s="7">
+      <c r="U58" s="6">
         <v>3529806.7231428311</v>
       </c>
-      <c r="V58" s="7">
+      <c r="V58" s="6">
         <v>3674299.1377394181</v>
       </c>
-      <c r="W58" s="7">
+      <c r="W58" s="6">
         <v>3834214.650212252</v>
       </c>
-      <c r="X58" s="7">
+      <c r="X58" s="6">
         <v>3644625.5628350764</v>
       </c>
-      <c r="Y58" s="7">
+      <c r="Y58" s="6">
         <v>3453347.2414757567</v>
       </c>
-      <c r="Z58" s="7">
+      <c r="Z58" s="6">
         <v>3324842.9212827925</v>
       </c>
-      <c r="AA58" s="7">
+      <c r="AA58" s="6">
         <v>3649454.9610852837</v>
       </c>
-      <c r="AB58" s="7">
+      <c r="AB58" s="6">
         <v>3660747.9783982644</v>
       </c>
-      <c r="AC58" s="7">
+      <c r="AC58" s="6">
         <v>3584874.1267341063</v>
       </c>
-      <c r="AD58" s="7">
+      <c r="AD58" s="6">
         <v>3634406.4612130667</v>
       </c>
-      <c r="AE58" s="7">
+      <c r="AE58" s="6">
         <v>3675719.0030060369</v>
       </c>
-      <c r="AF58" s="7">
+      <c r="AF58" s="6">
         <v>3659402.196570436</v>
       </c>
-      <c r="AG58" s="7">
+      <c r="AG58" s="6">
         <v>3633828.3728714786</v>
       </c>
-      <c r="AH58" s="7">
+      <c r="AH58" s="6">
         <v>3477397.8907954781</v>
       </c>
-      <c r="AI58" s="7">
+      <c r="AI58" s="6">
         <v>3314851.1303187655</v>
       </c>
+      <c r="AJ58" s="6">
+        <v>2.1283950000000003</v>
+      </c>
     </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>43</v>
       </c>
@@ -6860,83 +7043,86 @@
       <c r="J59" s="1">
         <v>2</v>
       </c>
-      <c r="K59" s="7">
+      <c r="K59" s="6">
         <v>5.8415600000000003</v>
       </c>
-      <c r="L59" s="7">
+      <c r="L59" s="6">
         <v>1200718.3922679368</v>
       </c>
-      <c r="M59" s="7">
+      <c r="M59" s="6">
         <v>4226.2772512595529</v>
       </c>
-      <c r="N59" s="7">
+      <c r="N59" s="6">
         <v>1082.2409492519373</v>
       </c>
-      <c r="O59" s="7">
+      <c r="O59" s="6">
         <v>3144.0363020076061</v>
       </c>
-      <c r="P59" s="7">
+      <c r="P59" s="6">
         <v>3.8141056784689003</v>
       </c>
-      <c r="Q59" s="7">
+      <c r="Q59" s="6">
         <v>137.7724490714134</v>
       </c>
-      <c r="R59" s="7">
+      <c r="R59" s="6">
         <v>4342900.743199015</v>
       </c>
-      <c r="S59" s="7">
+      <c r="S59" s="6">
         <v>4492036.7705228878</v>
       </c>
-      <c r="T59" s="7">
+      <c r="T59" s="6">
         <v>4624156.9176937155</v>
       </c>
-      <c r="U59" s="7">
+      <c r="U59" s="6">
         <v>4447748.7034174222</v>
       </c>
-      <c r="V59" s="7">
+      <c r="V59" s="6">
         <v>4255068.6590863252</v>
       </c>
-      <c r="W59" s="7">
+      <c r="W59" s="6">
         <v>4046088.8657134105</v>
       </c>
-      <c r="X59" s="7">
+      <c r="X59" s="6">
         <v>3837049.144880475</v>
       </c>
-      <c r="Y59" s="7">
+      <c r="Y59" s="6">
         <v>3689450.4763660175</v>
       </c>
-      <c r="Z59" s="7">
+      <c r="Z59" s="6">
         <v>3565881.5076775081</v>
       </c>
-      <c r="AA59" s="7">
+      <c r="AA59" s="6">
         <v>4329030.8373930342</v>
       </c>
-      <c r="AB59" s="7">
+      <c r="AB59" s="6">
         <v>4479117.9613138745</v>
       </c>
-      <c r="AC59" s="7">
+      <c r="AC59" s="6">
         <v>4469783.0345117645</v>
       </c>
-      <c r="AD59" s="7">
+      <c r="AD59" s="6">
         <v>4431941.7284837337</v>
       </c>
-      <c r="AE59" s="7">
+      <c r="AE59" s="6">
         <v>4237421.8625963209</v>
       </c>
-      <c r="AF59" s="7">
+      <c r="AF59" s="6">
         <v>4035261.9562091287</v>
       </c>
-      <c r="AG59" s="7">
+      <c r="AG59" s="6">
         <v>3859548.4640151164</v>
       </c>
-      <c r="AH59" s="7">
+      <c r="AH59" s="6">
         <v>3696498.9223696948</v>
       </c>
-      <c r="AI59" s="7">
+      <c r="AI59" s="6">
         <v>3664688.2811688054</v>
       </c>
+      <c r="AJ59" s="6">
+        <v>2.0951702000000001</v>
+      </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>43</v>
       </c>
@@ -6967,83 +7153,86 @@
       <c r="J60" s="1">
         <v>50</v>
       </c>
-      <c r="K60" s="7">
+      <c r="K60" s="6">
         <v>13.5901</v>
       </c>
-      <c r="L60" s="7">
+      <c r="L60" s="6">
         <v>3289064.4461280904</v>
       </c>
-      <c r="M60" s="7">
+      <c r="M60" s="6">
         <v>9032.1854347851404</v>
       </c>
-      <c r="N60" s="7">
+      <c r="N60" s="6">
         <v>2283.2440711825761</v>
       </c>
-      <c r="O60" s="7">
+      <c r="O60" s="6">
         <v>6748.9413636025647</v>
       </c>
-      <c r="P60" s="7">
+      <c r="P60" s="6">
         <v>4.1703012133582762</v>
       </c>
-      <c r="Q60" s="7">
+      <c r="Q60" s="6">
         <v>116.98455927803464</v>
       </c>
-      <c r="R60" s="7">
+      <c r="R60" s="6">
         <v>7706485.9784410615</v>
       </c>
-      <c r="S60" s="7">
+      <c r="S60" s="6">
         <v>9031122.0686489176</v>
       </c>
-      <c r="T60" s="7">
+      <c r="T60" s="6">
         <v>10486729.63280822</v>
       </c>
-      <c r="U60" s="7">
+      <c r="U60" s="6">
         <v>11892092.086363558</v>
       </c>
-      <c r="V60" s="7">
+      <c r="V60" s="6">
         <v>12583897.365025036</v>
       </c>
-      <c r="W60" s="7">
+      <c r="W60" s="6">
         <v>12531913.804305356</v>
       </c>
-      <c r="X60" s="7">
+      <c r="X60" s="6">
         <v>12181863.536114134</v>
       </c>
-      <c r="Y60" s="7">
+      <c r="Y60" s="6">
         <v>11395262.110001881</v>
       </c>
-      <c r="Z60" s="7">
+      <c r="Z60" s="6">
         <v>10453817.657563008</v>
       </c>
-      <c r="AA60" s="7">
+      <c r="AA60" s="6">
         <v>7568346.8003986226</v>
       </c>
-      <c r="AB60" s="7">
+      <c r="AB60" s="6">
         <v>8884172.7160061412</v>
       </c>
-      <c r="AC60" s="7">
+      <c r="AC60" s="6">
         <v>10266007.362720037</v>
       </c>
-      <c r="AD60" s="7">
+      <c r="AD60" s="6">
         <v>11439995.055740712</v>
       </c>
-      <c r="AE60" s="7">
+      <c r="AE60" s="6">
         <v>12203622.423470384</v>
       </c>
-      <c r="AF60" s="7">
+      <c r="AF60" s="6">
         <v>12379617.251828508</v>
       </c>
-      <c r="AG60" s="7">
+      <c r="AG60" s="6">
         <v>11936589.846745811</v>
       </c>
-      <c r="AH60" s="7">
+      <c r="AH60" s="6">
         <v>11251879.636069877</v>
       </c>
-      <c r="AI60" s="7">
+      <c r="AI60" s="6">
         <v>10379838.61255276</v>
       </c>
+      <c r="AJ60" s="6">
+        <v>2.6238082</v>
+      </c>
     </row>
-    <row r="61" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>43</v>
       </c>
@@ -7074,83 +7263,86 @@
       <c r="J61" s="4">
         <v>50</v>
       </c>
-      <c r="K61" s="8">
+      <c r="K61" s="7">
         <v>14.009499999999999</v>
       </c>
-      <c r="L61" s="8">
+      <c r="L61" s="7">
         <v>3571750.1628045174</v>
       </c>
-      <c r="M61" s="8">
+      <c r="M61" s="7">
         <v>9218.5028993657706</v>
       </c>
-      <c r="N61" s="8">
+      <c r="N61" s="7">
         <v>2745.0549043323308</v>
       </c>
-      <c r="O61" s="8">
+      <c r="O61" s="7">
         <v>6473.4479950334426</v>
       </c>
-      <c r="P61" s="8">
+      <c r="P61" s="7">
         <v>3.9995886757957075</v>
       </c>
-      <c r="Q61" s="8">
+      <c r="Q61" s="7">
         <v>105.28403160200644</v>
       </c>
-      <c r="R61" s="8">
+      <c r="R61" s="7">
         <v>8462123.4132440556</v>
       </c>
-      <c r="S61" s="8">
+      <c r="S61" s="7">
         <v>10045483.716069195</v>
       </c>
-      <c r="T61" s="8">
+      <c r="T61" s="7">
         <v>11848379.099573268</v>
       </c>
-      <c r="U61" s="8">
+      <c r="U61" s="7">
         <v>13287754.38539663</v>
       </c>
-      <c r="V61" s="8">
+      <c r="V61" s="7">
         <v>13710215.337688386</v>
       </c>
-      <c r="W61" s="8">
+      <c r="W61" s="7">
         <v>13569071.740315659</v>
       </c>
-      <c r="X61" s="8">
+      <c r="X61" s="7">
         <v>12697490.577262221</v>
       </c>
-      <c r="Y61" s="8">
+      <c r="Y61" s="7">
         <v>11434715.262409432</v>
       </c>
-      <c r="Z61" s="8">
+      <c r="Z61" s="7">
         <v>10238974.306030538</v>
       </c>
-      <c r="AA61" s="8">
+      <c r="AA61" s="7">
         <v>8264173.5681853974</v>
       </c>
-      <c r="AB61" s="8">
+      <c r="AB61" s="7">
         <v>9872965.587554317</v>
       </c>
-      <c r="AC61" s="8">
+      <c r="AC61" s="7">
         <v>11441354.150776302</v>
       </c>
-      <c r="AD61" s="8">
+      <c r="AD61" s="7">
         <v>12711483.744261811</v>
       </c>
-      <c r="AE61" s="8">
+      <c r="AE61" s="7">
         <v>13426939.704578286</v>
       </c>
-      <c r="AF61" s="8">
+      <c r="AF61" s="7">
         <v>13184434.166542018</v>
       </c>
-      <c r="AG61" s="8">
+      <c r="AG61" s="7">
         <v>12410797.749061428</v>
       </c>
-      <c r="AH61" s="8">
+      <c r="AH61" s="7">
         <v>11336470.588050675</v>
       </c>
-      <c r="AI61" s="8">
+      <c r="AI61" s="7">
         <v>10049209.063895488</v>
       </c>
+      <c r="AJ61" s="7">
+        <v>2.4930460000000001</v>
+      </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>44</v>
       </c>
@@ -7181,83 +7373,86 @@
       <c r="J62" s="1">
         <v>50</v>
       </c>
-      <c r="K62" s="7">
+      <c r="K62" s="6">
         <v>12.566599999999999</v>
       </c>
-      <c r="L62" s="7">
+      <c r="L62" s="6">
         <v>2108933.637019034</v>
       </c>
-      <c r="M62" s="7">
+      <c r="M62" s="6">
         <v>9864.3762529659525</v>
       </c>
-      <c r="N62" s="7">
+      <c r="N62" s="6">
         <v>2035.0661295885398</v>
       </c>
-      <c r="O62" s="7">
+      <c r="O62" s="6">
         <v>7829.310123377415</v>
       </c>
-      <c r="P62" s="7">
+      <c r="P62" s="6">
         <v>3.6777978447361082</v>
       </c>
-      <c r="Q62" s="7">
+      <c r="Q62" s="6">
         <v>175.45365614966161</v>
       </c>
-      <c r="R62" s="7">
+      <c r="R62" s="6">
         <v>8203556.9511615559</v>
       </c>
-      <c r="S62" s="7">
+      <c r="S62" s="6">
         <v>8988156.7546107396</v>
       </c>
-      <c r="T62" s="7">
+      <c r="T62" s="6">
         <v>10013906.678868396</v>
       </c>
-      <c r="U62" s="7">
+      <c r="U62" s="6">
         <v>11334795.277426388</v>
       </c>
-      <c r="V62" s="7">
+      <c r="V62" s="6">
         <v>12328133.001263691</v>
       </c>
-      <c r="W62" s="7">
+      <c r="W62" s="6">
         <v>12831731.670598242</v>
       </c>
-      <c r="X62" s="7">
+      <c r="X62" s="6">
         <v>12940700.354219455</v>
       </c>
-      <c r="Y62" s="7">
+      <c r="Y62" s="6">
         <v>12418943.463139182</v>
       </c>
-      <c r="Z62" s="7">
+      <c r="Z62" s="6">
         <v>11458794.221517023</v>
       </c>
-      <c r="AA62" s="7">
+      <c r="AA62" s="6">
         <v>8206291.725171471</v>
       </c>
-      <c r="AB62" s="7">
+      <c r="AB62" s="6">
         <v>9018780.5955925919</v>
       </c>
-      <c r="AC62" s="7">
+      <c r="AC62" s="6">
         <v>10025995.886259817</v>
       </c>
-      <c r="AD62" s="7">
+      <c r="AD62" s="6">
         <v>11051164.0984251</v>
       </c>
-      <c r="AE62" s="7">
+      <c r="AE62" s="6">
         <v>12036901.442554057</v>
       </c>
-      <c r="AF62" s="7">
+      <c r="AF62" s="6">
         <v>12626991.745283704</v>
       </c>
-      <c r="AG62" s="7">
+      <c r="AG62" s="6">
         <v>12621963.5164064</v>
       </c>
-      <c r="AH62" s="7">
+      <c r="AH62" s="6">
         <v>12154745.417453988</v>
       </c>
-      <c r="AI62" s="7">
+      <c r="AI62" s="6">
         <v>11314416.424508194</v>
       </c>
+      <c r="AJ62" s="6">
+        <v>2.2173900000000004</v>
+      </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>44</v>
       </c>
@@ -7288,83 +7483,86 @@
       <c r="J63" s="1">
         <v>50</v>
       </c>
-      <c r="K63" s="7">
+      <c r="K63" s="6">
         <v>13.736700000000001</v>
       </c>
-      <c r="L63" s="7">
+      <c r="L63" s="6">
         <v>2816897.1982053262</v>
       </c>
-      <c r="M63" s="7">
+      <c r="M63" s="6">
         <v>10038.343378842814</v>
       </c>
-      <c r="N63" s="7">
+      <c r="N63" s="6">
         <v>3116.6814612185526</v>
       </c>
-      <c r="O63" s="7">
+      <c r="O63" s="6">
         <v>6921.6619176242566</v>
       </c>
-      <c r="P63" s="7">
+      <c r="P63" s="6">
         <v>4.7505292902979379</v>
       </c>
-      <c r="Q63" s="7">
+      <c r="Q63" s="6">
         <v>172.66364432054371</v>
       </c>
-      <c r="R63" s="7">
+      <c r="R63" s="6">
         <v>8230695.3747049887</v>
       </c>
-      <c r="S63" s="7">
+      <c r="S63" s="6">
         <v>9538173.0741112418</v>
       </c>
-      <c r="T63" s="7">
+      <c r="T63" s="6">
         <v>11098437.139468929</v>
       </c>
-      <c r="U63" s="7">
+      <c r="U63" s="6">
         <v>12319558.161569972</v>
       </c>
-      <c r="V63" s="7">
+      <c r="V63" s="6">
         <v>12746641.887890739</v>
       </c>
-      <c r="W63" s="7">
+      <c r="W63" s="6">
         <v>12799274.609815672</v>
       </c>
-      <c r="X63" s="7">
+      <c r="X63" s="6">
         <v>12358379.09318772</v>
       </c>
-      <c r="Y63" s="7">
+      <c r="Y63" s="6">
         <v>11669202.576415919</v>
       </c>
-      <c r="Z63" s="7">
+      <c r="Z63" s="6">
         <v>10821137.256861998</v>
       </c>
-      <c r="AA63" s="7">
+      <c r="AA63" s="6">
         <v>8234376.679268023</v>
       </c>
-      <c r="AB63" s="7">
+      <c r="AB63" s="6">
         <v>9451831.8567371015</v>
       </c>
-      <c r="AC63" s="7">
+      <c r="AC63" s="6">
         <v>10751900.705029592</v>
       </c>
-      <c r="AD63" s="7">
+      <c r="AD63" s="6">
         <v>11865576.421009786</v>
       </c>
-      <c r="AE63" s="7">
+      <c r="AE63" s="6">
         <v>12554835.602166535</v>
       </c>
-      <c r="AF63" s="7">
+      <c r="AF63" s="6">
         <v>12549508.142963734</v>
       </c>
-      <c r="AG63" s="7">
+      <c r="AG63" s="6">
         <v>12208142.510573501</v>
       </c>
-      <c r="AH63" s="7">
+      <c r="AH63" s="6">
         <v>11538784.021214591</v>
       </c>
-      <c r="AI63" s="7">
+      <c r="AI63" s="6">
         <v>10548922.531340584</v>
       </c>
+      <c r="AJ63" s="6">
+        <v>3.2298090000000004</v>
+      </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>44</v>
       </c>
@@ -7395,83 +7593,86 @@
       <c r="J64" s="1">
         <v>50</v>
       </c>
-      <c r="K64" s="7">
+      <c r="K64" s="6">
         <v>13.4582</v>
       </c>
-      <c r="L64" s="7">
+      <c r="L64" s="6">
         <v>3156073.0267511434</v>
       </c>
-      <c r="M64" s="7">
+      <c r="M64" s="6">
         <v>10188.792347679693</v>
       </c>
-      <c r="N64" s="7">
+      <c r="N64" s="6">
         <v>2604.7876877560243</v>
       </c>
-      <c r="O64" s="7">
+      <c r="O64" s="6">
         <v>7584.0046599236666</v>
       </c>
-      <c r="P64" s="7">
+      <c r="P64" s="6">
         <v>4.392825507095881</v>
       </c>
-      <c r="Q64" s="7">
+      <c r="Q64" s="6">
         <v>146.88216281724678</v>
       </c>
-      <c r="R64" s="7">
+      <c r="R64" s="6">
         <v>7984067.2564927926</v>
       </c>
-      <c r="S64" s="7">
+      <c r="S64" s="6">
         <v>9459088.8131622672</v>
       </c>
-      <c r="T64" s="7">
+      <c r="T64" s="6">
         <v>11048927.692542644</v>
       </c>
-      <c r="U64" s="7">
+      <c r="U64" s="6">
         <v>12587178.832838461</v>
       </c>
-      <c r="V64" s="7">
+      <c r="V64" s="6">
         <v>13453044.211885437</v>
       </c>
-      <c r="W64" s="7">
+      <c r="W64" s="6">
         <v>13518728.106880231</v>
       </c>
-      <c r="X64" s="7">
+      <c r="X64" s="6">
         <v>13021844.284655264</v>
       </c>
-      <c r="Y64" s="7">
+      <c r="Y64" s="6">
         <v>12062981.75991039</v>
       </c>
-      <c r="Z64" s="7">
+      <c r="Z64" s="6">
         <v>10905221.815022003</v>
       </c>
-      <c r="AA64" s="7">
+      <c r="AA64" s="6">
         <v>8014343.9906189367</v>
       </c>
-      <c r="AB64" s="7">
+      <c r="AB64" s="6">
         <v>9269732.0674544517</v>
       </c>
-      <c r="AC64" s="7">
+      <c r="AC64" s="6">
         <v>10801215.371126428</v>
       </c>
-      <c r="AD64" s="7">
+      <c r="AD64" s="6">
         <v>12133040.82801911</v>
       </c>
-      <c r="AE64" s="7">
+      <c r="AE64" s="6">
         <v>13036333.015876045</v>
       </c>
-      <c r="AF64" s="7">
+      <c r="AF64" s="6">
         <v>13233932.743825909</v>
       </c>
-      <c r="AG64" s="7">
+      <c r="AG64" s="6">
         <v>12749434.765670963</v>
       </c>
-      <c r="AH64" s="7">
+      <c r="AH64" s="6">
         <v>11869913.325207688</v>
       </c>
-      <c r="AI64" s="7">
+      <c r="AI64" s="6">
         <v>10468586.503397355</v>
       </c>
+      <c r="AJ64" s="6">
+        <v>2.7305499999999996</v>
+      </c>
     </row>
-    <row r="65" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>44</v>
       </c>
@@ -7502,83 +7703,86 @@
       <c r="J65" s="1">
         <v>2</v>
       </c>
-      <c r="K65" s="7">
+      <c r="K65" s="6">
         <v>5.4879499999999997</v>
       </c>
-      <c r="L65" s="7">
+      <c r="L65" s="6">
         <v>1151014.6273658371</v>
       </c>
-      <c r="M65" s="7">
+      <c r="M65" s="6">
         <v>4548.1945407276326</v>
       </c>
-      <c r="N65" s="7">
+      <c r="N65" s="6">
         <v>1197.9145323927883</v>
       </c>
-      <c r="O65" s="7">
+      <c r="O65" s="6">
         <v>3350.2800083348475</v>
       </c>
-      <c r="P65" s="7">
+      <c r="P65" s="6">
         <v>4.256475068712871</v>
       </c>
-      <c r="Q65" s="7">
+      <c r="Q65" s="6">
         <v>171.81019885093946</v>
       </c>
-      <c r="R65" s="7">
+      <c r="R65" s="6">
         <v>2884448.3002249151</v>
       </c>
-      <c r="S65" s="7">
+      <c r="S65" s="6">
         <v>3091907.2405840326</v>
       </c>
-      <c r="T65" s="7">
+      <c r="T65" s="6">
         <v>3122289.9295745655</v>
       </c>
-      <c r="U65" s="7">
+      <c r="U65" s="6">
         <v>3265030.8025081935</v>
       </c>
-      <c r="V65" s="7">
+      <c r="V65" s="6">
         <v>3312507.5594288446</v>
       </c>
-      <c r="W65" s="7">
+      <c r="W65" s="6">
         <v>3308528.395834967</v>
       </c>
-      <c r="X65" s="7">
+      <c r="X65" s="6">
         <v>3337313.5390242366</v>
       </c>
-      <c r="Y65" s="7">
+      <c r="Y65" s="6">
         <v>3156667.8267808207</v>
       </c>
-      <c r="Z65" s="7">
+      <c r="Z65" s="6">
         <v>3173029.3659618753</v>
       </c>
-      <c r="AA65" s="7">
+      <c r="AA65" s="6">
         <v>2864235.2796415794</v>
       </c>
-      <c r="AB65" s="7">
+      <c r="AB65" s="6">
         <v>2998660.3496358357</v>
       </c>
-      <c r="AC65" s="7">
+      <c r="AC65" s="6">
         <v>3176111.6155520529</v>
       </c>
-      <c r="AD65" s="7">
+      <c r="AD65" s="6">
         <v>3214587.2537928512</v>
       </c>
-      <c r="AE65" s="7">
+      <c r="AE65" s="6">
         <v>3286635.6862190892</v>
       </c>
-      <c r="AF65" s="7">
+      <c r="AF65" s="6">
         <v>3324864.2820702833</v>
       </c>
-      <c r="AG65" s="7">
+      <c r="AG65" s="6">
         <v>3230814.5898462576</v>
       </c>
-      <c r="AH65" s="7">
+      <c r="AH65" s="6">
         <v>3253098.6515736058</v>
       </c>
-      <c r="AI65" s="7">
+      <c r="AI65" s="6">
         <v>3190275.3501116652</v>
       </c>
+      <c r="AJ65" s="12">
+        <v>2.5063054399999998</v>
+      </c>
     </row>
-    <row r="66" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>44</v>
       </c>
@@ -7609,83 +7813,86 @@
       <c r="J66" s="1">
         <v>2</v>
       </c>
-      <c r="K66" s="7">
+      <c r="K66" s="6">
         <v>5.8254099999999998</v>
       </c>
-      <c r="L66" s="7">
+      <c r="L66" s="6">
         <v>829864.2010776446</v>
       </c>
-      <c r="M66" s="7">
+      <c r="M66" s="6">
         <v>4539.6704380624597</v>
       </c>
-      <c r="N66" s="7">
+      <c r="N66" s="6">
         <v>1179.7221689977921</v>
       </c>
-      <c r="O66" s="7">
+      <c r="O66" s="6">
         <v>3359.9482690646742</v>
       </c>
-      <c r="P66" s="7">
+      <c r="P66" s="6">
         <v>4.4867796673189826</v>
       </c>
-      <c r="Q66" s="7">
+      <c r="Q66" s="6">
         <v>254.99140805170379</v>
       </c>
-      <c r="R66" s="7">
+      <c r="R66" s="6">
         <v>3755318.6845111861</v>
       </c>
-      <c r="S66" s="7">
+      <c r="S66" s="6">
         <v>3908731.7452109726</v>
       </c>
-      <c r="T66" s="7">
+      <c r="T66" s="6">
         <v>3895466.6198228477</v>
       </c>
-      <c r="U66" s="7">
+      <c r="U66" s="6">
         <v>3892075.6515512802</v>
       </c>
-      <c r="V66" s="7">
+      <c r="V66" s="6">
         <v>3807562.3334328248</v>
       </c>
-      <c r="W66" s="7">
+      <c r="W66" s="6">
         <v>3625862.617746505</v>
       </c>
-      <c r="X66" s="7">
+      <c r="X66" s="6">
         <v>3552951.6085832324</v>
       </c>
-      <c r="Y66" s="7">
+      <c r="Y66" s="6">
         <v>3482268.8614537069</v>
       </c>
-      <c r="Z66" s="7">
+      <c r="Z66" s="6">
         <v>3519551.026214873</v>
       </c>
-      <c r="AA66" s="7">
+      <c r="AA66" s="6">
         <v>3728959.4538289481</v>
       </c>
-      <c r="AB66" s="7">
+      <c r="AB66" s="6">
         <v>3824109.0294413213</v>
       </c>
-      <c r="AC66" s="7">
+      <c r="AC66" s="6">
         <v>3900385.9165386907</v>
       </c>
-      <c r="AD66" s="7">
+      <c r="AD66" s="6">
         <v>3851012.9100614488</v>
       </c>
-      <c r="AE66" s="7">
+      <c r="AE66" s="6">
         <v>3754255.7826081505</v>
       </c>
-      <c r="AF66" s="7">
+      <c r="AF66" s="6">
         <v>3675853.2960935375</v>
       </c>
-      <c r="AG66" s="7">
+      <c r="AG66" s="6">
         <v>3552615.3467010288</v>
       </c>
-      <c r="AH66" s="7">
+      <c r="AH66" s="6">
         <v>3536172.4486477664</v>
       </c>
-      <c r="AI66" s="7">
+      <c r="AI66" s="6">
         <v>3436741.7130575506</v>
       </c>
+      <c r="AJ66" s="12">
+        <v>2.3440625000000002</v>
+      </c>
     </row>
-    <row r="67" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>44</v>
       </c>
@@ -7716,83 +7923,86 @@
       <c r="J67" s="4">
         <v>2</v>
       </c>
-      <c r="K67" s="8">
+      <c r="K67" s="7">
         <v>6.7766000000000002</v>
       </c>
-      <c r="L67" s="8">
+      <c r="L67" s="7">
         <v>1160437.0679055045</v>
       </c>
-      <c r="M67" s="8">
+      <c r="M67" s="7">
         <v>5008.2668655035741</v>
       </c>
-      <c r="N67" s="8">
+      <c r="N67" s="7">
         <v>1217.9005746403288</v>
       </c>
-      <c r="O67" s="8">
+      <c r="O67" s="7">
         <v>3790.3662908632396</v>
       </c>
-      <c r="P67" s="8">
+      <c r="P67" s="7">
         <v>3.8677552694214881</v>
       </c>
-      <c r="Q67" s="8">
+      <c r="Q67" s="7">
         <v>174.73945780519253</v>
       </c>
-      <c r="R67" s="8">
+      <c r="R67" s="7">
         <v>4397064.6852285871</v>
       </c>
-      <c r="S67" s="8">
+      <c r="S67" s="7">
         <v>4539560.0097320471</v>
       </c>
-      <c r="T67" s="8">
+      <c r="T67" s="7">
         <v>4528811.6882654009</v>
       </c>
-      <c r="U67" s="8">
+      <c r="U67" s="7">
         <v>4478379.049930891</v>
       </c>
-      <c r="V67" s="8">
+      <c r="V67" s="7">
         <v>4353493.703547772</v>
       </c>
-      <c r="W67" s="8">
+      <c r="W67" s="7">
         <v>4334574.8164821649</v>
       </c>
-      <c r="X67" s="8">
+      <c r="X67" s="7">
         <v>4502017.0045491429</v>
       </c>
-      <c r="Y67" s="8">
+      <c r="Y67" s="7">
         <v>4597360.3817105191</v>
       </c>
-      <c r="Z67" s="8">
+      <c r="Z67" s="7">
         <v>4260879.024304809</v>
       </c>
-      <c r="AA67" s="8">
+      <c r="AA67" s="7">
         <v>4232538.0296263658</v>
       </c>
-      <c r="AB67" s="8">
+      <c r="AB67" s="7">
         <v>4461965.8859844198</v>
       </c>
-      <c r="AC67" s="8">
+      <c r="AC67" s="7">
         <v>4508761.9929531738</v>
       </c>
-      <c r="AD67" s="8">
+      <c r="AD67" s="7">
         <v>4439422.4921807731</v>
       </c>
-      <c r="AE67" s="8">
+      <c r="AE67" s="7">
         <v>4405303.6797281122</v>
       </c>
-      <c r="AF67" s="8">
+      <c r="AF67" s="7">
         <v>4426509.8487542132</v>
       </c>
-      <c r="AG67" s="8">
+      <c r="AG67" s="7">
         <v>4462101.9052819517</v>
       </c>
-      <c r="AH67" s="8">
+      <c r="AH67" s="7">
         <v>4378130.1886006258</v>
       </c>
-      <c r="AI67" s="8">
+      <c r="AI67" s="7">
         <v>4346072.6784139648</v>
       </c>
+      <c r="AJ67" s="13">
+        <v>2.2687056000000001</v>
+      </c>
     </row>
-    <row r="68" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>44</v>
       </c>
@@ -7823,83 +8033,86 @@
       <c r="J68" s="1">
         <v>2</v>
       </c>
-      <c r="K68" s="7">
+      <c r="K68" s="6">
         <v>4.6527000000000003</v>
       </c>
-      <c r="L68" s="7">
+      <c r="L68" s="6">
         <v>1020949.5628362276</v>
       </c>
-      <c r="M68" s="7">
+      <c r="M68" s="6">
         <v>4318.2823152684923</v>
       </c>
-      <c r="N68" s="7">
+      <c r="N68" s="6">
         <v>1521.347440899907</v>
       </c>
-      <c r="O68" s="7">
+      <c r="O68" s="6">
         <v>2796.9348743685891</v>
       </c>
-      <c r="P68" s="7">
+      <c r="P68" s="6">
         <v>5.7915149467213105</v>
       </c>
-      <c r="Q68" s="7">
+      <c r="Q68" s="6">
         <v>256.81512211479895</v>
       </c>
-      <c r="R68" s="7">
+      <c r="R68" s="6">
         <v>2074581.3820029823</v>
       </c>
-      <c r="S68" s="7">
+      <c r="S68" s="6">
         <v>2025895.5325133214</v>
       </c>
-      <c r="T68" s="7">
+      <c r="T68" s="6">
         <v>2009588.5265845361</v>
       </c>
-      <c r="U68" s="7">
+      <c r="U68" s="6">
         <v>2031369.368610455</v>
       </c>
-      <c r="V68" s="7">
+      <c r="V68" s="6">
         <v>1935044.7198747774</v>
       </c>
-      <c r="W68" s="7">
+      <c r="W68" s="6">
         <v>1669735.5217451532</v>
       </c>
-      <c r="X68" s="7">
+      <c r="X68" s="6">
         <v>1496678.1436847176</v>
       </c>
-      <c r="Y68" s="7">
+      <c r="Y68" s="6">
         <v>1543664.5561650405</v>
       </c>
-      <c r="Z68" s="7">
+      <c r="Z68" s="6">
         <v>1420800.9360080655</v>
       </c>
-      <c r="AA68" s="7">
+      <c r="AA68" s="6">
         <v>2047640.9906974805</v>
       </c>
-      <c r="AB68" s="7">
+      <c r="AB68" s="6">
         <v>2041567.827025552</v>
       </c>
-      <c r="AC68" s="7">
+      <c r="AC68" s="6">
         <v>2028628.7580643129</v>
       </c>
-      <c r="AD68" s="7">
+      <c r="AD68" s="6">
         <v>1971612.2764917477</v>
       </c>
-      <c r="AE68" s="7">
+      <c r="AE68" s="6">
         <v>1832884.8779143929</v>
       </c>
-      <c r="AF68" s="7">
+      <c r="AF68" s="6">
         <v>1687863.0672904199</v>
       </c>
-      <c r="AG68" s="7">
+      <c r="AG68" s="6">
         <v>1604226.9749143692</v>
       </c>
-      <c r="AH68" s="7">
+      <c r="AH68" s="6">
         <v>1457752.8402870221</v>
       </c>
-      <c r="AI68" s="7">
+      <c r="AI68" s="6">
         <v>1403447.2767509099</v>
       </c>
+      <c r="AJ68" s="12">
+        <v>3.6834530000000001</v>
+      </c>
     </row>
-    <row r="69" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>44</v>
       </c>
@@ -7930,83 +8143,86 @@
       <c r="J69" s="1">
         <v>2</v>
       </c>
-      <c r="K69" s="7">
+      <c r="K69" s="6">
         <v>6.5720799999999997</v>
       </c>
-      <c r="L69" s="7">
+      <c r="L69" s="6">
         <v>1013124.7153204391</v>
       </c>
-      <c r="M69" s="7">
+      <c r="M69" s="6">
         <v>4739.0321903993272</v>
       </c>
-      <c r="N69" s="7">
+      <c r="N69" s="6">
         <v>1322.3960331668925</v>
       </c>
-      <c r="O69" s="7">
+      <c r="O69" s="6">
         <v>3416.6361572324395</v>
       </c>
-      <c r="P69" s="7">
+      <c r="P69" s="6">
         <v>4.2786538666666667</v>
       </c>
-      <c r="Q69" s="7">
+      <c r="Q69" s="6">
         <v>208.5582895287765</v>
       </c>
-      <c r="R69" s="7">
+      <c r="R69" s="6">
         <v>3790126.2225320097</v>
       </c>
-      <c r="S69" s="7">
+      <c r="S69" s="6">
         <v>3890923.129794511</v>
       </c>
-      <c r="T69" s="7">
+      <c r="T69" s="6">
         <v>4125478.9244336151</v>
       </c>
-      <c r="U69" s="7">
+      <c r="U69" s="6">
         <v>4205264.3793105781</v>
       </c>
-      <c r="V69" s="7">
+      <c r="V69" s="6">
         <v>4037518.348741963</v>
       </c>
-      <c r="W69" s="7">
+      <c r="W69" s="6">
         <v>4077415.7422948801</v>
       </c>
-      <c r="X69" s="7">
+      <c r="X69" s="6">
         <v>4383677.0704330197</v>
       </c>
-      <c r="Y69" s="7">
+      <c r="Y69" s="6">
         <v>4664277.8992124097</v>
       </c>
-      <c r="Z69" s="7">
+      <c r="Z69" s="6">
         <v>4265057.7321245829</v>
       </c>
-      <c r="AA69" s="7">
+      <c r="AA69" s="6">
         <v>3740060.3044540528</v>
       </c>
-      <c r="AB69" s="7">
+      <c r="AB69" s="6">
         <v>3950698.7935073916</v>
       </c>
-      <c r="AC69" s="7">
+      <c r="AC69" s="6">
         <v>4041991.4736310486</v>
       </c>
-      <c r="AD69" s="7">
+      <c r="AD69" s="6">
         <v>4081024.7259262339</v>
       </c>
-      <c r="AE69" s="7">
+      <c r="AE69" s="6">
         <v>4140353.3467351324</v>
       </c>
-      <c r="AF69" s="7">
+      <c r="AF69" s="6">
         <v>4203483.1697485307</v>
       </c>
-      <c r="AG69" s="7">
+      <c r="AG69" s="6">
         <v>4351147.7094975272</v>
       </c>
-      <c r="AH69" s="7">
+      <c r="AH69" s="6">
         <v>4323553.9558592141</v>
       </c>
-      <c r="AI69" s="7">
+      <c r="AI69" s="6">
         <v>4203584.6169810332</v>
       </c>
+      <c r="AJ69" s="12">
+        <v>2.5266932</v>
+      </c>
     </row>
-    <row r="70" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>44</v>
       </c>
@@ -8037,83 +8253,86 @@
       <c r="J70" s="1">
         <v>50</v>
       </c>
-      <c r="K70" s="7">
+      <c r="K70" s="6">
         <v>13.179</v>
       </c>
-      <c r="L70" s="7">
+      <c r="L70" s="6">
         <v>2701928.4775373684</v>
       </c>
-      <c r="M70" s="7">
+      <c r="M70" s="6">
         <v>9322.6515421826098</v>
       </c>
-      <c r="N70" s="7">
+      <c r="N70" s="6">
         <v>2909.0549379978434</v>
       </c>
-      <c r="O70" s="7">
+      <c r="O70" s="6">
         <v>6413.5966041847669</v>
       </c>
-      <c r="P70" s="7">
+      <c r="P70" s="6">
         <v>4.7888263398619673</v>
       </c>
-      <c r="Q70" s="7">
+      <c r="Q70" s="6">
         <v>169.83069489706077</v>
       </c>
-      <c r="R70" s="7">
+      <c r="R70" s="6">
         <v>7102012.2562517617</v>
       </c>
-      <c r="S70" s="7">
+      <c r="S70" s="6">
         <v>8415898.9111962672</v>
       </c>
-      <c r="T70" s="7">
+      <c r="T70" s="6">
         <v>9818632.5469664652</v>
       </c>
-      <c r="U70" s="7">
+      <c r="U70" s="6">
         <v>10832717.093716698</v>
       </c>
-      <c r="V70" s="7">
+      <c r="V70" s="6">
         <v>11266111.181369718</v>
       </c>
-      <c r="W70" s="7">
+      <c r="W70" s="6">
         <v>11101909.626634283</v>
       </c>
-      <c r="X70" s="7">
+      <c r="X70" s="6">
         <v>10528730.523021366</v>
       </c>
-      <c r="Y70" s="7">
+      <c r="Y70" s="6">
         <v>9760389.1663357522</v>
       </c>
-      <c r="Z70" s="7">
+      <c r="Z70" s="6">
         <v>8847907.6129424926</v>
       </c>
-      <c r="AA70" s="7">
+      <c r="AA70" s="6">
         <v>7123275.4039001344</v>
       </c>
-      <c r="AB70" s="7">
+      <c r="AB70" s="6">
         <v>8242244.8434028449</v>
       </c>
-      <c r="AC70" s="7">
+      <c r="AC70" s="6">
         <v>9472582.545263337</v>
       </c>
-      <c r="AD70" s="7">
+      <c r="AD70" s="6">
         <v>10492686.783238269</v>
       </c>
-      <c r="AE70" s="7">
+      <c r="AE70" s="6">
         <v>10965661.528560061</v>
       </c>
-      <c r="AF70" s="7">
+      <c r="AF70" s="6">
         <v>10884947.023693344</v>
       </c>
-      <c r="AG70" s="7">
+      <c r="AG70" s="6">
         <v>10388017.113622546</v>
       </c>
-      <c r="AH70" s="7">
+      <c r="AH70" s="6">
         <v>9615417.7309382651</v>
       </c>
-      <c r="AI70" s="7">
+      <c r="AI70" s="6">
         <v>8699075.6066776216</v>
       </c>
+      <c r="AJ70" s="6">
+        <v>3.0035819999999998</v>
+      </c>
     </row>
-    <row r="71" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>44</v>
       </c>
@@ -8144,83 +8363,86 @@
       <c r="J71" s="1">
         <v>2</v>
       </c>
-      <c r="K71" s="7">
+      <c r="K71" s="6">
         <v>5.5578700000000003</v>
       </c>
-      <c r="L71" s="7">
+      <c r="L71" s="6">
         <v>807749.49012524239</v>
       </c>
-      <c r="M71" s="7">
+      <c r="M71" s="6">
         <v>5483.5344796121071</v>
       </c>
-      <c r="N71" s="7">
+      <c r="N71" s="6">
         <v>1736.2019488072226</v>
       </c>
-      <c r="O71" s="7">
+      <c r="O71" s="6">
         <v>3747.3325308048852</v>
       </c>
-      <c r="P71" s="7">
+      <c r="P71" s="6">
         <v>5.8276025178684812</v>
       </c>
-      <c r="Q71" s="7">
+      <c r="Q71" s="6">
         <v>411.63077873400141</v>
       </c>
-      <c r="R71" s="7">
+      <c r="R71" s="6">
         <v>2668609.1321958737</v>
       </c>
-      <c r="S71" s="7">
+      <c r="S71" s="6">
         <v>2679402.9671900682</v>
       </c>
-      <c r="T71" s="7">
+      <c r="T71" s="6">
         <v>2700949.7248871387</v>
       </c>
-      <c r="U71" s="7">
+      <c r="U71" s="6">
         <v>2592205.8871506322</v>
       </c>
-      <c r="V71" s="7">
+      <c r="V71" s="6">
         <v>2556165.5560429902</v>
       </c>
-      <c r="W71" s="7">
+      <c r="W71" s="6">
         <v>2545547.261298134</v>
       </c>
-      <c r="X71" s="7">
+      <c r="X71" s="6">
         <v>2282954.7943807943</v>
       </c>
-      <c r="Y71" s="7">
+      <c r="Y71" s="6">
         <v>2060003.9676997671</v>
       </c>
-      <c r="Z71" s="7">
+      <c r="Z71" s="6">
         <v>1965050.4971607281</v>
       </c>
-      <c r="AA71" s="7">
+      <c r="AA71" s="6">
         <v>2624155.5080683902</v>
       </c>
-      <c r="AB71" s="7">
+      <c r="AB71" s="6">
         <v>2684682.0356305186</v>
       </c>
-      <c r="AC71" s="7">
+      <c r="AC71" s="6">
         <v>2635083.2686988576</v>
       </c>
-      <c r="AD71" s="7">
+      <c r="AD71" s="6">
         <v>2626563.9182022172</v>
       </c>
-      <c r="AE71" s="7">
+      <c r="AE71" s="6">
         <v>2568664.7085212693</v>
       </c>
-      <c r="AF71" s="7">
+      <c r="AF71" s="6">
         <v>2411847.6040333826</v>
       </c>
-      <c r="AG71" s="7">
+      <c r="AG71" s="6">
         <v>2277181.2525826194</v>
       </c>
-      <c r="AH71" s="7">
+      <c r="AH71" s="6">
         <v>2112107.2813285119</v>
       </c>
-      <c r="AI71" s="7">
+      <c r="AI71" s="6">
         <v>1976132.0672013799</v>
       </c>
+      <c r="AJ71" s="6">
+        <v>3.38892368</v>
+      </c>
     </row>
-    <row r="72" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>44</v>
       </c>
@@ -8251,83 +8473,86 @@
       <c r="J72" s="1">
         <v>50</v>
       </c>
-      <c r="K72" s="7">
+      <c r="K72" s="6">
         <v>13.413500000000001</v>
       </c>
-      <c r="L72" s="7">
+      <c r="L72" s="6">
         <v>3017000.3292398504</v>
       </c>
-      <c r="M72" s="7">
+      <c r="M72" s="6">
         <v>9986.1020950719012</v>
       </c>
-      <c r="N72" s="7">
+      <c r="N72" s="6">
         <v>2854.4064674631641</v>
       </c>
-      <c r="O72" s="7">
+      <c r="O72" s="6">
         <v>7131.6956276087431</v>
       </c>
-      <c r="P72" s="7">
+      <c r="P72" s="6">
         <v>4.8933022323739195</v>
       </c>
-      <c r="Q72" s="7">
+      <c r="Q72" s="6">
         <v>167.75370609134796</v>
       </c>
-      <c r="R72" s="7">
+      <c r="R72" s="6">
         <v>8259780.153861667</v>
       </c>
-      <c r="S72" s="7">
+      <c r="S72" s="6">
         <v>9485289.4677612018</v>
       </c>
-      <c r="T72" s="7">
+      <c r="T72" s="6">
         <v>10622803.974049468</v>
       </c>
-      <c r="U72" s="7">
+      <c r="U72" s="6">
         <v>11365492.370510038</v>
       </c>
-      <c r="V72" s="7">
+      <c r="V72" s="6">
         <v>11416510.441143354</v>
       </c>
-      <c r="W72" s="7">
+      <c r="W72" s="6">
         <v>11054894.192467518</v>
       </c>
-      <c r="X72" s="7">
+      <c r="X72" s="6">
         <v>10341517.134555725</v>
       </c>
-      <c r="Y72" s="7">
+      <c r="Y72" s="6">
         <v>9291853.6538337599</v>
       </c>
-      <c r="Z72" s="7">
+      <c r="Z72" s="6">
         <v>8187736.433232381</v>
       </c>
-      <c r="AA72" s="7">
+      <c r="AA72" s="6">
         <v>8169360.4732299624</v>
       </c>
-      <c r="AB72" s="7">
+      <c r="AB72" s="6">
         <v>9293434.0817813687</v>
       </c>
-      <c r="AC72" s="7">
+      <c r="AC72" s="6">
         <v>10340618.007910384</v>
       </c>
-      <c r="AD72" s="7">
+      <c r="AD72" s="6">
         <v>11005365.248598985</v>
       </c>
-      <c r="AE72" s="7">
+      <c r="AE72" s="6">
         <v>11208041.863895411</v>
       </c>
-      <c r="AF72" s="7">
+      <c r="AF72" s="6">
         <v>10852457.828096578</v>
       </c>
-      <c r="AG72" s="7">
+      <c r="AG72" s="6">
         <v>10096990.415468082</v>
       </c>
-      <c r="AH72" s="7">
+      <c r="AH72" s="6">
         <v>9139452.5211418513</v>
       </c>
-      <c r="AI72" s="7">
+      <c r="AI72" s="6">
         <v>8053420.6140141198</v>
       </c>
+      <c r="AJ72" s="6">
+        <v>3.0204040000000001</v>
+      </c>
     </row>
-    <row r="73" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>44</v>
       </c>
@@ -8358,83 +8583,86 @@
       <c r="J73" s="4">
         <v>50</v>
       </c>
-      <c r="K73" s="8">
+      <c r="K73" s="7">
         <v>14.408300000000001</v>
       </c>
-      <c r="L73" s="8">
+      <c r="L73" s="7">
         <v>3021503.9234796325</v>
       </c>
-      <c r="M73" s="8">
+      <c r="M73" s="7">
         <v>11242.595396331264</v>
       </c>
-      <c r="N73" s="8">
+      <c r="N73" s="7">
         <v>3186.0599703664147</v>
       </c>
-      <c r="O73" s="8">
+      <c r="O73" s="7">
         <v>8056.5354259648448</v>
       </c>
-      <c r="P73" s="8">
+      <c r="P73" s="7">
         <v>5.1131158576271183</v>
       </c>
-      <c r="Q73" s="8">
+      <c r="Q73" s="7">
         <v>194.94504315990326</v>
       </c>
-      <c r="R73" s="8">
+      <c r="R73" s="7">
         <v>8428337.7357779127</v>
       </c>
-      <c r="S73" s="8">
+      <c r="S73" s="7">
         <v>10106794.687398391</v>
       </c>
-      <c r="T73" s="8">
+      <c r="T73" s="7">
         <v>11719149.317784833</v>
       </c>
-      <c r="U73" s="8">
+      <c r="U73" s="7">
         <v>12585691.598319387</v>
       </c>
-      <c r="V73" s="8">
+      <c r="V73" s="7">
         <v>12990470.587748043</v>
       </c>
-      <c r="W73" s="8">
+      <c r="W73" s="7">
         <v>12833287.183445068</v>
       </c>
-      <c r="X73" s="8">
+      <c r="X73" s="7">
         <v>12200143.402406527</v>
       </c>
-      <c r="Y73" s="8">
+      <c r="Y73" s="7">
         <v>11403986.00115549</v>
       </c>
-      <c r="Z73" s="8">
+      <c r="Z73" s="7">
         <v>10316168.876796452</v>
       </c>
-      <c r="AA73" s="8">
+      <c r="AA73" s="7">
         <v>8301756.3745862553</v>
       </c>
-      <c r="AB73" s="8">
+      <c r="AB73" s="7">
         <v>9804989.3928419761</v>
       </c>
-      <c r="AC73" s="8">
+      <c r="AC73" s="7">
         <v>11210847.448054807</v>
       </c>
-      <c r="AD73" s="8">
+      <c r="AD73" s="7">
         <v>12322104.921737228</v>
       </c>
-      <c r="AE73" s="8">
+      <c r="AE73" s="7">
         <v>12708283.528634572</v>
       </c>
-      <c r="AF73" s="8">
+      <c r="AF73" s="7">
         <v>12582909.181746218</v>
       </c>
-      <c r="AG73" s="8">
+      <c r="AG73" s="7">
         <v>12076492.786474129</v>
       </c>
-      <c r="AH73" s="8">
+      <c r="AH73" s="7">
         <v>11179338.614574844</v>
       </c>
-      <c r="AI73" s="8">
+      <c r="AI73" s="7">
         <v>9990636.458056353</v>
       </c>
+      <c r="AJ73" s="7">
+        <v>3.4877235</v>
+      </c>
     </row>
-    <row r="74" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>44</v>
       </c>
@@ -8465,83 +8693,86 @@
       <c r="J74" s="1">
         <v>2</v>
       </c>
-      <c r="K74" s="7">
+      <c r="K74" s="6">
         <v>6.9010699999999998</v>
       </c>
-      <c r="L74" s="7">
+      <c r="L74" s="6">
         <v>1269921.8385419014</v>
       </c>
-      <c r="M74" s="7">
+      <c r="M74" s="6">
         <v>4875.2565857940945</v>
       </c>
-      <c r="N74" s="7">
+      <c r="N74" s="6">
         <v>1291.0842986814714</v>
       </c>
-      <c r="O74" s="7">
+      <c r="O74" s="6">
         <v>3584.1722871126321</v>
       </c>
-      <c r="P74" s="7">
+      <c r="P74" s="6">
         <v>4.2405902608695651</v>
       </c>
-      <c r="Q74" s="7">
+      <c r="Q74" s="6">
         <v>171.18928639231294</v>
       </c>
-      <c r="R74" s="7">
+      <c r="R74" s="6">
         <v>4242901.0481925011</v>
       </c>
-      <c r="S74" s="7">
+      <c r="S74" s="6">
         <v>4289450.2657636721</v>
       </c>
-      <c r="T74" s="7">
+      <c r="T74" s="6">
         <v>4316965.3704233123</v>
       </c>
-      <c r="U74" s="7">
+      <c r="U74" s="6">
         <v>4401948.4115863536</v>
       </c>
-      <c r="V74" s="7">
+      <c r="V74" s="6">
         <v>4348636.7831268245</v>
       </c>
-      <c r="W74" s="7">
+      <c r="W74" s="6">
         <v>4433860.0437347302</v>
       </c>
-      <c r="X74" s="7">
+      <c r="X74" s="6">
         <v>4728988.1015359452</v>
       </c>
-      <c r="Y74" s="7">
+      <c r="Y74" s="6">
         <v>4696431.8848801842</v>
       </c>
-      <c r="Z74" s="7">
+      <c r="Z74" s="6">
         <v>4279013.7134188004</v>
       </c>
-      <c r="AA74" s="7">
+      <c r="AA74" s="6">
         <v>4051637.1027000817</v>
       </c>
-      <c r="AB74" s="7">
+      <c r="AB74" s="6">
         <v>4279612.7881962191</v>
       </c>
-      <c r="AC74" s="7">
+      <c r="AC74" s="6">
         <v>4344971.2721529622</v>
       </c>
-      <c r="AD74" s="7">
+      <c r="AD74" s="6">
         <v>4332743.199759434</v>
       </c>
-      <c r="AE74" s="7">
+      <c r="AE74" s="6">
         <v>4417846.6012264965</v>
       </c>
-      <c r="AF74" s="7">
+      <c r="AF74" s="6">
         <v>4530844.1066018492</v>
       </c>
-      <c r="AG74" s="7">
+      <c r="AG74" s="6">
         <v>4561370.402019769</v>
       </c>
-      <c r="AH74" s="7">
+      <c r="AH74" s="6">
         <v>4492762.1802812237</v>
       </c>
-      <c r="AI74" s="7">
+      <c r="AI74" s="6">
         <v>4435957.0110770138</v>
       </c>
+      <c r="AJ74" s="6">
+        <v>2.6608605000000001</v>
+      </c>
     </row>
-    <row r="75" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>44</v>
       </c>
@@ -8572,83 +8803,86 @@
       <c r="J75" s="1">
         <v>50</v>
       </c>
-      <c r="K75" s="7">
+      <c r="K75" s="6">
         <v>15.5212</v>
       </c>
-      <c r="L75" s="7">
+      <c r="L75" s="6">
         <v>4038821.2392434534</v>
       </c>
-      <c r="M75" s="7">
+      <c r="M75" s="6">
         <v>10521.021519435029</v>
       </c>
-      <c r="N75" s="7">
+      <c r="N75" s="6">
         <v>2484.7078541280789</v>
       </c>
-      <c r="O75" s="7">
+      <c r="O75" s="6">
         <v>8036.3136653069514</v>
       </c>
-      <c r="P75" s="7">
+      <c r="P75" s="6">
         <v>4.641698949950932</v>
       </c>
-      <c r="Q75" s="7">
+      <c r="Q75" s="6">
         <v>128.48654731222763</v>
       </c>
-      <c r="R75" s="7">
+      <c r="R75" s="6">
         <v>11268315.269053299</v>
       </c>
-      <c r="S75" s="7">
+      <c r="S75" s="6">
         <v>13217242.340792764</v>
       </c>
-      <c r="T75" s="7">
+      <c r="T75" s="6">
         <v>14934660.83687561</v>
       </c>
-      <c r="U75" s="7">
+      <c r="U75" s="6">
         <v>15758139.893250328</v>
       </c>
-      <c r="V75" s="7">
+      <c r="V75" s="6">
         <v>15754909.737499053</v>
       </c>
-      <c r="W75" s="7">
+      <c r="W75" s="6">
         <v>15178027.112061063</v>
       </c>
-      <c r="X75" s="7">
+      <c r="X75" s="6">
         <v>14274963.206530932</v>
       </c>
-      <c r="Y75" s="7">
+      <c r="Y75" s="6">
         <v>13283572.743293528</v>
       </c>
-      <c r="Z75" s="7">
+      <c r="Z75" s="6">
         <v>11777908.814972773</v>
       </c>
-      <c r="AA75" s="7">
+      <c r="AA75" s="6">
         <v>10951630.292714601</v>
       </c>
-      <c r="AB75" s="7">
+      <c r="AB75" s="6">
         <v>12844988.757457927</v>
       </c>
-      <c r="AC75" s="7">
+      <c r="AC75" s="6">
         <v>14376283.434459563</v>
       </c>
-      <c r="AD75" s="7">
+      <c r="AD75" s="6">
         <v>15333823.774100279</v>
       </c>
-      <c r="AE75" s="7">
+      <c r="AE75" s="6">
         <v>15462644.386057293</v>
       </c>
-      <c r="AF75" s="7">
+      <c r="AF75" s="6">
         <v>14978468.756373856</v>
       </c>
-      <c r="AG75" s="7">
+      <c r="AG75" s="6">
         <v>14167750.812842187</v>
       </c>
-      <c r="AH75" s="7">
+      <c r="AH75" s="6">
         <v>12906770.113087032</v>
       </c>
-      <c r="AI75" s="7">
+      <c r="AI75" s="6">
         <v>11519063.238606704</v>
       </c>
+      <c r="AJ75" s="6">
+        <v>3.1187300000000002</v>
+      </c>
     </row>
-    <row r="76" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>44</v>
       </c>
@@ -8679,83 +8913,86 @@
       <c r="J76" s="1">
         <v>2</v>
       </c>
-      <c r="K76" s="9">
+      <c r="K76" s="8">
         <v>6.1210899999999997</v>
       </c>
-      <c r="L76" s="11">
+      <c r="L76" s="10">
         <v>1206675.8793196818</v>
       </c>
-      <c r="M76" s="11">
+      <c r="M76" s="10">
         <v>4992.7333605269741</v>
       </c>
-      <c r="N76" s="11">
+      <c r="N76" s="10">
         <v>1764.3685767407994</v>
       </c>
-      <c r="O76" s="11">
+      <c r="O76" s="10">
         <v>3228.3647837861686</v>
       </c>
-      <c r="P76" s="11">
+      <c r="P76" s="10">
         <v>6.8454060260309273</v>
       </c>
-      <c r="Q76" s="11">
+      <c r="Q76" s="10">
         <v>299.62718268091146</v>
       </c>
-      <c r="R76" s="10">
+      <c r="R76" s="9">
         <v>1163620.5307454816</v>
       </c>
-      <c r="S76" s="10">
+      <c r="S76" s="9">
         <v>1255202.5363488451</v>
       </c>
-      <c r="T76" s="10">
+      <c r="T76" s="9">
         <v>1421993.2084577514</v>
       </c>
-      <c r="U76" s="10">
+      <c r="U76" s="9">
         <v>1569925.1431572591</v>
       </c>
-      <c r="V76" s="10">
+      <c r="V76" s="9">
         <v>2234242.2267258377</v>
       </c>
-      <c r="W76" s="10">
+      <c r="W76" s="9">
         <v>3362565.6067209137</v>
       </c>
-      <c r="X76" s="10">
+      <c r="X76" s="9">
         <v>3249236.7911550105</v>
       </c>
-      <c r="Y76" s="10">
+      <c r="Y76" s="9">
         <v>2972058.9687339873</v>
       </c>
-      <c r="Z76" s="10">
+      <c r="Z76" s="9">
         <v>2813086.6974220942</v>
       </c>
-      <c r="AA76" s="10">
+      <c r="AA76" s="9">
         <v>973341.40005220741</v>
       </c>
-      <c r="AB76" s="10">
+      <c r="AB76" s="9">
         <v>1279897.6636409499</v>
       </c>
-      <c r="AC76" s="10">
+      <c r="AC76" s="9">
         <v>1395033.6021013507</v>
       </c>
-      <c r="AD76" s="10">
+      <c r="AD76" s="9">
         <v>1737895.3455135669</v>
       </c>
-      <c r="AE76" s="10">
+      <c r="AE76" s="9">
         <v>2140491.1065012706</v>
       </c>
-      <c r="AF76" s="10">
+      <c r="AF76" s="9">
         <v>2647801.5215366804</v>
       </c>
-      <c r="AG76" s="10">
+      <c r="AG76" s="9">
         <v>3155275.6285304138</v>
       </c>
-      <c r="AH76" s="10">
+      <c r="AH76" s="9">
         <v>3015472.470644407</v>
       </c>
-      <c r="AI76" s="10">
+      <c r="AI76" s="9">
         <v>2845375.4467195841</v>
       </c>
+      <c r="AJ76" s="6">
+        <v>5.2055562000000002</v>
+      </c>
     </row>
-    <row r="77" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>44</v>
       </c>
@@ -8786,83 +9023,86 @@
       <c r="J77" s="1">
         <v>50</v>
       </c>
-      <c r="K77" s="7">
+      <c r="K77" s="6">
         <v>15.0379</v>
       </c>
-      <c r="L77" s="7">
+      <c r="L77" s="6">
         <v>3585534.0727804699</v>
       </c>
-      <c r="M77" s="7">
+      <c r="M77" s="6">
         <v>10496.418007944452</v>
       </c>
-      <c r="N77" s="7">
+      <c r="N77" s="6">
         <v>2909.3105736091265</v>
       </c>
-      <c r="O77" s="7">
+      <c r="O77" s="6">
         <v>7587.107434335333</v>
       </c>
-      <c r="P77" s="7">
+      <c r="P77" s="6">
         <v>4.7816678260238161</v>
       </c>
-      <c r="Q77" s="7">
+      <c r="Q77" s="6">
         <v>145.64671685748391</v>
       </c>
-      <c r="R77" s="7">
+      <c r="R77" s="6">
         <v>6141939.7206837069</v>
       </c>
-      <c r="S77" s="7">
+      <c r="S77" s="6">
         <v>7428940.4894149238</v>
       </c>
-      <c r="T77" s="7">
+      <c r="T77" s="6">
         <v>8856841.998911947</v>
       </c>
-      <c r="U77" s="7">
+      <c r="U77" s="6">
         <v>9973398.6949927825</v>
       </c>
-      <c r="V77" s="7">
+      <c r="V77" s="6">
         <v>10616766.244712193</v>
       </c>
-      <c r="W77" s="7">
+      <c r="W77" s="6">
         <v>10836802.497070855</v>
       </c>
-      <c r="X77" s="7">
+      <c r="X77" s="6">
         <v>10669132.346404443</v>
       </c>
-      <c r="Y77" s="7">
+      <c r="Y77" s="6">
         <v>10261093.256145814</v>
       </c>
-      <c r="Z77" s="7">
+      <c r="Z77" s="6">
         <v>9699484.414150428</v>
       </c>
-      <c r="AA77" s="7">
+      <c r="AA77" s="6">
         <v>6235014.5045778276</v>
       </c>
-      <c r="AB77" s="7">
+      <c r="AB77" s="6">
         <v>7253681.0908937566</v>
       </c>
-      <c r="AC77" s="7">
+      <c r="AC77" s="6">
         <v>8515152.4283235688</v>
       </c>
-      <c r="AD77" s="7">
+      <c r="AD77" s="6">
         <v>9657277.6850006059</v>
       </c>
-      <c r="AE77" s="7">
+      <c r="AE77" s="6">
         <v>10387189.521588983</v>
       </c>
-      <c r="AF77" s="7">
+      <c r="AF77" s="6">
         <v>10642884.881819928</v>
       </c>
-      <c r="AG77" s="7">
+      <c r="AG77" s="6">
         <v>10541093.038050892</v>
       </c>
-      <c r="AH77" s="7">
+      <c r="AH77" s="6">
         <v>10161228.337003576</v>
       </c>
-      <c r="AI77" s="7">
+      <c r="AI77" s="6">
         <v>9592554.8086781595</v>
       </c>
+      <c r="AJ77" s="6">
+        <v>3.2963500000000003</v>
+      </c>
     </row>
-    <row r="78" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>44</v>
       </c>
@@ -8893,83 +9133,86 @@
       <c r="J78" s="1">
         <v>50</v>
       </c>
-      <c r="K78" s="7">
+      <c r="K78" s="6">
         <v>15.1938</v>
       </c>
-      <c r="L78" s="7">
+      <c r="L78" s="6">
         <v>4071618.064604742</v>
       </c>
-      <c r="M78" s="7">
+      <c r="M78" s="6">
         <v>10423.498481771294</v>
       </c>
-      <c r="N78" s="7">
+      <c r="N78" s="6">
         <v>3572.3914954265365</v>
       </c>
-      <c r="O78" s="7">
+      <c r="O78" s="6">
         <v>6851.1069863447483</v>
       </c>
-      <c r="P78" s="7">
+      <c r="P78" s="6">
         <v>4.061993260980592</v>
       </c>
-      <c r="Q78" s="7">
+      <c r="Q78" s="6">
         <v>109.02029193323285</v>
       </c>
-      <c r="R78" s="7">
+      <c r="R78" s="6">
         <v>10330503.963502156</v>
       </c>
-      <c r="S78" s="7">
+      <c r="S78" s="6">
         <v>12299553.880710576</v>
       </c>
-      <c r="T78" s="7">
+      <c r="T78" s="6">
         <v>13965151.044152563</v>
       </c>
-      <c r="U78" s="7">
+      <c r="U78" s="6">
         <v>14682399.547353981</v>
       </c>
-      <c r="V78" s="7">
+      <c r="V78" s="6">
         <v>14850336.943615744</v>
       </c>
-      <c r="W78" s="7">
+      <c r="W78" s="6">
         <v>14280051.81094683</v>
       </c>
-      <c r="X78" s="7">
+      <c r="X78" s="6">
         <v>13214111.293560712</v>
       </c>
-      <c r="Y78" s="7">
+      <c r="Y78" s="6">
         <v>12073126.248628555</v>
       </c>
-      <c r="Z78" s="7">
+      <c r="Z78" s="6">
         <v>10653307.205838492</v>
       </c>
-      <c r="AA78" s="7">
+      <c r="AA78" s="6">
         <v>10146545.622867808</v>
       </c>
-      <c r="AB78" s="7">
+      <c r="AB78" s="6">
         <v>11875954.623744104</v>
       </c>
-      <c r="AC78" s="7">
+      <c r="AC78" s="6">
         <v>13385759.100967698</v>
       </c>
-      <c r="AD78" s="7">
+      <c r="AD78" s="6">
         <v>14394147.936150532</v>
       </c>
-      <c r="AE78" s="7">
+      <c r="AE78" s="6">
         <v>14478430.962311881</v>
       </c>
-      <c r="AF78" s="7">
+      <c r="AF78" s="6">
         <v>13984526.149341295</v>
       </c>
-      <c r="AG78" s="7">
+      <c r="AG78" s="6">
         <v>13084180.432490559</v>
       </c>
-      <c r="AH78" s="7">
+      <c r="AH78" s="6">
         <v>11796331.225849643</v>
       </c>
-      <c r="AI78" s="7">
+      <c r="AI78" s="6">
         <v>10314866.900941689</v>
       </c>
+      <c r="AJ78" s="6">
+        <v>2.8724499999999997</v>
+      </c>
     </row>
-    <row r="79" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>44</v>
       </c>
@@ -9000,80 +9243,83 @@
       <c r="J79" s="4">
         <v>2</v>
       </c>
-      <c r="K79" s="8">
+      <c r="K79" s="7">
         <v>8.1847799999999999</v>
       </c>
-      <c r="L79" s="8">
+      <c r="L79" s="7">
         <v>1783882.5972697779</v>
       </c>
-      <c r="M79" s="8">
+      <c r="M79" s="7">
         <v>6016.0070791490389</v>
       </c>
-      <c r="N79" s="8">
+      <c r="N79" s="7">
         <v>1869.6104458186428</v>
       </c>
-      <c r="O79" s="8">
+      <c r="O79" s="7">
         <v>4146.3966333303961</v>
       </c>
-      <c r="P79" s="8">
+      <c r="P79" s="7">
         <v>4.2915705919480516</v>
       </c>
-      <c r="Q79" s="8">
+      <c r="Q79" s="7">
         <v>152.19069998990179</v>
       </c>
-      <c r="R79" s="8">
+      <c r="R79" s="7">
         <v>3353807.2266779765</v>
       </c>
-      <c r="S79" s="8">
+      <c r="S79" s="7">
         <v>4008455.3942691307</v>
       </c>
-      <c r="T79" s="8">
+      <c r="T79" s="7">
         <v>4104075.4363839338</v>
       </c>
-      <c r="U79" s="8">
+      <c r="U79" s="7">
         <v>4448912.7641885774</v>
       </c>
-      <c r="V79" s="8">
+      <c r="V79" s="7">
         <v>5093956.1107698251</v>
       </c>
-      <c r="W79" s="8">
+      <c r="W79" s="7">
         <v>5134418.876687739</v>
       </c>
-      <c r="X79" s="8">
+      <c r="X79" s="7">
         <v>4944748.9084658902</v>
       </c>
-      <c r="Y79" s="8">
+      <c r="Y79" s="7">
         <v>4646056.2269365368</v>
       </c>
-      <c r="Z79" s="8">
+      <c r="Z79" s="7">
         <v>4559025.5339102643</v>
       </c>
-      <c r="AA79" s="8">
+      <c r="AA79" s="7">
         <v>3036491.0528198271</v>
       </c>
-      <c r="AB79" s="8">
+      <c r="AB79" s="7">
         <v>3691202.5783266863</v>
       </c>
-      <c r="AC79" s="8">
+      <c r="AC79" s="7">
         <v>4217214.6308684712</v>
       </c>
-      <c r="AD79" s="8">
+      <c r="AD79" s="7">
         <v>4545750.9122584881</v>
       </c>
-      <c r="AE79" s="8">
+      <c r="AE79" s="7">
         <v>4767148.3223548541</v>
       </c>
-      <c r="AF79" s="8">
+      <c r="AF79" s="7">
         <v>5018243.6619539056</v>
       </c>
-      <c r="AG79" s="8">
+      <c r="AG79" s="7">
         <v>4878044.9908605926</v>
       </c>
-      <c r="AH79" s="8">
+      <c r="AH79" s="7">
         <v>4744059.6721137231</v>
       </c>
-      <c r="AI79" s="8">
+      <c r="AI79" s="7">
         <v>4430359.1002791366</v>
+      </c>
+      <c r="AJ79" s="7">
+        <v>2.8098820400000002</v>
       </c>
     </row>
   </sheetData>
